--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -53,6 +53,9 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00888888"/>
     </font>
@@ -61,9 +64,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -105,18 +105,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -511,69 +516,258 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0 pesquisas</t>
+          <t>14 pesquisas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(sem dados)</t>
-        </is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3.84</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Lula vs Flávio</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>0 pesquisas</t>
-        </is>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Cury</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>(sem dados)</t>
-        </is>
+          <t>Daciolo</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>35.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Lula vs Zema</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>0 pesquisas</t>
-        </is>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>(sem dados)</t>
-        </is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>42.29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Renan</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Flávio vs Zema</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>0 pesquisas</t>
-        </is>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Rui</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>14 pesquisas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>44.16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>45.43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>12 pesquisas</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>45.91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>39.53</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Flávio vs Zema</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>0 pesquisas</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>(sem dados)</t>
         </is>
@@ -593,13 +787,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,7 +835,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -639,22 +846,1037 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Média (%)</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Cury</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Daciolo</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>42.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Renan</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Rui</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>PESQUISAS UTILIZADAS</t>
         </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>instituto</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>data_fim_campo</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>amostra</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>peso_final</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Cury</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Daciolo</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Renan</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>Rui</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1.514560590142393</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.8714206790188705</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.8130642430320129</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.9300954052460574</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q28" s="10" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.4257587016015145</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.4061261981781178</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.3881737829494479</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.3206670264407789</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0.4151368749394808</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0.1896539407469422</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0.1729117628226748</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0.2215352390629677</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O36" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P36" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q36" s="10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v/>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q37" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0.05081651518950081</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P38" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -671,13 +1893,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,7 +1932,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -717,22 +1943,524 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Média (%)</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>44.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>45.43</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PESQUISAS UTILIZADAS</t>
         </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>instituto</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>data_fim_campo</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>amostra</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>peso_final</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1.514560590142393</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.8714206790188705</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.8130642430320129</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.9300954052460574</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.4257587016015145</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.4061261981781178</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0.3881737829494479</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.3206670264407789</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.4151368749394808</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.1896539407469422</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.1729117628226748</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.2215352390629677</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.05081651518950081</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -749,13 +2477,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -784,7 +2516,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -795,22 +2527,464 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Média (%)</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>45.91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>39.53</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PESQUISAS UTILIZADAS</t>
         </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>instituto</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>data_fim_campo</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>amostra</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>peso_final</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1.514560590142393</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.8714206790188705</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.8130642430320129</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.9300954052460574</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.4257587016015145</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.4061261981781178</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0.3881737829494479</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.3206670264407789</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.4151368749394808</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.1896539407469422</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.05081651518950081</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -873,12 +3047,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Média (%)</t>
         </is>
@@ -905,14 +3079,3285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nenhuma pesquisa no banco.</t>
-        </is>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>cenario</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>instituto</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>contratante</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>data_inicio_campo</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>data_fim_campo</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>amostra</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>margem_erro</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>turno</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>metodologia</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>votos_validos</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>registro_tse</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>url_fonte</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>Cury</t>
+        </is>
+      </c>
+      <c r="P1" s="8" t="inlineStr">
+        <is>
+          <t>Daciolo</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="R1" s="8" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="S1" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="T1" s="8" t="inlineStr">
+        <is>
+          <t>Renan</t>
+        </is>
+      </c>
+      <c r="U1" s="8" t="inlineStr">
+        <is>
+          <t>Rui</t>
+        </is>
+      </c>
+      <c r="V1" s="8" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+      <c r="W1" s="8" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="X1" s="8" t="inlineStr">
+        <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="Y1" s="8" t="inlineStr">
+        <is>
+          <t>Não sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>BR-06939/2026</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O2" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="10" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="T2" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U2" s="9" t="n"/>
+      <c r="V2" s="9" t="n"/>
+      <c r="W2" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="X2" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y2" s="10" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>BR-00290/2026</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="n"/>
+      <c r="N3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="R3" s="9" t="n"/>
+      <c r="S3" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="T3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>BR-03598/2026</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>BR-07992/2026</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="10" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X5" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y5" s="10" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>BR-09285/2026</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="T6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>BR-08282/2026</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="T7" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X7" s="10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>BR-03770/2026</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>BR-00605/2026</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="10" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="T9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>BR-04227/2026</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="10" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="10" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X10" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>BR-03715/2026</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="R12" s="9" t="n"/>
+      <c r="S12" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>BR-07600/2026</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>BR-00249/2026</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R14" s="9" t="n"/>
+      <c r="S14" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>BR-06939/2026</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>BR-00290/2026</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>BR-03598/2026</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y18" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>BR-07992/2026</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="10" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>BR-09285/2026</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y20" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>BR-08282/2026</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="10" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y21" s="10" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>BR-03770/2026</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R22" s="9" t="n"/>
+      <c r="S22" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>BR-00605/2026</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="10" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y23" s="10" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>BR-04227/2026</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="10" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y25" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>BR-03715/2026</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>BR-07600/2026</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="10" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>BR-00249/2026</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="R28" s="9" t="n"/>
+      <c r="S28" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y29" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>BR-06939/2026</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="9" t="n"/>
+      <c r="S30" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
+      <c r="W30" s="10" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="X30" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="Y30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>BR-00290/2026</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="X31" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>BR-03598/2026</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
+      <c r="S32" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="X32" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y32" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>BR-07992/2026</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="X33" s="10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>BR-09285/2026</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
+      <c r="S34" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="9" t="n"/>
+      <c r="V34" s="9" t="n"/>
+      <c r="W34" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>BR-08282/2026</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Y35" s="10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>BR-03770/2026</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="9" t="n"/>
+      <c r="S36" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T36" s="9" t="n"/>
+      <c r="U36" s="9" t="n"/>
+      <c r="V36" s="9" t="n"/>
+      <c r="W36" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y36" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>BR-00605/2026</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="9" t="n"/>
+      <c r="S37" s="10" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="X37" s="10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y37" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>BR-04227/2026</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
+      <c r="S38" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="X38" s="10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="9" t="n"/>
+      <c r="S39" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X39" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y39" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>BR-00249/2026</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="9" t="n"/>
+      <c r="S40" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T40" s="9" t="n"/>
+      <c r="U40" s="9" t="n"/>
+      <c r="V40" s="9" t="n"/>
+      <c r="W40" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="X40" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y40" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="9" t="n"/>
+      <c r="S41" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="X41" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y41" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -942,124 +6387,124 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Instituto</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>AtlasIntel</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Datafolha</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Genial/Quaest</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Ipec</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Ipespe</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Paraná Pesquisas</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Quaest</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Real Time Big Data</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Veredictum</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1108,17 +6553,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Turno</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Candidatos exigidos</t>
         </is>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -12,8 +12,11 @@
     <sheet name="Lula vs Flávio" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Lula vs Zema" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Flávio vs Zema" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Todas as Pesquisas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Configuração" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Evolução 1º Turno" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Evolução Lula vs Flávio" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Evolução Lula vs Zema" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Todas as Pesquisas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Configuração" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +68,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -105,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +130,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -196,6 +206,678 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Intenção de voto — 1º Turno</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$C$6:$C$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$D$6:$D$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$E$6:$E$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$F$6:$F$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!G5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$G$6:$G$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Evolução 1º Turno'!H5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução 1º Turno'!$H$6:$H$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% intenção de voto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Intenção de voto — Lula vs Flávio</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Evolução Lula vs Flávio'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução Lula vs Flávio'!$C$6:$C$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Evolução Lula vs Flávio'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução Lula vs Flávio'!$D$6:$D$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% intenção de voto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Intenção de voto — Lula vs Zema</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Evolução Lula vs Zema'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução Lula vs Zema'!$C$6:$C$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Evolução Lula vs Zema'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolução Lula vs Zema'!$D$6:$D$24</f>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% intenção de voto</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,6 +1463,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pesos por instituto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Genial/Quaest</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Ipec</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ipespe</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Veredictum</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Parâmetros da ponderação</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Half-life (dias)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Amostra de referência</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Janela de pesquisas (dias)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Cenários ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Turno</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Candidatos exigidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1º Turno</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>(todos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lula, Flávio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lula, Zema</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flávio vs Zema</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Flávio, Zema</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3074,6 +4025,1308 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evolução temporal — 1º Turno</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Janela: 30 dias | Passo: 7 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Nº pesq.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Renan</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Samara</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evolução temporal — Lula vs Flávio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Janela: 30 dias | Passo: 7 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Nº pesq.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>43.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>43.47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>44.97</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>45.53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>46.92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>45.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>45.38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>46.29</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>46.44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>44.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evolução temporal — Lula vs Zema</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Janela: 30 dias | Passo: 7 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Nº pesq.</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Zema</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>40.66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>40.66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>40.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>41.57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>41.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6363,273 +8616,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pesos por instituto</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Instituto</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>AtlasIntel</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Datafolha</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Futura</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Genial/Quaest</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Ipec</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ipespe</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Paraná Pesquisas</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Quaest</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Ranking</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Real Time Big Data</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Veredictum</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Parâmetros da ponderação</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Half-life (dias)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Amostra de referência</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Janela de pesquisas (dias)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Cenários ativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Cenário</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Turno</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Candidatos exigidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1º Turno</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>(todos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lula vs Flávio</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lula, Flávio</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Lula vs Zema</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lula, Zema</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Flávio vs Zema</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Flávio, Zema</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1169,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>14 pesquisas</t>
+          <t>23 pesquisas</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3.84</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="10">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>35.5</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="11">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>42.29</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="15">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1309,147 +1309,157 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Branco/Nulo</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>5.77</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Não sabe</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B19" s="6" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Lula vs Flávio</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>14 pesquisas</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Flávio</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>44.16</v>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>22 pesquisas</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Lula</t>
+          <t>Flávio</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45.43</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Branco/Nulo</t>
+          <t>Lula</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9.06</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>8.609999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Não sabe</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B25" s="6" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Lula vs Zema</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>12 pesquisas</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Lula</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>45.91</v>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>16 pesquisas</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Zema</t>
+          <t>Lula</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>39.53</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Branco/Nulo</t>
+          <t>Zema</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>12.75</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>12.44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Não sabe</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B31" s="6" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Flávio vs Zema</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>0 pesquisas</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>(sem dados)</t>
         </is>
@@ -1738,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1758,6 +1768,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1786,7 +1797,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -1815,7 +1826,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1825,7 +1836,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.84</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="10">
@@ -1835,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1856,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="12">
@@ -1855,7 +1866,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>35.5</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="13">
@@ -1875,7 +1886,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>42.29</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="15">
@@ -1885,7 +1896,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -1895,7 +1906,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="17">
@@ -1905,7 +1916,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18">
@@ -1915,502 +1926,475 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Branco/Nulo</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>5.77</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>Branco/Nulo</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Não sabe</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="B21" s="6" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>PESQUISAS UTILIZADAS</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>data_fim_campo</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>amostra</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>peso_final</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Aldo</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Caiado</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Cury</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Daciolo</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Flávio</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Hertz</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>Renan</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>Rui</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t>Samara</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>Zema</t>
         </is>
       </c>
-      <c r="P24" s="8" t="inlineStr">
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>Branco/Nulo</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="R25" s="8" t="inlineStr">
         <is>
           <t>Não sabe</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>AtlasIntel</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>5032</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1.514560590142393</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v/>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P25" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>1.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2004</v>
+        <v>5032</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>1.514560590142393</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I26" s="10" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="J26" s="10" t="n">
         <v/>
       </c>
       <c r="K26" s="10" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="N26" s="10" t="n">
-        <v>2</v>
+        <v/>
       </c>
       <c r="O26" s="10" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="P26" s="10" t="n">
-        <v>9</v>
+        <v/>
       </c>
       <c r="Q26" s="10" t="n">
-        <v>9</v>
+        <v>1.4</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.8130642430320129</v>
+        <v>0.8714206790188705</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F27" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K27" s="10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L27" s="10" t="n">
         <v>2</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P27" s="10" t="n">
-        <v>10</v>
+        <v/>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>5008</v>
+        <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.8130642430320129</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>39.7</v>
+        <v>33</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>46.6</v>
+        <v>39</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="10" t="n">
         <v/>
       </c>
       <c r="N28" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P28" s="10" t="n">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>0.1</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.6123724356957946</v>
       </c>
       <c r="E29" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="J29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v/>
-      </c>
       <c r="K29" s="10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="10" t="n">
         <v>3</v>
       </c>
       <c r="P29" s="10" t="n">
-        <v>11</v>
+        <v/>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2000</v>
+        <v>5008</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.9300954052460574</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="I30" s="10" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v/>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P30" s="10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q30" s="10" t="n">
-        <v>4.5</v>
+      <c r="R30" s="10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.4257587016015145</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v/>
+        <v>2</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J31" s="10" t="n">
         <v/>
       </c>
       <c r="K31" s="10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>2</v>
@@ -2419,58 +2403,61 @@
         <v/>
       </c>
       <c r="N31" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P31" s="10" t="n">
-        <v>10</v>
+        <v/>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.4061261981781178</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="J32" s="10" t="n">
         <v/>
       </c>
       <c r="K32" s="10" t="n">
-        <v>40.4</v>
+        <v>39.8</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="M32" s="10" t="n">
         <v/>
@@ -2479,55 +2466,58 @@
         <v/>
       </c>
       <c r="O32" s="10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P32" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q32" s="10" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>5028</v>
+        <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.3881737829494479</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="G33" s="10" t="n">
         <v/>
       </c>
       <c r="H33" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>40.1</v>
+        <v>35</v>
       </c>
       <c r="J33" s="10" t="n">
         <v/>
       </c>
       <c r="K33" s="10" t="n">
-        <v>45.9</v>
+        <v>39</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="M33" s="10" t="n">
         <v/>
@@ -2536,94 +2526,100 @@
         <v/>
       </c>
       <c r="O33" s="10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P33" s="10" t="n">
-        <v>1.9</v>
+        <v/>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>0.3</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.3206670264407789</v>
       </c>
       <c r="E34" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v/>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v/>
-      </c>
-      <c r="K34" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="L34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P34" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q34" s="10" t="n">
-        <v>5</v>
+      <c r="R34" s="10" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.1729117628226748</v>
+        <v>0.3138814693848235</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G35" s="10" t="n">
         <v/>
@@ -2632,31 +2628,34 @@
         <v/>
       </c>
       <c r="I35" s="10" t="n">
-        <v>33</v>
+        <v>37.8</v>
       </c>
       <c r="J35" s="10" t="n">
         <v/>
       </c>
       <c r="K35" s="10" t="n">
-        <v>39</v>
+        <v>41.3</v>
       </c>
       <c r="L35" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="M35" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="10" t="n">
+      <c r="P35" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="P35" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q35" s="10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2667,20 +2666,20 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4986</v>
+        <v>5028</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.2215352390629677</v>
+        <v>0.4151368749394808</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="G36" s="10" t="n">
         <v/>
@@ -2689,16 +2688,16 @@
         <v/>
       </c>
       <c r="I36" s="10" t="n">
-        <v>37.9</v>
+        <v>40.1</v>
       </c>
       <c r="J36" s="10" t="n">
         <v/>
       </c>
       <c r="K36" s="10" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="M36" s="10" t="n">
         <v/>
@@ -2707,37 +2706,40 @@
         <v/>
       </c>
       <c r="O36" s="10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P36" s="10" t="n">
-        <v>3.8</v>
+        <v/>
       </c>
       <c r="Q36" s="10" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="R36" s="10" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.1679163460868971</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G37" s="10" t="n">
         <v/>
@@ -2746,16 +2748,16 @@
         <v/>
       </c>
       <c r="I37" s="10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J37" s="10" t="n">
         <v/>
       </c>
       <c r="K37" s="10" t="n">
-        <v>39</v>
+        <v>40.3</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M37" s="10" t="n">
         <v/>
@@ -2764,13 +2766,16 @@
         <v/>
       </c>
       <c r="O37" s="10" t="n">
-        <v/>
+        <v>5</v>
       </c>
       <c r="P37" s="10" t="n">
-        <v>16</v>
+        <v/>
       </c>
       <c r="Q37" s="10" t="n">
-        <v>6</v>
+        <v>4.7</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="38">
@@ -2781,20 +2786,20 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.05081651518950081</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v/>
+        <v>4</v>
       </c>
       <c r="G38" s="10" t="n">
         <v/>
@@ -2812,21 +2817,624 @@
         <v>39</v>
       </c>
       <c r="L38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O38" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="M38" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="10" t="n">
+      <c r="P38" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P38" s="10" t="n">
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>0.1729117628226748</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R39" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0.1464308831840453</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O40" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P40" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.2215352390629677</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L41" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O41" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P41" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R41" s="10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="P42" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R42" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>0.0730898348362876</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0.07667810167904221</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R44" s="10" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>5418</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>0.102869000432589</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I45" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O45" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0.06107249802714037</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N46" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O46" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>0.05195236850892425</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O47" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P47" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R47" s="10" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>0.05081651518950081</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O48" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="R48" s="10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2844,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2883,7 +3491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -2912,7 +3520,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.16</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="9">
@@ -2922,7 +3530,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45.43</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="10">
@@ -2932,7 +3540,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>9.06</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2942,7 +3550,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="14">
@@ -3087,271 +3695,271 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.6123724356957946</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>47.8</v>
+        <v>45.3</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>47.5</v>
+        <v>44.7</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v/>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.9300954052460574</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>42</v>
+        <v>47.8</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>40</v>
+        <v>47.5</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.4257587016015145</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>42.6</v>
+        <v>40</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>2.1</v>
+        <v>16</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.4061261981781178</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>45</v>
+        <v>42.6</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.3881737829494479</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>5028</v>
+        <v>1500</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.3206670264407789</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>47.6</v>
+        <v>45.8</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v/>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.3138814693848235</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>41</v>
+        <v>45.2</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>41</v>
+        <v>44.1</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2004</v>
+        <v>5028</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.1729117628226748</v>
+        <v>0.4151368749394808</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>43</v>
+        <v>47.6</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>46</v>
+        <v>46.6</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>4986</v>
+        <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.2215352390629677</v>
+        <v>0.1679163460868971</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>46.3</v>
+        <v>45.3</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v/>
+        <v>3.2</v>
       </c>
     </row>
     <row r="28">
@@ -3362,23 +3970,23 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>2</v>
@@ -3387,30 +3995,270 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
+        <v>0.1729117628226748</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.1464308831840453</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>4986</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.2215352390629677</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0.0730898348362876</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0.07667810167904221</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0.06107249802714037</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0.05195236850892425</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>0.05081651518950081</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E37" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F37" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G37" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H37" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3428,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3467,7 +4315,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -3496,7 +4344,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45.91</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="9">
@@ -3506,7 +4354,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.53</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="10">
@@ -3516,7 +4364,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12.75</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="11">
@@ -3526,7 +4374,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.51</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="14">
@@ -3671,241 +4519,241 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.6123724356957946</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>47.4</v>
+        <v>44</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>46.5</v>
+        <v>39</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.9300954052460574</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>43</v>
+        <v>47.4</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>36</v>
+        <v>46.5</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>17</v>
+        <v>6.1</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>4</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.4257587016015145</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.4061261981781178</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>11</v>
+        <v>14.9</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.3881737829494479</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>38.7</v>
+        <v>42</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>5028</v>
+        <v>1500</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.3206670264407789</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>46.6</v>
+        <v>44.7</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>43.7</v>
+        <v>38.7</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v/>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2004</v>
+        <v>5028</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.4151368749394808</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>44</v>
+        <v>46.6</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>34</v>
+        <v>43.7</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.1679163460868971</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>43</v>
+        <v>46.1</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="27">
@@ -3916,25 +4764,145 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.05081651518950081</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>19</v>
       </c>
       <c r="H27" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.09931172875702197</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0.0730898348362876</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.06107249802714037</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.05081651518950081</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H31" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4095,7 +5063,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Cury</t>
         </is>
       </c>
     </row>
@@ -4130,20 +5098,22 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39</v>
+        <v>39.3</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E7" s="5" t="n"/>
+        <v>29.78</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>5.5</v>
+      </c>
       <c r="F7" s="12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -4154,20 +5124,22 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>39</v>
+        <v>42.07</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E8" s="5" t="n"/>
+        <v>32.83</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>4.42</v>
+      </c>
       <c r="F8" s="12" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
@@ -4178,20 +5150,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>39</v>
+        <v>41.56</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="n"/>
+        <v>32.89</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>4.23</v>
+      </c>
       <c r="F9" s="12" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H9" s="5" t="n"/>
     </row>
@@ -4202,20 +5176,22 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>39</v>
+        <v>41.2</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
+        <v>32.91</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>4.4</v>
+      </c>
       <c r="F10" s="12" t="n">
-        <v>5</v>
+        <v>4.19</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="H10" s="5" t="n"/>
     </row>
@@ -4226,20 +5202,22 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39</v>
+        <v>41.15</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>32</v>
+        <v>33.47</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="5" t="n"/>
+        <v>4.17</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>3.86</v>
+      </c>
       <c r="G11" s="12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H11" s="5" t="n"/>
     </row>
@@ -4250,20 +5228,22 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>39</v>
+        <v>39.39</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32</v>
+        <v>32.63</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="5" t="n"/>
+        <v>4.23</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>4.36</v>
+      </c>
       <c r="G12" s="12" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="H12" s="5" t="n"/>
     </row>
@@ -4274,22 +5254,22 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43.14</v>
+        <v>41.93</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>36.07</v>
+        <v>35.8</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>3.9</v>
+        <v>4.38</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="H13" s="5" t="n"/>
     </row>
@@ -4300,22 +5280,22 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>41.69</v>
+        <v>41.42</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>35</v>
+        <v>35.36</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.4</v>
+        <v>4.24</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="H14" s="5" t="n"/>
     </row>
@@ -4326,22 +5306,22 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>41.28</v>
+        <v>40.97</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>34.53</v>
+        <v>34.96</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>4.34</v>
+        <v>4.45</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="H15" s="5" t="n"/>
     </row>
@@ -4352,22 +5332,22 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>41.28</v>
+        <v>40.97</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34.53</v>
+        <v>34.96</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>4.34</v>
+        <v>4.45</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
@@ -4378,22 +5358,22 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>42.68</v>
+        <v>42.26</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>36.55</v>
+        <v>36.27</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.84</v>
+        <v>4.13</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>3.26</v>
+        <v>2.96</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -4404,22 +5384,22 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>43.74</v>
+        <v>42.5</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>37.56</v>
+        <v>37.23</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3.33</v>
+        <v>2.45</v>
       </c>
       <c r="H18" s="5" t="n"/>
     </row>
@@ -4430,24 +5410,26 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>41.38</v>
+        <v>41.36</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>37.41</v>
+        <v>37.48</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>4.91</v>
+        <v>4.69</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H19" s="5" t="n"/>
+        <v>2.45</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4456,25 +5438,25 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>40.42</v>
+        <v>40.55</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>36.23</v>
+        <v>36.45</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="21">
@@ -4484,25 +5466,25 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>38.95</v>
+        <v>39.35</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>35.19</v>
+        <v>35.63</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>5.54</v>
+        <v>5.21</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="22">
@@ -4530,7 +5512,7 @@
         <v>3.27</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="23">
@@ -4540,25 +5522,25 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>42.71</v>
+        <v>42.01</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>37.29</v>
+        <v>36.95</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>4.3</v>
+        <v>4.63</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24">
@@ -4568,25 +5550,25 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>41.37</v>
+        <v>41.11</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>36.05</v>
+        <v>36.04</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.42</v>
+        <v>3.83</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>3.17</v>
+        <v>2.84</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -4672,13 +5654,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>44</v>
+        <v>45.11</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>38</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="8">
@@ -4688,13 +5670,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>44</v>
+        <v>43.91</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>38</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="9">
@@ -4704,13 +5686,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>38</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="10">
@@ -4720,13 +5702,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>44</v>
+        <v>44.57</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>38</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="11">
@@ -4736,13 +5718,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>43</v>
+        <v>43.89</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>38</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="12">
@@ -4752,13 +5734,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43</v>
+        <v>44.38</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>38</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="13">
@@ -4768,13 +5750,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>45.21</v>
+        <v>44.91</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>43.73</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="14">
@@ -4784,13 +5766,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>45.49</v>
+        <v>45.1</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>43.47</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="15">
@@ -4800,13 +5782,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.45</v>
+        <v>44.9</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>43.6</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="16">
@@ -4816,13 +5798,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.45</v>
+        <v>44.9</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>43.6</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="17">
@@ -4832,13 +5814,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.1</v>
+        <v>45.51</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>44.97</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="18">
@@ -4848,13 +5830,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>44.84</v>
+        <v>45.02</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>45.53</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="19">
@@ -4864,13 +5846,13 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>44.9</v>
+        <v>44.77</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>46.92</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="20">
@@ -4880,13 +5862,13 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>43.83</v>
+        <v>43.87</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>45.85</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="21">
@@ -4896,13 +5878,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>43.09</v>
+        <v>43.26</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>45.38</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="22">
@@ -4928,13 +5910,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.56</v>
+        <v>44.59</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>46.44</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="24">
@@ -4944,13 +5926,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.96</v>
+        <v>44.91</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>44.75</v>
+        <v>44.86</v>
       </c>
     </row>
   </sheetData>
@@ -5052,13 +6034,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>46</v>
+        <v>44.25</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>31</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="9">
@@ -5068,13 +6050,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>46</v>
+        <v>44.25</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>31</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="10">
@@ -5084,13 +6066,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>46</v>
+        <v>44.55</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>31</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="11">
@@ -5100,13 +6082,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>43</v>
+        <v>43.57</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>32</v>
+        <v>35.01</v>
       </c>
     </row>
     <row r="12">
@@ -5116,13 +6098,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43</v>
+        <v>43.85</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="13">
@@ -5132,13 +6114,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43</v>
+        <v>43.85</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>32</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="14">
@@ -5164,13 +6146,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44</v>
+        <v>44.99</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>34</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="16">
@@ -5180,13 +6162,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44</v>
+        <v>44.99</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="17">
@@ -5196,13 +6178,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.78</v>
+        <v>45.85</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>40.66</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="18">
@@ -5212,13 +6194,13 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.78</v>
+        <v>45.85</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>40.66</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="19">
@@ -5292,13 +6274,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>45.74</v>
+        <v>45.29</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>42</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="24">
@@ -5308,13 +6290,13 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.88</v>
+        <v>45.52</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>41.38</v>
+        <v>40.93</v>
       </c>
     </row>
   </sheetData>
@@ -5332,7 +6314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5360,6 +6342,7 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5480,10 +6463,15 @@
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="Y1" s="8" t="inlineStr">
+        <is>
           <t>Branco/Nulo</t>
         </is>
       </c>
-      <c r="Y1" s="8" t="inlineStr">
+      <c r="Z1" s="8" t="inlineStr">
         <is>
           <t>Não sabe</t>
         </is>
@@ -5567,10 +6555,11 @@
       <c r="W2" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="X2" s="10" t="n">
+      <c r="X2" s="9" t="n"/>
+      <c r="Y2" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y2" s="10" t="n">
+      <c r="Z2" s="10" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -5656,10 +6645,11 @@
       <c r="W3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X3" s="10" t="n">
+      <c r="X3" s="9" t="n"/>
+      <c r="Y3" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Y3" s="10" t="n">
+      <c r="Z3" s="10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5747,10 +6737,11 @@
       <c r="W4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X4" s="10" t="n">
+      <c r="X4" s="9" t="n"/>
+      <c r="Y4" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Y4" s="10" t="n">
+      <c r="Z4" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5762,36 +6753,36 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
@@ -5799,44 +6790,53 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
+          <t>BR-05356/2026</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M5" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P5" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P5" s="9" t="n"/>
       <c r="Q5" s="10" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R5" s="9" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" s="10" t="n">
-        <v>46.6</v>
+        <v>40</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="U5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X5" s="10" t="n">
-        <v>0.5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X5" s="9" t="n"/>
       <c r="Y5" s="10" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
+      </c>
+      <c r="Z5" s="10" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
@@ -5847,36 +6847,36 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
@@ -5884,48 +6884,45 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-07992/2026</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M6" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="P6" s="9" t="n"/>
       <c r="Q6" s="10" t="n">
-        <v>32</v>
+        <v>39.7</v>
       </c>
       <c r="R6" s="9" t="n"/>
       <c r="S6" s="10" t="n">
-        <v>37</v>
+        <v>46.6</v>
       </c>
       <c r="T6" s="10" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="U6" s="9" t="n"/>
-      <c r="V6" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="V6" s="9" t="n"/>
       <c r="W6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X6" s="10" t="n">
-        <v>11</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="X6" s="9" t="n"/>
       <c r="Y6" s="10" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="Z6" s="10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -5936,36 +6933,36 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
@@ -5973,46 +6970,49 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>BR-08282/2026</t>
+          <t>BR-09285/2026</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M7" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="10" t="n">
-        <v>37.3</v>
+        <v>32</v>
       </c>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="10" t="n">
-        <v>39.8</v>
+        <v>37</v>
       </c>
       <c r="T7" s="10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
+      <c r="V7" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="W7" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>7.1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X7" s="9" t="n"/>
       <c r="Y7" s="10" t="n">
-        <v>4.5</v>
+        <v>11</v>
+      </c>
+      <c r="Z7" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6023,12 +7023,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -6038,14 +7038,14 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1</v>
@@ -6060,44 +7060,47 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>BR-03770/2026</t>
+          <t>BR-08282/2026</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M8" s="10" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" s="9" t="n"/>
+        <v>4.8</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>1.3</v>
+      </c>
       <c r="P8" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>35</v>
+        <v>37.3</v>
       </c>
       <c r="R8" s="9" t="n"/>
       <c r="S8" s="10" t="n">
-        <v>39</v>
+        <v>39.8</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="U8" s="9" t="n"/>
       <c r="V8" s="9" t="n"/>
       <c r="W8" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X8" s="10" t="n">
-        <v>10</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="X8" s="9" t="n"/>
       <c r="Y8" s="10" t="n">
-        <v>4</v>
+        <v>7.1</v>
+      </c>
+      <c r="Z8" s="10" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -6108,29 +7111,29 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>1</v>
@@ -6145,42 +7148,45 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-03770/2026</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
+      <c r="P9" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" s="10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="10" t="n">
-        <v>40.4</v>
+        <v>39</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U9" s="9" t="n"/>
       <c r="V9" s="9" t="n"/>
       <c r="W9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="X9" s="9" t="n"/>
       <c r="Y9" s="10" t="n">
-        <v>8.5</v>
+        <v>10</v>
+      </c>
+      <c r="Z9" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6191,36 +7197,36 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>5028</v>
+        <v>1500</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
@@ -6228,42 +7234,43 @@
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-00605/2026</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M10" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
       <c r="Q10" s="10" t="n">
-        <v>40.1</v>
+        <v>37</v>
       </c>
       <c r="R10" s="9" t="n"/>
       <c r="S10" s="10" t="n">
-        <v>45.9</v>
+        <v>40.4</v>
       </c>
       <c r="T10" s="10" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="U10" s="9" t="n"/>
       <c r="V10" s="9" t="n"/>
       <c r="W10" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X10" s="10" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X10" s="9" t="n"/>
       <c r="Y10" s="10" t="n">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="Z10" s="10" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="11">
@@ -6274,29 +7281,29 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>1</v>
@@ -6311,41 +7318,42 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-00873/2026</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="10" t="n">
-        <v>32</v>
+        <v>37.8</v>
       </c>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="10" t="n">
-        <v>39</v>
+        <v>41.3</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" s="9" t="n"/>
       <c r="V11" s="9" t="n"/>
       <c r="W11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" s="10" t="n">
-        <v>16</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X11" s="9" t="n"/>
       <c r="Y11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z11" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6357,36 +7365,36 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2004</v>
+        <v>5028</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
@@ -6394,42 +7402,43 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>BR-03715/2026</t>
+          <t>BR-04227/2026</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
       <c r="Q12" s="10" t="n">
-        <v>33</v>
+        <v>40.1</v>
       </c>
       <c r="R12" s="9" t="n"/>
       <c r="S12" s="10" t="n">
-        <v>39</v>
+        <v>45.9</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="U12" s="9" t="n"/>
       <c r="V12" s="9" t="n"/>
       <c r="W12" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X12" s="10" t="n">
-        <v>12</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="X12" s="9" t="n"/>
       <c r="Y12" s="10" t="n">
-        <v>3</v>
+        <v>1.9</v>
+      </c>
+      <c r="Z12" s="10" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -6440,36 +7449,36 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>4986</v>
+        <v>1500</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
@@ -6477,42 +7486,43 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>BR-07600/2026</t>
+          <t>BR-00386/2026</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M13" s="10" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="10" t="n">
-        <v>37.9</v>
+        <v>35</v>
       </c>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="10" t="n">
-        <v>45</v>
+        <v>40.3</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="U13" s="9" t="n"/>
       <c r="V13" s="9" t="n"/>
       <c r="W13" s="10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X13" s="10" t="n">
-        <v>3.8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="X13" s="9" t="n"/>
       <c r="Y13" s="10" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
+      </c>
+      <c r="Z13" s="10" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="14">
@@ -6533,12 +7543,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
@@ -6552,7 +7562,7 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
@@ -6560,12 +7570,12 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-05809/2026</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M14" s="10" t="n">
@@ -6584,16 +7594,19 @@
         <v>39</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n"/>
       <c r="V14" s="9" t="n"/>
-      <c r="W14" s="9" t="n"/>
-      <c r="X14" s="10" t="n">
+      <c r="W14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Y14" s="10" t="n">
-        <v>6</v>
+      <c r="Z14" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -6604,22 +7617,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
@@ -6641,80 +7654,83 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-03715/2026</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="9" t="n"/>
+      <c r="N15" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="10" t="n">
         <v>39</v>
       </c>
       <c r="T15" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" s="9" t="n"/>
       <c r="V15" s="9" t="n"/>
       <c r="W15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X15" s="10" t="n">
-        <v>13</v>
-      </c>
+      <c r="X15" s="9" t="n"/>
       <c r="Y15" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="Z15" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>5032</v>
+        <v>2080</v>
       </c>
       <c r="G16" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
@@ -6722,72 +7738,83 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>BR-06939/2026</t>
+          <t>BR-07974/2026</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
       <c r="Q16" s="10" t="n">
-        <v>41.8</v>
+        <v>36.6</v>
       </c>
       <c r="R16" s="9" t="n"/>
       <c r="S16" s="10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="T16" s="9" t="n"/>
+        <v>40.5</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="U16" s="9" t="n"/>
       <c r="V16" s="9" t="n"/>
-      <c r="W16" s="9" t="n"/>
-      <c r="X16" s="10" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y16" s="9" t="n"/>
+      <c r="W16" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z16" s="10" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2004</v>
+        <v>4986</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
@@ -6795,40 +7822,49 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>BR-00290/2026</t>
+          <t>BR-07600/2026</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="10" t="n">
-        <v>45</v>
+        <v>37.9</v>
       </c>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T17" s="9" t="n"/>
+      <c r="T17" s="10" t="n">
+        <v>2.9</v>
+      </c>
       <c r="U17" s="9" t="n"/>
       <c r="V17" s="9" t="n"/>
-      <c r="W17" s="9" t="n"/>
-      <c r="X17" s="10" t="n">
-        <v>9</v>
-      </c>
+      <c r="W17" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X17" s="9" t="n"/>
       <c r="Y17" s="10" t="n">
-        <v>1</v>
+        <v>3.8</v>
+      </c>
+      <c r="Z17" s="10" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6843,12 +7879,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
@@ -6858,11 +7894,11 @@
         <v>2</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
@@ -6870,74 +7906,81 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>BR-03598/2026</t>
+          <t>BR-00249/2026</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
       <c r="Q18" s="10" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="R18" s="9" t="n"/>
       <c r="S18" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="T18" s="9" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="U18" s="9" t="n"/>
       <c r="V18" s="9" t="n"/>
       <c r="W18" s="9" t="n"/>
-      <c r="X18" s="10" t="n">
-        <v>14</v>
-      </c>
+      <c r="X18" s="9" t="n"/>
       <c r="Y18" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="Z18" s="10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="G19" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
@@ -6945,68 +7988,79 @@
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
+          <t>BR-08425/2026</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>5.1</v>
+      </c>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="10" t="n">
-        <v>47.8</v>
+        <v>33</v>
       </c>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="10" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="T19" s="9" t="n"/>
+        <v>39.5</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="U19" s="9" t="n"/>
       <c r="V19" s="9" t="n"/>
-      <c r="W19" s="9" t="n"/>
-      <c r="X19" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y19" s="9" t="n"/>
+      <c r="W19" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z19" s="10" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -7018,74 +8072,85 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-08254/2026</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
       <c r="Q20" s="10" t="n">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="R20" s="9" t="n"/>
       <c r="S20" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="T20" s="9" t="n"/>
+        <v>39.8</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="U20" s="9" t="n"/>
       <c r="V20" s="9" t="n"/>
-      <c r="W20" s="9" t="n"/>
+      <c r="W20" s="10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="X20" s="10" t="n">
-        <v>16</v>
+        <v>6.5</v>
       </c>
       <c r="Y20" s="10" t="n">
-        <v>2</v>
+        <v>6.8</v>
+      </c>
+      <c r="Z20" s="10" t="n">
+        <v>4.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2000</v>
+        <v>5418</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
@@ -7093,115 +8158,131 @@
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>BR-08282/2026</t>
+          <t>BR-02804/2026</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-atlasintel-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>4.3</v>
+      </c>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="10" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="10" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="T21" s="9" t="n"/>
+        <v>48.8</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>3.4</v>
+      </c>
       <c r="U21" s="9" t="n"/>
       <c r="V21" s="9" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="10" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="W21" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X21" s="9" t="n"/>
       <c r="Y21" s="10" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
+      </c>
+      <c r="Z21" s="10" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>100% Cidades/Futura</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>BR-03770/2026</t>
-        </is>
-      </c>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
       <c r="Q22" s="10" t="n">
-        <v>46</v>
+        <v>34.3</v>
       </c>
       <c r="R22" s="9" t="n"/>
       <c r="S22" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="T22" s="9" t="n"/>
+        <v>35.4</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>1.7</v>
+      </c>
       <c r="U22" s="9" t="n"/>
       <c r="V22" s="9" t="n"/>
-      <c r="W22" s="9" t="n"/>
+      <c r="W22" s="10" t="n">
+        <v>4.4</v>
+      </c>
       <c r="X22" s="10" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="Y22" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="Z22" s="10" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -7216,26 +8297,26 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
@@ -7243,74 +8324,83 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-06731/2026</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="10" t="n">
-        <v>45.8</v>
+        <v>27.6</v>
       </c>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="10" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="T23" s="9" t="n"/>
+        <v>39.6</v>
+      </c>
+      <c r="T23" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="U23" s="9" t="n"/>
       <c r="V23" s="9" t="n"/>
-      <c r="W23" s="9" t="n"/>
-      <c r="X23" s="10" t="n">
-        <v>6.6</v>
-      </c>
+      <c r="W23" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="X23" s="9" t="n"/>
       <c r="Y23" s="10" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
+      </c>
+      <c r="Z23" s="10" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>5028</v>
+        <v>2004</v>
       </c>
       <c r="G24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
@@ -7318,33 +8408,42 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-00835/2026</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
       <c r="Q24" s="10" t="n">
-        <v>47.6</v>
+        <v>32</v>
       </c>
       <c r="R24" s="9" t="n"/>
       <c r="S24" s="10" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="T24" s="9" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="T24" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="U24" s="9" t="n"/>
       <c r="V24" s="9" t="n"/>
-      <c r="W24" s="9" t="n"/>
-      <c r="X24" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y24" s="9" t="n"/>
+      <c r="W24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" s="10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -7354,36 +8453,36 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2004</v>
+        <v>5032</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
@@ -7391,12 +8490,12 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-06939/2026</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M25" s="9" t="n"/>
@@ -7404,22 +8503,21 @@
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="10" t="n">
-        <v>41</v>
+        <v>41.8</v>
       </c>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="10" t="n">
-        <v>41</v>
+        <v>48.9</v>
       </c>
       <c r="T25" s="9" t="n"/>
       <c r="U25" s="9" t="n"/>
       <c r="V25" s="9" t="n"/>
       <c r="W25" s="9" t="n"/>
-      <c r="X25" s="10" t="n">
-        <v>16</v>
-      </c>
+      <c r="X25" s="9" t="n"/>
       <c r="Y25" s="10" t="n">
-        <v>2</v>
-      </c>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -7439,12 +8537,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F26" s="9" t="n">
@@ -7466,12 +8564,12 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>BR-03715/2026</t>
+          <t>BR-00290/2026</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M26" s="9" t="n"/>
@@ -7479,20 +8577,21 @@
       <c r="O26" s="9" t="n"/>
       <c r="P26" s="9" t="n"/>
       <c r="Q26" s="10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R26" s="9" t="n"/>
       <c r="S26" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T26" s="9" t="n"/>
       <c r="U26" s="9" t="n"/>
       <c r="V26" s="9" t="n"/>
       <c r="W26" s="9" t="n"/>
-      <c r="X26" s="10" t="n">
-        <v>10</v>
-      </c>
+      <c r="X26" s="9" t="n"/>
       <c r="Y26" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7504,36 +8603,36 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>4986</v>
+        <v>2004</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
@@ -7541,12 +8640,12 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>BR-07600/2026</t>
+          <t>BR-03598/2026</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M27" s="9" t="n"/>
@@ -7554,20 +8653,23 @@
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="10" t="n">
-        <v>46.3</v>
+        <v>41</v>
       </c>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="10" t="n">
-        <v>46.2</v>
+        <v>42</v>
       </c>
       <c r="T27" s="9" t="n"/>
       <c r="U27" s="9" t="n"/>
       <c r="V27" s="9" t="n"/>
       <c r="W27" s="9" t="n"/>
-      <c r="X27" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -7577,36 +8679,36 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H28" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
@@ -7614,12 +8716,12 @@
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-05356/2026</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M28" s="9" t="n"/>
@@ -7627,21 +8729,22 @@
       <c r="O28" s="9" t="n"/>
       <c r="P28" s="9" t="n"/>
       <c r="Q28" s="10" t="n">
-        <v>38</v>
+        <v>45.3</v>
       </c>
       <c r="R28" s="9" t="n"/>
       <c r="S28" s="10" t="n">
-        <v>43</v>
+        <v>44.7</v>
       </c>
       <c r="T28" s="9" t="n"/>
       <c r="U28" s="9" t="n"/>
       <c r="V28" s="9" t="n"/>
       <c r="W28" s="9" t="n"/>
-      <c r="X28" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="X28" s="9" t="n"/>
       <c r="Y28" s="10" t="n">
-        <v>2</v>
+        <v>6.5</v>
+      </c>
+      <c r="Z28" s="10" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="29">
@@ -7652,36 +8755,36 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
@@ -7689,12 +8792,12 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-07992/2026</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M29" s="9" t="n"/>
@@ -7702,61 +8805,60 @@
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="10" t="n">
-        <v>38</v>
+        <v>47.8</v>
       </c>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="10" t="n">
-        <v>44</v>
+        <v>47.5</v>
       </c>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n"/>
-      <c r="X29" s="10" t="n">
-        <v>13</v>
-      </c>
+      <c r="X29" s="9" t="n"/>
       <c r="Y29" s="10" t="n">
-        <v>4</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="Z29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>5032</v>
+        <v>2004</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
@@ -7764,65 +8866,68 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>BR-06939/2026</t>
+          <t>BR-09285/2026</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M30" s="9" t="n"/>
       <c r="N30" s="9" t="n"/>
       <c r="O30" s="9" t="n"/>
       <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
+      <c r="Q30" s="10" t="n">
+        <v>42</v>
+      </c>
       <c r="R30" s="9" t="n"/>
       <c r="S30" s="10" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="T30" s="9" t="n"/>
       <c r="U30" s="9" t="n"/>
       <c r="V30" s="9" t="n"/>
-      <c r="W30" s="10" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="X30" s="10" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y30" s="9" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z30" s="10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F31" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H31" s="9" t="n">
         <v>2</v>
@@ -7837,60 +8942,61 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>BR-00290/2026</t>
+          <t>BR-08282/2026</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
+      <c r="Q31" s="10" t="n">
+        <v>48</v>
+      </c>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="10" t="n">
-        <v>46</v>
+        <v>42.6</v>
       </c>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
-      <c r="W31" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="X31" s="10" t="n">
-        <v>13</v>
-      </c>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
       <c r="Y31" s="10" t="n">
-        <v>2</v>
+        <v>2.1</v>
+      </c>
+      <c r="Z31" s="10" t="n">
+        <v>7.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
@@ -7904,7 +9010,7 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
@@ -7912,74 +9018,75 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>BR-03598/2026</t>
+          <t>BR-03770/2026</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M32" s="9" t="n"/>
       <c r="N32" s="9" t="n"/>
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
+      <c r="Q32" s="10" t="n">
+        <v>46</v>
+      </c>
       <c r="R32" s="9" t="n"/>
       <c r="S32" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T32" s="9" t="n"/>
       <c r="U32" s="9" t="n"/>
       <c r="V32" s="9" t="n"/>
-      <c r="W32" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="X32" s="10" t="n">
-        <v>15</v>
-      </c>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
       <c r="Y32" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F33" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
@@ -7987,65 +9094,68 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
+          <t>BR-00605/2026</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
       <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
+      <c r="Q33" s="10" t="n">
+        <v>45.8</v>
+      </c>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="10" t="n">
-        <v>47.4</v>
+        <v>45.5</v>
       </c>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n"/>
       <c r="V33" s="9" t="n"/>
-      <c r="W33" s="10" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="X33" s="10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z33" s="10" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>2</v>
@@ -8060,74 +9170,75 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-00873/2026</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M34" s="9" t="n"/>
       <c r="N34" s="9" t="n"/>
       <c r="O34" s="9" t="n"/>
       <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
+      <c r="Q34" s="10" t="n">
+        <v>45.2</v>
+      </c>
       <c r="R34" s="9" t="n"/>
       <c r="S34" s="10" t="n">
-        <v>43</v>
+        <v>44.1</v>
       </c>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="9" t="n"/>
       <c r="V34" s="9" t="n"/>
-      <c r="W34" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="X34" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="9" t="n"/>
       <c r="Y34" s="10" t="n">
-        <v>4</v>
+        <v>6.2</v>
+      </c>
+      <c r="Z34" s="10" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2000</v>
+        <v>5028</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
@@ -8135,74 +9246,73 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>BR-08282/2026</t>
+          <t>BR-04227/2026</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
+      <c r="Q35" s="10" t="n">
+        <v>47.6</v>
+      </c>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="10" t="n">
-        <v>44.8</v>
+        <v>46.6</v>
       </c>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
-      <c r="W35" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="X35" s="10" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
       <c r="Y35" s="10" t="n">
-        <v>2.2</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="Z35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H36" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
@@ -8210,74 +9320,75 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>BR-03770/2026</t>
+          <t>BR-00386/2026</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M36" s="9" t="n"/>
       <c r="N36" s="9" t="n"/>
       <c r="O36" s="9" t="n"/>
       <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
+      <c r="Q36" s="10" t="n">
+        <v>45.3</v>
+      </c>
       <c r="R36" s="9" t="n"/>
       <c r="S36" s="10" t="n">
-        <v>45</v>
+        <v>47.4</v>
       </c>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="9" t="n"/>
       <c r="V36" s="9" t="n"/>
-      <c r="W36" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="X36" s="10" t="n">
-        <v>11</v>
-      </c>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="9" t="n"/>
       <c r="Y36" s="10" t="n">
-        <v>2</v>
+        <v>4.1</v>
+      </c>
+      <c r="Z36" s="10" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
@@ -8285,74 +9396,75 @@
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-05809/2026</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
+      <c r="Q37" s="10" t="n">
+        <v>41</v>
+      </c>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="10" t="n">
-        <v>44.7</v>
+        <v>41</v>
       </c>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
-      <c r="W37" s="10" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="X37" s="10" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="9" t="n"/>
       <c r="Y37" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>16</v>
+      </c>
+      <c r="Z37" s="10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F38" s="9" t="n">
-        <v>5028</v>
+        <v>2004</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
@@ -8360,65 +9472,68 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-03715/2026</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M38" s="9" t="n"/>
       <c r="N38" s="9" t="n"/>
       <c r="O38" s="9" t="n"/>
       <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
+      <c r="Q38" s="10" t="n">
+        <v>43</v>
+      </c>
       <c r="R38" s="9" t="n"/>
       <c r="S38" s="10" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="T38" s="9" t="n"/>
       <c r="U38" s="9" t="n"/>
       <c r="V38" s="9" t="n"/>
-      <c r="W38" s="10" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="X38" s="10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="9" t="n"/>
+      <c r="Y38" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F39" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>2</v>
@@ -8433,74 +9548,75 @@
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-07974/2026</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
         </is>
       </c>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
+      <c r="Q39" s="10" t="n">
+        <v>44.4</v>
+      </c>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
-      <c r="W39" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X39" s="10" t="n">
-        <v>19</v>
-      </c>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="9" t="n"/>
       <c r="Y39" s="10" t="n">
-        <v>3</v>
+        <v>6.9</v>
+      </c>
+      <c r="Z39" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F40" s="9" t="n">
-        <v>2004</v>
+        <v>4986</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
@@ -8508,40 +9624,39 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-07600/2026</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M40" s="9" t="n"/>
       <c r="N40" s="9" t="n"/>
       <c r="O40" s="9" t="n"/>
       <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
+      <c r="Q40" s="10" t="n">
+        <v>46.3</v>
+      </c>
       <c r="R40" s="9" t="n"/>
       <c r="S40" s="10" t="n">
-        <v>43</v>
+        <v>46.2</v>
       </c>
       <c r="T40" s="9" t="n"/>
       <c r="U40" s="9" t="n"/>
       <c r="V40" s="9" t="n"/>
-      <c r="W40" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="X40" s="10" t="n">
-        <v>21</v>
-      </c>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="9" t="n"/>
       <c r="Y40" s="10" t="n">
-        <v>4</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="Z40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -8556,12 +9671,12 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F41" s="9" t="n">
@@ -8583,33 +9698,1616 @@
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-00249/2026</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
+      <c r="Q41" s="10" t="n">
+        <v>38</v>
+      </c>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n"/>
+      <c r="Y41" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z41" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>BR-08425/2026</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="R42" s="9" t="n"/>
+      <c r="S42" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="T42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="V42" s="9" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="9" t="n"/>
+      <c r="Y42" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z42" s="10" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>BR-08254/2026</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="10" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="R43" s="9" t="n"/>
+      <c r="S43" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n"/>
+      <c r="Y43" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="n"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
+      <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="R44" s="9" t="n"/>
+      <c r="S44" s="10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="T44" s="9" t="n"/>
+      <c r="U44" s="9" t="n"/>
+      <c r="V44" s="9" t="n"/>
+      <c r="W44" s="9" t="n"/>
+      <c r="X44" s="9" t="n"/>
+      <c r="Y44" s="10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z44" s="10" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>BR-06731/2026</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z45" s="10" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Flávio</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
+      <c r="P46" s="9" t="n"/>
+      <c r="Q46" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="R46" s="9" t="n"/>
+      <c r="S46" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T46" s="9" t="n"/>
+      <c r="U46" s="9" t="n"/>
+      <c r="V46" s="9" t="n"/>
+      <c r="W46" s="9" t="n"/>
+      <c r="X46" s="9" t="n"/>
+      <c r="Y46" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z46" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>5032</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>BR-06939/2026</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="10" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="10" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="Z47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>BR-00290/2026</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="9" t="n"/>
+      <c r="Q48" s="9" t="n"/>
+      <c r="R48" s="9" t="n"/>
+      <c r="S48" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T48" s="9" t="n"/>
+      <c r="U48" s="9" t="n"/>
+      <c r="V48" s="9" t="n"/>
+      <c r="W48" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="X48" s="9" t="n"/>
+      <c r="Y48" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z48" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>BR-03598/2026</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="9" t="n"/>
+      <c r="S49" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T49" s="9" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="9" t="n"/>
+      <c r="W49" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="X49" s="9" t="n"/>
+      <c r="Y49" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z49" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>BR-05356/2026</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="9" t="n"/>
+      <c r="S50" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T50" s="9" t="n"/>
+      <c r="U50" s="9" t="n"/>
+      <c r="V50" s="9" t="n"/>
+      <c r="W50" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="X50" s="9" t="n"/>
+      <c r="Y50" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z50" s="10" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>5008</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>BR-07992/2026</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="9" t="n"/>
+      <c r="S51" s="10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="T51" s="9" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="9" t="n"/>
+      <c r="W51" s="10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="X51" s="9" t="n"/>
+      <c r="Y51" s="10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Z51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>BR-09285/2026</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n"/>
+      <c r="R52" s="9" t="n"/>
+      <c r="S52" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T52" s="9" t="n"/>
+      <c r="U52" s="9" t="n"/>
+      <c r="V52" s="9" t="n"/>
+      <c r="W52" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="X52" s="9" t="n"/>
+      <c r="Y52" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z52" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>BR-08282/2026</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="X53" s="9" t="n"/>
+      <c r="Y53" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Z53" s="10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>BR-03770/2026</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="9" t="n"/>
+      <c r="S54" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T54" s="9" t="n"/>
+      <c r="U54" s="9" t="n"/>
+      <c r="V54" s="9" t="n"/>
+      <c r="W54" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="X54" s="9" t="n"/>
+      <c r="Y54" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z54" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>BR-00605/2026</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="S55" s="10" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="T55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="V55" s="9" t="n"/>
+      <c r="W55" s="10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="X55" s="9" t="n"/>
+      <c r="Y55" s="10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Z55" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>BR-04227/2026</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="9" t="n"/>
+      <c r="S56" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T56" s="9" t="n"/>
+      <c r="U56" s="9" t="n"/>
+      <c r="V56" s="9" t="n"/>
+      <c r="W56" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="X56" s="9" t="n"/>
+      <c r="Y56" s="10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>BR-00386/2026</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="10" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="T57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="X57" s="9" t="n"/>
+      <c r="Y57" s="10" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Z57" s="10" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="9" t="n"/>
+      <c r="S58" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T58" s="9" t="n"/>
+      <c r="U58" s="9" t="n"/>
+      <c r="V58" s="9" t="n"/>
+      <c r="W58" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X58" s="9" t="n"/>
+      <c r="Y58" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z58" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>BR-00249/2026</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="9" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="9" t="n"/>
+      <c r="S59" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T59" s="9" t="n"/>
+      <c r="U59" s="9" t="n"/>
+      <c r="V59" s="9" t="n"/>
+      <c r="W59" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="X59" s="9" t="n"/>
+      <c r="Y59" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z59" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>BR-08425/2026</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="9" t="n"/>
+      <c r="Q60" s="9" t="n"/>
+      <c r="R60" s="9" t="n"/>
+      <c r="S60" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T60" s="9" t="n"/>
+      <c r="U60" s="9" t="n"/>
+      <c r="V60" s="9" t="n"/>
+      <c r="W60" s="10" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="X60" s="9" t="n"/>
+      <c r="Y60" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z60" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="9" t="n"/>
+      <c r="S61" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="T61" s="9" t="n"/>
+      <c r="U61" s="9" t="n"/>
+      <c r="V61" s="9" t="n"/>
+      <c r="W61" s="10" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="X61" s="9" t="n"/>
+      <c r="Y61" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z61" s="10" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="9" t="n"/>
+      <c r="S62" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T62" s="9" t="n"/>
+      <c r="U62" s="9" t="n"/>
+      <c r="V62" s="9" t="n"/>
+      <c r="W62" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="X41" s="10" t="n">
+      <c r="X62" s="9" t="n"/>
+      <c r="Y62" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Z62" s="10" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         <v>5032</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1.514560590142393</v>
+        <v>1.479967978455294</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.2</v>
@@ -2133,7 +2133,7 @@
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>0.8515174032030288</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.8130642430320129</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.6123724356957946</v>
+        <v>0.5983858299345048</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.8</v>
@@ -2313,7 +2313,7 @@
         <v>5008</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.9088519968310748</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0.3</v>
@@ -2373,7 +2373,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.4160343594175414</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>2000</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.3968502629920498</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0.3</v>
@@ -2493,7 +2493,7 @@
         <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>1</v>
@@ -2553,7 +2553,7 @@
         <v>1500</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.313342981434775</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.6</v>
@@ -2613,7 +2613,7 @@
         <v>2080</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.3138814693848235</v>
+        <v>0.3067124067161689</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>1.1</v>
@@ -2673,7 +2673,7 @@
         <v>5028</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.4056551356117546</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.6</v>
@@ -2733,7 +2733,7 @@
         <v>1500</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1679163460868971</v>
+        <v>0.1640811314418663</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0.8</v>
@@ -2793,7 +2793,7 @@
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537124</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>1</v>
@@ -2853,7 +2853,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.1729117628226748</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>2</v>
@@ -2913,7 +2913,7 @@
         <v>2080</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.1464308831840453</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0.4</v>
@@ -2973,7 +2973,7 @@
         <v>4986</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.2215352390629677</v>
+        <v>0.2164753672098426</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1.1</v>
@@ -3033,7 +3033,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>1</v>
@@ -3093,7 +3093,7 @@
         <v>1500</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.0730898348362876</v>
+        <v>0.07142046070149105</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>0.5</v>
@@ -3153,7 +3153,7 @@
         <v>2080</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.07667810167904221</v>
+        <v>0.07492677141629081</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>1.1</v>
@@ -3213,7 +3213,7 @@
         <v>5418</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.102869000432589</v>
+        <v>0.1005194692155711</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>1</v>
@@ -3273,7 +3273,7 @@
         <v>2000</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.06107249802714037</v>
+        <v>0.05967760024440102</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0.6</v>
@@ -3333,7 +3333,7 @@
         <v>2000</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0.2</v>
@@ -3393,7 +3393,7 @@
         <v>2004</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.05081651518950081</v>
+        <v>0.04965586437851098</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>2</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.514560590142393</v>
+        <v>1.479967978455294</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>41.8</v>
@@ -3647,7 +3647,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>0.8515174032030288</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>45</v>
@@ -3677,7 +3677,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8130642430320129</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>41</v>
@@ -3707,7 +3707,7 @@
         <v>1500</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.6123724356957946</v>
+        <v>0.5983858299345048</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>45.3</v>
@@ -3737,7 +3737,7 @@
         <v>5008</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.9088519968310748</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>47.8</v>
@@ -3767,7 +3767,7 @@
         <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.4160343594175414</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>42</v>
@@ -3797,7 +3797,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.3968502629920498</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>48</v>
@@ -3827,7 +3827,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>46</v>
@@ -3857,7 +3857,7 @@
         <v>1500</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.313342981434775</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>45.8</v>
@@ -3887,7 +3887,7 @@
         <v>2080</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3138814693848235</v>
+        <v>0.3067124067161689</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>45.2</v>
@@ -3917,7 +3917,7 @@
         <v>5028</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.4056551356117546</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>47.6</v>
@@ -3947,7 +3947,7 @@
         <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.1679163460868971</v>
+        <v>0.1640811314418663</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>45.3</v>
@@ -3977,7 +3977,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537124</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>41</v>
@@ -4007,7 +4007,7 @@
         <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.1729117628226748</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>43</v>
@@ -4037,7 +4037,7 @@
         <v>2080</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.1464308831840453</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>44.4</v>
@@ -4067,7 +4067,7 @@
         <v>4986</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.2215352390629677</v>
+        <v>0.2164753672098426</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>46.3</v>
@@ -4097,7 +4097,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>38</v>
@@ -4127,7 +4127,7 @@
         <v>1500</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.0730898348362876</v>
+        <v>0.07142046070149105</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>41.1</v>
@@ -4157,7 +4157,7 @@
         <v>2080</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.07667810167904221</v>
+        <v>0.07492677141629081</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>42.2</v>
@@ -4187,7 +4187,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.06107249802714037</v>
+        <v>0.05967760024440102</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>48.1</v>
@@ -4217,7 +4217,7 @@
         <v>2000</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>36</v>
@@ -4247,7 +4247,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.05081651518950081</v>
+        <v>0.04965586437851098</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>38</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.514560590142393</v>
+        <v>1.479967978455294</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>47.8</v>
@@ -4471,7 +4471,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>0.8515174032030288</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>46</v>
@@ -4501,7 +4501,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8130642430320129</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>44</v>
@@ -4531,7 +4531,7 @@
         <v>1500</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.6123724356957946</v>
+        <v>0.5983858299345048</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>44</v>
@@ -4561,7 +4561,7 @@
         <v>5008</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.9300954052460574</v>
+        <v>0.9088519968310748</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>47.4</v>
@@ -4591,7 +4591,7 @@
         <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.4257587016015145</v>
+        <v>0.4160343594175414</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>43</v>
@@ -4621,7 +4621,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.4061261981781178</v>
+        <v>0.3968502629920498</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>44.8</v>
@@ -4651,7 +4651,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.3881737829494479</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>45</v>
@@ -4681,7 +4681,7 @@
         <v>1500</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.3206670264407789</v>
+        <v>0.313342981434775</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>44.7</v>
@@ -4711,7 +4711,7 @@
         <v>5028</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.4151368749394808</v>
+        <v>0.4056551356117546</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>46.6</v>
@@ -4741,7 +4741,7 @@
         <v>1500</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.1679163460868971</v>
+        <v>0.1640811314418663</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>46.1</v>
@@ -4771,7 +4771,7 @@
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537124</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>44</v>
@@ -4801,7 +4801,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.09931172875702197</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>43</v>
@@ -4831,7 +4831,7 @@
         <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.0730898348362876</v>
+        <v>0.07142046070149105</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>45</v>
@@ -4861,7 +4861,7 @@
         <v>2000</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.06107249802714037</v>
+        <v>0.05967760024440102</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>42.8</v>
@@ -4891,7 +4891,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.05081651518950081</v>
+        <v>0.04965586437851098</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>46</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>23 pesquisas</t>
+          <t>30 pesquisas</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.02</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>35.52</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="11">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>41.98</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="15">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="16">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3.72</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="17">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="19">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4.11</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="21">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>22 pesquisas</t>
+          <t>25 pesquisas</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>44.25</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="23">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45.32</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="27">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>16 pesquisas</t>
+          <t>18 pesquisas</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45.72</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>39.41</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="30">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12.44</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="31">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="33">
@@ -1748,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.02</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="11">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>35.52</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="14">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>41.98</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="15">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="17">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="18">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3.72</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="21">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4.11</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="24">
@@ -2181,343 +2181,343 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>0.8515174032030288</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F28" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L28" s="10" t="n">
         <v>2</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P28" s="10" t="n">
         <v/>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R28" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.5983858299345048</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" s="10" t="n">
         <v/>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.9088519968310748</v>
+        <v>0.5983858299345048</v>
       </c>
       <c r="E30" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v/>
-      </c>
       <c r="I30" s="10" t="n">
-        <v>39.7</v>
+        <v>36</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>46.6</v>
+        <v>40</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P30" s="10" t="n">
         <v/>
       </c>
       <c r="Q30" s="10" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.4160343594175414</v>
+        <v>0.9088519968310748</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I31" s="10" t="n">
-        <v>32</v>
+        <v>39.7</v>
       </c>
       <c r="J31" s="10" t="n">
         <v/>
       </c>
       <c r="K31" s="10" t="n">
-        <v>37</v>
+        <v>46.6</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="M31" s="10" t="n">
         <v/>
       </c>
       <c r="N31" s="10" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="O31" s="10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P31" s="10" t="n">
         <v/>
       </c>
       <c r="Q31" s="10" t="n">
-        <v>11</v>
+        <v>0.5</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.3968502629920498</v>
+        <v>0.4160343594175414</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>37.3</v>
+        <v>32</v>
       </c>
       <c r="J32" s="10" t="n">
         <v/>
       </c>
       <c r="K32" s="10" t="n">
-        <v>39.8</v>
+        <v>37</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M32" s="10" t="n">
         <v/>
       </c>
       <c r="N32" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P32" s="10" t="n">
         <v/>
       </c>
       <c r="Q32" s="10" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.3793078814938844</v>
+        <v>0.3968502629920498</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>35</v>
+        <v>37.3</v>
       </c>
       <c r="J33" s="10" t="n">
         <v/>
       </c>
       <c r="K33" s="10" t="n">
-        <v>39</v>
+        <v>39.8</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M33" s="10" t="n">
         <v/>
@@ -2526,58 +2526,58 @@
         <v/>
       </c>
       <c r="O33" s="10" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P33" s="10" t="n">
         <v/>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="R33" s="10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.313342981434775</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G34" s="10" t="n">
         <v/>
       </c>
       <c r="H34" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J34" s="10" t="n">
         <v/>
       </c>
       <c r="K34" s="10" t="n">
-        <v>40.4</v>
+        <v>39</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="10" t="n">
         <v/>
@@ -2586,40 +2586,40 @@
         <v/>
       </c>
       <c r="O34" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" s="10" t="n">
         <v/>
       </c>
       <c r="Q34" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R34" s="10" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>2080</v>
+        <v>1500</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.3067124067161689</v>
+        <v>0.313342981434775</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="G35" s="10" t="n">
         <v/>
@@ -2628,16 +2628,16 @@
         <v/>
       </c>
       <c r="I35" s="10" t="n">
-        <v>37.8</v>
+        <v>37</v>
       </c>
       <c r="J35" s="10" t="n">
         <v/>
       </c>
       <c r="K35" s="10" t="n">
-        <v>41.3</v>
+        <v>40.4</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="M35" s="10" t="n">
         <v/>
@@ -2652,34 +2652,34 @@
         <v/>
       </c>
       <c r="Q35" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5028</v>
+        <v>2080</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.4056551356117546</v>
+        <v>0.3067124067161689</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G36" s="10" t="n">
         <v/>
@@ -2688,16 +2688,16 @@
         <v/>
       </c>
       <c r="I36" s="10" t="n">
-        <v>40.1</v>
+        <v>37.8</v>
       </c>
       <c r="J36" s="10" t="n">
         <v/>
       </c>
       <c r="K36" s="10" t="n">
-        <v>45.9</v>
+        <v>41.3</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="M36" s="10" t="n">
         <v/>
@@ -2706,58 +2706,58 @@
         <v/>
       </c>
       <c r="O36" s="10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P36" s="10" t="n">
         <v/>
       </c>
       <c r="Q36" s="10" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>1500</v>
+        <v>2080</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1640811314418663</v>
+        <v>0.3067124067161689</v>
       </c>
       <c r="E37" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G37" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v/>
-      </c>
       <c r="H37" s="10" t="n">
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J37" s="10" t="n">
         <v/>
       </c>
       <c r="K37" s="10" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="M37" s="10" t="n">
         <v/>
@@ -2766,40 +2766,40 @@
         <v/>
       </c>
       <c r="O37" s="10" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="P37" s="10" t="n">
         <v/>
       </c>
       <c r="Q37" s="10" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>2004</v>
+        <v>5028</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.1853222387537124</v>
+        <v>0.4056551356117546</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G38" s="10" t="n">
         <v/>
@@ -2808,16 +2808,16 @@
         <v/>
       </c>
       <c r="I38" s="10" t="n">
-        <v>32</v>
+        <v>40.1</v>
       </c>
       <c r="J38" s="10" t="n">
         <v/>
       </c>
       <c r="K38" s="10" t="n">
-        <v>39</v>
+        <v>45.9</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="M38" s="10" t="n">
         <v/>
@@ -2826,40 +2826,40 @@
         <v/>
       </c>
       <c r="O38" s="10" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="P38" s="10" t="n">
         <v/>
       </c>
       <c r="Q38" s="10" t="n">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="R38" s="10" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.1689624527017146</v>
+        <v>0.1640811314418663</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G39" s="10" t="n">
         <v/>
@@ -2868,16 +2868,16 @@
         <v/>
       </c>
       <c r="I39" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J39" s="10" t="n">
         <v/>
       </c>
       <c r="K39" s="10" t="n">
-        <v>39</v>
+        <v>40.3</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="M39" s="10" t="n">
         <v/>
@@ -2892,34 +2892,34 @@
         <v/>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="R39" s="10" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>2080</v>
+        <v>2004</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.1430863971899205</v>
+        <v>0.1853222387537124</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G40" s="10" t="n">
         <v/>
@@ -2928,16 +2928,16 @@
         <v/>
       </c>
       <c r="I40" s="10" t="n">
-        <v>36.6</v>
+        <v>32</v>
       </c>
       <c r="J40" s="10" t="n">
         <v/>
       </c>
       <c r="K40" s="10" t="n">
-        <v>40.5</v>
+        <v>39</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M40" s="10" t="n">
         <v/>
@@ -2946,40 +2946,40 @@
         <v/>
       </c>
       <c r="O40" s="10" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="P40" s="10" t="n">
         <v/>
       </c>
       <c r="Q40" s="10" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>4986</v>
+        <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.2164753672098426</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="G41" s="10" t="n">
         <v/>
@@ -2988,16 +2988,16 @@
         <v/>
       </c>
       <c r="I41" s="10" t="n">
-        <v>37.9</v>
+        <v>33</v>
       </c>
       <c r="J41" s="10" t="n">
         <v/>
       </c>
       <c r="K41" s="10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M41" s="10" t="n">
         <v/>
@@ -3006,40 +3006,40 @@
         <v/>
       </c>
       <c r="O41" s="10" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P41" s="10" t="n">
         <v/>
       </c>
       <c r="Q41" s="10" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G42" s="10" t="n">
         <v/>
@@ -3048,16 +3048,16 @@
         <v/>
       </c>
       <c r="I42" s="10" t="n">
-        <v>32</v>
+        <v>36.6</v>
       </c>
       <c r="J42" s="10" t="n">
         <v/>
       </c>
       <c r="K42" s="10" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M42" s="10" t="n">
         <v/>
@@ -3066,58 +3066,58 @@
         <v/>
       </c>
       <c r="O42" s="10" t="n">
-        <v/>
+        <v>4.3</v>
       </c>
       <c r="P42" s="10" t="n">
         <v/>
       </c>
       <c r="Q42" s="10" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="R42" s="10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C43" s="9" t="n">
-        <v>1500</v>
+        <v>2080</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J43" s="10" t="n">
         <v/>
       </c>
       <c r="K43" s="10" t="n">
-        <v>39.5</v>
+        <v>40.2</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="M43" s="10" t="n">
         <v/>
@@ -3126,40 +3126,40 @@
         <v/>
       </c>
       <c r="O43" s="10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="P43" s="10" t="n">
         <v/>
       </c>
       <c r="Q43" s="10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>2080</v>
+        <v>4986</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.07492677141629081</v>
+        <v>0.2164753672098426</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="G44" s="10" t="n">
         <v/>
@@ -3168,16 +3168,16 @@
         <v/>
       </c>
       <c r="I44" s="10" t="n">
-        <v>33.1</v>
+        <v>37.9</v>
       </c>
       <c r="J44" s="10" t="n">
         <v/>
       </c>
       <c r="K44" s="10" t="n">
-        <v>39.8</v>
+        <v>45</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="M44" s="10" t="n">
         <v/>
@@ -3186,16 +3186,16 @@
         <v/>
       </c>
       <c r="O44" s="10" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="P44" s="10" t="n">
-        <v>6.5</v>
+        <v/>
       </c>
       <c r="Q44" s="10" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="R44" s="10" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -3206,38 +3206,38 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>5418</v>
+        <v>5020</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.1005194692155711</v>
+        <v>0.2172121960982981</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="H45" s="10" t="n">
         <v/>
       </c>
       <c r="I45" s="10" t="n">
-        <v>35</v>
+        <v>38.9</v>
       </c>
       <c r="J45" s="10" t="n">
         <v/>
       </c>
       <c r="K45" s="10" t="n">
-        <v>48.8</v>
+        <v>45.2</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="M45" s="10" t="n">
         <v/>
@@ -3246,100 +3246,100 @@
         <v/>
       </c>
       <c r="O45" s="10" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="P45" s="10" t="n">
         <v/>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.1089275848773588</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="J46" s="10" t="n">
         <v/>
       </c>
       <c r="K46" s="10" t="n">
-        <v>35.4</v>
+        <v>38</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M46" s="10" t="n">
         <v/>
       </c>
       <c r="N46" s="10" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="O46" s="10" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="P46" s="10" t="n">
-        <v>9.1</v>
+        <v/>
       </c>
       <c r="Q46" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G47" s="10" t="n">
         <v/>
@@ -3348,16 +3348,16 @@
         <v/>
       </c>
       <c r="I47" s="10" t="n">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="J47" s="10" t="n">
         <v/>
       </c>
       <c r="K47" s="10" t="n">
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="M47" s="10" t="n">
         <v/>
@@ -3366,75 +3366,495 @@
         <v/>
       </c>
       <c r="O47" s="10" t="n">
-        <v>5.4</v>
+        <v/>
       </c>
       <c r="P47" s="10" t="n">
         <v/>
       </c>
       <c r="Q47" s="10" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="R47" s="10" t="n">
-        <v>12.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>0.07142046070149105</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O48" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R48" s="10" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>0.07492677141629081</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N49" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O49" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P49" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q49" s="10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R49" s="10" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Paraná Pesquisas</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>0.07492677141629081</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="L50" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M50" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O50" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P50" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="R50" s="10" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>5418</v>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>0.1005194692155711</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I51" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="L51" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O51" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P51" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R51" s="10" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I52" s="10" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K52" s="10" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L52" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M52" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N52" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O52" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P52" s="10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Q52" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" s="10" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I53" s="10" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K53" s="10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L53" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N53" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O53" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P53" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R53" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>0.05076577477226472</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K54" s="10" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O54" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P54" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R54" s="10" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>Quaest</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>2026-01-11</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C55" s="9" t="n">
         <v>2004</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D55" s="10" t="n">
         <v>0.04965586437851098</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E55" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="I48" s="10" t="n">
+      <c r="F55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="I55" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="J48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="K48" s="10" t="n">
+      <c r="J55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="K55" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L55" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="M48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="10" t="n">
+      <c r="M55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="N55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="O55" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P48" s="10" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="10" t="n">
+      <c r="P55" s="10" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R55" s="10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3452,7 +3872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3491,7 +3911,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -3520,7 +3940,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.25</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="9">
@@ -3530,7 +3950,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45.32</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="10">
@@ -3540,7 +3960,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="11">
@@ -3550,7 +3970,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="14">
@@ -4085,180 +4505,270 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2004</v>
+        <v>5020</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.2172121960982981</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>38</v>
+        <v>47.5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>43</v>
+        <v>46.1</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.1089275848773588</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>41.1</v>
+        <v>42</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>45.8</v>
+        <v>40</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>2080</v>
+        <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.07492677141629081</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>42.2</v>
+        <v>38</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C35" s="9" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.07142046070149105</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>48.1</v>
+        <v>41.1</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>41.9</v>
+        <v>45.8</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>2000</v>
+        <v>2080</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.07492677141629081</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>36</v>
+        <v>42.2</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>46.2</v>
+        <v>44.8</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>0.05076577477226472</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
           <t>Quaest</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>2026-01-11</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C40" s="9" t="n">
         <v>2004</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D40" s="10" t="n">
         <v>0.04965586437851098</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E40" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F40" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G40" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H40" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4276,7 +4786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4315,7 +4825,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -4344,7 +4854,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45.72</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="9">
@@ -4354,7 +4864,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.41</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="10">
@@ -4364,7 +4874,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12.44</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="11">
@@ -4374,7 +4884,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="14">
@@ -4794,115 +5304,175 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.1089275848773588</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.09704344573736197</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.07142046070149105</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>42.8</v>
+        <v>45</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>40.5</v>
+        <v>34.5</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.05967760024440102</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
           <t>Quaest</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>2026-01-11</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C33" s="9" t="n">
         <v>2004</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D33" s="10" t="n">
         <v>0.04965586437851098</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E33" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F33" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G33" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="H33" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5124,24 +5694,26 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>42.07</v>
+        <v>41.41</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>32.83</v>
+        <v>33.08</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4.09</v>
+        <v>3.91</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
+        <v>2.18</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5150,24 +5722,26 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41.56</v>
+        <v>40.89</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>32.89</v>
+        <v>33.09</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
+        <v>1.96</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>1.14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5176,24 +5750,26 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>41.2</v>
+        <v>40.71</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32.91</v>
+        <v>33.08</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.19</v>
+        <v>3.88</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H10" s="5" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>1.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -5202,24 +5778,26 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>41.15</v>
+        <v>40.22</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.47</v>
+        <v>33.41</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H11" s="5" t="n"/>
+        <v>1.93</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -5228,24 +5806,26 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>39.39</v>
+        <v>39.11</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.63</v>
+        <v>32.81</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>4.36</v>
+        <v>3.56</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H12" s="5" t="n"/>
+        <v>1.61</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>1.04</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -5254,24 +5834,26 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.93</v>
+        <v>41.97</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>35.8</v>
+        <v>35.91</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>4.44</v>
+        <v>4.28</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>4.38</v>
+        <v>3.77</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H13" s="5" t="n"/>
+        <v>2.63</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -5280,24 +5862,26 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>41.42</v>
+        <v>41.67</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>35.36</v>
+        <v>35.65</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.36</v>
+        <v>3.82</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H14" s="5" t="n"/>
+        <v>2.81</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -5306,24 +5890,26 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>40.97</v>
+        <v>41.33</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>34.96</v>
+        <v>35.33</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H15" s="5" t="n"/>
+        <v>2.47</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -5332,24 +5918,26 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>40.97</v>
+        <v>41.62</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34.96</v>
+        <v>35.54</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>4.45</v>
+        <v>4.27</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H16" s="5" t="n"/>
+        <v>2.51</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -5384,24 +5972,26 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>42.5</v>
+        <v>42.12</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>37.23</v>
+        <v>36.76</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H18" s="5" t="n"/>
+        <v>2.15</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -5410,25 +6000,25 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>41.36</v>
+        <v>41.28</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>37.48</v>
+        <v>37.13</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>4.69</v>
+        <v>4.46</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20">
@@ -5438,25 +6028,25 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>40.55</v>
+        <v>40.58</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>36.45</v>
+        <v>36.29</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>4.93</v>
+        <v>4.71</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="21">
@@ -5466,25 +6056,25 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>39.35</v>
+        <v>39.56</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>35.63</v>
+        <v>35.56</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>5.21</v>
+        <v>4.9</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="22">
@@ -5550,25 +6140,25 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>41.11</v>
+        <v>40.45</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>36.04</v>
+        <v>35.82</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>
@@ -5670,13 +6260,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>43.91</v>
+        <v>43.12</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>41.13</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9">
@@ -5686,13 +6276,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>44.2</v>
+        <v>43.55</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>41.47</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="10">
@@ -5702,13 +6292,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>44.57</v>
+        <v>43.99</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>41.38</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="11">
@@ -5718,13 +6308,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>43.89</v>
+        <v>42.62</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>41.76</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="12">
@@ -5734,13 +6324,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>44.38</v>
+        <v>43.02</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>40.2</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="13">
@@ -5750,13 +6340,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.91</v>
+        <v>44.58</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>43.56</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="14">
@@ -5766,13 +6356,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>45.1</v>
+        <v>44.74</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>43.69</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="15">
@@ -5782,13 +6372,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.9</v>
+        <v>44.67</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.05</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="16">
@@ -5798,13 +6388,13 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.9</v>
+        <v>45.14</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>44.05</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="17">
@@ -6034,13 +6624,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>44.25</v>
+        <v>43.39</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>36.19</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="9">
@@ -6050,13 +6640,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>44.25</v>
+        <v>43.39</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>36.19</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="10">
@@ -6066,13 +6656,13 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>44.55</v>
+        <v>43.87</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>35.52</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="11">
@@ -6082,13 +6672,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>43.57</v>
+        <v>42.87</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>35.01</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="12">
@@ -6098,13 +6688,13 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43.85</v>
+        <v>43.12</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>33.06</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="13">
@@ -6114,13 +6704,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43.85</v>
+        <v>43.12</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>33.06</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="14">
@@ -6130,13 +6720,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>43</v>
+        <v>42.47</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>32</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="15">
@@ -6146,13 +6736,13 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.99</v>
+        <v>44.28</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.88</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="16">
@@ -6314,7 +6904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6661,22 +7251,22 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -6690,7 +7280,7 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
@@ -6698,51 +7288,47 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>BR-03598/2026</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
+          <t>BR-00290/2026</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n"/>
       <c r="N4" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U4" s="9" t="n"/>
+      <c r="U4" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X4" s="9" t="n"/>
       <c r="Y4" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6753,29 +7339,29 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>1</v>
@@ -6790,53 +7376,51 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>BR-05356/2026</t>
+          <t>BR-03598/2026</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M5" s="10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T5" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U5" s="9" t="n"/>
       <c r="V5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X5" s="9" t="n"/>
       <c r="Y5" s="10" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="10" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -6847,36 +7431,36 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
@@ -6884,45 +7468,53 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
+          <t>BR-05356/2026</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M6" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P6" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N6" s="10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P6" s="9" t="n"/>
       <c r="Q6" s="10" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R6" s="9" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" s="10" t="n">
-        <v>46.6</v>
+        <v>40</v>
       </c>
       <c r="T6" s="10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" s="10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X6" s="9" t="n"/>
       <c r="Y6" s="10" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" s="10" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7">
@@ -6933,36 +7525,36 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2004</v>
+        <v>5008</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
@@ -6970,49 +7562,45 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-07992/2026</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M7" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="P7" s="9" t="n"/>
       <c r="Q7" s="10" t="n">
-        <v>32</v>
+        <v>39.7</v>
       </c>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="10" t="n">
-        <v>37</v>
+        <v>46.6</v>
       </c>
       <c r="T7" s="10" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="U7" s="9" t="n"/>
-      <c r="V7" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="V7" s="9" t="n"/>
       <c r="W7" s="10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X7" s="9" t="n"/>
       <c r="Y7" s="10" t="n">
-        <v>11</v>
+        <v>0.5</v>
       </c>
       <c r="Z7" s="10" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -7023,36 +7611,36 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
@@ -7060,47 +7648,49 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>BR-08282/2026</t>
+          <t>BR-09285/2026</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M8" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>37.3</v>
+        <v>32</v>
       </c>
       <c r="R8" s="9" t="n"/>
       <c r="S8" s="10" t="n">
-        <v>39.8</v>
+        <v>37</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
+      <c r="V8" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="W8" s="10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X8" s="9" t="n"/>
       <c r="Y8" s="10" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="Z8" s="10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7111,12 +7701,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -7126,14 +7716,14 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>1</v>
@@ -7148,45 +7738,47 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>BR-03770/2026</t>
+          <t>BR-08282/2026</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M9" s="10" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" s="9" t="n"/>
+        <v>4.8</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>1.3</v>
+      </c>
       <c r="P9" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>35</v>
+        <v>37.3</v>
       </c>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="10" t="n">
-        <v>39</v>
+        <v>39.8</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="U9" s="9" t="n"/>
       <c r="V9" s="9" t="n"/>
       <c r="W9" s="10" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="X9" s="9" t="n"/>
       <c r="Y9" s="10" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="Z9" s="10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -7197,29 +7789,29 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>1</v>
@@ -7234,43 +7826,45 @@
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-03770/2026</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M10" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
+      <c r="P10" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" s="10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R10" s="9" t="n"/>
       <c r="S10" s="10" t="n">
-        <v>40.4</v>
+        <v>39</v>
       </c>
       <c r="T10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U10" s="9" t="n"/>
       <c r="V10" s="9" t="n"/>
       <c r="W10" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X10" s="9" t="n"/>
       <c r="Y10" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z10" s="10" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -7281,36 +7875,36 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2080</v>
+        <v>1500</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
@@ -7318,31 +7912,31 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>BR-00873/2026</t>
+          <t>BR-00605/2026</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M11" s="10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="10" t="n">
-        <v>37.8</v>
+        <v>37</v>
       </c>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="10" t="n">
-        <v>41.3</v>
+        <v>40.4</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="U11" s="9" t="n"/>
       <c r="V11" s="9" t="n"/>
@@ -7351,10 +7945,10 @@
       </c>
       <c r="X11" s="9" t="n"/>
       <c r="Y11" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="10" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
@@ -7365,36 +7959,36 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>5028</v>
+        <v>2080</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
@@ -7402,43 +7996,43 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-00873/2026</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
       <c r="Q12" s="10" t="n">
-        <v>40.1</v>
+        <v>37.8</v>
       </c>
       <c r="R12" s="9" t="n"/>
       <c r="S12" s="10" t="n">
-        <v>45.9</v>
+        <v>41.3</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="U12" s="9" t="n"/>
       <c r="V12" s="9" t="n"/>
       <c r="W12" s="10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X12" s="9" t="n"/>
       <c r="Y12" s="10" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="Z12" s="10" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -7449,36 +8043,36 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1500</v>
+        <v>2080</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
@@ -7486,43 +8080,43 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>BR-00386/2026</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
-        </is>
-      </c>
+          <t>BR-00873/2026</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n"/>
       <c r="M13" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
+      <c r="P13" s="10" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Q13" s="10" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="10" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="U13" s="9" t="n"/>
       <c r="V13" s="9" t="n"/>
       <c r="W13" s="10" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="X13" s="9" t="n"/>
       <c r="Y13" s="10" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -7533,36 +8127,36 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2004</v>
+        <v>5028</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
@@ -7570,43 +8164,43 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-04227/2026</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
       <c r="Q14" s="10" t="n">
-        <v>32</v>
+        <v>40.1</v>
       </c>
       <c r="R14" s="9" t="n"/>
       <c r="S14" s="10" t="n">
-        <v>39</v>
+        <v>45.9</v>
       </c>
       <c r="T14" s="10" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="U14" s="9" t="n"/>
       <c r="V14" s="9" t="n"/>
       <c r="W14" s="10" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="X14" s="9" t="n"/>
       <c r="Y14" s="10" t="n">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" s="10" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -7617,36 +8211,36 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
@@ -7654,31 +8248,31 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>BR-03715/2026</t>
+          <t>BR-00386/2026</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="10" t="n">
-        <v>39</v>
+        <v>40.3</v>
       </c>
       <c r="T15" s="10" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="U15" s="9" t="n"/>
       <c r="V15" s="9" t="n"/>
@@ -7687,10 +8281,10 @@
       </c>
       <c r="X15" s="9" t="n"/>
       <c r="Y15" s="10" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" s="10" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="16">
@@ -7701,29 +8295,29 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2080</v>
+        <v>2004</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>1</v>
@@ -7738,43 +8332,43 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>BR-07974/2026</t>
+          <t>BR-05809/2026</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M16" s="10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
       <c r="Q16" s="10" t="n">
-        <v>36.6</v>
+        <v>32</v>
       </c>
       <c r="R16" s="9" t="n"/>
       <c r="S16" s="10" t="n">
-        <v>40.5</v>
+        <v>39</v>
       </c>
       <c r="T16" s="10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n"/>
       <c r="V16" s="9" t="n"/>
       <c r="W16" s="10" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="X16" s="9" t="n"/>
       <c r="Y16" s="10" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -7785,36 +8379,36 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>4986</v>
+        <v>2004</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
@@ -7822,43 +8416,43 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>BR-07600/2026</t>
+          <t>BR-03715/2026</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M17" s="10" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="10" t="n">
-        <v>37.9</v>
+        <v>33</v>
       </c>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="T17" s="10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U17" s="9" t="n"/>
       <c r="V17" s="9" t="n"/>
       <c r="W17" s="10" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="X17" s="9" t="n"/>
       <c r="Y17" s="10" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="Z17" s="10" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -7869,36 +8463,36 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
@@ -7906,41 +8500,43 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-07974/2026</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
         </is>
       </c>
       <c r="M18" s="10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
       <c r="Q18" s="10" t="n">
-        <v>32</v>
+        <v>36.6</v>
       </c>
       <c r="R18" s="9" t="n"/>
       <c r="S18" s="10" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="T18" s="10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U18" s="9" t="n"/>
       <c r="V18" s="9" t="n"/>
-      <c r="W18" s="9" t="n"/>
+      <c r="W18" s="10" t="n">
+        <v>4.3</v>
+      </c>
       <c r="X18" s="9" t="n"/>
       <c r="Y18" s="10" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="19">
@@ -7951,36 +8547,36 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1500</v>
+        <v>2080</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
@@ -7988,43 +8584,43 @@
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>BR-08425/2026</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
-        </is>
-      </c>
+          <t>BR-07974/2026</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n"/>
       <c r="M19" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q19" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="10" t="n">
-        <v>39.5</v>
+        <v>40.2</v>
       </c>
       <c r="T19" s="10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="U19" s="9" t="n"/>
       <c r="V19" s="9" t="n"/>
       <c r="W19" s="10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="X19" s="9" t="n"/>
       <c r="Y19" s="10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z19" s="10" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="20">
@@ -8035,36 +8631,36 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>2080</v>
+        <v>4986</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
@@ -8072,45 +8668,43 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>BR-08254/2026</t>
+          <t>BR-07600/2026</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M20" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
       <c r="Q20" s="10" t="n">
-        <v>33.1</v>
+        <v>37.9</v>
       </c>
       <c r="R20" s="9" t="n"/>
       <c r="S20" s="10" t="n">
-        <v>39.8</v>
+        <v>45</v>
       </c>
       <c r="T20" s="10" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="U20" s="9" t="n"/>
       <c r="V20" s="9" t="n"/>
       <c r="W20" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X20" s="10" t="n">
-        <v>6.5</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="X20" s="9" t="n"/>
       <c r="Y20" s="10" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="Z20" s="10" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -8131,16 +8725,16 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>5418</v>
+        <v>5020</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>1</v>
@@ -8158,43 +8752,41 @@
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>BR-02804/2026</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-atlasintel-presidente-janeiro-2026/</t>
-        </is>
-      </c>
+          <t>BR-05112/2026</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="n"/>
       <c r="M21" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O21" s="9" t="n"/>
+        <v>4.1</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0.8</v>
+      </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="10" t="n">
-        <v>35</v>
+        <v>38.9</v>
       </c>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="10" t="n">
-        <v>48.8</v>
+        <v>45.2</v>
       </c>
       <c r="T21" s="10" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="U21" s="9" t="n"/>
       <c r="V21" s="9" t="n"/>
       <c r="W21" s="10" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="X21" s="9" t="n"/>
       <c r="Y21" s="10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -8205,26 +8797,26 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Futura</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>2</v>
@@ -8240,43 +8832,47 @@
       <c r="J22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
-        </is>
-      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>BR-08165/2026</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="n"/>
       <c r="M22" s="10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q22" s="10" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="R22" s="9" t="n"/>
       <c r="S22" s="10" t="n">
-        <v>35.4</v>
+        <v>38</v>
       </c>
       <c r="T22" s="10" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="U22" s="9" t="n"/>
-      <c r="V22" s="9" t="n"/>
+      <c r="V22" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="W22" s="10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X22" s="10" t="n">
-        <v>9.1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="X22" s="9" t="n"/>
       <c r="Y22" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z22" s="10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -8287,36 +8883,36 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
@@ -8324,43 +8920,41 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>BR-06731/2026</t>
+          <t>BR-00249/2026</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M23" s="10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="10" t="n">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="10" t="n">
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="T23" s="10" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="U23" s="9" t="n"/>
       <c r="V23" s="9" t="n"/>
-      <c r="W23" s="10" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="W23" s="9" t="n"/>
       <c r="X23" s="9" t="n"/>
       <c r="Y23" s="10" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="Z23" s="10" t="n">
-        <v>12.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -8371,36 +8965,36 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2004</v>
+        <v>1500</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
@@ -8408,81 +9002,83 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-08425/2026</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="9" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>5.1</v>
+      </c>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
       <c r="Q24" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R24" s="9" t="n"/>
       <c r="S24" s="10" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="T24" s="10" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="U24" s="9" t="n"/>
       <c r="V24" s="9" t="n"/>
       <c r="W24" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="10" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="Z24" s="10" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>5032</v>
+        <v>2080</v>
       </c>
       <c r="G25" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
@@ -8490,69 +9086,81 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>BR-06939/2026</t>
+          <t>BR-08254/2026</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="10" t="n">
-        <v>41.8</v>
+        <v>33.1</v>
       </c>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="T25" s="9" t="n"/>
+        <v>39.8</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="U25" s="9" t="n"/>
       <c r="V25" s="9" t="n"/>
-      <c r="W25" s="9" t="n"/>
-      <c r="X25" s="9" t="n"/>
+      <c r="W25" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>6.5</v>
+      </c>
       <c r="Y25" s="10" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z25" s="9" t="n"/>
+        <v>6.8</v>
+      </c>
+      <c r="Z25" s="10" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -8564,75 +9172,83 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>BR-00290/2026</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="9" t="n"/>
-      <c r="P26" s="9" t="n"/>
+          <t>BR-08254/2026</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q26" s="10" t="n">
-        <v>45</v>
+        <v>33.1</v>
       </c>
       <c r="R26" s="9" t="n"/>
       <c r="S26" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="T26" s="9" t="n"/>
+        <v>39.8</v>
+      </c>
+      <c r="T26" s="10" t="n">
+        <v>1.5</v>
+      </c>
       <c r="U26" s="9" t="n"/>
       <c r="V26" s="9" t="n"/>
-      <c r="W26" s="9" t="n"/>
+      <c r="W26" s="10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="X26" s="9" t="n"/>
       <c r="Y26" s="10" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="Z26" s="10" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2004</v>
+        <v>5418</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
@@ -8640,71 +9256,79 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>BR-03598/2026</t>
+          <t>BR-02804/2026</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-atlasintel-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>4.3</v>
+      </c>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="10" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="T27" s="9" t="n"/>
+        <v>48.8</v>
+      </c>
+      <c r="T27" s="10" t="n">
+        <v>3.4</v>
+      </c>
       <c r="U27" s="9" t="n"/>
       <c r="V27" s="9" t="n"/>
-      <c r="W27" s="9" t="n"/>
+      <c r="W27" s="10" t="n">
+        <v>2.8</v>
+      </c>
       <c r="X27" s="9" t="n"/>
       <c r="Y27" s="10" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" s="10" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>100% Cidades/Futura</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -8714,73 +9338,79 @@
       <c r="J28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>BR-05356/2026</t>
-        </is>
-      </c>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
-        </is>
-      </c>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>3.7</v>
+      </c>
       <c r="O28" s="9" t="n"/>
       <c r="P28" s="9" t="n"/>
       <c r="Q28" s="10" t="n">
-        <v>45.3</v>
+        <v>34.3</v>
       </c>
       <c r="R28" s="9" t="n"/>
       <c r="S28" s="10" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="T28" s="9" t="n"/>
+        <v>35.4</v>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>1.7</v>
+      </c>
       <c r="U28" s="9" t="n"/>
       <c r="V28" s="9" t="n"/>
-      <c r="W28" s="9" t="n"/>
-      <c r="X28" s="9" t="n"/>
+      <c r="W28" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X28" s="10" t="n">
+        <v>9.1</v>
+      </c>
       <c r="Y28" s="10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>100% Cidades/Futura</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>5008</v>
+        <v>2000</v>
       </c>
       <c r="G29" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H29" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -8792,69 +9422,79 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="9" t="n"/>
-      <c r="P29" s="9" t="n"/>
+          <t>BR-06845/2026</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q29" s="10" t="n">
-        <v>47.8</v>
+        <v>34.2</v>
       </c>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="10" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="T29" s="9" t="n"/>
+        <v>38.5</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
+      <c r="W29" s="10" t="n">
+        <v>3.1</v>
+      </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Z29" s="9" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="Z29" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -8866,71 +9506,79 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-06731/2026</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="O30" s="9" t="n"/>
       <c r="P30" s="9" t="n"/>
       <c r="Q30" s="10" t="n">
-        <v>42</v>
+        <v>27.6</v>
       </c>
       <c r="R30" s="9" t="n"/>
       <c r="S30" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="T30" s="9" t="n"/>
+        <v>39.6</v>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="U30" s="9" t="n"/>
       <c r="V30" s="9" t="n"/>
-      <c r="W30" s="9" t="n"/>
+      <c r="W30" s="10" t="n">
+        <v>5.4</v>
+      </c>
       <c r="X30" s="9" t="n"/>
       <c r="Y30" s="10" t="n">
-        <v>16</v>
+        <v>5.6</v>
       </c>
       <c r="Z30" s="10" t="n">
-        <v>2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Flávio</t>
+          <t>1º Turno</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="F31" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -8942,35 +9590,41 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>BR-08282/2026</t>
+          <t>BR-00835/2026</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="n"/>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="10" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="T31" s="9" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="T31" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
+      <c r="W31" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="10" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="10" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -8981,36 +9635,36 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>2004</v>
+        <v>5032</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
@@ -9018,12 +9672,12 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>BR-03770/2026</t>
+          <t>BR-06939/2026</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M32" s="9" t="n"/>
@@ -9031,11 +9685,11 @@
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="9" t="n"/>
       <c r="Q32" s="10" t="n">
-        <v>46</v>
+        <v>41.8</v>
       </c>
       <c r="R32" s="9" t="n"/>
       <c r="S32" s="10" t="n">
-        <v>45</v>
+        <v>48.9</v>
       </c>
       <c r="T32" s="9" t="n"/>
       <c r="U32" s="9" t="n"/>
@@ -9043,11 +9697,9 @@
       <c r="W32" s="9" t="n"/>
       <c r="X32" s="9" t="n"/>
       <c r="Y32" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z32" s="10" t="n">
-        <v>1</v>
-      </c>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -9057,29 +9709,29 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>2</v>
@@ -9094,12 +9746,12 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-00290/2026</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M33" s="9" t="n"/>
@@ -9107,11 +9759,11 @@
       <c r="O33" s="9" t="n"/>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="10" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="10" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n"/>
@@ -9119,10 +9771,10 @@
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="10" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="Z33" s="10" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -9133,29 +9785,29 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2080</v>
+        <v>2004</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H34" s="9" t="n">
         <v>2</v>
@@ -9170,12 +9822,12 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>BR-00873/2026</t>
+          <t>BR-03598/2026</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M34" s="9" t="n"/>
@@ -9183,11 +9835,11 @@
       <c r="O34" s="9" t="n"/>
       <c r="P34" s="9" t="n"/>
       <c r="Q34" s="10" t="n">
-        <v>45.2</v>
+        <v>41</v>
       </c>
       <c r="R34" s="9" t="n"/>
       <c r="S34" s="10" t="n">
-        <v>44.1</v>
+        <v>42</v>
       </c>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="9" t="n"/>
@@ -9195,10 +9847,10 @@
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="9" t="n"/>
       <c r="Y34" s="10" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="Z34" s="10" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -9209,36 +9861,36 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F35" s="9" t="n">
-        <v>5028</v>
+        <v>1500</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
@@ -9246,12 +9898,12 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-05356/2026</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M35" s="9" t="n"/>
@@ -9259,11 +9911,11 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="10" t="n">
-        <v>47.6</v>
+        <v>45.3</v>
       </c>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="10" t="n">
-        <v>46.6</v>
+        <v>44.7</v>
       </c>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
@@ -9271,9 +9923,11 @@
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
       <c r="Y35" s="10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z35" s="9" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z35" s="10" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -9283,36 +9937,36 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>1500</v>
+        <v>5008</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H36" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
@@ -9320,12 +9974,12 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>BR-00386/2026</t>
+          <t>BR-07992/2026</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M36" s="9" t="n"/>
@@ -9333,11 +9987,11 @@
       <c r="O36" s="9" t="n"/>
       <c r="P36" s="9" t="n"/>
       <c r="Q36" s="10" t="n">
-        <v>45.3</v>
+        <v>47.8</v>
       </c>
       <c r="R36" s="9" t="n"/>
       <c r="S36" s="10" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="9" t="n"/>
@@ -9345,11 +9999,9 @@
       <c r="W36" s="9" t="n"/>
       <c r="X36" s="9" t="n"/>
       <c r="Y36" s="10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z36" s="10" t="n">
-        <v>3.2</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="Z36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -9369,12 +10021,12 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F37" s="9" t="n">
@@ -9396,12 +10048,12 @@
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-09285/2026</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M37" s="9" t="n"/>
@@ -9409,11 +10061,11 @@
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
@@ -9435,29 +10087,29 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F38" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>2</v>
@@ -9472,12 +10124,12 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>BR-03715/2026</t>
+          <t>BR-08282/2026</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M38" s="9" t="n"/>
@@ -9485,11 +10137,11 @@
       <c r="O38" s="9" t="n"/>
       <c r="P38" s="9" t="n"/>
       <c r="Q38" s="10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="R38" s="9" t="n"/>
       <c r="S38" s="10" t="n">
-        <v>46</v>
+        <v>42.6</v>
       </c>
       <c r="T38" s="9" t="n"/>
       <c r="U38" s="9" t="n"/>
@@ -9497,10 +10149,10 @@
       <c r="W38" s="9" t="n"/>
       <c r="X38" s="9" t="n"/>
       <c r="Y38" s="10" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" s="10" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="39">
@@ -9511,36 +10163,36 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="F39" s="9" t="n">
-        <v>2080</v>
+        <v>2004</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H39" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
@@ -9548,12 +10200,12 @@
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>BR-07974/2026</t>
+          <t>BR-03770/2026</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M39" s="9" t="n"/>
@@ -9561,11 +10213,11 @@
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="10" t="n">
-        <v>44.4</v>
+        <v>46</v>
       </c>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="10" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
@@ -9573,10 +10225,10 @@
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
       <c r="Y39" s="10" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="Z39" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -9587,36 +10239,36 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F40" s="9" t="n">
-        <v>4986</v>
+        <v>1500</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
@@ -9624,12 +10276,12 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>BR-07600/2026</t>
+          <t>BR-00605/2026</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M40" s="9" t="n"/>
@@ -9637,11 +10289,11 @@
       <c r="O40" s="9" t="n"/>
       <c r="P40" s="9" t="n"/>
       <c r="Q40" s="10" t="n">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
       <c r="R40" s="9" t="n"/>
       <c r="S40" s="10" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="T40" s="9" t="n"/>
       <c r="U40" s="9" t="n"/>
@@ -9649,9 +10301,11 @@
       <c r="W40" s="9" t="n"/>
       <c r="X40" s="9" t="n"/>
       <c r="Y40" s="10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z40" s="9" t="n"/>
+        <v>6.6</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -9661,36 +10315,36 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F41" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H41" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
@@ -9698,12 +10352,12 @@
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-00873/2026</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M41" s="9" t="n"/>
@@ -9711,11 +10365,11 @@
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="10" t="n">
-        <v>38</v>
+        <v>45.2</v>
       </c>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="10" t="n">
-        <v>43</v>
+        <v>44.1</v>
       </c>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
@@ -9723,10 +10377,10 @@
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
       <c r="Y41" s="10" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="Z41" s="10" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="42">
@@ -9737,36 +10391,36 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F42" s="9" t="n">
-        <v>1500</v>
+        <v>5028</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
@@ -9774,12 +10428,12 @@
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>BR-08425/2026</t>
+          <t>BR-04227/2026</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M42" s="9" t="n"/>
@@ -9787,11 +10441,11 @@
       <c r="O42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
       <c r="Q42" s="10" t="n">
-        <v>41.1</v>
+        <v>47.6</v>
       </c>
       <c r="R42" s="9" t="n"/>
       <c r="S42" s="10" t="n">
-        <v>45.8</v>
+        <v>46.6</v>
       </c>
       <c r="T42" s="9" t="n"/>
       <c r="U42" s="9" t="n"/>
@@ -9799,11 +10453,9 @@
       <c r="W42" s="9" t="n"/>
       <c r="X42" s="9" t="n"/>
       <c r="Y42" s="10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z42" s="10" t="n">
-        <v>5.7</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="Z42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -9813,29 +10465,29 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F43" s="9" t="n">
-        <v>2080</v>
+        <v>1500</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>2</v>
@@ -9850,12 +10502,12 @@
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>BR-08254/2026</t>
+          <t>BR-00386/2026</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M43" s="9" t="n"/>
@@ -9863,11 +10515,11 @@
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="10" t="n">
-        <v>42.2</v>
+        <v>45.3</v>
       </c>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="10" t="n">
-        <v>44.8</v>
+        <v>47.4</v>
       </c>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
@@ -9875,10 +10527,10 @@
       <c r="W43" s="9" t="n"/>
       <c r="X43" s="9" t="n"/>
       <c r="Y43" s="10" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="Z43" s="10" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="44">
@@ -9889,26 +10541,26 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Futura</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>2</v>
@@ -9924,10 +10576,14 @@
       <c r="J44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="9" t="n"/>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M44" s="9" t="n"/>
@@ -9935,11 +10591,11 @@
       <c r="O44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
       <c r="Q44" s="10" t="n">
-        <v>48.1</v>
+        <v>41</v>
       </c>
       <c r="R44" s="9" t="n"/>
       <c r="S44" s="10" t="n">
-        <v>41.9</v>
+        <v>41</v>
       </c>
       <c r="T44" s="9" t="n"/>
       <c r="U44" s="9" t="n"/>
@@ -9947,10 +10603,10 @@
       <c r="W44" s="9" t="n"/>
       <c r="X44" s="9" t="n"/>
       <c r="Y44" s="10" t="n">
-        <v>8.9</v>
+        <v>16</v>
       </c>
       <c r="Z44" s="10" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -9961,36 +10617,36 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F45" s="9" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
@@ -9998,12 +10654,12 @@
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>BR-06731/2026</t>
+          <t>BR-03715/2026</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
       <c r="M45" s="9" t="n"/>
@@ -10011,11 +10667,11 @@
       <c r="O45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="10" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
@@ -10023,10 +10679,10 @@
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n"/>
       <c r="Y45" s="10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z45" s="10" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -10037,36 +10693,36 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F46" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H46" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
@@ -10074,12 +10730,12 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-07974/2026</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
         </is>
       </c>
       <c r="M46" s="9" t="n"/>
@@ -10087,11 +10743,11 @@
       <c r="O46" s="9" t="n"/>
       <c r="P46" s="9" t="n"/>
       <c r="Q46" s="10" t="n">
-        <v>38</v>
+        <v>44.4</v>
       </c>
       <c r="R46" s="9" t="n"/>
       <c r="S46" s="10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="T46" s="9" t="n"/>
       <c r="U46" s="9" t="n"/>
@@ -10099,16 +10755,16 @@
       <c r="W46" s="9" t="n"/>
       <c r="X46" s="9" t="n"/>
       <c r="Y46" s="10" t="n">
-        <v>13</v>
+        <v>6.9</v>
       </c>
       <c r="Z46" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -10123,16 +10779,16 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F47" s="9" t="n">
-        <v>5032</v>
+        <v>4986</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>1</v>
@@ -10150,73 +10806,73 @@
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>BR-06939/2026</t>
+          <t>BR-07600/2026</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
+      <c r="Q47" s="10" t="n">
+        <v>46.3</v>
+      </c>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="10" t="n">
-        <v>47.8</v>
+        <v>46.2</v>
       </c>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
-      <c r="W47" s="10" t="n">
-        <v>37.6</v>
-      </c>
+      <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
       <c r="Y47" s="10" t="n">
-        <v>14.6</v>
+        <v>7.5</v>
       </c>
       <c r="Z47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F48" s="9" t="n">
-        <v>2004</v>
+        <v>5020</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
@@ -10224,41 +10880,35 @@
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>BR-00290/2026</t>
-        </is>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
-        </is>
-      </c>
+          <t>BR-05112/2026</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="n"/>
       <c r="M48" s="9" t="n"/>
       <c r="N48" s="9" t="n"/>
       <c r="O48" s="9" t="n"/>
       <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
+      <c r="Q48" s="10" t="n">
+        <v>47.5</v>
+      </c>
       <c r="R48" s="9" t="n"/>
       <c r="S48" s="10" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="T48" s="9" t="n"/>
       <c r="U48" s="9" t="n"/>
       <c r="V48" s="9" t="n"/>
-      <c r="W48" s="10" t="n">
-        <v>40</v>
-      </c>
+      <c r="W48" s="9" t="n"/>
       <c r="X48" s="9" t="n"/>
       <c r="Y48" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z48" s="10" t="n">
-        <v>2</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="Z48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -10273,12 +10923,12 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="F49" s="9" t="n">
@@ -10300,75 +10950,71 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>BR-03598/2026</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
-        </is>
-      </c>
+          <t>BR-08165/2026</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
+      <c r="Q49" s="10" t="n">
+        <v>42</v>
+      </c>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
-      <c r="W49" s="10" t="n">
-        <v>37</v>
-      </c>
+      <c r="W49" s="9" t="n"/>
       <c r="X49" s="9" t="n"/>
       <c r="Y49" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z49" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F50" s="9" t="n">
-        <v>1500</v>
+        <v>2004</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
@@ -10376,75 +11022,75 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>BR-05356/2026</t>
+          <t>BR-00249/2026</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M50" s="9" t="n"/>
       <c r="N50" s="9" t="n"/>
       <c r="O50" s="9" t="n"/>
       <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
+      <c r="Q50" s="10" t="n">
+        <v>38</v>
+      </c>
       <c r="R50" s="9" t="n"/>
       <c r="S50" s="10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T50" s="9" t="n"/>
       <c r="U50" s="9" t="n"/>
       <c r="V50" s="9" t="n"/>
-      <c r="W50" s="10" t="n">
-        <v>39</v>
-      </c>
+      <c r="W50" s="9" t="n"/>
       <c r="X50" s="9" t="n"/>
       <c r="Y50" s="10" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="Z50" s="10" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Canal Meio</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F51" s="9" t="n">
-        <v>5008</v>
+        <v>1500</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
@@ -10452,66 +11098,68 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>BR-07992/2026</t>
+          <t>BR-08425/2026</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
         </is>
       </c>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
+      <c r="Q51" s="10" t="n">
+        <v>41.1</v>
+      </c>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="10" t="n">
-        <v>47.4</v>
+        <v>45.8</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
-      <c r="W51" s="10" t="n">
-        <v>46.5</v>
-      </c>
+      <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
       <c r="Y51" s="10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Z51" s="9" t="n"/>
+        <v>7.4</v>
+      </c>
+      <c r="Z51" s="10" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>2004</v>
+        <v>2080</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>2</v>
@@ -10526,151 +11174,147 @@
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>BR-09285/2026</t>
+          <t>BR-08254/2026</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
         </is>
       </c>
       <c r="M52" s="9" t="n"/>
       <c r="N52" s="9" t="n"/>
       <c r="O52" s="9" t="n"/>
       <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
+      <c r="Q52" s="10" t="n">
+        <v>42.2</v>
+      </c>
       <c r="R52" s="9" t="n"/>
       <c r="S52" s="10" t="n">
-        <v>43</v>
+        <v>44.8</v>
       </c>
       <c r="T52" s="9" t="n"/>
       <c r="U52" s="9" t="n"/>
       <c r="V52" s="9" t="n"/>
-      <c r="W52" s="10" t="n">
-        <v>36</v>
-      </c>
+      <c r="W52" s="9" t="n"/>
       <c r="X52" s="9" t="n"/>
       <c r="Y52" s="10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z52" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Futura Inteligência</t>
+          <t>100% Cidades/Futura</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Futura Pesquisas</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F53" s="9" t="n">
         <v>2000</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>BR-08282/2026</t>
-        </is>
-      </c>
+      <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
         </is>
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
       <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
+      <c r="Q53" s="10" t="n">
+        <v>48.1</v>
+      </c>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="10" t="n">
-        <v>44.8</v>
+        <v>41.9</v>
       </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
-      <c r="W53" s="10" t="n">
-        <v>38</v>
-      </c>
+      <c r="W53" s="9" t="n"/>
       <c r="X53" s="9" t="n"/>
       <c r="Y53" s="10" t="n">
-        <v>14.9</v>
+        <v>8.9</v>
       </c>
       <c r="Z53" s="10" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>100% Cidades/Futura</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Futura Pesquisas</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
@@ -10678,41 +11322,37 @@
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>BR-03770/2026</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
-        </is>
-      </c>
+          <t>BR-06845/2026</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="n"/>
       <c r="M54" s="9" t="n"/>
       <c r="N54" s="9" t="n"/>
       <c r="O54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
+      <c r="Q54" s="10" t="n">
+        <v>42.5</v>
+      </c>
       <c r="R54" s="9" t="n"/>
       <c r="S54" s="10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="T54" s="9" t="n"/>
       <c r="U54" s="9" t="n"/>
       <c r="V54" s="9" t="n"/>
-      <c r="W54" s="10" t="n">
-        <v>42</v>
-      </c>
+      <c r="W54" s="9" t="n"/>
       <c r="X54" s="9" t="n"/>
       <c r="Y54" s="10" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z54" s="10" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -10727,26 +11367,26 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
@@ -10754,75 +11394,75 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>BR-00605/2026</t>
+          <t>BR-06731/2026</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
         </is>
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
+      <c r="Q55" s="10" t="n">
+        <v>36</v>
+      </c>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="10" t="n">
-        <v>44.7</v>
+        <v>46.2</v>
       </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
-      <c r="W55" s="10" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="W55" s="9" t="n"/>
       <c r="X55" s="9" t="n"/>
       <c r="Y55" s="10" t="n">
-        <v>7.3</v>
+        <v>12</v>
       </c>
       <c r="Z55" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Lula vs Zema</t>
+          <t>Lula vs Flávio</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>Banco Genial</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>5028</v>
+        <v>2004</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
@@ -10830,34 +11470,36 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>BR-04227/2026</t>
+          <t>BR-00835/2026</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
         </is>
       </c>
       <c r="M56" s="9" t="n"/>
       <c r="N56" s="9" t="n"/>
       <c r="O56" s="9" t="n"/>
       <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
+      <c r="Q56" s="10" t="n">
+        <v>38</v>
+      </c>
       <c r="R56" s="9" t="n"/>
       <c r="S56" s="10" t="n">
-        <v>46.6</v>
+        <v>44</v>
       </c>
       <c r="T56" s="9" t="n"/>
       <c r="U56" s="9" t="n"/>
       <c r="V56" s="9" t="n"/>
-      <c r="W56" s="10" t="n">
-        <v>43.7</v>
-      </c>
+      <c r="W56" s="9" t="n"/>
       <c r="X56" s="9" t="n"/>
       <c r="Y56" s="10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z56" s="9" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="Z56" s="10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -10867,36 +11509,36 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Meio/Ideia</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Canal Meio</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1500</v>
+        <v>5032</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
@@ -10904,12 +11546,12 @@
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>BR-00386/2026</t>
+          <t>BR-06939/2026</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M57" s="9" t="n"/>
@@ -10919,21 +11561,19 @@
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="10" t="n">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
       <c r="T57" s="9" t="n"/>
       <c r="U57" s="9" t="n"/>
       <c r="V57" s="9" t="n"/>
       <c r="W57" s="10" t="n">
-        <v>38</v>
+        <v>37.6</v>
       </c>
       <c r="X57" s="9" t="n"/>
       <c r="Y57" s="10" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Z57" s="10" t="n">
-        <v>5.3</v>
-      </c>
+        <v>14.6</v>
+      </c>
+      <c r="Z57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
@@ -10943,22 +11583,22 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Banco Genial</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F58" s="9" t="n">
@@ -10972,7 +11612,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>presencial</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
@@ -10980,12 +11620,12 @@
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>BR-05809/2026</t>
+          <t>BR-00290/2026</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M58" s="9" t="n"/>
@@ -10995,20 +11635,20 @@
       <c r="Q58" s="9" t="n"/>
       <c r="R58" s="9" t="n"/>
       <c r="S58" s="10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T58" s="9" t="n"/>
       <c r="U58" s="9" t="n"/>
       <c r="V58" s="9" t="n"/>
       <c r="W58" s="10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="X58" s="9" t="n"/>
       <c r="Y58" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z58" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -11029,12 +11669,12 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F59" s="9" t="n">
@@ -11048,7 +11688,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
@@ -11056,12 +11696,12 @@
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>BR-00249/2026</t>
+          <t>BR-03598/2026</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M59" s="9" t="n"/>
@@ -11071,17 +11711,17 @@
       <c r="Q59" s="9" t="n"/>
       <c r="R59" s="9" t="n"/>
       <c r="S59" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
       <c r="V59" s="9" t="n"/>
       <c r="W59" s="10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="X59" s="9" t="n"/>
       <c r="Y59" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z59" s="10" t="n">
         <v>4</v>
@@ -11105,12 +11745,12 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F60" s="9" t="n">
@@ -11132,12 +11772,12 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>BR-08425/2026</t>
+          <t>BR-05356/2026</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
       <c r="M60" s="9" t="n"/>
@@ -11147,20 +11787,20 @@
       <c r="Q60" s="9" t="n"/>
       <c r="R60" s="9" t="n"/>
       <c r="S60" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T60" s="9" t="n"/>
       <c r="U60" s="9" t="n"/>
       <c r="V60" s="9" t="n"/>
       <c r="W60" s="10" t="n">
-        <v>34.5</v>
+        <v>39</v>
       </c>
       <c r="X60" s="9" t="n"/>
       <c r="Y60" s="10" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Z60" s="10" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="61">
@@ -11171,45 +11811,49 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>100% Cidades/Futura</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Futura</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>2000</v>
+        <v>5008</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>telefonica</t>
+          <t>online</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="9" t="n"/>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>BR-07992/2026</t>
+        </is>
+      </c>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M61" s="9" t="n"/>
@@ -11219,21 +11863,19 @@
       <c r="Q61" s="9" t="n"/>
       <c r="R61" s="9" t="n"/>
       <c r="S61" s="10" t="n">
-        <v>42.8</v>
+        <v>47.4</v>
       </c>
       <c r="T61" s="9" t="n"/>
       <c r="U61" s="9" t="n"/>
       <c r="V61" s="9" t="n"/>
       <c r="W61" s="10" t="n">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
       <c r="X61" s="9" t="n"/>
       <c r="Y61" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z61" s="10" t="n">
-        <v>2.7</v>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="Z61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -11253,12 +11895,12 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F62" s="9" t="n">
@@ -11272,7 +11914,7 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>presencial</t>
+          <t>telefonica</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
@@ -11280,12 +11922,12 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>BR-00835/2026</t>
+          <t>BR-09285/2026</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
       <c r="M62" s="9" t="n"/>
@@ -11295,19 +11937,917 @@
       <c r="Q62" s="9" t="n"/>
       <c r="R62" s="9" t="n"/>
       <c r="S62" s="10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T62" s="9" t="n"/>
       <c r="U62" s="9" t="n"/>
       <c r="V62" s="9" t="n"/>
       <c r="W62" s="10" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="X62" s="9" t="n"/>
       <c r="Y62" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z62" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Futura Inteligência</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>BR-08282/2026</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="9" t="n"/>
+      <c r="S63" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T63" s="9" t="n"/>
+      <c r="U63" s="9" t="n"/>
+      <c r="V63" s="9" t="n"/>
+      <c r="W63" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="X63" s="9" t="n"/>
+      <c r="Y63" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Z63" s="10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Datafolha</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>BR-03770/2026</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="n"/>
+      <c r="N64" s="9" t="n"/>
+      <c r="O64" s="9" t="n"/>
+      <c r="P64" s="9" t="n"/>
+      <c r="Q64" s="9" t="n"/>
+      <c r="R64" s="9" t="n"/>
+      <c r="S64" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T64" s="9" t="n"/>
+      <c r="U64" s="9" t="n"/>
+      <c r="V64" s="9" t="n"/>
+      <c r="W64" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="X64" s="9" t="n"/>
+      <c r="Y64" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z64" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>BR-00605/2026</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
+      <c r="S65" s="10" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="T65" s="9" t="n"/>
+      <c r="U65" s="9" t="n"/>
+      <c r="V65" s="9" t="n"/>
+      <c r="W65" s="10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="X65" s="9" t="n"/>
+      <c r="Y65" s="10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Z65" s="10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>AtlasIntel</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>5028</v>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>BR-04227/2026</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
+      <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="9" t="n"/>
+      <c r="S66" s="10" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T66" s="9" t="n"/>
+      <c r="U66" s="9" t="n"/>
+      <c r="V66" s="9" t="n"/>
+      <c r="W66" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="X66" s="9" t="n"/>
+      <c r="Y66" s="10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>BR-00386/2026</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="9" t="n"/>
+      <c r="S67" s="10" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="T67" s="9" t="n"/>
+      <c r="U67" s="9" t="n"/>
+      <c r="V67" s="9" t="n"/>
+      <c r="W67" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="X67" s="9" t="n"/>
+      <c r="Y67" s="10" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Z67" s="10" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>BR-05809/2026</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="n"/>
+      <c r="N68" s="9" t="n"/>
+      <c r="O68" s="9" t="n"/>
+      <c r="P68" s="9" t="n"/>
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="9" t="n"/>
+      <c r="S68" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="T68" s="9" t="n"/>
+      <c r="U68" s="9" t="n"/>
+      <c r="V68" s="9" t="n"/>
+      <c r="W68" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X68" s="9" t="n"/>
+      <c r="Y68" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="Z62" s="10" t="n">
+      <c r="Z68" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>BR-08165/2026</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
+      <c r="S69" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="T69" s="9" t="n"/>
+      <c r="U69" s="9" t="n"/>
+      <c r="V69" s="9" t="n"/>
+      <c r="W69" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="X69" s="9" t="n"/>
+      <c r="Y69" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z69" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>BR-00249/2026</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="n"/>
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="9" t="n"/>
+      <c r="S70" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="T70" s="9" t="n"/>
+      <c r="U70" s="9" t="n"/>
+      <c r="V70" s="9" t="n"/>
+      <c r="W70" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="X70" s="9" t="n"/>
+      <c r="Y70" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z70" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Meio/Ideia</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Canal Meio</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>BR-08425/2026</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="9" t="n"/>
+      <c r="S71" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T71" s="9" t="n"/>
+      <c r="U71" s="9" t="n"/>
+      <c r="V71" s="9" t="n"/>
+      <c r="W71" s="10" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="X71" s="9" t="n"/>
+      <c r="Y71" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z71" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>telefonica</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="9" t="n"/>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="n"/>
+      <c r="N72" s="9" t="n"/>
+      <c r="O72" s="9" t="n"/>
+      <c r="P72" s="9" t="n"/>
+      <c r="Q72" s="9" t="n"/>
+      <c r="R72" s="9" t="n"/>
+      <c r="S72" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="T72" s="9" t="n"/>
+      <c r="U72" s="9" t="n"/>
+      <c r="V72" s="9" t="n"/>
+      <c r="W72" s="10" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="X72" s="9" t="n"/>
+      <c r="Y72" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z72" s="10" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>100% Cidades/Futura</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Futura Pesquisas</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>BR-06845/2026</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="9" t="n"/>
+      <c r="S73" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="T73" s="9" t="n"/>
+      <c r="U73" s="9" t="n"/>
+      <c r="V73" s="9" t="n"/>
+      <c r="W73" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="X73" s="9" t="n"/>
+      <c r="Y73" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Z73" s="10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Lula vs Zema</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Banco Genial</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>presencial</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>BR-00835/2026</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="n"/>
+      <c r="N74" s="9" t="n"/>
+      <c r="O74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="Q74" s="9" t="n"/>
+      <c r="R74" s="9" t="n"/>
+      <c r="S74" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="T74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
+      <c r="V74" s="9" t="n"/>
+      <c r="W74" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="X74" s="9" t="n"/>
+      <c r="Y74" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z74" s="10" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.73</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34.08</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="11">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="12">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>42</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>4.23</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="14">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="16">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.72</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="17">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.76</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="19">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4.18</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="21">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>44.73</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="23">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>44.9</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>8.24</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3.24</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="27">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45.19</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>39.68</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="30">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12.21</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="31">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>4.43</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="33">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.73</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="11">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34.08</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="14">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>42</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="15">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4.23</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="16">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="18">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.72</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>5.76</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="21">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4.18</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="24">
@@ -2373,7 +2373,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.8515174032030288</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -2433,7 +2433,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.8515174032030288</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -2613,7 +2613,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.4160343594175414</v>
+        <v>0.8320687188350827</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.3793078814938844</v>
+        <v>1.137923644481653</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>2004</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.1853222387537124</v>
+        <v>0.3706444775074247</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         <v>2004</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.1689624527017146</v>
+        <v>0.506887358105144</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>2</v>
@@ -3693,7 +3693,7 @@
         <v>2004</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.1089275848773588</v>
+        <v>0.2178551697547177</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>2004</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.1940868914747239</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>2004</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.04965586437851098</v>
+        <v>0.09931172875702196</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.73</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="9">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>44.9</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="10">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8.24</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.24</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="14">
@@ -4487,7 +4487,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.8515174032030288</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>45</v>
@@ -4547,7 +4547,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>41</v>
@@ -4667,7 +4667,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.4160343594175414</v>
+        <v>0.8320687188350827</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>42</v>
@@ -4727,7 +4727,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3793078814938844</v>
+        <v>1.137923644481653</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>46</v>
@@ -4877,7 +4877,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.1853222387537124</v>
+        <v>0.3706444775074247</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>41</v>
@@ -4907,7 +4907,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.1689624527017146</v>
+        <v>0.506887358105144</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>43</v>
@@ -5027,7 +5027,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.1089275848773588</v>
+        <v>0.2178551697547177</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>42</v>
@@ -5057,7 +5057,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.1940868914747239</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>38</v>
@@ -5237,7 +5237,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.04965586437851098</v>
+        <v>0.09931172875702196</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>38</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45.19</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="9">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.68</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="10">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12.21</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="11">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>4.43</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="14">
@@ -5461,7 +5461,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.8515174032030288</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>46</v>
@@ -5521,7 +5521,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>44</v>
@@ -5641,7 +5641,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.4160343594175414</v>
+        <v>0.8320687188350827</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>43</v>
@@ -5701,7 +5701,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3793078814938844</v>
+        <v>1.137923644481653</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>45</v>
@@ -5821,7 +5821,7 @@
         <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.1853222387537124</v>
+        <v>0.3706444775074247</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>44</v>
@@ -5851,7 +5851,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.1089275848773588</v>
+        <v>0.2178551697547177</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>42</v>
@@ -5881,7 +5881,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.09704344573736197</v>
+        <v>0.1940868914747239</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>43</v>
@@ -6001,7 +6001,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.04965586437851098</v>
+        <v>0.09931172875702196</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>46</v>
@@ -6211,19 +6211,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>29.78</v>
+        <v>30.51</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>5.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -6237,19 +6237,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>41.41</v>
+        <v>41.08</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>33.08</v>
+        <v>32.94</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>4.39</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>1.2</v>
@@ -6265,19 +6265,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>40.89</v>
+        <v>40.71</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>33.09</v>
+        <v>32.98</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.55</v>
+        <v>3.69</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>4.15</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>1.14</v>
@@ -6293,19 +6293,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>40.71</v>
+        <v>40.57</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>33.08</v>
+        <v>32.99</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3.88</v>
+        <v>3.97</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>4.28</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>1.14</v>
@@ -6321,22 +6321,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.22</v>
+        <v>39.79</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.41</v>
+        <v>33.2</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="12">
@@ -6349,22 +6349,22 @@
         <v>5</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>39.11</v>
+        <v>38.9</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.81</v>
+        <v>32.72</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="13">
@@ -6377,22 +6377,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.97</v>
+        <v>41.37</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>35.91</v>
+        <v>35.33</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.77</v>
+        <v>3.69</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -6405,22 +6405,22 @@
         <v>7</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>41.67</v>
+        <v>40.72</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>35.65</v>
+        <v>34.71</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.82</v>
+        <v>4.04</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -6433,22 +6433,22 @@
         <v>8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>41.33</v>
+        <v>40.53</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.33</v>
+        <v>34.49</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -6461,19 +6461,19 @@
         <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>41.62</v>
+        <v>40.84</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>35.54</v>
+        <v>34.68</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>0.84</v>
@@ -6489,19 +6489,19 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>42.26</v>
+        <v>41.08</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>36.27</v>
+        <v>34.96</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -6515,19 +6515,19 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>42.12</v>
+        <v>41.75</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>36.76</v>
+        <v>36.19</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0.8</v>
@@ -6543,19 +6543,19 @@
         <v>6</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>41.28</v>
+        <v>40.68</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>37.13</v>
+        <v>36.57</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>1.08</v>
@@ -6571,22 +6571,22 @@
         <v>7</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>40.58</v>
+        <v>39.85</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>36.29</v>
+        <v>35.54</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>4.71</v>
+        <v>4.91</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="21">
@@ -6599,22 +6599,22 @@
         <v>6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>39.56</v>
+        <v>39.11</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>35.56</v>
+        <v>34.98</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="22">
@@ -6627,22 +6627,22 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>41.83</v>
+        <v>40.67</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>36.89</v>
+        <v>35.92</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>4.69</v>
+        <v>4.91</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3.27</v>
+        <v>2.86</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="23">
@@ -6655,22 +6655,22 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>41.56</v>
+        <v>41</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>36.29</v>
+        <v>35.77</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.72</v>
+        <v>4.87</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="24">
@@ -6683,22 +6683,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>38.87</v>
+        <v>38.6</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.8</v>
+        <v>35.33</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.89</v>
+        <v>3.61</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>
@@ -6787,10 +6787,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>36.99</v>
+        <v>37.32</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>45.11</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="8">
@@ -6803,10 +6803,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>41.5</v>
+        <v>40.86</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>43.12</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="9">
@@ -6819,10 +6819,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41.68</v>
+        <v>41.15</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>43.55</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="10">
@@ -6835,7 +6835,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>41.57</v>
+        <v>41.14</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>43.99</v>
@@ -6851,10 +6851,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>41.91</v>
+        <v>41.36</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>42.62</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="12">
@@ -6867,10 +6867,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>40.76</v>
+        <v>40.52</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>43.02</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="13">
@@ -6883,10 +6883,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.36</v>
+        <v>43.54</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>44.58</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="14">
@@ -6899,10 +6899,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>44.36</v>
+        <v>43.47</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>44.74</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="15">
@@ -6915,10 +6915,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.49</v>
+        <v>43.71</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.67</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="16">
@@ -6931,10 +6931,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.73</v>
+        <v>43.94</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>45.14</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="17">
@@ -6947,10 +6947,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.03</v>
+        <v>44.04</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>45.51</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="18">
@@ -6963,10 +6963,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.4</v>
+        <v>44.75</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>45.02</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="19">
@@ -6979,10 +6979,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>46.63</v>
+        <v>46.44</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>44.77</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="20">
@@ -6995,10 +6995,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>45.76</v>
+        <v>45.35</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>43.87</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="21">
@@ -7011,10 +7011,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>45.35</v>
+        <v>45.05</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>43.26</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="22">
@@ -7027,10 +7027,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>46.29</v>
+        <v>45.73</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>44.75</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="23">
@@ -7043,10 +7043,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>45.66</v>
+        <v>45.22</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>44.24</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="24">
@@ -7059,10 +7059,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.63</v>
+        <v>44.97</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>44.3</v>
+        <v>44.21</v>
       </c>
     </row>
   </sheetData>
@@ -7167,10 +7167,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>43.39</v>
+        <v>43.98</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>36.44</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="9">
@@ -7183,10 +7183,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>43.39</v>
+        <v>43.98</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>36.44</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -7199,10 +7199,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>43.87</v>
+        <v>44.23</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>35.86</v>
+        <v>35.03</v>
       </c>
     </row>
     <row r="11">
@@ -7215,10 +7215,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>42.87</v>
+        <v>42.74</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>35.29</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="12">
@@ -7231,10 +7231,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43.12</v>
+        <v>42.84</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>33.82</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="13">
@@ -7247,10 +7247,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43.12</v>
+        <v>42.84</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>33.82</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="14">
@@ -7279,10 +7279,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.28</v>
+        <v>43.88</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.67</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="16">
@@ -7295,10 +7295,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.99</v>
+        <v>44.64</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>35.88</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="17">
@@ -7311,10 +7311,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.85</v>
+        <v>45.49</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>40.08</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="18">
@@ -7327,10 +7327,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.85</v>
+        <v>45.49</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>40.08</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="19">
@@ -7343,10 +7343,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>45.32</v>
+        <v>45.21</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>40.71</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="20">
@@ -7359,10 +7359,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>44.81</v>
+        <v>44.61</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>39.68</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="21">
@@ -7375,10 +7375,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>44.33</v>
+        <v>44.31</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>38.6</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="22">
@@ -7391,10 +7391,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.49</v>
+        <v>45.1</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>41.57</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="23">
@@ -7407,10 +7407,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.77</v>
+        <v>44.56</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>41.4</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="24">
@@ -7423,10 +7423,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.71</v>
+        <v>44.94</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>41.1</v>
+        <v>40.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="10">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34.12</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="11">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>41.01</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="14">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="15">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="17">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.65</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="18">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="19">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="21">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>44.37</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="23">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>44.54</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>9.130000000000001</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="27">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45.08</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>39.36</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="30">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12.8</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="31">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="11">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="12">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34.12</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="13">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>41.01</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="15">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="16">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="19">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7.65</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="20">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="21">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="24">
@@ -2733,7 +2733,7 @@
         <v>2000</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.675174973084095</v>
+        <v>0.2025524919252285</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -3093,7 +3093,7 @@
         <v>2080</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.3067124067161689</v>
+        <v>0.1533562033580844</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>0.2</v>
@@ -3153,7 +3153,7 @@
         <v>2080</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.3067124067161689</v>
+        <v>0.1533562033580844</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>1.1</v>
@@ -3453,7 +3453,7 @@
         <v>2080</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.1430863971899205</v>
+        <v>0.07154319859496026</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>0.4</v>
@@ -3513,7 +3513,7 @@
         <v>2080</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.1430863971899205</v>
+        <v>0.07154319859496026</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0.2</v>
@@ -3873,7 +3873,7 @@
         <v>2080</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.07492677141629081</v>
+        <v>0.03746338570814541</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1.1</v>
@@ -3933,7 +3933,7 @@
         <v>2080</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.07492677141629081</v>
+        <v>0.03746338570814541</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.3</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.37</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="9">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>44.54</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="10">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>9.130000000000001</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="11">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="14">
@@ -4607,7 +4607,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.675174973084095</v>
+        <v>0.2025524919252285</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>44</v>
@@ -4787,7 +4787,7 @@
         <v>2080</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3067124067161689</v>
+        <v>0.1533562033580844</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>45.2</v>
@@ -4937,7 +4937,7 @@
         <v>2080</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.1430863971899205</v>
+        <v>0.07154319859496026</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>44.4</v>
@@ -5117,7 +5117,7 @@
         <v>2080</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.07492677141629081</v>
+        <v>0.03746338570814541</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>42.2</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45.08</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="9">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.36</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="10">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12.8</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="11">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="14">
@@ -5581,7 +5581,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.675174973084095</v>
+        <v>0.2025524919252285</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>43</v>
@@ -6265,22 +6265,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>40.71</v>
+        <v>40.87</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>32.98</v>
+        <v>32.96</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.69</v>
+        <v>3.84</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10">
@@ -6293,22 +6293,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>40.57</v>
+        <v>40.68</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32.99</v>
+        <v>32.97</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3.97</v>
+        <v>4.14</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.28</v>
+        <v>4.39</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11">
@@ -6324,19 +6324,19 @@
         <v>39.79</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.2</v>
+        <v>33.21</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="12">
@@ -6349,22 +6349,22 @@
         <v>5</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>38.9</v>
+        <v>38.78</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.72</v>
+        <v>32.67</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="13">
@@ -6377,19 +6377,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.37</v>
+        <v>41.51</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>35.33</v>
+        <v>35.34</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>0.9</v>
@@ -6405,19 +6405,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>40.72</v>
+        <v>40.75</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>34.71</v>
+        <v>34.66</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.04</v>
+        <v>4.11</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0.9</v>
@@ -6433,19 +6433,19 @@
         <v>8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>40.53</v>
+        <v>40.54</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>34.49</v>
+        <v>34.43</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0.9</v>
@@ -6461,22 +6461,22 @@
         <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>40.84</v>
+        <v>40.89</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34.68</v>
+        <v>34.62</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="17">
@@ -6515,19 +6515,19 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>41.75</v>
+        <v>41.92</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>36.19</v>
+        <v>36.12</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0.8</v>
@@ -6543,22 +6543,22 @@
         <v>6</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>40.68</v>
+        <v>40.63</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>36.57</v>
+        <v>36.58</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="20">
@@ -6571,22 +6571,22 @@
         <v>7</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>39.85</v>
+        <v>39.74</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>35.54</v>
+        <v>35.46</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>4.91</v>
+        <v>5.06</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="21">
@@ -6599,22 +6599,22 @@
         <v>6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>39.11</v>
+        <v>38.91</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>34.98</v>
+        <v>34.83</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>5.06</v>
+        <v>5.24</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="22">
@@ -6655,22 +6655,22 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>41</v>
+        <v>41.16</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>35.77</v>
+        <v>36.05</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="24">
@@ -6683,22 +6683,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>38.6</v>
+        <v>38.53</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.33</v>
+        <v>35.39</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -6819,10 +6819,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41.15</v>
+        <v>41.02</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>43.61</v>
+        <v>43.47</v>
       </c>
     </row>
     <row r="10">
@@ -6835,10 +6835,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>41.14</v>
+        <v>41.04</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>43.99</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="11">
@@ -6851,10 +6851,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>41.36</v>
+        <v>41.31</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>42.26</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="12">
@@ -6867,10 +6867,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>40.52</v>
+        <v>40.4</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>42.43</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="13">
@@ -6883,10 +6883,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43.54</v>
+        <v>43.47</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>43.97</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="14">
@@ -6899,10 +6899,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>43.47</v>
+        <v>43.42</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>44.57</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="15">
@@ -6915,10 +6915,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>43.71</v>
+        <v>43.69</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.27</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="16">
@@ -6931,10 +6931,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>43.94</v>
+        <v>43.92</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>44.84</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="17">
@@ -6963,10 +6963,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>44.75</v>
+        <v>44.68</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>44.43</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="19">
@@ -6979,10 +6979,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>46.44</v>
+        <v>46.52</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>44.83</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="20">
@@ -6995,10 +6995,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>45.35</v>
+        <v>45.36</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>43.65</v>
+        <v>43.63</v>
       </c>
     </row>
     <row r="21">
@@ -7011,10 +7011,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>45.05</v>
+        <v>45.04</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>43.25</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22">
@@ -7043,10 +7043,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>45.22</v>
+        <v>45.41</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>43.72</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="24">
@@ -7059,10 +7059,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.97</v>
+        <v>45.03</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>44.21</v>
+        <v>44.29</v>
       </c>
     </row>
   </sheetData>
@@ -7407,10 +7407,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.56</v>
+        <v>44.81</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>40.74</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="24">
@@ -7423,10 +7423,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.94</v>
+        <v>45.08</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>40.38</v>
+        <v>40.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         <v>5032</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.2</v>
@@ -2133,7 +2133,7 @@
         <v>5032</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>5032</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>1.2</v>
@@ -2253,7 +2253,7 @@
         <v>5032</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.5</v>
@@ -2313,7 +2313,7 @@
         <v>5032</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E30" s="10" t="n">
         <v/>
@@ -2373,7 +2373,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -2433,7 +2433,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -2493,7 +2493,7 @@
         <v>2000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.8122523963562355</v>
+        <v>0.7937005259840997</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -2553,7 +2553,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.8122523963562355</v>
+        <v>0.7937005259840997</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -2613,7 +2613,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1.588987660112351</v>
+        <v>1.552695131797792</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>1500</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.5983858299345048</v>
+        <v>0.5847186786903008</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.8</v>
@@ -2733,7 +2733,7 @@
         <v>2000</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.2025524919252285</v>
+        <v>0.1979261866159341</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -2793,7 +2793,7 @@
         <v>5008</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.9088519968310748</v>
+        <v>0.8880937885348543</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.3</v>
@@ -2853,7 +2853,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.8320687188350827</v>
+        <v>0.813064243032013</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>2000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.3968502629920498</v>
+        <v>0.3877861904584337</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0.3</v>
@@ -2973,7 +2973,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1.137923644481653</v>
+        <v>1.111933432522275</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1</v>
@@ -3033,7 +3033,7 @@
         <v>1500</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.313342981434775</v>
+        <v>0.3061862178478973</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0.6</v>
@@ -3093,7 +3093,7 @@
         <v>2080</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.1533562033580844</v>
+        <v>0.1498535428325816</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>0.2</v>
@@ -3153,7 +3153,7 @@
         <v>2080</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.1533562033580844</v>
+        <v>0.1498535428325816</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>1.1</v>
@@ -3213,7 +3213,7 @@
         <v>5028</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.4056551356117546</v>
+        <v>0.3963899595095718</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0.6</v>
@@ -3273,7 +3273,7 @@
         <v>1500</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.1640811314418663</v>
+        <v>0.1603335132203894</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0.8</v>
@@ -3333,7 +3333,7 @@
         <v>2004</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.3706444775074247</v>
+        <v>0.3621789459414829</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         <v>2004</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.506887358105144</v>
+        <v>0.495310034845741</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>2</v>
@@ -3453,7 +3453,7 @@
         <v>2080</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.07154319859496026</v>
+        <v>0.06990914968073636</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>0.4</v>
@@ -3513,7 +3513,7 @@
         <v>2080</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.07154319859496026</v>
+        <v>0.06990914968073636</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0.2</v>
@@ -3573,7 +3573,7 @@
         <v>4986</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.2164753672098426</v>
+        <v>0.2115310629895616</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>1.1</v>
@@ -3633,7 +3633,7 @@
         <v>5020</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.2172121960982981</v>
+        <v>0.2122510626829462</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0.5</v>
@@ -3693,7 +3693,7 @@
         <v>2004</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.2178551697547177</v>
+        <v>0.2128793508007572</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>2004</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.1940868914747239</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>1500</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.0697892151246283</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>0.5</v>
@@ -3873,7 +3873,7 @@
         <v>2080</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.03746338570814541</v>
+        <v>0.03660772079601134</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1.1</v>
@@ -3933,7 +3933,7 @@
         <v>2080</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.03746338570814541</v>
+        <v>0.03660772079601134</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.3</v>
@@ -3993,7 +3993,7 @@
         <v>5418</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.1005194692155711</v>
+        <v>0.09822360136571462</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>2000</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.6</v>
@@ -4113,7 +4113,7 @@
         <v>2000</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0.4</v>
@@ -4173,7 +4173,7 @@
         <v>2000</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.04960628287400623</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0.2</v>
@@ -4233,7 +4233,7 @@
         <v>2004</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.09931172875702196</v>
+        <v>0.09704344573736196</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>2</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>41.8</v>
@@ -4487,7 +4487,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>45</v>
@@ -4517,7 +4517,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8122523963562355</v>
+        <v>0.7937005259840997</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>50</v>
@@ -4547,7 +4547,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1.588987660112351</v>
+        <v>1.552695131797792</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>41</v>
@@ -4577,7 +4577,7 @@
         <v>1500</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.5983858299345048</v>
+        <v>0.5847186786903008</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>45.3</v>
@@ -4607,7 +4607,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.2025524919252285</v>
+        <v>0.1979261866159341</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>44</v>
@@ -4637,7 +4637,7 @@
         <v>5008</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.9088519968310748</v>
+        <v>0.8880937885348543</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>47.8</v>
@@ -4667,7 +4667,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.8320687188350827</v>
+        <v>0.813064243032013</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>42</v>
@@ -4697,7 +4697,7 @@
         <v>2000</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.3968502629920498</v>
+        <v>0.3877861904584337</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>48</v>
@@ -4727,7 +4727,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.137923644481653</v>
+        <v>1.111933432522275</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>46</v>
@@ -4757,7 +4757,7 @@
         <v>1500</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.313342981434775</v>
+        <v>0.3061862178478973</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>45.8</v>
@@ -4787,7 +4787,7 @@
         <v>2080</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.1533562033580844</v>
+        <v>0.1498535428325816</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>45.2</v>
@@ -4817,7 +4817,7 @@
         <v>5028</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.4056551356117546</v>
+        <v>0.3963899595095718</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>47.6</v>
@@ -4847,7 +4847,7 @@
         <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.1640811314418663</v>
+        <v>0.1603335132203894</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>45.3</v>
@@ -4877,7 +4877,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.3706444775074247</v>
+        <v>0.3621789459414829</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>41</v>
@@ -4907,7 +4907,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.506887358105144</v>
+        <v>0.495310034845741</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>43</v>
@@ -4937,7 +4937,7 @@
         <v>2080</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.07154319859496026</v>
+        <v>0.06990914968073636</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>44.4</v>
@@ -4967,7 +4967,7 @@
         <v>4986</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.2164753672098426</v>
+        <v>0.2115310629895616</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>46.3</v>
@@ -4997,7 +4997,7 @@
         <v>5020</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.2172121960982981</v>
+        <v>0.2122510626829462</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>47.5</v>
@@ -5027,7 +5027,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.2178551697547177</v>
+        <v>0.2128793508007572</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>42</v>
@@ -5057,7 +5057,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.1940868914747239</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>38</v>
@@ -5087,7 +5087,7 @@
         <v>1500</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.0697892151246283</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>41.1</v>
@@ -5117,7 +5117,7 @@
         <v>2080</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.03746338570814541</v>
+        <v>0.03660772079601134</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>42.2</v>
@@ -5147,7 +5147,7 @@
         <v>2000</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>48.1</v>
@@ -5177,7 +5177,7 @@
         <v>2000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>42.5</v>
@@ -5207,7 +5207,7 @@
         <v>2000</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.04960628287400623</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>36</v>
@@ -5237,7 +5237,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.09931172875702196</v>
+        <v>0.09704344573736196</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>38</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.479967978455294</v>
+        <v>1.44616546311107</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>47.8</v>
@@ -5461,7 +5461,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>46</v>
@@ -5491,7 +5491,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8122523963562355</v>
+        <v>0.7937005259840997</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>43</v>
@@ -5521,7 +5521,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1.588987660112351</v>
+        <v>1.552695131797792</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>44</v>
@@ -5551,7 +5551,7 @@
         <v>1500</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.5983858299345048</v>
+        <v>0.5847186786903008</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>44</v>
@@ -5581,7 +5581,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.2025524919252285</v>
+        <v>0.1979261866159341</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>43</v>
@@ -5611,7 +5611,7 @@
         <v>5008</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.9088519968310748</v>
+        <v>0.8880937885348543</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>47.4</v>
@@ -5641,7 +5641,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.8320687188350827</v>
+        <v>0.813064243032013</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>43</v>
@@ -5671,7 +5671,7 @@
         <v>2000</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.3968502629920498</v>
+        <v>0.3877861904584337</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>44.8</v>
@@ -5701,7 +5701,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.137923644481653</v>
+        <v>1.111933432522275</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>45</v>
@@ -5731,7 +5731,7 @@
         <v>1500</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.313342981434775</v>
+        <v>0.3061862178478973</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>44.7</v>
@@ -5761,7 +5761,7 @@
         <v>5028</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.4056551356117546</v>
+        <v>0.3963899595095718</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>46.6</v>
@@ -5791,7 +5791,7 @@
         <v>1500</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.1640811314418663</v>
+        <v>0.1603335132203894</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>46.1</v>
@@ -5821,7 +5821,7 @@
         <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.3706444775074247</v>
+        <v>0.3621789459414829</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>44</v>
@@ -5851,7 +5851,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.2178551697547177</v>
+        <v>0.2128793508007572</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>42</v>
@@ -5881,7 +5881,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.1940868914747239</v>
+        <v>0.1896539407469422</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>43</v>
@@ -5911,7 +5911,7 @@
         <v>1500</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.07142046070149105</v>
+        <v>0.0697892151246283</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>45</v>
@@ -5941,7 +5941,7 @@
         <v>2000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>42.8</v>
@@ -5971,7 +5971,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.05967760024440102</v>
+        <v>0.05831456197105047</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>41.8</v>
@@ -6001,7 +6001,7 @@
         <v>2004</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.09931172875702196</v>
+        <v>0.09704344573736196</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>46</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.48</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="10">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34.09</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="11">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="12">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>41.04</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.71</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="14">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="15">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.16</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="17">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>6.83</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="19">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="21">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>44.38</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="23">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>44.6</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>9.25</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="27">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45.16</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="29">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>39.26</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="30">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12.95</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="31">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="9">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.48</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="11">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="12">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34.09</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="13">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="14">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>41.04</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="15">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3.71</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="16">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="17">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="18">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.16</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6.83</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="21">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="24">
@@ -2073,7 +2073,7 @@
         <v>5032</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.2</v>
@@ -2133,7 +2133,7 @@
         <v>5032</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>5032</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>1.2</v>
@@ -2253,7 +2253,7 @@
         <v>5032</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.5</v>
@@ -2313,7 +2313,7 @@
         <v>5032</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E30" s="10" t="n">
         <v/>
@@ -2373,7 +2373,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>1.664137437670165</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -2433,7 +2433,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>1.664137437670165</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -2733,7 +2733,7 @@
         <v>2000</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1979261866159341</v>
+        <v>0.6597539553864471</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -2793,7 +2793,7 @@
         <v>5008</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.8880937885348543</v>
+        <v>1.776187577069709</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.3</v>
@@ -2973,7 +2973,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1.111933432522275</v>
+        <v>0.7412889550148496</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>5028</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.3963899595095718</v>
+        <v>0.7927799190191437</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0.6</v>
@@ -3393,7 +3393,7 @@
         <v>2004</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.495310034845741</v>
+        <v>0.3302066898971607</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>2</v>
@@ -3573,7 +3573,7 @@
         <v>4986</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.2115310629895616</v>
+        <v>0.4230621259791232</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>1.1</v>
@@ -3633,7 +3633,7 @@
         <v>5020</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.2122510626829462</v>
+        <v>0.4245021253658925</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0.5</v>
@@ -3993,7 +3993,7 @@
         <v>5418</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.09822360136571462</v>
+        <v>0.1964472027314292</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.38</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="9">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>44.6</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="10">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>9.25</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="11">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -4457,7 +4457,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>41.8</v>
@@ -4487,7 +4487,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>1.664137437670165</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>45</v>
@@ -4607,7 +4607,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.1979261866159341</v>
+        <v>0.6597539553864471</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>44</v>
@@ -4637,7 +4637,7 @@
         <v>5008</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.8880937885348543</v>
+        <v>1.776187577069709</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>47.8</v>
@@ -4727,7 +4727,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.111933432522275</v>
+        <v>0.7412889550148496</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>46</v>
@@ -4817,7 +4817,7 @@
         <v>5028</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.3963899595095718</v>
+        <v>0.7927799190191437</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>47.6</v>
@@ -4907,7 +4907,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.495310034845741</v>
+        <v>0.3302066898971607</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>43</v>
@@ -4967,7 +4967,7 @@
         <v>4986</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.2115310629895616</v>
+        <v>0.4230621259791232</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>46.3</v>
@@ -4997,7 +4997,7 @@
         <v>5020</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.2122510626829462</v>
+        <v>0.4245021253658925</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>47.5</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45.16</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="9">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>39.26</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="10">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12.95</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="11">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -5431,7 +5431,7 @@
         <v>5032</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1.44616546311107</v>
+        <v>2.892330926222139</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>47.8</v>
@@ -5461,7 +5461,7 @@
         <v>2004</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>1.664137437670165</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>46</v>
@@ -5581,7 +5581,7 @@
         <v>2000</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.1979261866159341</v>
+        <v>0.6597539553864471</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>43</v>
@@ -5611,7 +5611,7 @@
         <v>5008</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.8880937885348543</v>
+        <v>1.776187577069709</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>47.4</v>
@@ -5701,7 +5701,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.111933432522275</v>
+        <v>0.7412889550148496</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>45</v>
@@ -5761,7 +5761,7 @@
         <v>5028</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3963899595095718</v>
+        <v>0.7927799190191437</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>46.6</v>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Cury</t>
+          <t>Samara</t>
         </is>
       </c>
     </row>
@@ -6237,23 +6237,21 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>41.08</v>
+        <v>42.73</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>32.94</v>
+        <v>33.38</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>1.2</v>
-      </c>
+        <v>2.42</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -6265,23 +6263,21 @@
         <v>7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>40.87</v>
+        <v>42.33</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>32.96</v>
+        <v>33.34</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>1.16</v>
-      </c>
+        <v>2.29</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6293,23 +6289,21 @@
         <v>8</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>40.68</v>
+        <v>42</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32.97</v>
+        <v>33.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.14</v>
+        <v>3.92</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>1.16</v>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -6321,22 +6315,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.79</v>
+        <v>40.82</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.21</v>
+        <v>33.42</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6364,7 +6358,7 @@
         <v>1.77</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6377,22 +6371,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.51</v>
+        <v>42.55</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>35.34</v>
+        <v>36.23</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.67</v>
+        <v>3.07</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6405,22 +6399,22 @@
         <v>7</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>40.75</v>
+        <v>41.99</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>34.66</v>
+        <v>35.74</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6433,22 +6427,22 @@
         <v>8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>40.54</v>
+        <v>41.61</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>34.43</v>
+        <v>35.37</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6461,23 +6455,21 @@
         <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>40.89</v>
+        <v>42.03</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34.62</v>
+        <v>35.64</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>0.82</v>
-      </c>
+        <v>2.85</v>
+      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -6489,19 +6481,19 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>41.08</v>
+        <v>42.45</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>34.96</v>
+        <v>36.4</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -6515,23 +6507,21 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>41.92</v>
+        <v>42.9</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>36.12</v>
+        <v>37.1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -6543,23 +6533,21 @@
         <v>6</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>40.63</v>
+        <v>41.7</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>36.58</v>
+        <v>37.37</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>1.16</v>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -6571,22 +6559,22 @@
         <v>7</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>39.74</v>
+        <v>40.56</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>35.46</v>
+        <v>36.06</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -6599,22 +6587,22 @@
         <v>6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>38.91</v>
+        <v>38.89</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>34.83</v>
+        <v>34.8</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6627,22 +6615,22 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>40.67</v>
+        <v>42.13</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>35.92</v>
+        <v>36.84</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>4.91</v>
+        <v>4.55</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.86</v>
+        <v>3.47</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -6655,22 +6643,22 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>41.16</v>
+        <v>42.18</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>36.05</v>
+        <v>36.59</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.85</v>
+        <v>4.54</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1.46</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="24">
@@ -6683,22 +6671,22 @@
         <v>8</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>38.53</v>
+        <v>39.45</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.39</v>
+        <v>35.8</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
@@ -6883,10 +6871,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43.47</v>
+        <v>44.52</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>43.98</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="14">
@@ -6899,10 +6887,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>43.42</v>
+        <v>44.36</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>44.61</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="15">
@@ -6915,10 +6903,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>43.69</v>
+        <v>44.43</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.29</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="16">
@@ -6931,10 +6919,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>43.92</v>
+        <v>44.72</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>44.89</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="17">
@@ -6947,10 +6935,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>44.04</v>
+        <v>45</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>45.05</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="18">
@@ -6963,10 +6951,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>44.68</v>
+        <v>45.47</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>44.47</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="19">
@@ -6979,10 +6967,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>46.52</v>
+        <v>46.78</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>44.88</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="20">
@@ -6995,10 +6983,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>45.36</v>
+        <v>45.56</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>43.63</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="21">
@@ -7011,10 +6999,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>45.04</v>
+        <v>44.89</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>43.2</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="22">
@@ -7027,10 +7015,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.73</v>
+        <v>46.16</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>44.25</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="23">
@@ -7043,10 +7031,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>45.41</v>
+        <v>45.76</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>43.83</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="24">
@@ -7059,10 +7047,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.03</v>
+        <v>45.32</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>44.29</v>
+        <v>44.53</v>
       </c>
     </row>
   </sheetData>
@@ -7311,10 +7299,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.49</v>
+        <v>45.82</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>38.88</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="18">
@@ -7327,10 +7315,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.49</v>
+        <v>45.82</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>38.88</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="19">
@@ -7343,10 +7331,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>45.21</v>
+        <v>45.49</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>41.14</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="20">
@@ -7359,10 +7347,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>44.61</v>
+        <v>44.83</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>39.76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -7375,10 +7363,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>44.31</v>
+        <v>44.2</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>39.16</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="22">
@@ -7391,10 +7379,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.1</v>
+        <v>45.61</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>41.02</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="23">
@@ -7407,10 +7395,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.81</v>
+        <v>45.16</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>40.54</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="24">
@@ -7423,10 +7411,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.08</v>
+        <v>45.13</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>40.26</v>
+        <v>41.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         <v>2000</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.9771599684342459</v>
+        <v>0.9548416039104165</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.4</v>
@@ -2133,7 +2133,7 @@
         <v>2000</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.9771599684342459</v>
+        <v>0.9548416039104165</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>1.6</v>
@@ -2193,7 +2193,7 @@
         <v>5032</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0.2</v>
@@ -2253,7 +2253,7 @@
         <v>5032</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E29" s="10" t="n">
         <v/>
@@ -2313,7 +2313,7 @@
         <v>5032</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1.2</v>
@@ -2373,7 +2373,7 @@
         <v>5032</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.5</v>
@@ -2433,7 +2433,7 @@
         <v>5032</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -2493,7 +2493,7 @@
         <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1.664137437670165</v>
+        <v>1.626128486064026</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -2553,7 +2553,7 @@
         <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>1.664137437670165</v>
+        <v>1.626128486064026</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -2613,7 +2613,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.7937005259840997</v>
+        <v>0.7755723809168673</v>
       </c>
       <c r="E35" s="10" t="n">
         <v/>
@@ -2673,7 +2673,7 @@
         <v>2000</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.7937005259840997</v>
+        <v>0.7755723809168673</v>
       </c>
       <c r="E36" s="10" t="n">
         <v/>
@@ -2733,7 +2733,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>1.517231525975538</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1500</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.5847186786903008</v>
+        <v>0.5713636856119283</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.8</v>
@@ -2853,7 +2853,7 @@
         <v>2000</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.6597539553864471</v>
+        <v>0.6446851542197896</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -2913,7 +2913,7 @@
         <v>5008</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1.776187577069709</v>
+        <v>1.735619396742736</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0.3</v>
@@ -2973,7 +2973,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.813064243032013</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.3877861904584337</v>
+        <v>0.3789291416275995</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0.3</v>
@@ -3093,7 +3093,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>1500</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.3061862178478973</v>
+        <v>0.2991929149672524</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0.6</v>
@@ -3213,7 +3213,7 @@
         <v>2080</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.1498535428325816</v>
+        <v>0.1464308831840453</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0.2</v>
@@ -3273,7 +3273,7 @@
         <v>2080</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.1498535428325816</v>
+        <v>0.1464308831840453</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>1.1</v>
@@ -3333,7 +3333,7 @@
         <v>5028</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.7927799190191437</v>
+        <v>0.7746728006440504</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0.6</v>
@@ -3393,7 +3393,7 @@
         <v>1500</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.1603335132203894</v>
+        <v>0.1566714907173875</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0.8</v>
@@ -3453,7 +3453,7 @@
         <v>2004</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.3621789459414829</v>
+        <v>0.3539067673837278</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>2004</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.3302066898971607</v>
+        <v>0.3226647586766863</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>2</v>
@@ -3573,7 +3573,7 @@
         <v>2080</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.06990914968073636</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0.4</v>
@@ -3633,7 +3633,7 @@
         <v>2080</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.06990914968073636</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0.2</v>
@@ -3693,7 +3693,7 @@
         <v>4986</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.4230621259791232</v>
+        <v>0.413399373667485</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>1.1</v>
@@ -3753,7 +3753,7 @@
         <v>5020</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.4245021253658925</v>
+        <v>0.4148064834228057</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0.5</v>
@@ -3813,7 +3813,7 @@
         <v>2004</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.2128793508007572</v>
+        <v>0.2080171797087706</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>2004</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537125</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1</v>
@@ -3933,7 +3933,7 @@
         <v>1500</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.0697892151246283</v>
+        <v>0.0681952272482326</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.5</v>
@@ -3993,7 +3993,7 @@
         <v>2080</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.03660772079601134</v>
+        <v>0.03577159929748013</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1.1</v>
@@ -4053,7 +4053,7 @@
         <v>2080</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.03660772079601134</v>
+        <v>0.03577159929748013</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.3</v>
@@ -4113,7 +4113,7 @@
         <v>5418</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.1964472027314292</v>
+        <v>0.1919603424200394</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>1</v>
@@ -4173,7 +4173,7 @@
         <v>2000</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0.6</v>
@@ -4233,7 +4233,7 @@
         <v>2000</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0.4</v>
@@ -4293,7 +4293,7 @@
         <v>2000</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.04960628287400623</v>
+        <v>0.04847327380730419</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0.2</v>
@@ -4353,7 +4353,7 @@
         <v>2004</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.09704344573736196</v>
+        <v>0.09482697037347115</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>2</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
         <v>2000</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.9771599684342459</v>
+        <v>0.9548416039104165</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>42.2</v>
@@ -4607,7 +4607,7 @@
         <v>5032</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>41.8</v>
@@ -4637,7 +4637,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.664137437670165</v>
+        <v>1.626128486064026</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>45</v>
@@ -4667,7 +4667,7 @@
         <v>2000</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7937005259840997</v>
+        <v>0.7755723809168673</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>50</v>
@@ -4697,7 +4697,7 @@
         <v>2004</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>1.517231525975538</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>41</v>
@@ -4727,7 +4727,7 @@
         <v>1500</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.5847186786903008</v>
+        <v>0.5713636856119283</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>45.3</v>
@@ -4757,7 +4757,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.6597539553864471</v>
+        <v>0.6446851542197896</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>44</v>
@@ -4787,7 +4787,7 @@
         <v>5008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.776187577069709</v>
+        <v>1.735619396742736</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>47.8</v>
@@ -4817,7 +4817,7 @@
         <v>2004</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.813064243032013</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>42</v>
@@ -4847,7 +4847,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3877861904584337</v>
+        <v>0.3789291416275995</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>48</v>
@@ -4877,7 +4877,7 @@
         <v>2004</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>46</v>
@@ -4907,7 +4907,7 @@
         <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3061862178478973</v>
+        <v>0.2991929149672524</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>45.8</v>
@@ -4937,7 +4937,7 @@
         <v>2080</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.1498535428325816</v>
+        <v>0.1464308831840453</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>45.2</v>
@@ -4967,7 +4967,7 @@
         <v>5028</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.7927799190191437</v>
+        <v>0.7746728006440504</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>47.6</v>
@@ -4997,7 +4997,7 @@
         <v>1500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.1603335132203894</v>
+        <v>0.1566714907173875</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>45.3</v>
@@ -5027,7 +5027,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3621789459414829</v>
+        <v>0.3539067673837278</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>41</v>
@@ -5057,7 +5057,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.3302066898971607</v>
+        <v>0.3226647586766863</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>43</v>
@@ -5087,7 +5087,7 @@
         <v>2080</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.06990914968073636</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>44.4</v>
@@ -5117,7 +5117,7 @@
         <v>4986</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.4230621259791232</v>
+        <v>0.413399373667485</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>46.3</v>
@@ -5147,7 +5147,7 @@
         <v>5020</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.4245021253658925</v>
+        <v>0.4148064834228057</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>47.5</v>
@@ -5177,7 +5177,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.2128793508007572</v>
+        <v>0.2080171797087706</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>42</v>
@@ -5207,7 +5207,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537125</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>38</v>
@@ -5237,7 +5237,7 @@
         <v>1500</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.0697892151246283</v>
+        <v>0.0681952272482326</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>41.1</v>
@@ -5267,7 +5267,7 @@
         <v>2080</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.03660772079601134</v>
+        <v>0.03577159929748013</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>42.2</v>
@@ -5297,7 +5297,7 @@
         <v>2000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>48.1</v>
@@ -5327,7 +5327,7 @@
         <v>2000</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>42.5</v>
@@ -5357,7 +5357,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.04960628287400623</v>
+        <v>0.04847327380730419</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>36</v>
@@ -5387,7 +5387,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.09704344573736196</v>
+        <v>0.09482697037347115</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>38</v>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
         <v>2000</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.9771599684342459</v>
+        <v>0.9548416039104165</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>48.3</v>
@@ -5611,7 +5611,7 @@
         <v>5032</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.892330926222139</v>
+        <v>2.826269996568619</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>47.8</v>
@@ -5641,7 +5641,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.664137437670165</v>
+        <v>1.626128486064026</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>46</v>
@@ -5671,7 +5671,7 @@
         <v>2000</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7937005259840997</v>
+        <v>0.7755723809168673</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>43</v>
@@ -5701,7 +5701,7 @@
         <v>2004</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>1.517231525975538</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>44</v>
@@ -5731,7 +5731,7 @@
         <v>1500</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.5847186786903008</v>
+        <v>0.5713636856119283</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>44</v>
@@ -5761,7 +5761,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.6597539553864471</v>
+        <v>0.6446851542197896</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>43</v>
@@ -5791,7 +5791,7 @@
         <v>5008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.776187577069709</v>
+        <v>1.735619396742736</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>47.4</v>
@@ -5821,7 +5821,7 @@
         <v>2004</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.813064243032013</v>
+        <v>0.7944938300561757</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>43</v>
@@ -5851,7 +5851,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3877861904584337</v>
+        <v>0.3789291416275995</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>44.8</v>
@@ -5881,7 +5881,7 @@
         <v>2004</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>45</v>
@@ -5911,7 +5911,7 @@
         <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3061862178478973</v>
+        <v>0.2991929149672524</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>44.7</v>
@@ -5941,7 +5941,7 @@
         <v>5028</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.7927799190191437</v>
+        <v>0.7746728006440504</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>46.6</v>
@@ -5971,7 +5971,7 @@
         <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.1603335132203894</v>
+        <v>0.1566714907173875</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>46.1</v>
@@ -6001,7 +6001,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.3621789459414829</v>
+        <v>0.3539067673837278</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>44</v>
@@ -6031,7 +6031,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.2128793508007572</v>
+        <v>0.2080171797087706</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>42</v>
@@ -6061,7 +6061,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.1896539407469422</v>
+        <v>0.1853222387537125</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>43</v>
@@ -6091,7 +6091,7 @@
         <v>1500</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.0697892151246283</v>
+        <v>0.0681952272482326</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>45</v>
@@ -6121,7 +6121,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>42.8</v>
@@ -6151,7 +6151,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.05831456197105047</v>
+        <v>0.05698265553488854</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>41.8</v>
@@ -6181,7 +6181,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.09704344573736196</v>
+        <v>0.09482697037347115</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>46</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -253,12 +253,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$C$6:$C$24</f>
+              <f>'Evolução 1º Turno'!$C$6:$C$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$D$6:$D$24</f>
+              <f>'Evolução 1º Turno'!$D$6:$D$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -319,12 +319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$E$6:$E$24</f>
+              <f>'Evolução 1º Turno'!$E$6:$E$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -352,12 +352,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$F$6:$F$24</f>
+              <f>'Evolução 1º Turno'!$F$6:$F$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$G$6:$G$24</f>
+              <f>'Evolução 1º Turno'!$G$6:$G$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -418,12 +418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$24</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$H$6:$H$24</f>
+              <f>'Evolução 1º Turno'!$H$6:$H$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -538,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$A$6:$A$24</f>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$C$6:$C$24</f>
+              <f>'Evolução Lula vs Flávio'!$C$6:$C$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$A$6:$A$24</f>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$D$6:$D$24</f>
+              <f>'Evolução Lula vs Flávio'!$D$6:$D$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -691,12 +691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$A$6:$A$24</f>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$C$6:$C$24</f>
+              <f>'Evolução Lula vs Zema'!$C$6:$C$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -724,12 +724,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$A$6:$A$24</f>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$D$6:$D$24</f>
+              <f>'Evolução Lula vs Zema'!$D$6:$D$25</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         <v>2000</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.9548416039104165</v>
+        <v>0.9330329915368074</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>0.4</v>
@@ -2133,7 +2133,7 @@
         <v>2000</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.9548416039104165</v>
+        <v>0.9330329915368074</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>1.6</v>
@@ -2193,7 +2193,7 @@
         <v>5032</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0.2</v>
@@ -2253,7 +2253,7 @@
         <v>5032</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E29" s="10" t="n">
         <v/>
@@ -2313,7 +2313,7 @@
         <v>5032</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1.2</v>
@@ -2373,7 +2373,7 @@
         <v>5032</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.5</v>
@@ -2433,7 +2433,7 @@
         <v>5032</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -2493,7 +2493,7 @@
         <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1.626128486064026</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -2553,7 +2553,7 @@
         <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>1.626128486064026</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -2613,7 +2613,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.7755723809168673</v>
+        <v>0.7578582832551991</v>
       </c>
       <c r="E35" s="10" t="n">
         <v/>
@@ -2673,7 +2673,7 @@
         <v>2000</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.7755723809168673</v>
+        <v>0.7578582832551991</v>
       </c>
       <c r="E36" s="10" t="n">
         <v/>
@@ -2733,7 +2733,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.517231525975538</v>
+        <v>1.482577910029699</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1500</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.5713636856119283</v>
+        <v>0.5583137209970264</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.8</v>
@@ -2853,7 +2853,7 @@
         <v>2000</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.6299605249474366</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -2913,7 +2913,7 @@
         <v>5008</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1.735619396742736</v>
+        <v>1.695977794934997</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0.3</v>
@@ -2973,7 +2973,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.3789291416275995</v>
+        <v>0.3702743880716411</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0.3</v>
@@ -3093,7 +3093,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.7243578918829656</v>
+        <v>0.7078135347674557</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>1500</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.2991929149672524</v>
+        <v>0.2923593393451504</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0.6</v>
@@ -3213,7 +3213,7 @@
         <v>2080</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.1464308831840453</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0.2</v>
@@ -3273,7 +3273,7 @@
         <v>2080</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.1464308831840453</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>1.1</v>
@@ -3333,7 +3333,7 @@
         <v>5028</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.7746728006440504</v>
+        <v>0.7569792494242092</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0.6</v>
@@ -3393,7 +3393,7 @@
         <v>1500</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.1566714907173875</v>
+        <v>0.1530931089239486</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0.8</v>
@@ -3453,7 +3453,7 @@
         <v>2004</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.3539067673837278</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>2004</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.3226647586766863</v>
+        <v>0.3152950854033543</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>2</v>
@@ -3573,7 +3573,7 @@
         <v>2080</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.06831242249529332</v>
+        <v>0.06675216460916768</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0.4</v>
@@ -3633,7 +3633,7 @@
         <v>2080</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.06831242249529332</v>
+        <v>0.06675216460916768</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0.2</v>
@@ -3693,7 +3693,7 @@
         <v>4986</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.413399373667485</v>
+        <v>0.4039573189236568</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>1.1</v>
@@ -3753,7 +3753,7 @@
         <v>5020</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.4148064834228057</v>
+        <v>0.4053322902477495</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0.5</v>
@@ -3813,7 +3813,7 @@
         <v>2004</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.2080171797087706</v>
+        <v>0.2032660607580033</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>2004</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.1853222387537125</v>
+        <v>0.1810894729707414</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1</v>
@@ -3933,7 +3933,7 @@
         <v>1500</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.0681952272482326</v>
+        <v>0.06663764610524919</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.5</v>
@@ -3993,7 +3993,7 @@
         <v>2080</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.03577159929748013</v>
+        <v>0.03495457484036817</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1.1</v>
@@ -4053,7 +4053,7 @@
         <v>2080</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.03577159929748013</v>
+        <v>0.03495457484036817</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.3</v>
@@ -4113,7 +4113,7 @@
         <v>5418</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.1919603424200394</v>
+        <v>0.1875759621397927</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>1</v>
@@ -4173,7 +4173,7 @@
         <v>2000</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0.6</v>
@@ -4233,7 +4233,7 @@
         <v>2000</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0.4</v>
@@ -4293,7 +4293,7 @@
         <v>2000</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.04847327380730419</v>
+        <v>0.04736614270344996</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0.2</v>
@@ -4353,7 +4353,7 @@
         <v>2004</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.09482697037347115</v>
+        <v>0.09266111937685623</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>2</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
         <v>2000</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.9548416039104165</v>
+        <v>0.9330329915368074</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>42.2</v>
@@ -4607,7 +4607,7 @@
         <v>5032</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>41.8</v>
@@ -4637,7 +4637,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.626128486064026</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>45</v>
@@ -4667,7 +4667,7 @@
         <v>2000</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7755723809168673</v>
+        <v>0.7578582832551991</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>50</v>
@@ -4697,7 +4697,7 @@
         <v>2004</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.517231525975538</v>
+        <v>1.482577910029699</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>41</v>
@@ -4727,7 +4727,7 @@
         <v>1500</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.5713636856119283</v>
+        <v>0.5583137209970264</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>45.3</v>
@@ -4757,7 +4757,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.6299605249474366</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>44</v>
@@ -4787,7 +4787,7 @@
         <v>5008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.735619396742736</v>
+        <v>1.695977794934997</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>47.8</v>
@@ -4817,7 +4817,7 @@
         <v>2004</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>42</v>
@@ -4847,7 +4847,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3789291416275995</v>
+        <v>0.3702743880716411</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>48</v>
@@ -4877,7 +4877,7 @@
         <v>2004</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7243578918829656</v>
+        <v>0.7078135347674557</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>46</v>
@@ -4907,7 +4907,7 @@
         <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.2991929149672524</v>
+        <v>0.2923593393451504</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>45.8</v>
@@ -4937,7 +4937,7 @@
         <v>2080</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.1464308831840453</v>
+        <v>0.1430863971899205</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>45.2</v>
@@ -4967,7 +4967,7 @@
         <v>5028</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.7746728006440504</v>
+        <v>0.7569792494242092</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>47.6</v>
@@ -4997,7 +4997,7 @@
         <v>1500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.1566714907173875</v>
+        <v>0.1530931089239486</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>45.3</v>
@@ -5027,7 +5027,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3539067673837278</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>41</v>
@@ -5057,7 +5057,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.3226647586766863</v>
+        <v>0.3152950854033543</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>43</v>
@@ -5087,7 +5087,7 @@
         <v>2080</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.06831242249529332</v>
+        <v>0.06675216460916768</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>44.4</v>
@@ -5117,7 +5117,7 @@
         <v>4986</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.413399373667485</v>
+        <v>0.4039573189236568</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>46.3</v>
@@ -5147,7 +5147,7 @@
         <v>5020</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.4148064834228057</v>
+        <v>0.4053322902477495</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>47.5</v>
@@ -5177,7 +5177,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.2080171797087706</v>
+        <v>0.2032660607580033</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>42</v>
@@ -5207,7 +5207,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1853222387537125</v>
+        <v>0.1810894729707414</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>38</v>
@@ -5237,7 +5237,7 @@
         <v>1500</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.0681952272482326</v>
+        <v>0.06663764610524919</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>41.1</v>
@@ -5267,7 +5267,7 @@
         <v>2080</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.03577159929748013</v>
+        <v>0.03495457484036817</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>42.2</v>
@@ -5297,7 +5297,7 @@
         <v>2000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>48.1</v>
@@ -5327,7 +5327,7 @@
         <v>2000</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>42.5</v>
@@ -5357,7 +5357,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.04847327380730419</v>
+        <v>0.04736614270344996</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>36</v>
@@ -5387,7 +5387,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.09482697037347115</v>
+        <v>0.09266111937685623</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>38</v>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
         <v>2000</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.9548416039104165</v>
+        <v>0.9330329915368074</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>48.3</v>
@@ -5611,7 +5611,7 @@
         <v>5032</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2.826269996568619</v>
+        <v>2.761717900633648</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>47.8</v>
@@ -5641,7 +5641,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.626128486064026</v>
+        <v>1.588987660112351</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>46</v>
@@ -5671,7 +5671,7 @@
         <v>2000</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.7755723809168673</v>
+        <v>0.7578582832551991</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>43</v>
@@ -5701,7 +5701,7 @@
         <v>2004</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.517231525975538</v>
+        <v>1.482577910029699</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>44</v>
@@ -5731,7 +5731,7 @@
         <v>1500</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.5713636856119283</v>
+        <v>0.5583137209970264</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>44</v>
@@ -5761,7 +5761,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.6299605249474366</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>43</v>
@@ -5791,7 +5791,7 @@
         <v>5008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.735619396742736</v>
+        <v>1.695977794934997</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>47.4</v>
@@ -5821,7 +5821,7 @@
         <v>2004</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.7944938300561757</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>43</v>
@@ -5851,7 +5851,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.3789291416275995</v>
+        <v>0.3702743880716411</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>44.8</v>
@@ -5881,7 +5881,7 @@
         <v>2004</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7243578918829656</v>
+        <v>0.7078135347674557</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>45</v>
@@ -5911,7 +5911,7 @@
         <v>1500</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.2991929149672524</v>
+        <v>0.2923593393451504</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>44.7</v>
@@ -5941,7 +5941,7 @@
         <v>5028</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.7746728006440504</v>
+        <v>0.7569792494242092</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>46.6</v>
@@ -5971,7 +5971,7 @@
         <v>1500</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.1566714907173875</v>
+        <v>0.1530931089239486</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>46.1</v>
@@ -6001,7 +6001,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.3539067673837278</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>44</v>
@@ -6031,7 +6031,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.2080171797087706</v>
+        <v>0.2032660607580033</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>42</v>
@@ -6061,7 +6061,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.1853222387537125</v>
+        <v>0.1810894729707414</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>43</v>
@@ -6091,7 +6091,7 @@
         <v>1500</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.0681952272482326</v>
+        <v>0.06663764610524919</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>45</v>
@@ -6121,7 +6121,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>42.8</v>
@@ -6151,7 +6151,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.05698265553488854</v>
+        <v>0.05568116988377122</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>41.8</v>
@@ -6181,7 +6181,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.09482697037347115</v>
+        <v>0.09266111937685623</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>46</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6866,6 +6866,34 @@
         <v>2.48</v>
       </c>
       <c r="H24" s="12" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>1.44</v>
       </c>
     </row>
@@ -6884,7 +6912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6920,12 +6948,12 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
           <t>Flávio</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Lula</t>
         </is>
       </c>
     </row>
@@ -6939,10 +6967,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>38</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6955,10 +6983,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>37.32</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>44.74</v>
       </c>
     </row>
     <row r="8">
@@ -6971,10 +6999,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>40.86</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>43.28</v>
       </c>
     </row>
     <row r="9">
@@ -6987,10 +7015,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>41.02</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>43.47</v>
       </c>
     </row>
     <row r="10">
@@ -7003,10 +7031,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>41.04</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>43.91</v>
       </c>
     </row>
     <row r="11">
@@ -7019,10 +7047,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>41.31</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>42.11</v>
       </c>
     </row>
     <row r="12">
@@ -7035,10 +7063,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>40.4</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>42.26</v>
       </c>
     </row>
     <row r="13">
@@ -7051,10 +7079,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>44.52</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>44.64</v>
       </c>
     </row>
     <row r="14">
@@ -7067,10 +7095,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>44.36</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>44.87</v>
       </c>
     </row>
     <row r="15">
@@ -7083,10 +7111,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>44.43</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>44.54</v>
       </c>
     </row>
     <row r="16">
@@ -7099,10 +7127,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>44.72</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>45.09</v>
       </c>
     </row>
     <row r="17">
@@ -7115,10 +7143,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>45.32</v>
       </c>
     </row>
     <row r="18">
@@ -7131,10 +7159,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="12" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>45.47</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>45.05</v>
       </c>
     </row>
     <row r="19">
@@ -7147,10 +7175,10 @@
         <v>5</v>
       </c>
       <c r="C19" s="12" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>46.78</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>45.15</v>
       </c>
     </row>
     <row r="20">
@@ -7163,10 +7191,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="12" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>45.56</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>43.84</v>
       </c>
     </row>
     <row r="21">
@@ -7179,10 +7207,10 @@
         <v>5</v>
       </c>
       <c r="C21" s="12" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>44.89</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>42.92</v>
       </c>
     </row>
     <row r="22">
@@ -7195,10 +7223,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>46.16</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>44.9</v>
       </c>
     </row>
     <row r="23">
@@ -7211,10 +7239,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>45.76</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>44.51</v>
       </c>
     </row>
     <row r="24">
@@ -7227,10 +7255,26 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>45.32</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>44.53</v>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>44.11</v>
       </c>
     </row>
   </sheetData>
@@ -7248,7 +7292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7595,6 +7639,22 @@
       </c>
       <c r="D24" s="12" t="n">
         <v>41.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>39.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="8">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="9">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="11">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="12">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>42.17</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="13">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>4.29</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="14">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="15">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="18">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>6.3</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="19">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3.9</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="21">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>43.93</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="23">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45.79</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="24">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="25">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="27">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46.06</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="30">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>39.13</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="31">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>12.42</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="32">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3.66</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="34">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="10">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="11">
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="12">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="13">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>42.17</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="15">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4.29</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="16">
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="17">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="19">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="20">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6.3</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3.9</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="24">
@@ -2236,7 +2236,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1.825267511281646</v>
+        <v>0.9126337556408229</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>1</v>
@@ -2416,7 +2416,7 @@
         <v>5032</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -2476,7 +2476,7 @@
         <v>5032</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1.2</v>
@@ -2536,7 +2536,7 @@
         <v>5032</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0.5</v>
@@ -2596,7 +2596,7 @@
         <v>5032</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -2656,7 +2656,7 @@
         <v>5032</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>0.2</v>
@@ -2716,7 +2716,7 @@
         <v>5032</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.2</v>
@@ -2776,7 +2776,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -2836,7 +2836,7 @@
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E38" s="10" t="n">
         <v/>
@@ -2896,7 +2896,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1.448715783765931</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>5008</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1.657241608563864</v>
+        <v>0.828620804281932</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0.3</v>
@@ -3496,7 +3496,7 @@
         <v>2004</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.7586157629877688</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>2004</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>1</v>
@@ -3736,7 +3736,7 @@
         <v>2004</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
         <v>2080</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.1398182993614727</v>
+        <v>0.2796365987229454</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1.1</v>
@@ -3976,7 +3976,7 @@
         <v>2080</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.1398182993614727</v>
+        <v>0.2796365987229454</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0.2</v>
@@ -4036,7 +4036,7 @@
         <v>2080</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.1398182993614727</v>
+        <v>0.2796365987229454</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0.2</v>
@@ -4156,7 +4156,7 @@
         <v>5028</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.7396898194727396</v>
+        <v>0.3698449097363698</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0.6</v>
@@ -4276,7 +4276,7 @@
         <v>2004</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.3379249054034293</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>1</v>
@@ -4336,7 +4336,7 @@
         <v>2004</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.3080937357002146</v>
+        <v>0.1540468678501073</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>2</v>
@@ -4396,7 +4396,7 @@
         <v>2004</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.3080937357002146</v>
+        <v>0.1540468678501073</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>2</v>
@@ -4456,7 +4456,7 @@
         <v>2080</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>0.4</v>
@@ -4516,7 +4516,7 @@
         <v>2080</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>0.2</v>
@@ -4576,7 +4576,7 @@
         <v>2080</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0.2</v>
@@ -4636,7 +4636,7 @@
         <v>5020</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.3960744879438716</v>
+        <v>0.1980372439719358</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0.5</v>
@@ -4696,7 +4696,7 @@
         <v>4986</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.3947309210082231</v>
+        <v>0.1973654605041116</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>1.1</v>
@@ -4756,7 +4756,7 @@
         <v>2004</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.1986234575140439</v>
+        <v>0.09931172875702197</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
         <v>2004</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.1769533836918639</v>
+        <v>0.08847669184593196</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>1</v>
@@ -4936,7 +4936,7 @@
         <v>2080</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.03415621124764666</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E73" s="10" t="n">
         <v>1.1</v>
@@ -4996,7 +4996,7 @@
         <v>2080</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.03415621124764666</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0.3</v>
@@ -5056,7 +5056,7 @@
         <v>2080</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.03415621124764666</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E75" s="10" t="n">
         <v>0.3</v>
@@ -5116,7 +5116,7 @@
         <v>5418</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.1832917212435432</v>
+        <v>0.09164586062177159</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>1</v>
@@ -5416,7 +5416,7 @@
         <v>2004</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.09054473648537072</v>
+        <v>0.04527236824268536</v>
       </c>
       <c r="E81" s="10" t="n">
         <v>2</v>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>43.93</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="9">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45.79</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="11">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
@@ -5700,7 +5700,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.825267511281646</v>
+        <v>0.9126337556408229</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>43</v>
@@ -5730,7 +5730,7 @@
         <v>5032</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>41.8</v>
@@ -5760,7 +5760,7 @@
         <v>5032</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>41.8</v>
@@ -5790,7 +5790,7 @@
         <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>45</v>
@@ -5850,7 +5850,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.448715783765931</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>41</v>
@@ -5940,7 +5940,7 @@
         <v>5008</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1.657241608563864</v>
+        <v>0.828620804281932</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>47.8</v>
@@ -6000,7 +6000,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.7586157629877688</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>42</v>
@@ -6090,7 +6090,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>46</v>
@@ -6180,7 +6180,7 @@
         <v>2080</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.1398182993614727</v>
+        <v>0.2796365987229454</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>45.2</v>
@@ -6240,7 +6240,7 @@
         <v>5028</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.7396898194727396</v>
+        <v>0.3698449097363698</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>47.6</v>
@@ -6300,7 +6300,7 @@
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.3379249054034293</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>41</v>
@@ -6330,7 +6330,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.3080937357002146</v>
+        <v>0.1540468678501073</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>43</v>
@@ -6360,7 +6360,7 @@
         <v>2080</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>44.4</v>
@@ -6390,7 +6390,7 @@
         <v>5020</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.3960744879438716</v>
+        <v>0.1980372439719358</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>47.5</v>
@@ -6420,7 +6420,7 @@
         <v>4986</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.3947309210082231</v>
+        <v>0.1973654605041116</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>46.3</v>
@@ -6450,7 +6450,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.1986234575140439</v>
+        <v>0.09931172875702197</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>42</v>
@@ -6480,7 +6480,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.1769533836918639</v>
+        <v>0.08847669184593196</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>38</v>
@@ -6540,7 +6540,7 @@
         <v>2080</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.03415621124764666</v>
+        <v>0.06831242249529332</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>42.2</v>
@@ -6660,7 +6660,7 @@
         <v>2004</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.09054473648537072</v>
+        <v>0.04527236824268536</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>38</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>46.06</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="10">
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>39.13</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="11">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>12.42</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="12">
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3.66</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="15">
@@ -6903,7 +6903,7 @@
         <v>2004</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1.825267511281646</v>
+        <v>0.9126337556408229</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
@@ -6936,7 +6936,7 @@
         <v>5032</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2.698640176607467</v>
+        <v>1.349320088303734</v>
       </c>
       <c r="E19" s="10" t="n">
         <v/>
@@ -6969,7 +6969,7 @@
         <v>2004</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.552695131797792</v>
+        <v>0.7763475658988959</v>
       </c>
       <c r="E20" s="10" t="n">
         <v/>
@@ -7035,7 +7035,7 @@
         <v>2004</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1.448715783765931</v>
+        <v>0.7243578918829656</v>
       </c>
       <c r="E22" s="10" t="n">
         <v/>
@@ -7134,7 +7134,7 @@
         <v>5008</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.657241608563864</v>
+        <v>0.828620804281932</v>
       </c>
       <c r="E25" s="10" t="n">
         <v/>
@@ -7167,7 +7167,7 @@
         <v>2004</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7586157629877688</v>
+        <v>0.3793078814938844</v>
       </c>
       <c r="E26" s="10" t="n">
         <v/>
@@ -7233,7 +7233,7 @@
         <v>2004</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>0.3458235256453495</v>
       </c>
       <c r="E28" s="10" t="n">
         <v/>
@@ -7299,7 +7299,7 @@
         <v>5028</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.7396898194727396</v>
+        <v>0.3698449097363698</v>
       </c>
       <c r="E30" s="10" t="n">
         <v/>
@@ -7365,7 +7365,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.3379249054034293</v>
+        <v>0.1689624527017146</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -7398,7 +7398,7 @@
         <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.1986234575140439</v>
+        <v>0.09931172875702197</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -7431,7 +7431,7 @@
         <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.1769533836918639</v>
+        <v>0.08847669184593196</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -7563,7 +7563,7 @@
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.09054473648537072</v>
+        <v>0.04527236824268536</v>
       </c>
       <c r="E38" s="10" t="n">
         <v/>
@@ -7728,12 +7728,12 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
+          <t>Caiado</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
           <t>Renan</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Caiado</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -7760,10 +7760,10 @@
       <c r="E6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
@@ -7776,19 +7776,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>30.51</v>
+        <v>29.78</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1.56</v>
+        <v>5.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>5.5</v>
+        <v>1.34</v>
       </c>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -7802,19 +7802,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>42.26</v>
+        <v>40.95</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>33.47</v>
+        <v>33.26</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>2.37</v>
+        <v>4.38</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>4.36</v>
+        <v>2.15</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>1.2</v>
@@ -7830,22 +7830,22 @@
         <v>9</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41.83</v>
+        <v>40.52</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>33.41</v>
+        <v>33.2</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>4.22</v>
+        <v>1.91</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10">
@@ -7858,22 +7858,22 @@
         <v>10</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>41.59</v>
+        <v>40.41</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>33.37</v>
+        <v>33.18</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2.07</v>
+        <v>4.22</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>4.32</v>
+        <v>1.78</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="11">
@@ -7886,22 +7886,22 @@
         <v>10</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.64</v>
+        <v>40.05</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.45</v>
+        <v>33.44</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>2.12</v>
+        <v>4.22</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4.35</v>
+        <v>1.89</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -7914,22 +7914,22 @@
         <v>6</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>38.85</v>
+        <v>39.21</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.69</v>
+        <v>32.85</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>1.75</v>
+        <v>4.24</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>4.44</v>
+        <v>1.59</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="13">
@@ -7942,22 +7942,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>42.44</v>
+        <v>41.75</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>36.12</v>
+        <v>35.67</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>2.99</v>
+        <v>4.17</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="14">
@@ -7970,22 +7970,22 @@
         <v>9</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>41.47</v>
+        <v>41.2</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>35.25</v>
+        <v>35.17</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.07</v>
+        <v>3.83</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>3.07</v>
+        <v>4.08</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.25</v>
+        <v>2.68</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -7998,22 +7998,22 @@
         <v>10</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>41.22</v>
+        <v>40.99</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.01</v>
+        <v>34.98</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>2.75</v>
+        <v>4.22</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>4.31</v>
+        <v>2.42</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -8026,22 +8026,22 @@
         <v>9</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>41.52</v>
+        <v>41.2</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>35.2</v>
+        <v>35.12</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.9</v>
+        <v>3.79</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>2.82</v>
+        <v>4.16</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="17">
@@ -8054,19 +8054,19 @@
         <v>6</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>41.76</v>
+        <v>41.6</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>36.1</v>
+        <v>36.24</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>4.13</v>
+        <v>3.19</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -8080,22 +8080,22 @@
         <v>7</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>42.48</v>
+        <v>41.75</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>37.08</v>
+        <v>36.68</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2.81</v>
+        <v>3.87</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3.98</v>
+        <v>2.26</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="19">
@@ -8108,22 +8108,22 @@
         <v>11</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>40.44</v>
+        <v>40.21</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>36.19</v>
+        <v>35.98</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>2.47</v>
+        <v>4.14</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>4.34</v>
+        <v>2.19</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="20">
@@ -8136,22 +8136,22 @@
         <v>12</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>39.9</v>
+        <v>39.89</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>35.53</v>
+        <v>35.59</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>2.39</v>
+        <v>4.33</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4.6</v>
+        <v>2.17</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="21">
@@ -8164,22 +8164,22 @@
         <v>12</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>39.06</v>
+        <v>39.47</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>34.85</v>
+        <v>35.22</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.36</v>
+        <v>3.18</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>2.14</v>
+        <v>4.34</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>4.68</v>
+        <v>2.07</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -8192,22 +8192,22 @@
         <v>9</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>41.06</v>
+        <v>40.62</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>36.05</v>
+        <v>35.85</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>4.36</v>
+        <v>2.87</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
@@ -8220,22 +8220,22 @@
         <v>9</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>41.51</v>
+        <v>40.98</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>35.92</v>
+        <v>35.57</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>3.19</v>
+        <v>4.77</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>4.64</v>
+        <v>2.92</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24">
@@ -8248,22 +8248,22 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>39.4</v>
+        <v>39.11</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.66</v>
+        <v>35.68</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>2.49</v>
+        <v>3.62</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="25">
@@ -8276,22 +8276,22 @@
         <v>23</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>42.62</v>
+        <v>41.95</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>33.67</v>
+        <v>34.15</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>5.99</v>
+        <v>5.79</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>4.66</v>
+        <v>4.24</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -8380,10 +8380,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>44.74</v>
+        <v>45.11</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>37.32</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="8">
@@ -8396,10 +8396,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>43.28</v>
+        <v>43.12</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>40.86</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9">
@@ -8412,10 +8412,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>43.47</v>
+        <v>43.55</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>41.02</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="10">
@@ -8428,10 +8428,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>43.91</v>
+        <v>43.99</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>41.04</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="11">
@@ -8444,10 +8444,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>42.11</v>
+        <v>42.62</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>41.31</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="12">
@@ -8460,10 +8460,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>42.26</v>
+        <v>43.02</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>40.4</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="13">
@@ -8476,10 +8476,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.64</v>
+        <v>44.58</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>44.52</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="14">
@@ -8492,7 +8492,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>44.87</v>
+        <v>44.74</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>44.36</v>
@@ -8508,10 +8508,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.54</v>
+        <v>44.67</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.43</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="16">
@@ -8524,10 +8524,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>45.09</v>
+        <v>45.14</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>44.72</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="17">
@@ -8540,10 +8540,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.43</v>
+        <v>45.63</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>45.15</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="18">
@@ -8556,10 +8556,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.2</v>
+        <v>45.24</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>45.56</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="19">
@@ -8572,10 +8572,10 @@
         <v>8</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>44.78</v>
+        <v>44.45</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>45.48</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="20">
@@ -8588,10 +8588,10 @@
         <v>9</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>43.84</v>
+        <v>43.87</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>44.8</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="21">
@@ -8604,10 +8604,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>43.59</v>
+        <v>43.9</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>44.26</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="22">
@@ -8620,10 +8620,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>44.77</v>
+        <v>44.61</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>45.34</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="23">
@@ -8636,10 +8636,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.7</v>
+        <v>44.55</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>45.25</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="24">
@@ -8652,10 +8652,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.64</v>
+        <v>44.48</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>45.3</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="25">
@@ -8668,10 +8668,10 @@
         <v>12</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>46.47</v>
+        <v>46.12</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>43.79</v>
+        <v>44.17</v>
       </c>
     </row>
   </sheetData>
@@ -8784,10 +8784,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>43.98</v>
+        <v>43.39</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>35.2</v>
+        <v>36.44</v>
       </c>
       <c r="E8" s="5" t="n"/>
     </row>
@@ -8801,10 +8801,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>43.98</v>
+        <v>43.39</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>35.2</v>
+        <v>36.44</v>
       </c>
       <c r="E9" s="5" t="n"/>
     </row>
@@ -8818,10 +8818,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>44.23</v>
+        <v>43.87</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>35.03</v>
+        <v>35.86</v>
       </c>
       <c r="E10" s="5" t="n"/>
     </row>
@@ -8835,10 +8835,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>42.74</v>
+        <v>42.87</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>34.71</v>
+        <v>35.29</v>
       </c>
       <c r="E11" s="5" t="n"/>
     </row>
@@ -8852,10 +8852,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>42.84</v>
+        <v>43.12</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>33.72</v>
+        <v>33.82</v>
       </c>
       <c r="E12" s="5" t="n"/>
     </row>
@@ -8869,10 +8869,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>42.84</v>
+        <v>43.12</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>33.72</v>
+        <v>33.82</v>
       </c>
       <c r="E13" s="5" t="n"/>
     </row>
@@ -8903,10 +8903,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>43.88</v>
+        <v>44.28</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.16</v>
+        <v>35.67</v>
       </c>
       <c r="E15" s="5" t="n"/>
     </row>
@@ -8920,10 +8920,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.64</v>
+        <v>44.99</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>35.23</v>
+        <v>35.88</v>
       </c>
       <c r="E16" s="5" t="n"/>
     </row>
@@ -8937,10 +8937,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.82</v>
+        <v>45.85</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>40.33</v>
+        <v>40.08</v>
       </c>
       <c r="E17" s="5" t="n"/>
     </row>
@@ -8954,10 +8954,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.82</v>
+        <v>45.85</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>40.33</v>
+        <v>40.08</v>
       </c>
       <c r="E18" s="5" t="n"/>
     </row>
@@ -8971,10 +8971,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>45.49</v>
+        <v>45.32</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>41.46</v>
+        <v>40.71</v>
       </c>
       <c r="E19" s="5" t="n"/>
     </row>
@@ -8988,10 +8988,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>44.83</v>
+        <v>44.81</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>40</v>
+        <v>39.68</v>
       </c>
       <c r="E20" s="5" t="n"/>
     </row>
@@ -9005,10 +9005,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>44.2</v>
+        <v>44.33</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>38.69</v>
+        <v>38.6</v>
       </c>
       <c r="E21" s="5" t="n"/>
     </row>
@@ -9022,10 +9022,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.61</v>
+        <v>45.49</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>42.14</v>
+        <v>41.57</v>
       </c>
       <c r="E22" s="5" t="n"/>
     </row>
@@ -9039,10 +9039,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>45.16</v>
+        <v>44.77</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>41.95</v>
+        <v>41.4</v>
       </c>
       <c r="E23" s="5" t="n"/>
     </row>
@@ -9056,10 +9056,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.13</v>
+        <v>44.71</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="E24" s="5" t="n"/>
     </row>
@@ -9073,10 +9073,10 @@
         <v>9</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>46.56</v>
+        <v>46.25</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>39.35</v>
+        <v>39.31</v>
       </c>
       <c r="E25" s="5" t="n"/>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1522,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1552,7 +1552,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>AtlasIntel</t>
+          <t>100%Cidades/Futura</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
@@ -1562,7 +1562,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Datafolha</t>
+          <t>AtlasIntel</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
@@ -1572,7 +1572,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Futura</t>
+          <t>Datafolha</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -1582,7 +1582,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Genial/Quaest</t>
+          <t>Futura Inteligência</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -1592,7 +1592,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ipec</t>
+          <t>Gerp</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
@@ -1602,7 +1602,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Ipespe</t>
+          <t>Instituto França</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -1612,7 +1612,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Paraná Pesquisas</t>
+          <t>Instituto Seta</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -1622,7 +1622,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -1632,7 +1632,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Meio/Ideia</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -1642,7 +1642,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Real Time Big Data</t>
+          <t>Nexus/FSB</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -1652,129 +1652,179 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Veredictum</t>
+          <t>Paraná Pesquisas</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Quaest</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Veritá</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Parâmetros da ponderação</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Half-life (dias)</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B24" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Amostra de referência</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B25" t="n">
         <v>2000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Janela de pesquisas (dias)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Cenários ativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Cenário</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Turno</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Candidatos exigidos</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Janela de pesquisas (dias)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Cenários ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Turno</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Candidatos exigidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>1º Turno</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>(todos)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Lula vs Flávio</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B32" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Lula, Flávio</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Lula vs Zema</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B33" t="n">
         <v>2</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Lula, Zema</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Flávio vs Zema</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B34" t="n">
         <v>2</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Flávio, Zema</t>
         </is>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="9">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34.55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>41.34</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="13">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="14">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="15">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7.65</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="18">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>6.38</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="19">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="21">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>44.37</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="23">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="24">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>8.789999999999999</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="27">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46.11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>38.98</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="31">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>12.15</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="32">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="34">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="9">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="11">
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="12">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34.55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>41.34</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="15">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="16">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="17">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="18">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="19">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7.65</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="20">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6.38</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="21">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="24">
@@ -2166,7 +2166,7 @@
         <v>2045</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.9434712242407221</v>
+        <v>0.6604298569685054</v>
       </c>
       <c r="E26" s="10" t="n">
         <v/>
@@ -2226,7 +2226,7 @@
         <v>2045</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.9434712242407221</v>
+        <v>0.6604298569685054</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -2286,7 +2286,7 @@
         <v>2000</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.8908987181403393</v>
+        <v>0.6236291026982375</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>2000</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.8705505632961241</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.4</v>
@@ -2406,7 +2406,7 @@
         <v>2000</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.8705505632961241</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1.6</v>
@@ -2466,7 +2466,7 @@
         <v>2000</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.8705505632961241</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.4</v>
@@ -2526,7 +2526,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>2.614262037056612</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1</v>
@@ -2586,7 +2586,7 @@
         <v>5032</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0.2</v>
@@ -2646,7 +2646,7 @@
         <v>5032</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -2706,7 +2706,7 @@
         <v>5032</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>1.2</v>
@@ -2766,7 +2766,7 @@
         <v>5032</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.5</v>
@@ -2826,7 +2826,7 @@
         <v>5032</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -2886,7 +2886,7 @@
         <v>5032</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.2</v>
@@ -2946,7 +2946,7 @@
         <v>2004</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>2.223866865044549</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -3006,7 +3006,7 @@
         <v>2004</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>2.223866865044549</v>
       </c>
       <c r="E40" s="10" t="n">
         <v/>
@@ -3066,7 +3066,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>2.223866865044549</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.4949747468305833</v>
       </c>
       <c r="E42" s="10" t="n">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>2000</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.4949747468305833</v>
       </c>
       <c r="E43" s="10" t="n">
         <v/>
@@ -3246,7 +3246,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>2000</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0.3</v>
@@ -3486,7 +3486,7 @@
         <v>2000</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.5877739531418044</v>
+        <v>1.175547906283609</v>
       </c>
       <c r="E48" s="10" t="n">
         <v/>
@@ -3546,7 +3546,7 @@
         <v>2000</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.5877739531418044</v>
+        <v>1.175547906283609</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>1</v>
@@ -3606,7 +3606,7 @@
         <v>5008</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.7912016177940993</v>
+        <v>1.582403235588199</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0.3</v>
@@ -3666,7 +3666,7 @@
         <v>2028</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.4919881569624319</v>
+        <v>0.3443917098737023</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
@@ -3726,7 +3726,7 @@
         <v>2004</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.3621789459414828</v>
+        <v>1.086536837824448</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>2000</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.345478219991944</v>
+        <v>0.2418347539943608</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0.3</v>
@@ -3906,7 +3906,7 @@
         <v>2004</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.3302066898971606</v>
+        <v>0.9906200696914819</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>2004</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.3302066898971606</v>
+        <v>0.9906200696914819</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>1030</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.226040862147149</v>
+        <v>0.1582286035030043</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0.4</v>
@@ -4146,7 +4146,7 @@
         <v>2080</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.2670086584366707</v>
+        <v>0.5340173168733414</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.2</v>
@@ -4206,7 +4206,7 @@
         <v>2080</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.2670086584366707</v>
+        <v>0.5340173168733414</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0.2</v>
@@ -4266,7 +4266,7 @@
         <v>2080</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.2670086584366707</v>
+        <v>0.5340173168733414</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>1.1</v>
@@ -4326,7 +4326,7 @@
         <v>2000</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.2558434729991938</v>
+        <v>0.1790904310994356</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>2000</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.2332582478842019</v>
+        <v>0.1632807735189413</v>
       </c>
       <c r="E63" s="10" t="n">
         <v/>
@@ -4446,7 +4446,7 @@
         <v>2000</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.2332582478842019</v>
+        <v>0.1632807735189413</v>
       </c>
       <c r="E64" s="10" t="n">
         <v/>
@@ -4506,7 +4506,7 @@
         <v>5028</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.3531433068107785</v>
+        <v>0.7062866136215571</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>0.6</v>
@@ -4626,7 +4626,7 @@
         <v>2004</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.1613323793383432</v>
+        <v>0.4839971380150294</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>1</v>
@@ -4686,7 +4686,7 @@
         <v>2004</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.1470903583753725</v>
+        <v>0.4412710751261174</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>2</v>
@@ -4746,7 +4746,7 @@
         <v>2004</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.1470903583753725</v>
+        <v>0.4412710751261174</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>2</v>
@@ -4806,7 +4806,7 @@
         <v>2000</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.1371031224618283</v>
+        <v>0.2742062449236565</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>2</v>
@@ -4866,7 +4866,7 @@
         <v>2000</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.1371031224618283</v>
+        <v>0.2742062449236565</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>2</v>
@@ -4926,7 +4926,7 @@
         <v>2080</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.1245639436736983</v>
+        <v>0.2491278873473965</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>0.4</v>
@@ -4986,7 +4986,7 @@
         <v>2080</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.1245639436736983</v>
+        <v>0.2491278873473965</v>
       </c>
       <c r="E73" s="10" t="n">
         <v>0.2</v>
@@ -5046,7 +5046,7 @@
         <v>2080</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.1245639436736983</v>
+        <v>0.2491278873473965</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>0.2</v>
@@ -5106,7 +5106,7 @@
         <v>4986</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.1884527528642637</v>
+        <v>0.3769055057285275</v>
       </c>
       <c r="E75" s="10" t="n">
         <v>1.1</v>
@@ -5166,7 +5166,7 @@
         <v>5020</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.1890941996681615</v>
+        <v>0.3781883993363231</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0.5</v>
@@ -5226,7 +5226,7 @@
         <v>4986</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.1884527528642637</v>
+        <v>0.3769055057285275</v>
       </c>
       <c r="E77" s="10" t="n">
         <v>1.1</v>
@@ -5286,7 +5286,7 @@
         <v>2004</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.09482697037347111</v>
+        <v>0.2844809111204133</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>2004</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.08448122635085732</v>
+        <v>0.253443679052572</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>1</v>
@@ -5406,7 +5406,7 @@
         <v>2000</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.08058564427747369</v>
+        <v>0.1611712885549474</v>
       </c>
       <c r="E80" s="10" t="n">
         <v/>
@@ -5466,7 +5466,7 @@
         <v>2000</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.08058564427747369</v>
+        <v>0.1611712885549474</v>
       </c>
       <c r="E81" s="10" t="n">
         <v>3</v>
@@ -5526,7 +5526,7 @@
         <v>2000</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.08058564427747369</v>
+        <v>0.1611712885549474</v>
       </c>
       <c r="E82" s="10" t="n">
         <v>3</v>
@@ -5646,7 +5646,7 @@
         <v>2000</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.07179364718731469</v>
+        <v>0.05025555303112028</v>
       </c>
       <c r="E84" s="10" t="n">
         <v/>
@@ -5706,7 +5706,7 @@
         <v>2080</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E85" s="10" t="n">
         <v>1.1</v>
@@ -5766,7 +5766,7 @@
         <v>2080</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0.3</v>
@@ -5826,7 +5826,7 @@
         <v>2080</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E87" s="10" t="n">
         <v>0.3</v>
@@ -5886,7 +5886,7 @@
         <v>5418</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.08750728054784289</v>
+        <v>0.1750145610956858</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>1</v>
@@ -6066,7 +6066,7 @@
         <v>2000</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.03636665795624697</v>
       </c>
       <c r="E91" s="10" t="n">
         <v>0.4</v>
@@ -6246,7 +6246,7 @@
         <v>2004</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.04322794070566868</v>
+        <v>0.129683822117006</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>2</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>44.37</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="9">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="10">
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8.789999999999999</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
@@ -6470,7 +6470,7 @@
         <v>2045</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.9434712242407221</v>
+        <v>0.6604298569685054</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>43</v>
@@ -6500,7 +6500,7 @@
         <v>2000</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.8908987181403393</v>
+        <v>0.6236291026982375</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>47</v>
@@ -6530,7 +6530,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8705505632961241</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>42.2</v>
@@ -6560,7 +6560,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>2.614262037056612</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>43</v>
@@ -6590,7 +6590,7 @@
         <v>5032</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>41.8</v>
@@ -6620,7 +6620,7 @@
         <v>5032</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>41.8</v>
@@ -6650,7 +6650,7 @@
         <v>2004</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>2.223866865044549</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>45</v>
@@ -6680,7 +6680,7 @@
         <v>2000</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.4949747468305833</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>50</v>
@@ -6710,7 +6710,7 @@
         <v>2004</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>41</v>
@@ -6740,7 +6740,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>46.9</v>
@@ -6770,7 +6770,7 @@
         <v>2000</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.6446851542197896</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>46.9</v>
@@ -6830,7 +6830,7 @@
         <v>2000</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.5877739531418044</v>
+        <v>1.175547906283609</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>44</v>
@@ -6860,7 +6860,7 @@
         <v>5008</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.7912016177940993</v>
+        <v>1.582403235588199</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>47.8</v>
@@ -6890,7 +6890,7 @@
         <v>2028</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.4919881569624319</v>
+        <v>0.3443917098737023</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>45</v>
@@ -6920,7 +6920,7 @@
         <v>2004</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3621789459414828</v>
+        <v>1.086536837824448</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>42</v>
@@ -6980,7 +6980,7 @@
         <v>2000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.345478219991944</v>
+        <v>0.2418347539943608</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>48</v>
@@ -7010,7 +7010,7 @@
         <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.3302066898971606</v>
+        <v>0.9906200696914819</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>46</v>
@@ -7070,7 +7070,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.226040862147149</v>
+        <v>0.1582286035030043</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>41</v>
@@ -7100,7 +7100,7 @@
         <v>2080</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.2670086584366707</v>
+        <v>0.5340173168733414</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>45.2</v>
@@ -7130,7 +7130,7 @@
         <v>2000</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.2558434729991938</v>
+        <v>0.1790904310994356</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>46</v>
@@ -7160,7 +7160,7 @@
         <v>2000</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.2332582478842019</v>
+        <v>0.1632807735189413</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>48</v>
@@ -7190,7 +7190,7 @@
         <v>5028</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.3531433068107785</v>
+        <v>0.7062866136215571</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>47.6</v>
@@ -7250,7 +7250,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.1613323793383432</v>
+        <v>0.4839971380150294</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>41</v>
@@ -7280,7 +7280,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.1470903583753725</v>
+        <v>0.4412710751261174</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>43</v>
@@ -7310,7 +7310,7 @@
         <v>2000</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.1371031224618283</v>
+        <v>0.2742062449236565</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>41</v>
@@ -7340,7 +7340,7 @@
         <v>2080</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.1245639436736983</v>
+        <v>0.2491278873473965</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>44.4</v>
@@ -7370,7 +7370,7 @@
         <v>4986</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.1884527528642637</v>
+        <v>0.3769055057285275</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>46.3</v>
@@ -7400,7 +7400,7 @@
         <v>5020</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.1890941996681615</v>
+        <v>0.3781883993363231</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>47.5</v>
@@ -7430,7 +7430,7 @@
         <v>2004</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.09482697037347111</v>
+        <v>0.2844809111204133</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>42</v>
@@ -7460,7 +7460,7 @@
         <v>2004</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.08448122635085732</v>
+        <v>0.253443679052572</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>38</v>
@@ -7520,7 +7520,7 @@
         <v>2000</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.07179364718731469</v>
+        <v>0.05025555303112028</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>45</v>
@@ -7550,7 +7550,7 @@
         <v>2080</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.06522754306241191</v>
+        <v>0.1304550861248238</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>42.2</v>
@@ -7580,7 +7580,7 @@
         <v>5418</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.08750728054784289</v>
+        <v>0.1750145610956858</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>45</v>
@@ -7700,7 +7700,7 @@
         <v>2004</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.04322794070566868</v>
+        <v>0.129683822117006</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>38</v>
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>46.11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>38.98</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="11">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>12.15</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="12">
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="15">
@@ -7910,7 +7910,7 @@
         <v>2045</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.9434712242407221</v>
+        <v>0.6604298569685054</v>
       </c>
       <c r="E17" s="10" t="n">
         <v/>
@@ -7943,7 +7943,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.8705505632961241</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E18" s="10" t="n">
         <v/>
@@ -7976,7 +7976,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.8714206790188705</v>
+        <v>2.614262037056612</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>5032</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1.288386957304482</v>
+        <v>2.576773914608964</v>
       </c>
       <c r="E20" s="10" t="n">
         <v/>
@@ -8042,7 +8042,7 @@
         <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.7412889550148496</v>
+        <v>2.223866865044549</v>
       </c>
       <c r="E21" s="10" t="n">
         <v/>
@@ -8075,7 +8075,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.7071067811865476</v>
+        <v>0.4949747468305833</v>
       </c>
       <c r="E22" s="10" t="n">
         <v/>
@@ -8108,7 +8108,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.6916470512906989</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="E23" s="10" t="n">
         <v/>
@@ -8174,7 +8174,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.5877739531418044</v>
+        <v>1.175547906283609</v>
       </c>
       <c r="E25" s="10" t="n">
         <v/>
@@ -8207,7 +8207,7 @@
         <v>5008</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.7912016177940993</v>
+        <v>1.582403235588199</v>
       </c>
       <c r="E26" s="10" t="n">
         <v/>
@@ -8240,7 +8240,7 @@
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.3621789459414828</v>
+        <v>1.086536837824448</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -8273,7 +8273,7 @@
         <v>2000</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.345478219991944</v>
+        <v>0.2418347539943608</v>
       </c>
       <c r="E28" s="10" t="n">
         <v/>
@@ -8306,7 +8306,7 @@
         <v>2004</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.3302066898971606</v>
+        <v>0.9906200696914819</v>
       </c>
       <c r="E29" s="10" t="n">
         <v/>
@@ -8372,7 +8372,7 @@
         <v>5028</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3531433068107785</v>
+        <v>0.7062866136215571</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -8438,7 +8438,7 @@
         <v>2004</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.1613323793383432</v>
+        <v>0.4839971380150294</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -8471,7 +8471,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.1371031224618283</v>
+        <v>0.2742062449236565</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -8504,7 +8504,7 @@
         <v>4986</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.1884527528642637</v>
+        <v>0.3769055057285275</v>
       </c>
       <c r="E35" s="10" t="n">
         <v/>
@@ -8537,7 +8537,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.09482697037347111</v>
+        <v>0.2844809111204133</v>
       </c>
       <c r="E36" s="10" t="n">
         <v/>
@@ -8570,7 +8570,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.08448122635085732</v>
+        <v>0.253443679052572</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -8636,7 +8636,7 @@
         <v>5418</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.08750728054784289</v>
+        <v>0.1750145610956858</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -8735,7 +8735,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.04322794070566868</v>
+        <v>0.129683822117006</v>
       </c>
       <c r="E42" s="10" t="n">
         <v/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Cury</t>
+          <t>Samara</t>
         </is>
       </c>
     </row>
@@ -8948,19 +8948,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39.6</v>
+        <v>39.36</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>29.78</v>
+        <v>30.88</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>5.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -8974,23 +8974,21 @@
         <v>7</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>40.86</v>
+        <v>41.93</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>33.26</v>
+        <v>33.32</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>3.98</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>1.2</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -9002,23 +9000,21 @@
         <v>10</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>40.5</v>
+        <v>41.03</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>33.2</v>
+        <v>33.22</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>1.14</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9030,23 +9026,21 @@
         <v>15</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>40.11</v>
+        <v>40.47</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32.83</v>
+        <v>32.65</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3.85</v>
+        <v>3.73</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>1.14</v>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9058,22 +9052,22 @@
         <v>14</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>39.88</v>
+        <v>40.01</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.04</v>
+        <v>32.78</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1.1</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="12">
@@ -9086,22 +9080,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>39.34</v>
+        <v>39.25</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.57</v>
+        <v>32.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>4.24</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -9114,13 +9108,13 @@
         <v>13</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.7</v>
+        <v>41.64</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>35.42</v>
+        <v>35.31</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>4.17</v>
@@ -9129,7 +9123,7 @@
         <v>2.58</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="14">
@@ -9142,22 +9136,22 @@
         <v>15</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>41.15</v>
+        <v>40.89</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>34.73</v>
+        <v>34.52</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>2.63</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="15">
@@ -9170,22 +9164,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>41.18</v>
+        <v>40.91</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>35.07</v>
+        <v>34.76</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2.44</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="16">
@@ -9198,23 +9192,21 @@
         <v>12</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>41.35</v>
+        <v>41.12</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>35.18</v>
+        <v>34.89</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>0.64</v>
-      </c>
+        <v>2.47</v>
+      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9226,19 +9218,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>40.32</v>
+        <v>40.59</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>35.78</v>
+        <v>35.01</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -9252,23 +9244,21 @@
         <v>9</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>40.84</v>
+        <v>41.35</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>36.64</v>
+        <v>36.39</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>0.54</v>
-      </c>
+        <v>1.94</v>
+      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -9280,23 +9270,21 @@
         <v>13</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>39.87</v>
+        <v>40.31</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>36.05</v>
+        <v>35.99</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0.43</v>
-      </c>
+        <v>2.06</v>
+      </c>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9308,22 +9296,22 @@
         <v>14</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>39.61</v>
+        <v>39.79</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>35.69</v>
+        <v>35.36</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="21">
@@ -9336,22 +9324,22 @@
         <v>12</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>39.47</v>
+        <v>39.28</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>35.22</v>
+        <v>34.8</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4.34</v>
+        <v>4.56</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -9364,22 +9352,22 @@
         <v>9</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>40.62</v>
+        <v>40.71</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>35.85</v>
+        <v>35.68</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>4.3</v>
+        <v>4.56</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="23">
@@ -9392,22 +9380,22 @@
         <v>10</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>40.84</v>
+        <v>40.98</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>35.79</v>
+        <v>35.49</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0.93</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="24">
@@ -9420,22 +9408,22 @@
         <v>13</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>39.16</v>
+        <v>39.36</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.8</v>
+        <v>35.35</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -9448,22 +9436,22 @@
         <v>26</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>41.76</v>
+        <v>42.15</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>34.34</v>
+        <v>33.68</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>4.09</v>
+        <v>4.45</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -9552,10 +9540,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>45.11</v>
+        <v>44.56</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>36.99</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="8">
@@ -9568,10 +9556,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>44.97</v>
+        <v>45.56</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>42.6</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="9">
@@ -9584,10 +9572,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>44.94</v>
+        <v>45.39</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>42.52</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="10">
@@ -9600,10 +9588,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>45.06</v>
+        <v>45.4</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>42.71</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="11">
@@ -9616,10 +9604,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>43.9</v>
+        <v>43.51</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>42.77</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="12">
@@ -9632,10 +9620,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43.4</v>
+        <v>42.56</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>41.56</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="13">
@@ -9648,10 +9636,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.62</v>
+        <v>44.21</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>44.42</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="14">
@@ -9664,10 +9652,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>44.36</v>
+        <v>44.23</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>43.89</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="15">
@@ -9680,10 +9668,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.36</v>
+        <v>43.93</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>44.08</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="16">
@@ -9696,10 +9684,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>44.74</v>
+        <v>44.4</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>44.26</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="17">
@@ -9712,10 +9700,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.18</v>
+        <v>44.72</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>45.3</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="18">
@@ -9728,10 +9716,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.2</v>
+        <v>44.65</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>45.94</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="19">
@@ -9744,10 +9732,10 @@
         <v>9</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>44.5</v>
+        <v>44.87</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>45.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="20">
@@ -9760,10 +9748,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>43.96</v>
+        <v>43.74</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>44.94</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="21">
@@ -9776,10 +9764,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>43.9</v>
+        <v>43.39</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>44.38</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="22">
@@ -9792,10 +9780,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>44.61</v>
+        <v>44.52</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>45.04</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="23">
@@ -9808,10 +9796,10 @@
         <v>9</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.51</v>
+        <v>44.23</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>45.52</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="24">
@@ -9824,10 +9812,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.46</v>
+        <v>44.36</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>45.86</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="25">
@@ -9840,10 +9828,10 @@
         <v>15</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>46</v>
+        <v>46.14</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>44.37</v>
+        <v>43.73</v>
       </c>
     </row>
   </sheetData>
@@ -9956,10 +9944,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>45.48</v>
+        <v>46.34</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>37.39</v>
+        <v>36.38</v>
       </c>
       <c r="E8" s="5" t="n"/>
     </row>
@@ -9973,10 +9961,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>45.48</v>
+        <v>46.34</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>37.39</v>
+        <v>36.38</v>
       </c>
       <c r="E9" s="5" t="n"/>
     </row>
@@ -9990,10 +9978,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>45.38</v>
+        <v>46.17</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>36.79</v>
+        <v>36.14</v>
       </c>
       <c r="E10" s="5" t="n"/>
     </row>
@@ -10007,10 +9995,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>44.11</v>
+        <v>43.93</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>36.04</v>
+        <v>35.33</v>
       </c>
       <c r="E11" s="5" t="n"/>
     </row>
@@ -10024,10 +10012,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>43.12</v>
+        <v>42.73</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>33.82</v>
+        <v>33.68</v>
       </c>
       <c r="E12" s="5" t="n"/>
     </row>
@@ -10041,10 +10029,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.38</v>
+        <v>43.99</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>37.27</v>
+        <v>36.77</v>
       </c>
       <c r="E13" s="5" t="n"/>
     </row>
@@ -10058,10 +10046,10 @@
         <v>4</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>44.2</v>
+        <v>43.94</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>37</v>
+        <v>36.48</v>
       </c>
       <c r="E14" s="5" t="n"/>
     </row>
@@ -10075,10 +10063,10 @@
         <v>5</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>44.67</v>
+        <v>44.31</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>37.11</v>
+        <v>36.58</v>
       </c>
       <c r="E15" s="5" t="n"/>
     </row>
@@ -10092,10 +10080,10 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>45.07</v>
+        <v>44.82</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>37.43</v>
+        <v>36.93</v>
       </c>
       <c r="E16" s="5" t="n"/>
     </row>
@@ -10109,10 +10097,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.53</v>
+        <v>45.33</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>39.2</v>
+        <v>38.79</v>
       </c>
       <c r="E17" s="5" t="n"/>
     </row>
@@ -10126,10 +10114,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.85</v>
+        <v>45.6</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>40.08</v>
+        <v>39.57</v>
       </c>
       <c r="E18" s="5" t="n"/>
     </row>
@@ -10143,10 +10131,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>45.32</v>
+        <v>45.45</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>40.71</v>
+        <v>41.7</v>
       </c>
       <c r="E19" s="5" t="n"/>
     </row>
@@ -10160,10 +10148,10 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>44.81</v>
+        <v>44.64</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>39.68</v>
+        <v>39.82</v>
       </c>
       <c r="E20" s="5" t="n"/>
     </row>
@@ -10177,10 +10165,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>44.33</v>
+        <v>44.11</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>38.6</v>
+        <v>38.76</v>
       </c>
       <c r="E21" s="5" t="n"/>
     </row>
@@ -10194,10 +10182,10 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.49</v>
+        <v>45.36</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>41.57</v>
+        <v>41.7</v>
       </c>
       <c r="E22" s="5" t="n"/>
     </row>
@@ -10211,10 +10199,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.77</v>
+        <v>44.72</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>41.4</v>
+        <v>41.58</v>
       </c>
       <c r="E23" s="5" t="n"/>
     </row>
@@ -10228,10 +10216,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.71</v>
+        <v>45.01</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>41.1</v>
+        <v>40.79</v>
       </c>
       <c r="E24" s="5" t="n"/>
     </row>
@@ -10245,10 +10233,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>46.57</v>
+        <v>46.54</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>39.16</v>
+        <v>39.21</v>
       </c>
       <c r="E25" s="5" t="n"/>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>2045</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.6604298569685054</v>
+        <v>0.6453456181883783</v>
       </c>
       <c r="E26" s="10" t="n">
         <v/>
@@ -2226,7 +2226,7 @@
         <v>2045</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.6604298569685054</v>
+        <v>0.6453456181883783</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -2286,7 +2286,7 @@
         <v>2000</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.6236291026982375</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>2000</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0.4</v>
@@ -2406,7 +2406,7 @@
         <v>2000</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1.6</v>
@@ -2466,7 +2466,7 @@
         <v>2000</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.4</v>
@@ -2526,7 +2526,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2.614262037056612</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1</v>
@@ -2586,7 +2586,7 @@
         <v>2100</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.8517653796574984</v>
+        <v>0.8323110314995047</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0.1</v>
@@ -2646,7 +2646,7 @@
         <v>5032</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0.5</v>
@@ -2706,7 +2706,7 @@
         <v>5032</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>0.2</v>
@@ -2766,7 +2766,7 @@
         <v>5032</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E36" s="10" t="n">
         <v/>
@@ -2826,7 +2826,7 @@
         <v>5032</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>0.2</v>
@@ -2886,7 +2886,7 @@
         <v>5032</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>1.2</v>
@@ -2946,7 +2946,7 @@
         <v>5032</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -3006,7 +3006,7 @@
         <v>2004</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2.223866865044549</v>
+        <v>2.173073675648897</v>
       </c>
       <c r="E40" s="10" t="n">
         <v/>
@@ -3066,7 +3066,7 @@
         <v>2004</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>2.223866865044549</v>
+        <v>2.173073675648897</v>
       </c>
       <c r="E41" s="10" t="n">
         <v/>
@@ -3126,7 +3126,7 @@
         <v>2004</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.223866865044549</v>
+        <v>2.173073675648897</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>2000</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.4949747468305833</v>
+        <v>0.4836695079887215</v>
       </c>
       <c r="E43" s="10" t="n">
         <v/>
@@ -3246,7 +3246,7 @@
         <v>2000</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.4949747468305833</v>
+        <v>0.4836695079887215</v>
       </c>
       <c r="E44" s="10" t="n">
         <v/>
@@ -3306,7 +3306,7 @@
         <v>2004</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
         <v>2000</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.4512796079538526</v>
+        <v>0.4409723674632056</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>0.3</v>
@@ -3426,7 +3426,7 @@
         <v>1500</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.5209251213179019</v>
+        <v>0.5090271751036068</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0.8</v>
@@ -3486,7 +3486,7 @@
         <v>1500</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.5209251213179019</v>
+        <v>0.5090271751036068</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0.6</v>
@@ -3546,7 +3546,7 @@
         <v>2000</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1.175547906283609</v>
+        <v>1.148698354997035</v>
       </c>
       <c r="E49" s="10" t="n">
         <v/>
@@ -3606,7 +3606,7 @@
         <v>2000</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1.175547906283609</v>
+        <v>1.148698354997035</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>1</v>
@@ -3666,7 +3666,7 @@
         <v>5008</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1.582403235588199</v>
+        <v>1.546261095737613</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0.3</v>
@@ -3726,7 +3726,7 @@
         <v>2028</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.3443917098737023</v>
+        <v>0.336525792349203</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>2004</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>1.086536837824448</v>
+        <v>1.061720302151183</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>2002</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.3537301231164799</v>
+        <v>0.3456509159387414</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>2002</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.3537301231164799</v>
+        <v>0.3456509159387414</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>1.5</v>
@@ -3966,7 +3966,7 @@
         <v>2000</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.2418347539943608</v>
+        <v>0.2363112405794332</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0.3</v>
@@ -4026,7 +4026,7 @@
         <v>2004</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.9906200696914819</v>
+        <v>0.9679942760300587</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>1</v>
@@ -4086,7 +4086,7 @@
         <v>2004</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.9906200696914819</v>
+        <v>0.9679942760300587</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>1500</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.2727809089929303</v>
+        <v>0.2665505844209967</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0.6</v>
@@ -4206,7 +4206,7 @@
         <v>1030</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.1582286035030043</v>
+        <v>0.1546146572043905</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0.4</v>
@@ -4266,7 +4266,7 @@
         <v>2080</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.5340173168733414</v>
+        <v>0.5218203444992953</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0.2</v>
@@ -4326,7 +4326,7 @@
         <v>2080</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.5340173168733414</v>
+        <v>0.5218203444992953</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0.2</v>
@@ -4386,7 +4386,7 @@
         <v>2080</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.5340173168733414</v>
+        <v>0.5218203444992953</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>1.1</v>
@@ -4446,7 +4446,7 @@
         <v>2000</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.1790904310994356</v>
+        <v>0.175</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>0</v>
@@ -4506,7 +4506,7 @@
         <v>2000</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.1632807735189413</v>
+        <v>0.1595514354976879</v>
       </c>
       <c r="E65" s="10" t="n">
         <v/>
@@ -4566,7 +4566,7 @@
         <v>2000</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.1632807735189413</v>
+        <v>0.1595514354976879</v>
       </c>
       <c r="E66" s="10" t="n">
         <v/>
@@ -4626,7 +4626,7 @@
         <v>5028</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.7062866136215571</v>
+        <v>0.6901550050719714</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0.6</v>
@@ -4686,7 +4686,7 @@
         <v>4200</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.6455174483634446</v>
+        <v>0.6307738094665787</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0.6</v>
@@ -4746,7 +4746,7 @@
         <v>1500</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.1428409214029821</v>
+        <v>0.1395784302492566</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>0.8</v>
@@ -4806,7 +4806,7 @@
         <v>2004</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.4839971380150294</v>
+        <v>0.4729426281050314</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>1</v>
@@ -4866,7 +4866,7 @@
         <v>2004</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.4412710751261174</v>
+        <v>0.4311924298411825</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>2</v>
@@ -4926,7 +4926,7 @@
         <v>2004</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.4412710751261174</v>
+        <v>0.4311924298411825</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>2000</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.2742062449236565</v>
+        <v>0.2679433656340733</v>
       </c>
       <c r="E73" s="10" t="n">
         <v>2</v>
@@ -5046,7 +5046,7 @@
         <v>2000</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.2742062449236565</v>
+        <v>0.2679433656340733</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>2</v>
@@ -5106,7 +5106,7 @@
         <v>2080</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.2491278873473965</v>
+        <v>0.2434377985364723</v>
       </c>
       <c r="E75" s="10" t="n">
         <v>0.4</v>
@@ -5166,7 +5166,7 @@
         <v>2080</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.2491278873473965</v>
+        <v>0.2434377985364723</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>0.2</v>
@@ -5226,7 +5226,7 @@
         <v>2080</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.2491278873473965</v>
+        <v>0.2434377985364723</v>
       </c>
       <c r="E77" s="10" t="n">
         <v>0.2</v>
@@ -5286,7 +5286,7 @@
         <v>5020</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.3781883993363231</v>
+        <v>0.3695505643576795</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>0.5</v>
@@ -5346,7 +5346,7 @@
         <v>4986</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.3769055057285275</v>
+        <v>0.3682969720803814</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>1.1</v>
@@ -5406,7 +5406,7 @@
         <v>4986</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.3769055057285275</v>
+        <v>0.3682969720803814</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>1.1</v>
@@ -5466,7 +5466,7 @@
         <v>2004</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.2844809111204133</v>
+        <v>0.2779833581305687</v>
       </c>
       <c r="E81" s="10" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
         <v>2004</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.253443679052572</v>
+        <v>0.2476550174228705</v>
       </c>
       <c r="E82" s="10" t="n">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         <v>2000</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.1611712885549474</v>
+        <v>0.1574901312368592</v>
       </c>
       <c r="E83" s="10" t="n">
         <v/>
@@ -5646,7 +5646,7 @@
         <v>2000</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.1611712885549474</v>
+        <v>0.1574901312368592</v>
       </c>
       <c r="E84" s="10" t="n">
         <v>3</v>
@@ -5706,7 +5706,7 @@
         <v>2000</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.1611712885549474</v>
+        <v>0.1574901312368592</v>
       </c>
       <c r="E85" s="10" t="n">
         <v>3</v>
@@ -5766,7 +5766,7 @@
         <v>1500</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.06217512229455173</v>
+        <v>0.06075504053873955</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0.5</v>
@@ -5826,7 +5826,7 @@
         <v>2000</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.05025555303112028</v>
+        <v>0.04910771461353507</v>
       </c>
       <c r="E87" s="10" t="n">
         <v/>
@@ -5886,7 +5886,7 @@
         <v>2080</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.1304550861248238</v>
+        <v>0.1274754878398196</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>0.3</v>
@@ -5946,7 +5946,7 @@
         <v>2080</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>0.1304550861248238</v>
+        <v>0.1274754878398196</v>
       </c>
       <c r="E89" s="10" t="n">
         <v>0.3</v>
@@ -6006,7 +6006,7 @@
         <v>2080</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>0.1304550861248238</v>
+        <v>0.1274754878398196</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>1.1</v>
@@ -6066,7 +6066,7 @@
         <v>5418</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.1750145610956858</v>
+        <v>0.1710172229957937</v>
       </c>
       <c r="E91" s="10" t="n">
         <v>1</v>
@@ -6126,7 +6126,7 @@
         <v>2000</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0.6</v>
@@ -6186,7 +6186,7 @@
         <v>2000</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E93" s="10" t="n">
         <v>0.4</v>
@@ -6246,7 +6246,7 @@
         <v>2000</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.03636665795624697</v>
+        <v>0.03553604234058531</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0.4</v>
@@ -6306,7 +6306,7 @@
         <v>2000</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.04419417382415922</v>
+        <v>0.043184777498993</v>
       </c>
       <c r="E95" s="10" t="n">
         <v>0.2</v>
@@ -6366,7 +6366,7 @@
         <v>2000</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.04419417382415922</v>
+        <v>0.043184777498993</v>
       </c>
       <c r="E96" s="10" t="n">
         <v>0.4</v>
@@ -6426,7 +6426,7 @@
         <v>2004</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.129683822117006</v>
+        <v>0.126721839526286</v>
       </c>
       <c r="E97" s="10" t="n">
         <v>2</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
         <v>2045</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.6604298569685054</v>
+        <v>0.6453456181883783</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>43</v>
@@ -6680,7 +6680,7 @@
         <v>2000</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.6236291026982375</v>
+        <v>0.6093853943072869</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>47</v>
@@ -6710,7 +6710,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>42.2</v>
@@ -6740,7 +6740,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2.614262037056612</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>43</v>
@@ -6770,7 +6770,7 @@
         <v>2100</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.8517653796574984</v>
+        <v>0.8323110314995047</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>38.1</v>
@@ -6800,7 +6800,7 @@
         <v>5032</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>41.8</v>
@@ -6830,7 +6830,7 @@
         <v>5032</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>41.8</v>
@@ -6860,7 +6860,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2.223866865044549</v>
+        <v>2.173073675648897</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>45</v>
@@ -6890,7 +6890,7 @@
         <v>2000</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.4949747468305833</v>
+        <v>0.4836695079887215</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>50</v>
@@ -6920,7 +6920,7 @@
         <v>2004</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>41</v>
@@ -6950,7 +6950,7 @@
         <v>2000</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.4512796079538526</v>
+        <v>0.4409723674632056</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>46.9</v>
@@ -6980,7 +6980,7 @@
         <v>2000</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.4512796079538526</v>
+        <v>0.4409723674632056</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>46.9</v>
@@ -7010,7 +7010,7 @@
         <v>1500</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.5209251213179019</v>
+        <v>0.5090271751036068</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>45.3</v>
@@ -7040,7 +7040,7 @@
         <v>2000</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1.175547906283609</v>
+        <v>1.148698354997035</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>44</v>
@@ -7070,7 +7070,7 @@
         <v>5008</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1.582403235588199</v>
+        <v>1.546261095737613</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>47.8</v>
@@ -7100,7 +7100,7 @@
         <v>2028</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.3443917098737023</v>
+        <v>0.336525792349203</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>45</v>
@@ -7130,7 +7130,7 @@
         <v>2004</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1.086536837824448</v>
+        <v>1.061720302151183</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>42</v>
@@ -7160,7 +7160,7 @@
         <v>2002</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.3537301231164799</v>
+        <v>0.3456509159387414</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>40.2</v>
@@ -7190,7 +7190,7 @@
         <v>2002</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.3537301231164799</v>
+        <v>0.3456509159387414</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>40.2</v>
@@ -7220,7 +7220,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.2418347539943608</v>
+        <v>0.2363112405794332</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>48</v>
@@ -7250,7 +7250,7 @@
         <v>2004</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.9906200696914819</v>
+        <v>0.9679942760300587</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>46</v>
@@ -7280,7 +7280,7 @@
         <v>1030</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.1582286035030043</v>
+        <v>0.1546146572043905</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>41</v>
@@ -7310,7 +7310,7 @@
         <v>1500</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.2727809089929303</v>
+        <v>0.2665505844209967</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>45.8</v>
@@ -7340,7 +7340,7 @@
         <v>2080</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.5340173168733414</v>
+        <v>0.5218203444992953</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>45.2</v>
@@ -7370,7 +7370,7 @@
         <v>2000</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.1790904310994356</v>
+        <v>0.175</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>46</v>
@@ -7400,7 +7400,7 @@
         <v>2000</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.1632807735189413</v>
+        <v>0.1595514354976879</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>48</v>
@@ -7430,7 +7430,7 @@
         <v>5028</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.7062866136215571</v>
+        <v>0.6901550050719714</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>47.6</v>
@@ -7460,7 +7460,7 @@
         <v>4200</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.6455174483634446</v>
+        <v>0.6307738094665787</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>47.6</v>
@@ -7490,7 +7490,7 @@
         <v>1500</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.1428409214029821</v>
+        <v>0.1395784302492566</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>45.3</v>
@@ -7520,7 +7520,7 @@
         <v>2004</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.4839971380150294</v>
+        <v>0.4729426281050314</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>41</v>
@@ -7550,7 +7550,7 @@
         <v>2004</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.4412710751261174</v>
+        <v>0.4311924298411825</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>43</v>
@@ -7580,7 +7580,7 @@
         <v>2000</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.2742062449236565</v>
+        <v>0.2679433656340733</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>41</v>
@@ -7610,7 +7610,7 @@
         <v>2080</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.2491278873473965</v>
+        <v>0.2434377985364723</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>44.4</v>
@@ -7640,7 +7640,7 @@
         <v>5020</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.3781883993363231</v>
+        <v>0.3695505643576795</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>47.5</v>
@@ -7670,7 +7670,7 @@
         <v>4986</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.3769055057285275</v>
+        <v>0.3682969720803814</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>46.3</v>
@@ -7700,7 +7700,7 @@
         <v>2004</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.2844809111204133</v>
+        <v>0.2779833581305687</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>42</v>
@@ -7730,7 +7730,7 @@
         <v>2004</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.253443679052572</v>
+        <v>0.2476550174228705</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>38</v>
@@ -7760,7 +7760,7 @@
         <v>1500</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.06217512229455173</v>
+        <v>0.06075504053873955</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>41.1</v>
@@ -7790,7 +7790,7 @@
         <v>2000</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.05025555303112028</v>
+        <v>0.04910771461353507</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>45</v>
@@ -7820,7 +7820,7 @@
         <v>2080</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.1304550861248238</v>
+        <v>0.1274754878398196</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>42.2</v>
@@ -7850,7 +7850,7 @@
         <v>5418</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.1750145610956858</v>
+        <v>0.1710172229957937</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>45</v>
@@ -7880,7 +7880,7 @@
         <v>2000</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>48.1</v>
@@ -7910,7 +7910,7 @@
         <v>2000</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>42.5</v>
@@ -7940,7 +7940,7 @@
         <v>2000</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.04419417382415922</v>
+        <v>0.043184777498993</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>36</v>
@@ -7970,7 +7970,7 @@
         <v>2004</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.129683822117006</v>
+        <v>0.126721839526286</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>38</v>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
         <v>2045</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.6604298569685054</v>
+        <v>0.6453456181883783</v>
       </c>
       <c r="E17" s="10" t="n">
         <v/>
@@ -8213,7 +8213,7 @@
         <v>2000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="E18" s="10" t="n">
         <v/>
@@ -8246,7 +8246,7 @@
         <v>2004</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2.614262037056612</v>
+        <v>2.554552209609086</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         <v>5032</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2.576773914608964</v>
+        <v>2.517920317061483</v>
       </c>
       <c r="E20" s="10" t="n">
         <v/>
@@ -8312,7 +8312,7 @@
         <v>2004</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2.223866865044549</v>
+        <v>2.173073675648897</v>
       </c>
       <c r="E21" s="10" t="n">
         <v/>
@@ -8345,7 +8345,7 @@
         <v>2000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.4949747468305833</v>
+        <v>0.4836695079887215</v>
       </c>
       <c r="E22" s="10" t="n">
         <v/>
@@ -8378,7 +8378,7 @@
         <v>2004</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="E23" s="10" t="n">
         <v/>
@@ -8411,7 +8411,7 @@
         <v>1500</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.5209251213179019</v>
+        <v>0.5090271751036068</v>
       </c>
       <c r="E24" s="10" t="n">
         <v/>
@@ -8444,7 +8444,7 @@
         <v>2000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1.175547906283609</v>
+        <v>1.148698354997035</v>
       </c>
       <c r="E25" s="10" t="n">
         <v/>
@@ -8477,7 +8477,7 @@
         <v>5008</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1.582403235588199</v>
+        <v>1.546261095737613</v>
       </c>
       <c r="E26" s="10" t="n">
         <v/>
@@ -8510,7 +8510,7 @@
         <v>2004</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>1.086536837824448</v>
+        <v>1.061720302151183</v>
       </c>
       <c r="E27" s="10" t="n">
         <v/>
@@ -8543,7 +8543,7 @@
         <v>2002</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.3537301231164799</v>
+        <v>0.3456509159387414</v>
       </c>
       <c r="E28" s="10" t="n">
         <v/>
@@ -8576,7 +8576,7 @@
         <v>2000</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.2418347539943608</v>
+        <v>0.2363112405794332</v>
       </c>
       <c r="E29" s="10" t="n">
         <v/>
@@ -8609,7 +8609,7 @@
         <v>2004</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.9906200696914819</v>
+        <v>0.9679942760300587</v>
       </c>
       <c r="E30" s="10" t="n">
         <v/>
@@ -8642,7 +8642,7 @@
         <v>1500</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.2727809089929303</v>
+        <v>0.2665505844209967</v>
       </c>
       <c r="E31" s="10" t="n">
         <v/>
@@ -8675,7 +8675,7 @@
         <v>5028</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.7062866136215571</v>
+        <v>0.6901550050719714</v>
       </c>
       <c r="E32" s="10" t="n">
         <v/>
@@ -8708,7 +8708,7 @@
         <v>1500</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.1428409214029821</v>
+        <v>0.1395784302492566</v>
       </c>
       <c r="E33" s="10" t="n">
         <v/>
@@ -8741,7 +8741,7 @@
         <v>2004</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.4839971380150294</v>
+        <v>0.4729426281050314</v>
       </c>
       <c r="E34" s="10" t="n">
         <v/>
@@ -8774,7 +8774,7 @@
         <v>2000</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.2742062449236565</v>
+        <v>0.2679433656340733</v>
       </c>
       <c r="E35" s="10" t="n">
         <v/>
@@ -8807,7 +8807,7 @@
         <v>4986</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.3769055057285275</v>
+        <v>0.3682969720803814</v>
       </c>
       <c r="E36" s="10" t="n">
         <v/>
@@ -8840,7 +8840,7 @@
         <v>2004</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.2844809111204133</v>
+        <v>0.2779833581305687</v>
       </c>
       <c r="E37" s="10" t="n">
         <v/>
@@ -8873,7 +8873,7 @@
         <v>2004</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.253443679052572</v>
+        <v>0.2476550174228705</v>
       </c>
       <c r="E38" s="10" t="n">
         <v/>
@@ -8906,7 +8906,7 @@
         <v>1500</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.06217512229455173</v>
+        <v>0.06075504053873955</v>
       </c>
       <c r="E39" s="10" t="n">
         <v/>
@@ -8939,7 +8939,7 @@
         <v>5418</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.1750145610956858</v>
+        <v>0.1710172229957937</v>
       </c>
       <c r="E40" s="10" t="n">
         <v/>
@@ -8972,7 +8972,7 @@
         <v>2000</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E41" s="10" t="n">
         <v/>
@@ -9005,7 +9005,7 @@
         <v>2000</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.05195236850892425</v>
+        <v>0.05076577477226472</v>
       </c>
       <c r="E42" s="10" t="n">
         <v/>
@@ -9038,7 +9038,7 @@
         <v>2004</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.129683822117006</v>
+        <v>0.126721839526286</v>
       </c>
       <c r="E43" s="10" t="n">
         <v/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -10558,7 +10558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z145"/>
+  <dimension ref="A1:AA145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10587,6 +10587,7 @@
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10632,90 +10633,95 @@
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
           <t>metodologia</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>votos_validos</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>registro_tse</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>url_fonte</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Aldo</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Caiado</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Cury</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Daciolo</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="R1" s="8" t="inlineStr">
         <is>
           <t>Flávio</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Hertz</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
         <is>
           <t>Renan</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="V1" s="8" t="inlineStr">
         <is>
           <t>Rui</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="W1" s="8" t="inlineStr">
         <is>
           <t>Samara</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="X1" s="8" t="inlineStr">
         <is>
           <t>Zema</t>
         </is>
       </c>
-      <c r="X1" s="8" t="inlineStr">
+      <c r="Y1" s="8" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
       </c>
-      <c r="Y1" s="8" t="inlineStr">
+      <c r="Z1" s="8" t="inlineStr">
         <is>
           <t>Branco/Nulo</t>
         </is>
       </c>
-      <c r="Z1" s="8" t="inlineStr">
+      <c r="AA1" s="8" t="inlineStr">
         <is>
           <t>Não sabe</t>
         </is>
@@ -10756,50 +10762,51 @@
       <c r="H2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>BR-04193/2026</t>
         </is>
       </c>
-      <c r="L2" s="9" t="n"/>
       <c r="M2" s="9" t="n"/>
-      <c r="N2" s="10" t="n">
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="O2" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="n">
+      <c r="S2" s="9" t="n"/>
+      <c r="T2" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T2" s="10" t="n">
+      <c r="U2" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U2" s="9" t="n"/>
       <c r="V2" s="9" t="n"/>
-      <c r="W2" s="10" t="n">
+      <c r="W2" s="9" t="n"/>
+      <c r="X2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X2" s="9" t="n"/>
-      <c r="Y2" s="10" t="n">
+      <c r="Y2" s="9" t="n"/>
+      <c r="Z2" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z2" s="10" t="n">
+      <c r="AA2" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10838,46 +10845,47 @@
       <c r="H3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>BR-04193/2026</t>
         </is>
       </c>
-      <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="10" t="n">
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="O3" s="9" t="n"/>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="10" t="n">
+      <c r="Q3" s="9" t="n"/>
+      <c r="R3" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R3" s="9" t="n"/>
-      <c r="S3" s="10" t="n">
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="T3" s="10" t="n">
+      <c r="U3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U3" s="9" t="n"/>
       <c r="V3" s="9" t="n"/>
-      <c r="W3" s="10" t="n">
+      <c r="W3" s="9" t="n"/>
+      <c r="X3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="9" t="n"/>
-      <c r="Y3" s="10" t="n">
+      <c r="Y3" s="9" t="n"/>
+      <c r="Z3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Z3" s="10" t="n">
+      <c r="AA3" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10916,56 +10924,57 @@
       <c r="H4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>BR-07971/2026</t>
         </is>
       </c>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M4" s="9" t="n"/>
       <c r="N4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="O4" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P4" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="R4" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="U4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U4" s="9" t="n"/>
-      <c r="V4" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V4" s="9" t="n"/>
       <c r="W4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X4" s="9" t="n"/>
-      <c r="Y4" s="10" t="n">
+      <c r="Y4" s="9" t="n"/>
+      <c r="Z4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Z4" s="10" t="n">
+      <c r="AA4" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11004,52 +11013,53 @@
       <c r="H5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>BR-06529/2026</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="O5" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="P5" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="Q5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="R5" s="10" t="n">
         <v>35.6</v>
       </c>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="n">
         <v>42.7</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="U5" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="U5" s="9" t="n"/>
       <c r="V5" s="9" t="n"/>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="10" t="n">
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z5" s="10" t="n">
+      <c r="AA5" s="10" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -11088,50 +11098,51 @@
       <c r="H6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>BR-06529/2026</t>
         </is>
       </c>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="O6" s="10" t="n">
         <v>13.1</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="P6" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="Q6" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q6" s="9" t="n"/>
       <c r="R6" s="9" t="n"/>
-      <c r="S6" s="10" t="n">
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T6" s="10" t="n">
+      <c r="U6" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="U6" s="9" t="n"/>
       <c r="V6" s="9" t="n"/>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="10" t="n">
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="Z6" s="10" t="n">
+      <c r="AA6" s="10" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -11170,56 +11181,57 @@
       <c r="H7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>BR-06529/2026</t>
         </is>
       </c>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="O7" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="P7" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="Q7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="R7" s="10" t="n">
         <v>35.6</v>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10" t="n">
         <v>42.7</v>
       </c>
-      <c r="T7" s="10" t="n">
+      <c r="U7" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V7" s="9" t="n"/>
       <c r="W7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="10" t="n">
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z7" s="10" t="n">
+      <c r="AA7" s="10" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -11258,62 +11270,63 @@
       <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>BR-07489/2026</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026-2/</t>
         </is>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="N8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="O8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="P8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="Q8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="R8" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="R8" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="U8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="V8" s="10" t="n">
         <v>1</v>
-      </c>
-      <c r="V8" s="10" t="n">
-        <v>3</v>
       </c>
       <c r="W8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="10" t="n">
+      <c r="X8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z8" s="10" t="n">
+      <c r="AA8" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11352,50 +11365,51 @@
       <c r="H9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>BR-02416/2026</t>
         </is>
       </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="O9" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="P9" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="10" t="n">
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="10" t="n">
         <v>41.5</v>
       </c>
-      <c r="T9" s="10" t="n">
+      <c r="U9" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="U9" s="9" t="n"/>
       <c r="V9" s="9" t="n"/>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="10" t="n">
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="10" t="n">
         <v>4.9</v>
       </c>
-      <c r="Z9" s="10" t="n">
+      <c r="AA9" s="10" t="n">
         <v>9.4</v>
       </c>
     </row>
@@ -11434,54 +11448,55 @@
       <c r="H10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="N10" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="O10" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="P10" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="10" t="n">
         <v>34.3</v>
       </c>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="10" t="n">
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="U10" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="U10" s="9" t="n"/>
       <c r="V10" s="9" t="n"/>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n"/>
+      <c r="X10" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="10" t="n">
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z10" s="10" t="n">
+      <c r="AA10" s="10" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -11520,38 +11535,39 @@
       <c r="H11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="T11" s="9" t="n"/>
       <c r="U11" s="9" t="n"/>
       <c r="V11" s="9" t="n"/>
       <c r="W11" s="9" t="n"/>
       <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="10" t="n">
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z11" s="10" t="n">
+      <c r="AA11" s="10" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -11590,48 +11606,49 @@
       <c r="H12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="O12" s="10" t="n">
         <v>13.8</v>
       </c>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="10" t="n">
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q12" s="9" t="n"/>
       <c r="R12" s="9" t="n"/>
-      <c r="S12" s="10" t="n">
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="10" t="n">
         <v>46.7</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="U12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="U12" s="9" t="n"/>
       <c r="V12" s="9" t="n"/>
-      <c r="W12" s="10" t="n">
+      <c r="W12" s="9" t="n"/>
+      <c r="X12" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="10" t="n">
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z12" s="10" t="n">
+      <c r="AA12" s="10" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -11670,52 +11687,53 @@
       <c r="H13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="10" t="n">
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="R13" s="9" t="n"/>
-      <c r="S13" s="10" t="n">
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="T13" s="10" t="n">
+      <c r="U13" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="U13" s="9" t="n"/>
       <c r="V13" s="9" t="n"/>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="10" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="Y13" s="9" t="n"/>
       <c r="Z13" s="10" t="n">
         <v>2.3</v>
       </c>
+      <c r="AA13" s="10" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -11752,48 +11770,49 @@
       <c r="H14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="P14" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="R14" s="9" t="n"/>
       <c r="S14" s="9" t="n"/>
-      <c r="T14" s="10" t="n">
+      <c r="T14" s="9" t="n"/>
+      <c r="U14" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U14" s="9" t="n"/>
       <c r="V14" s="9" t="n"/>
-      <c r="W14" s="10" t="n">
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="10" t="n">
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="10" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z14" s="10" t="n">
+      <c r="AA14" s="10" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -11832,56 +11851,57 @@
       <c r="H15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="P15" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="P15" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="10" t="n">
         <v>34.3</v>
       </c>
-      <c r="R15" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="U15" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V15" s="9" t="n"/>
       <c r="W15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="10" t="n">
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z15" s="10" t="n">
+      <c r="AA15" s="10" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -11920,60 +11940,61 @@
       <c r="H16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>BR-00290/2026</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="10" t="n">
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O16" s="10" t="n">
+      <c r="P16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P16" s="10" t="n">
+      <c r="Q16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="R16" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="10" t="n">
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T16" s="10" t="n">
+      <c r="U16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U16" s="10" t="n">
+      <c r="V16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="W16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="X16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="10" t="n">
-        <v>9</v>
-      </c>
+      <c r="Y16" s="9" t="n"/>
       <c r="Z16" s="10" t="n">
         <v>9</v>
       </c>
+      <c r="AA16" s="10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -12010,56 +12031,57 @@
       <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>BR-00290/2026</t>
         </is>
       </c>
-      <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
-      <c r="N17" s="10" t="n">
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O17" s="10" t="n">
+      <c r="P17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="R17" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="S17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="10" t="n">
+      <c r="T17" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T17" s="10" t="n">
+      <c r="U17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U17" s="10" t="n">
+      <c r="V17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="W17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="X17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="10" t="n">
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z17" s="10" t="n">
+      <c r="AA17" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12098,56 +12120,57 @@
       <c r="H18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>BR-00290/2026</t>
         </is>
       </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M18" s="9" t="n"/>
       <c r="N18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O18" s="10" t="n">
+      <c r="P18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="10" t="n">
+      <c r="Q18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="R18" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="S18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="T18" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="U18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U18" s="9" t="n"/>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W18" s="10" t="n">
+      <c r="X18" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="10" t="n">
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z18" s="10" t="n">
+      <c r="AA18" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12186,56 +12209,57 @@
       <c r="H19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>BR-03369/2026</t>
         </is>
       </c>
-      <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="N19" s="9" t="n"/>
       <c r="O19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="R19" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="T19" s="10" t="n">
+      <c r="U19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U19" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W19" s="10" t="n">
+      <c r="X19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X19" s="9" t="n"/>
-      <c r="Y19" s="10" t="n">
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="AA19" s="10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -12274,48 +12298,49 @@
       <c r="H20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>BR-03369/2026</t>
         </is>
       </c>
-      <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
-      <c r="N20" s="10" t="n">
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="R20" s="9" t="n"/>
-      <c r="S20" s="10" t="n">
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="T20" s="10" t="n">
+      <c r="U20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="9" t="n"/>
       <c r="V20" s="9" t="n"/>
-      <c r="W20" s="10" t="n">
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="X20" s="9" t="n"/>
-      <c r="Y20" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="Y20" s="9" t="n"/>
       <c r="Z20" s="10" t="n">
         <v>6</v>
       </c>
+      <c r="AA20" s="10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -12352,60 +12377,61 @@
       <c r="H21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>BR-03598/2026</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M21" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P21" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T21" s="10" t="n">
+      <c r="U21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U21" s="9" t="n"/>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="10" t="n">
+      <c r="X21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X21" s="9" t="n"/>
-      <c r="Y21" s="10" t="n">
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z21" s="10" t="n">
+      <c r="AA21" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12444,52 +12470,53 @@
       <c r="H22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>BR-03678/2026</t>
         </is>
       </c>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="O22" s="10" t="n">
         <v>4.8</v>
       </c>
-      <c r="O22" s="10" t="n">
+      <c r="P22" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="Q22" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="R22" s="10" t="n">
         <v>37.3</v>
       </c>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="10" t="n">
+      <c r="S22" s="9" t="n"/>
+      <c r="T22" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="U22" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="U22" s="9" t="n"/>
       <c r="V22" s="9" t="n"/>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="X22" s="9" t="n"/>
-      <c r="Y22" s="10" t="n">
+      <c r="Y22" s="9" t="n"/>
+      <c r="Z22" s="10" t="n">
         <v>7.1</v>
       </c>
-      <c r="Z22" s="10" t="n">
+      <c r="AA22" s="10" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -12528,62 +12555,63 @@
       <c r="H23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>BR-05356/2026</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="N23" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="N23" s="10" t="n">
+      <c r="O23" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="O23" s="10" t="n">
+      <c r="P23" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="Q23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="R23" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="R23" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T23" s="10" t="n">
+      <c r="U23" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="U23" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="V23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X23" s="9" t="n"/>
-      <c r="Y23" s="10" t="n">
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="Z23" s="10" t="n">
+      <c r="AA23" s="10" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -12622,56 +12650,57 @@
       <c r="H24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>BR-05356/2026</t>
         </is>
       </c>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="N24" s="10" t="n">
+      <c r="O24" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="O24" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="R24" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="10" t="n">
         <v>40.4</v>
       </c>
-      <c r="T24" s="10" t="n">
+      <c r="U24" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U24" s="9" t="n"/>
-      <c r="V24" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V24" s="9" t="n"/>
       <c r="W24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X24" s="9" t="n"/>
-      <c r="Y24" s="10" t="n">
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" s="10" t="n">
+      <c r="AA24" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -12710,52 +12739,53 @@
       <c r="H25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>BR-03627/2026</t>
         </is>
       </c>
-      <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
-      <c r="N25" s="10" t="n">
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="R25" s="9" t="n"/>
-      <c r="S25" s="10" t="n">
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T25" s="10" t="n">
+      <c r="U25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U25" s="10" t="n">
+      <c r="V25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="9" t="n"/>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X25" s="9" t="n"/>
-      <c r="Y25" s="10" t="n">
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Z25" s="10" t="n">
+      <c r="AA25" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12794,56 +12824,57 @@
       <c r="H26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>BR-03627/2026</t>
         </is>
       </c>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="10" t="n">
+      <c r="O26" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="R26" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T26" s="10" t="n">
+      <c r="U26" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U26" s="9" t="n"/>
-      <c r="V26" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V26" s="9" t="n"/>
       <c r="W26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X26" s="9" t="n"/>
-      <c r="Y26" s="10" t="n">
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Z26" s="10" t="n">
+      <c r="AA26" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12882,54 +12913,55 @@
       <c r="H27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>BR-07992/2026</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="N27" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N27" s="10" t="n">
+      <c r="O27" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O27" s="10" t="n">
+      <c r="P27" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="10" t="n">
         <v>39.7</v>
       </c>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="10" t="n">
         <v>46.6</v>
       </c>
-      <c r="T27" s="10" t="n">
+      <c r="U27" s="10" t="n">
         <v>5.3</v>
       </c>
-      <c r="U27" s="9" t="n"/>
       <c r="V27" s="9" t="n"/>
-      <c r="W27" s="10" t="n">
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="10" t="n">
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z27" s="10" t="n">
+      <c r="AA27" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -12968,56 +13000,57 @@
       <c r="H28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>BR-01075/2026</t>
         </is>
       </c>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M28" s="9" t="n"/>
       <c r="N28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O28" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="R28" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="T28" s="10" t="n">
+      <c r="U28" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U28" s="9" t="n"/>
-      <c r="V28" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V28" s="9" t="n"/>
       <c r="W28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X28" s="9" t="n"/>
-      <c r="Y28" s="10" t="n">
+      <c r="Y28" s="9" t="n"/>
+      <c r="Z28" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Z28" s="10" t="n">
+      <c r="AA28" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13056,58 +13089,59 @@
       <c r="H29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>BR-09285/2026</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M29" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="10" t="n">
+      <c r="P29" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P29" s="10" t="n">
+      <c r="Q29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="R29" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R29" s="9" t="n"/>
-      <c r="S29" s="10" t="n">
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="U29" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U29" s="9" t="n"/>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="X29" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X29" s="9" t="n"/>
-      <c r="Y29" s="10" t="n">
+      <c r="Y29" s="9" t="n"/>
+      <c r="Z29" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Z29" s="10" t="n">
+      <c r="AA29" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13146,56 +13180,57 @@
       <c r="H30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>BR-07871/2026</t>
         </is>
       </c>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M30" s="9" t="n"/>
       <c r="N30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O30" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="R30" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="R30" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="10" t="n">
         <v>39.2</v>
       </c>
-      <c r="T30" s="10" t="n">
+      <c r="U30" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="U30" s="9" t="n"/>
-      <c r="V30" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V30" s="9" t="n"/>
       <c r="W30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="X30" s="9" t="n"/>
-      <c r="Y30" s="10" t="n">
+      <c r="Y30" s="9" t="n"/>
+      <c r="Z30" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="Z30" s="10" t="n">
+      <c r="AA30" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13234,48 +13269,49 @@
       <c r="H31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>BR-02847/2026</t>
         </is>
       </c>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="N31" s="10" t="n">
+      <c r="O31" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="R31" s="9" t="n"/>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="10" t="n">
         <v>39.2</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="U31" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="X31" s="9" t="n"/>
-      <c r="Y31" s="10" t="n">
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z31" s="10" t="n">
+      <c r="AA31" s="10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -13314,56 +13350,57 @@
       <c r="H32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>BR-08282/2026</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="N32" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N32" s="10" t="n">
+      <c r="O32" s="10" t="n">
         <v>4.8</v>
       </c>
-      <c r="O32" s="10" t="n">
+      <c r="P32" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="P32" s="10" t="n">
+      <c r="Q32" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="R32" s="10" t="n">
         <v>37.3</v>
       </c>
-      <c r="R32" s="9" t="n"/>
-      <c r="S32" s="10" t="n">
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="U32" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="U32" s="9" t="n"/>
       <c r="V32" s="9" t="n"/>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="X32" s="9" t="n"/>
-      <c r="Y32" s="10" t="n">
+      <c r="Y32" s="9" t="n"/>
+      <c r="Z32" s="10" t="n">
         <v>7.1</v>
       </c>
-      <c r="Z32" s="10" t="n">
+      <c r="AA32" s="10" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -13402,54 +13439,55 @@
       <c r="H33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>BR-03770/2026</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="N33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="10" t="n">
+      <c r="O33" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="10" t="n">
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="R33" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R33" s="9" t="n"/>
-      <c r="S33" s="10" t="n">
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T33" s="10" t="n">
+      <c r="U33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U33" s="9" t="n"/>
       <c r="V33" s="9" t="n"/>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X33" s="9" t="n"/>
-      <c r="Y33" s="10" t="n">
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z33" s="10" t="n">
+      <c r="AA33" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13488,56 +13526,57 @@
       <c r="H34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>BR-03770/2026</t>
         </is>
       </c>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M34" s="9" t="n"/>
       <c r="N34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="O34" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="R34" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R34" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T34" s="10" t="n">
+      <c r="U34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U34" s="9" t="n"/>
-      <c r="V34" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V34" s="9" t="n"/>
       <c r="W34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X34" s="9" t="n"/>
-      <c r="Y34" s="10" t="n">
+      <c r="Y34" s="9" t="n"/>
+      <c r="Z34" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z34" s="10" t="n">
+      <c r="AA34" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13576,52 +13615,53 @@
       <c r="H35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>BR-00605/2026</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="N35" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="N35" s="10" t="n">
+      <c r="O35" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="10" t="n">
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="10" t="n">
         <v>40.4</v>
       </c>
-      <c r="T35" s="10" t="n">
+      <c r="U35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="10" t="n">
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" s="10" t="n">
+      <c r="AA35" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -13660,58 +13700,59 @@
       <c r="H36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>URA (telefone)</t>
         </is>
       </c>
-      <c r="J36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>BR-01960/2026</t>
         </is>
       </c>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N36" s="10" t="n">
+      <c r="O36" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="O36" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="10" t="n">
         <v>35.9</v>
       </c>
-      <c r="R36" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="T36" s="10" t="n">
+      <c r="U36" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="U36" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="W36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="X36" s="9" t="n"/>
-      <c r="Y36" s="10" t="n">
+      <c r="Y36" s="9" t="n"/>
+      <c r="Z36" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="Z36" s="10" t="n">
+      <c r="AA36" s="10" t="n">
         <v>15.9</v>
       </c>
     </row>
@@ -13750,52 +13791,53 @@
       <c r="H37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>BR-00873/2026</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="N37" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="O37" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10" t="n">
         <v>37.8</v>
       </c>
-      <c r="R37" s="9" t="n"/>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="10" t="n">
         <v>41.3</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="U37" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X37" s="9" t="n"/>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="9" t="n"/>
+      <c r="Z37" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z37" s="10" t="n">
+      <c r="AA37" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13834,52 +13876,53 @@
       <c r="H38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>BR-00873/2026</t>
         </is>
       </c>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N38" s="10" t="n">
+      <c r="O38" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="O38" s="10" t="n">
+      <c r="P38" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="P38" s="10" t="n">
+      <c r="Q38" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="R38" s="10" t="n">
         <v>35.1</v>
       </c>
-      <c r="R38" s="9" t="n"/>
-      <c r="S38" s="10" t="n">
+      <c r="S38" s="9" t="n"/>
+      <c r="T38" s="10" t="n">
         <v>40.8</v>
       </c>
-      <c r="T38" s="10" t="n">
+      <c r="U38" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="U38" s="9" t="n"/>
       <c r="V38" s="9" t="n"/>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="X38" s="9" t="n"/>
-      <c r="Y38" s="10" t="n">
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="10" t="n">
         <v>6.7</v>
       </c>
-      <c r="Z38" s="10" t="n">
+      <c r="AA38" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
@@ -13918,56 +13961,57 @@
       <c r="H39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>BR-00873/2026</t>
         </is>
       </c>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N39" s="10" t="n">
+      <c r="O39" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="O39" s="10" t="n">
+      <c r="P39" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="P39" s="10" t="n">
+      <c r="Q39" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="R39" s="10" t="n">
         <v>35.1</v>
       </c>
-      <c r="R39" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="10" t="n">
         <v>40.8</v>
       </c>
-      <c r="T39" s="10" t="n">
+      <c r="U39" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="U39" s="9" t="n"/>
-      <c r="V39" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V39" s="9" t="n"/>
       <c r="W39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="X39" s="9" t="n"/>
-      <c r="Y39" s="10" t="n">
+      <c r="Y39" s="9" t="n"/>
+      <c r="Z39" s="10" t="n">
         <v>6.7</v>
       </c>
-      <c r="Z39" s="10" t="n">
+      <c r="AA39" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
@@ -14006,56 +14050,57 @@
       <c r="H40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>BR-07875/2026</t>
         </is>
       </c>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M40" s="9" t="n"/>
       <c r="N40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="O40" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="R40" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="T40" s="10" t="n">
+      <c r="U40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U40" s="9" t="n"/>
-      <c r="V40" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V40" s="9" t="n"/>
       <c r="W40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X40" s="9" t="n"/>
-      <c r="Y40" s="10" t="n">
+      <c r="Y40" s="9" t="n"/>
+      <c r="Z40" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z40" s="10" t="n">
+      <c r="AA40" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14094,46 +14139,47 @@
       <c r="H41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>BR-02846/2026</t>
         </is>
       </c>
-      <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="R41" s="9" t="n"/>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T41" s="10" t="n">
+      <c r="U41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X41" s="9" t="n"/>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="9" t="n"/>
+      <c r="Z41" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Z41" s="10" t="n">
+      <c r="AA41" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -14172,46 +14218,47 @@
       <c r="H42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>BR-02846/2026</t>
         </is>
       </c>
-      <c r="L42" s="9" t="n"/>
       <c r="M42" s="9" t="n"/>
       <c r="N42" s="9" t="n"/>
       <c r="O42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="R42" s="9" t="n"/>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="9" t="n"/>
+      <c r="T42" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="U42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U42" s="9" t="n"/>
       <c r="V42" s="9" t="n"/>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X42" s="9" t="n"/>
-      <c r="Y42" s="10" t="n">
-        <v>4</v>
-      </c>
+      <c r="Y42" s="9" t="n"/>
       <c r="Z42" s="10" t="n">
         <v>4</v>
       </c>
+      <c r="AA42" s="10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -14248,52 +14295,53 @@
       <c r="H43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>BR-04227/2026</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="N43" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="N43" s="10" t="n">
+      <c r="O43" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10" t="n">
         <v>40.1</v>
       </c>
-      <c r="R43" s="9" t="n"/>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="9" t="n"/>
+      <c r="T43" s="10" t="n">
         <v>45.9</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="U43" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="X43" s="9" t="n"/>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="AA43" s="10" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -14332,48 +14380,49 @@
       <c r="H44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>BR-06058/2026</t>
         </is>
       </c>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="9" t="n"/>
+      <c r="N44" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="O44" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="9" t="n"/>
+      <c r="R44" s="10" t="n">
         <v>40.1</v>
       </c>
-      <c r="R44" s="9" t="n"/>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="9" t="n"/>
+      <c r="T44" s="10" t="n">
         <v>45.9</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="U44" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="U44" s="9" t="n"/>
       <c r="V44" s="9" t="n"/>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="9" t="n"/>
+      <c r="X44" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="X44" s="9" t="n"/>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="9" t="n"/>
+      <c r="Z44" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z44" s="10" t="n">
+      <c r="AA44" s="10" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -14412,52 +14461,53 @@
       <c r="H45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>BR-00386/2026</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr">
+      <c r="M45" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="N45" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="N45" s="10" t="n">
+      <c r="O45" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="10" t="n">
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R45" s="9" t="n"/>
-      <c r="S45" s="10" t="n">
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="10" t="n">
         <v>40.3</v>
       </c>
-      <c r="T45" s="10" t="n">
+      <c r="U45" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X45" s="9" t="n"/>
-      <c r="Y45" s="10" t="n">
+      <c r="Y45" s="9" t="n"/>
+      <c r="Z45" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="Z45" s="10" t="n">
+      <c r="AA45" s="10" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -14496,52 +14546,53 @@
       <c r="H46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>BR-05809/2026</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="N46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="O46" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O46" s="9" t="n"/>
       <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n"/>
+      <c r="R46" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R46" s="9" t="n"/>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="9" t="n"/>
+      <c r="T46" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="U46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U46" s="9" t="n"/>
       <c r="V46" s="9" t="n"/>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n"/>
+      <c r="X46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="X46" s="9" t="n"/>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="9" t="n"/>
+      <c r="Z46" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="AA46" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14580,52 +14631,53 @@
       <c r="H47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>BR-03715/2026</t>
         </is>
       </c>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="N47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N47" s="10" t="n">
+      <c r="O47" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="10" t="n">
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R47" s="9" t="n"/>
-      <c r="S47" s="10" t="n">
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="U47" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
-      <c r="W47" s="10" t="n">
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X47" s="9" t="n"/>
-      <c r="Y47" s="10" t="n">
+      <c r="Y47" s="9" t="n"/>
+      <c r="Z47" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z47" s="10" t="n">
+      <c r="AA47" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14664,56 +14716,57 @@
       <c r="H48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>BR-03715/2026</t>
         </is>
       </c>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="9" t="n"/>
+      <c r="N48" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="O48" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O48" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="P48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R48" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="U48" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="U48" s="9" t="n"/>
-      <c r="V48" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V48" s="9" t="n"/>
       <c r="W48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X48" s="9" t="n"/>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="9" t="n"/>
+      <c r="Z48" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="AA48" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14752,48 +14805,49 @@
       <c r="H49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>BR-09353/2026</t>
         </is>
       </c>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R49" s="9" t="n"/>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="U49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="X49" s="9" t="n"/>
-      <c r="Y49" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="Y49" s="9" t="n"/>
       <c r="Z49" s="10" t="n">
         <v>7</v>
       </c>
+      <c r="AA49" s="10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -14830,48 +14884,49 @@
       <c r="H50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
         <is>
           <t>BR-09353/2026</t>
         </is>
       </c>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="9" t="n"/>
+      <c r="N50" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="O50" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="O50" s="9" t="n"/>
       <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R50" s="9" t="n"/>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="9" t="n"/>
+      <c r="T50" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="U50" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U50" s="9" t="n"/>
       <c r="V50" s="9" t="n"/>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="9" t="n"/>
+      <c r="X50" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X50" s="9" t="n"/>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="9" t="n"/>
+      <c r="Z50" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="AA50" s="10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -14910,52 +14965,53 @@
       <c r="H51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
         <is>
           <t>BR-07974/2026</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr">
+      <c r="M51" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
         </is>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="N51" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="O51" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="10" t="n">
         <v>36.6</v>
       </c>
-      <c r="R51" s="9" t="n"/>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="10" t="n">
         <v>40.5</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="U51" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
-      <c r="W51" s="10" t="n">
+      <c r="W51" s="9" t="n"/>
+      <c r="X51" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="X51" s="9" t="n"/>
-      <c r="Y51" s="10" t="n">
+      <c r="Y51" s="9" t="n"/>
+      <c r="Z51" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z51" s="10" t="n">
+      <c r="AA51" s="10" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -14994,52 +15050,53 @@
       <c r="H52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="9" t="inlineStr">
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>BR-07974/2026</t>
         </is>
       </c>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="9" t="n"/>
+      <c r="N52" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N52" s="10" t="n">
+      <c r="O52" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="O52" s="10" t="n">
+      <c r="P52" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="P52" s="10" t="n">
+      <c r="Q52" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q52" s="10" t="n">
+      <c r="R52" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="10" t="n">
+      <c r="S52" s="9" t="n"/>
+      <c r="T52" s="10" t="n">
         <v>40.2</v>
       </c>
-      <c r="T52" s="10" t="n">
+      <c r="U52" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="U52" s="9" t="n"/>
       <c r="V52" s="9" t="n"/>
-      <c r="W52" s="10" t="n">
+      <c r="W52" s="9" t="n"/>
+      <c r="X52" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="X52" s="9" t="n"/>
-      <c r="Y52" s="10" t="n">
+      <c r="Y52" s="9" t="n"/>
+      <c r="Z52" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z52" s="10" t="n">
+      <c r="AA52" s="10" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -15078,56 +15135,57 @@
       <c r="H53" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>BR-07974/2026</t>
         </is>
       </c>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="10" t="n">
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N53" s="10" t="n">
+      <c r="O53" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="O53" s="10" t="n">
+      <c r="P53" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="P53" s="10" t="n">
+      <c r="Q53" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q53" s="10" t="n">
+      <c r="R53" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="R53" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="10" t="n">
         <v>40.2</v>
       </c>
-      <c r="T53" s="10" t="n">
+      <c r="U53" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="U53" s="9" t="n"/>
-      <c r="V53" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V53" s="9" t="n"/>
       <c r="W53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="X53" s="9" t="n"/>
-      <c r="Y53" s="10" t="n">
+      <c r="Y53" s="9" t="n"/>
+      <c r="Z53" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z53" s="10" t="n">
+      <c r="AA53" s="10" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -15166,52 +15224,53 @@
       <c r="H54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>BR-07600/2026</t>
         </is>
       </c>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M54" s="10" t="n">
+      <c r="N54" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="N54" s="10" t="n">
+      <c r="O54" s="10" t="n">
         <v>4.9</v>
       </c>
-      <c r="O54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="10" t="n">
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="10" t="n">
         <v>37.9</v>
       </c>
-      <c r="R54" s="9" t="n"/>
-      <c r="S54" s="10" t="n">
+      <c r="S54" s="9" t="n"/>
+      <c r="T54" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T54" s="10" t="n">
+      <c r="U54" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="U54" s="9" t="n"/>
       <c r="V54" s="9" t="n"/>
-      <c r="W54" s="10" t="n">
+      <c r="W54" s="9" t="n"/>
+      <c r="X54" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="X54" s="9" t="n"/>
-      <c r="Y54" s="10" t="n">
+      <c r="Y54" s="9" t="n"/>
+      <c r="Z54" s="10" t="n">
         <v>3.8</v>
       </c>
-      <c r="Z54" s="10" t="n">
+      <c r="AA54" s="10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15250,50 +15309,51 @@
       <c r="H55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
         <is>
           <t>BR-05112/2026</t>
         </is>
       </c>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="10" t="n">
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="N55" s="10" t="n">
+      <c r="O55" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="O55" s="10" t="n">
+      <c r="P55" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="10" t="n">
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="10" t="n">
         <v>38.9</v>
       </c>
-      <c r="R55" s="9" t="n"/>
-      <c r="S55" s="10" t="n">
+      <c r="S55" s="9" t="n"/>
+      <c r="T55" s="10" t="n">
         <v>45.2</v>
       </c>
-      <c r="T55" s="10" t="n">
+      <c r="U55" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
-      <c r="W55" s="10" t="n">
+      <c r="W55" s="9" t="n"/>
+      <c r="X55" s="10" t="n">
         <v>3.8</v>
       </c>
-      <c r="X55" s="9" t="n"/>
-      <c r="Y55" s="10" t="n">
+      <c r="Y55" s="9" t="n"/>
+      <c r="Z55" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z55" s="10" t="n">
+      <c r="AA55" s="10" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -15332,46 +15392,47 @@
       <c r="H56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I56" s="9" t="inlineStr">
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>BR-07600/2026</t>
         </is>
       </c>
-      <c r="L56" s="9" t="n"/>
-      <c r="M56" s="10" t="n">
+      <c r="M56" s="9" t="n"/>
+      <c r="N56" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="N56" s="9" t="n"/>
       <c r="O56" s="9" t="n"/>
       <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="10" t="n">
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="R56" s="9" t="n"/>
-      <c r="S56" s="10" t="n">
+      <c r="S56" s="9" t="n"/>
+      <c r="T56" s="10" t="n">
         <v>45.1</v>
       </c>
-      <c r="T56" s="10" t="n">
+      <c r="U56" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="U56" s="9" t="n"/>
       <c r="V56" s="9" t="n"/>
-      <c r="W56" s="10" t="n">
+      <c r="W56" s="9" t="n"/>
+      <c r="X56" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="X56" s="9" t="n"/>
-      <c r="Y56" s="10" t="n">
+      <c r="Y56" s="9" t="n"/>
+      <c r="Z56" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Z56" s="10" t="n">
+      <c r="AA56" s="10" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -15410,54 +15471,55 @@
       <c r="H57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
         <is>
           <t>BR-08165/2026</t>
         </is>
       </c>
-      <c r="L57" s="9" t="n"/>
-      <c r="M57" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="M57" s="9" t="n"/>
       <c r="N57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="O57" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="P57" s="10" t="n">
         <v>1</v>
       </c>
       <c r="Q57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R57" s="9" t="n"/>
-      <c r="S57" s="10" t="n">
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="T57" s="10" t="n">
+      <c r="U57" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U57" s="9" t="n"/>
-      <c r="V57" s="10" t="n">
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="W57" s="10" t="n">
+      <c r="X57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X57" s="9" t="n"/>
-      <c r="Y57" s="10" t="n">
+      <c r="Y57" s="9" t="n"/>
+      <c r="Z57" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z57" s="10" t="n">
+      <c r="AA57" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -15496,50 +15558,51 @@
       <c r="H58" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="9" t="inlineStr">
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
         <is>
           <t>BR-00249/2026</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
+      <c r="M58" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M58" s="10" t="n">
+      <c r="N58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="10" t="n">
+      <c r="O58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O58" s="9" t="n"/>
       <c r="P58" s="9" t="n"/>
-      <c r="Q58" s="10" t="n">
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R58" s="9" t="n"/>
-      <c r="S58" s="10" t="n">
+      <c r="S58" s="9" t="n"/>
+      <c r="T58" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T58" s="10" t="n">
+      <c r="U58" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U58" s="9" t="n"/>
       <c r="V58" s="9" t="n"/>
       <c r="W58" s="9" t="n"/>
       <c r="X58" s="9" t="n"/>
-      <c r="Y58" s="10" t="n">
+      <c r="Y58" s="9" t="n"/>
+      <c r="Z58" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Z58" s="10" t="n">
+      <c r="AA58" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -15578,40 +15641,41 @@
       <c r="H59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>BR-06428/2026</t>
         </is>
       </c>
-      <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
       <c r="O59" s="9" t="n"/>
       <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="10" t="n">
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="R59" s="9" t="n"/>
-      <c r="S59" s="10" t="n">
+      <c r="S59" s="9" t="n"/>
+      <c r="T59" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
       <c r="V59" s="9" t="n"/>
       <c r="W59" s="9" t="n"/>
       <c r="X59" s="9" t="n"/>
-      <c r="Y59" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y59" s="9" t="n"/>
       <c r="Z59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15650,44 +15714,45 @@
       <c r="H60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="9" t="inlineStr">
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>BR-06428/2026</t>
         </is>
       </c>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="10" t="n">
+      <c r="M60" s="9" t="n"/>
+      <c r="N60" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N60" s="9" t="n"/>
       <c r="O60" s="9" t="n"/>
       <c r="P60" s="9" t="n"/>
-      <c r="Q60" s="10" t="n">
+      <c r="Q60" s="9" t="n"/>
+      <c r="R60" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R60" s="9" t="n"/>
-      <c r="S60" s="10" t="n">
+      <c r="S60" s="9" t="n"/>
+      <c r="T60" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T60" s="9" t="n"/>
       <c r="U60" s="9" t="n"/>
       <c r="V60" s="9" t="n"/>
-      <c r="W60" s="10" t="n">
+      <c r="W60" s="9" t="n"/>
+      <c r="X60" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X60" s="9" t="n"/>
-      <c r="Y60" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y60" s="9" t="n"/>
       <c r="Z60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15726,42 +15791,43 @@
       <c r="H61" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
         <is>
           <t>BR-06428/2026</t>
         </is>
       </c>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="10" t="n">
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="N61" s="9" t="n"/>
       <c r="O61" s="9" t="n"/>
       <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="10" t="n">
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R61" s="9" t="n"/>
-      <c r="S61" s="10" t="n">
+      <c r="S61" s="9" t="n"/>
+      <c r="T61" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T61" s="9" t="n"/>
       <c r="U61" s="9" t="n"/>
       <c r="V61" s="9" t="n"/>
-      <c r="W61" s="10" t="n">
+      <c r="W61" s="9" t="n"/>
+      <c r="X61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X61" s="9" t="n"/>
       <c r="Y61" s="9" t="n"/>
       <c r="Z61" s="9" t="n"/>
+      <c r="AA61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -15798,52 +15864,53 @@
       <c r="H62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>BR-08425/2026</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
+      <c r="M62" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M62" s="10" t="n">
+      <c r="N62" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="N62" s="10" t="n">
+      <c r="O62" s="10" t="n">
         <v>5.1</v>
       </c>
-      <c r="O62" s="9" t="n"/>
       <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="10" t="n">
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R62" s="9" t="n"/>
-      <c r="S62" s="10" t="n">
+      <c r="S62" s="9" t="n"/>
+      <c r="T62" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="T62" s="10" t="n">
+      <c r="U62" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U62" s="9" t="n"/>
       <c r="V62" s="9" t="n"/>
-      <c r="W62" s="10" t="n">
+      <c r="W62" s="9" t="n"/>
+      <c r="X62" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="X62" s="9" t="n"/>
-      <c r="Y62" s="10" t="n">
+      <c r="Y62" s="9" t="n"/>
+      <c r="Z62" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z62" s="10" t="n">
+      <c r="AA62" s="10" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -15882,40 +15949,41 @@
       <c r="H63" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
         <is>
           <t>BR-04519/2026</t>
         </is>
       </c>
-      <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
       <c r="O63" s="9" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="10" t="n">
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R63" s="9" t="n"/>
-      <c r="S63" s="10" t="n">
+      <c r="S63" s="9" t="n"/>
+      <c r="T63" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T63" s="9" t="n"/>
       <c r="U63" s="9" t="n"/>
       <c r="V63" s="9" t="n"/>
       <c r="W63" s="9" t="n"/>
       <c r="X63" s="9" t="n"/>
-      <c r="Y63" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y63" s="9" t="n"/>
       <c r="Z63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15954,54 +16022,55 @@
       <c r="H64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="9" t="inlineStr">
+      <c r="I64" s="9" t="n"/>
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>BR-08254/2026</t>
         </is>
       </c>
-      <c r="L64" s="9" t="inlineStr">
+      <c r="M64" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="N64" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="N64" s="10" t="n">
+      <c r="O64" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O64" s="9" t="n"/>
       <c r="P64" s="9" t="n"/>
-      <c r="Q64" s="10" t="n">
+      <c r="Q64" s="9" t="n"/>
+      <c r="R64" s="10" t="n">
         <v>33.1</v>
       </c>
-      <c r="R64" s="9" t="n"/>
-      <c r="S64" s="10" t="n">
+      <c r="S64" s="9" t="n"/>
+      <c r="T64" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T64" s="10" t="n">
+      <c r="U64" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="U64" s="9" t="n"/>
       <c r="V64" s="9" t="n"/>
-      <c r="W64" s="10" t="n">
+      <c r="W64" s="9" t="n"/>
+      <c r="X64" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="X64" s="10" t="n">
+      <c r="Y64" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="Y64" s="10" t="n">
+      <c r="Z64" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z64" s="10" t="n">
+      <c r="AA64" s="10" t="n">
         <v>4.7</v>
       </c>
     </row>
@@ -16040,52 +16109,53 @@
       <c r="H65" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
         <is>
           <t>BR-08254/2026</t>
         </is>
       </c>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N65" s="10" t="n">
+      <c r="O65" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O65" s="10" t="n">
+      <c r="P65" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="P65" s="10" t="n">
+      <c r="Q65" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q65" s="10" t="n">
+      <c r="R65" s="10" t="n">
         <v>33.1</v>
       </c>
-      <c r="R65" s="9" t="n"/>
-      <c r="S65" s="10" t="n">
+      <c r="S65" s="9" t="n"/>
+      <c r="T65" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T65" s="10" t="n">
+      <c r="U65" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="U65" s="9" t="n"/>
       <c r="V65" s="9" t="n"/>
-      <c r="W65" s="10" t="n">
+      <c r="W65" s="9" t="n"/>
+      <c r="X65" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="X65" s="9" t="n"/>
-      <c r="Y65" s="10" t="n">
+      <c r="Y65" s="9" t="n"/>
+      <c r="Z65" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z65" s="10" t="n">
+      <c r="AA65" s="10" t="n">
         <v>10.6</v>
       </c>
     </row>
@@ -16124,56 +16194,57 @@
       <c r="H66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="9" t="inlineStr">
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>BR-08254/2026</t>
         </is>
       </c>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="10" t="n">
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="N66" s="10" t="n">
+      <c r="O66" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O66" s="10" t="n">
+      <c r="P66" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="P66" s="10" t="n">
+      <c r="Q66" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q66" s="10" t="n">
+      <c r="R66" s="10" t="n">
         <v>33.1</v>
       </c>
-      <c r="R66" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T66" s="10" t="n">
+      <c r="U66" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="U66" s="9" t="n"/>
-      <c r="V66" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V66" s="9" t="n"/>
       <c r="W66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="X66" s="9" t="n"/>
-      <c r="Y66" s="10" t="n">
+      <c r="Y66" s="9" t="n"/>
+      <c r="Z66" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z66" s="10" t="n">
+      <c r="AA66" s="10" t="n">
         <v>10.6</v>
       </c>
     </row>
@@ -16212,52 +16283,53 @@
       <c r="H67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="9" t="inlineStr">
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>BR-02804/2026</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr">
+      <c r="M67" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-atlasintel-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="N67" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="10" t="n">
+      <c r="O67" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="O67" s="9" t="n"/>
       <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="10" t="n">
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="R67" s="9" t="n"/>
-      <c r="S67" s="10" t="n">
+      <c r="S67" s="9" t="n"/>
+      <c r="T67" s="10" t="n">
         <v>48.8</v>
       </c>
-      <c r="T67" s="10" t="n">
+      <c r="U67" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="U67" s="9" t="n"/>
       <c r="V67" s="9" t="n"/>
-      <c r="W67" s="10" t="n">
+      <c r="W67" s="9" t="n"/>
+      <c r="X67" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="X67" s="9" t="n"/>
-      <c r="Y67" s="10" t="n">
+      <c r="Y67" s="9" t="n"/>
+      <c r="Z67" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z67" s="10" t="n">
+      <c r="AA67" s="10" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -16296,50 +16368,51 @@
       <c r="H68" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I68" s="9" t="inlineStr">
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="9" t="n"/>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="9" t="n"/>
+      <c r="M68" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M68" s="10" t="n">
+      <c r="N68" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="N68" s="10" t="n">
+      <c r="O68" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="O68" s="9" t="n"/>
       <c r="P68" s="9" t="n"/>
-      <c r="Q68" s="10" t="n">
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="10" t="n">
         <v>34.3</v>
       </c>
-      <c r="R68" s="9" t="n"/>
-      <c r="S68" s="10" t="n">
+      <c r="S68" s="9" t="n"/>
+      <c r="T68" s="10" t="n">
         <v>35.4</v>
       </c>
-      <c r="T68" s="10" t="n">
+      <c r="U68" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="U68" s="9" t="n"/>
       <c r="V68" s="9" t="n"/>
-      <c r="W68" s="10" t="n">
+      <c r="W68" s="9" t="n"/>
+      <c r="X68" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="X68" s="10" t="n">
+      <c r="Y68" s="10" t="n">
         <v>9.1</v>
       </c>
-      <c r="Y68" s="10" t="n">
+      <c r="Z68" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z68" s="10" t="n">
+      <c r="AA68" s="10" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -16378,52 +16451,53 @@
       <c r="H69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
         <is>
           <t>BR-06845/2026</t>
         </is>
       </c>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="10" t="n">
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N69" s="10" t="n">
+      <c r="O69" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="O69" s="10" t="n">
+      <c r="P69" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="P69" s="10" t="n">
+      <c r="Q69" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q69" s="10" t="n">
+      <c r="R69" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R69" s="9" t="n"/>
-      <c r="S69" s="10" t="n">
+      <c r="S69" s="9" t="n"/>
+      <c r="T69" s="10" t="n">
         <v>38.5</v>
       </c>
-      <c r="T69" s="10" t="n">
+      <c r="U69" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U69" s="9" t="n"/>
       <c r="V69" s="9" t="n"/>
-      <c r="W69" s="10" t="n">
+      <c r="W69" s="9" t="n"/>
+      <c r="X69" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="X69" s="9" t="n"/>
-      <c r="Y69" s="10" t="n">
+      <c r="Y69" s="9" t="n"/>
+      <c r="Z69" s="10" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z69" s="10" t="n">
+      <c r="AA69" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -16462,56 +16536,57 @@
       <c r="H70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I70" s="9" t="inlineStr">
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>BR-06845/2026</t>
         </is>
       </c>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="9" t="n"/>
+      <c r="N70" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="O70" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="O70" s="10" t="n">
+      <c r="P70" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="P70" s="10" t="n">
+      <c r="Q70" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q70" s="10" t="n">
+      <c r="R70" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R70" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="10" t="n">
         <v>38.5</v>
       </c>
-      <c r="T70" s="10" t="n">
+      <c r="U70" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U70" s="9" t="n"/>
-      <c r="V70" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="V70" s="9" t="n"/>
       <c r="W70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="X70" s="9" t="n"/>
-      <c r="Y70" s="10" t="n">
+      <c r="Y70" s="9" t="n"/>
+      <c r="Z70" s="10" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z70" s="10" t="n">
+      <c r="AA70" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -16550,52 +16625,53 @@
       <c r="H71" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="9" t="n"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
         <is>
           <t>BR-06731/2026</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="M71" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="N71" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="N71" s="10" t="n">
+      <c r="O71" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O71" s="9" t="n"/>
       <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="10" t="n">
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="R71" s="9" t="n"/>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="9" t="n"/>
+      <c r="T71" s="10" t="n">
         <v>39.6</v>
       </c>
-      <c r="T71" s="10" t="n">
+      <c r="U71" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U71" s="9" t="n"/>
       <c r="V71" s="9" t="n"/>
-      <c r="W71" s="10" t="n">
+      <c r="W71" s="9" t="n"/>
+      <c r="X71" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="X71" s="9" t="n"/>
-      <c r="Y71" s="10" t="n">
+      <c r="Y71" s="9" t="n"/>
+      <c r="Z71" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z71" s="10" t="n">
+      <c r="AA71" s="10" t="n">
         <v>12.9</v>
       </c>
     </row>
@@ -16634,46 +16710,47 @@
       <c r="H72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="9" t="inlineStr">
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
         <is>
           <t>BR-06731/2026</t>
         </is>
       </c>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="9" t="n"/>
+      <c r="N72" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="N72" s="10" t="n">
+      <c r="O72" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O72" s="9" t="n"/>
       <c r="P72" s="9" t="n"/>
       <c r="Q72" s="9" t="n"/>
       <c r="R72" s="9" t="n"/>
-      <c r="S72" s="10" t="n">
+      <c r="S72" s="9" t="n"/>
+      <c r="T72" s="10" t="n">
         <v>40.2</v>
       </c>
-      <c r="T72" s="10" t="n">
+      <c r="U72" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U72" s="9" t="n"/>
       <c r="V72" s="9" t="n"/>
-      <c r="W72" s="10" t="n">
+      <c r="W72" s="9" t="n"/>
+      <c r="X72" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="X72" s="9" t="n"/>
-      <c r="Y72" s="10" t="n">
+      <c r="Y72" s="9" t="n"/>
+      <c r="Z72" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="Z72" s="10" t="n">
+      <c r="AA72" s="10" t="n">
         <v>11.8</v>
       </c>
     </row>
@@ -16712,50 +16789,51 @@
       <c r="H73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I73" s="9" t="inlineStr">
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="K73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
         <is>
           <t>BR-00835/2026</t>
         </is>
       </c>
-      <c r="L73" s="9" t="inlineStr">
+      <c r="M73" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M73" s="10" t="n">
+      <c r="N73" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="N73" s="9" t="n"/>
       <c r="O73" s="9" t="n"/>
       <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="10" t="n">
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R73" s="9" t="n"/>
-      <c r="S73" s="10" t="n">
+      <c r="S73" s="9" t="n"/>
+      <c r="T73" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T73" s="10" t="n">
+      <c r="U73" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="U73" s="9" t="n"/>
       <c r="V73" s="9" t="n"/>
-      <c r="W73" s="10" t="n">
+      <c r="W73" s="9" t="n"/>
+      <c r="X73" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X73" s="9" t="n"/>
-      <c r="Y73" s="10" t="n">
+      <c r="Y73" s="9" t="n"/>
+      <c r="Z73" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Z73" s="10" t="n">
+      <c r="AA73" s="10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16794,40 +16872,41 @@
       <c r="H74" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="9" t="inlineStr">
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
         <is>
           <t>BR-04193/2026</t>
         </is>
       </c>
-      <c r="L74" s="9" t="n"/>
       <c r="M74" s="9" t="n"/>
       <c r="N74" s="9" t="n"/>
       <c r="O74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="10" t="n">
+      <c r="Q74" s="9" t="n"/>
+      <c r="R74" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R74" s="9" t="n"/>
-      <c r="S74" s="10" t="n">
+      <c r="S74" s="9" t="n"/>
+      <c r="T74" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="T74" s="9" t="n"/>
       <c r="U74" s="9" t="n"/>
       <c r="V74" s="9" t="n"/>
       <c r="W74" s="9" t="n"/>
       <c r="X74" s="9" t="n"/>
-      <c r="Y74" s="10" t="n">
+      <c r="Y74" s="9" t="n"/>
+      <c r="Z74" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z74" s="10" t="n">
+      <c r="AA74" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16866,40 +16945,41 @@
       <c r="H75" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
         <is>
           <t>BR-07971/2026</t>
         </is>
       </c>
-      <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="10" t="n">
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="R75" s="9" t="n"/>
-      <c r="S75" s="10" t="n">
+      <c r="S75" s="9" t="n"/>
+      <c r="T75" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T75" s="9" t="n"/>
       <c r="U75" s="9" t="n"/>
       <c r="V75" s="9" t="n"/>
       <c r="W75" s="9" t="n"/>
       <c r="X75" s="9" t="n"/>
-      <c r="Y75" s="10" t="n">
+      <c r="Y75" s="9" t="n"/>
+      <c r="Z75" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z75" s="10" t="n">
+      <c r="AA75" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16938,40 +17018,41 @@
       <c r="H76" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I76" s="9" t="inlineStr">
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
         <is>
           <t>BR-06529/2026</t>
         </is>
       </c>
-      <c r="L76" s="9" t="n"/>
       <c r="M76" s="9" t="n"/>
       <c r="N76" s="9" t="n"/>
       <c r="O76" s="9" t="n"/>
       <c r="P76" s="9" t="n"/>
-      <c r="Q76" s="10" t="n">
+      <c r="Q76" s="9" t="n"/>
+      <c r="R76" s="10" t="n">
         <v>42.2</v>
       </c>
-      <c r="R76" s="9" t="n"/>
-      <c r="S76" s="10" t="n">
+      <c r="S76" s="9" t="n"/>
+      <c r="T76" s="10" t="n">
         <v>47.7</v>
       </c>
-      <c r="T76" s="9" t="n"/>
       <c r="U76" s="9" t="n"/>
       <c r="V76" s="9" t="n"/>
       <c r="W76" s="9" t="n"/>
       <c r="X76" s="9" t="n"/>
-      <c r="Y76" s="10" t="n">
+      <c r="Y76" s="9" t="n"/>
+      <c r="Z76" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z76" s="10" t="n">
+      <c r="AA76" s="10" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -17010,44 +17091,45 @@
       <c r="H77" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
         <is>
           <t>BR-07489/2026</t>
         </is>
       </c>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="M77" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026-2/</t>
         </is>
       </c>
-      <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
       <c r="O77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="10" t="n">
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R77" s="9" t="n"/>
-      <c r="S77" s="10" t="n">
+      <c r="S77" s="9" t="n"/>
+      <c r="T77" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="T77" s="9" t="n"/>
       <c r="U77" s="9" t="n"/>
       <c r="V77" s="9" t="n"/>
       <c r="W77" s="9" t="n"/>
       <c r="X77" s="9" t="n"/>
-      <c r="Y77" s="10" t="n">
+      <c r="Y77" s="9" t="n"/>
+      <c r="Z77" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z77" s="10" t="n">
+      <c r="AA77" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17086,40 +17168,41 @@
       <c r="H78" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I78" s="9" t="n"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>BR-02416/2026</t>
         </is>
       </c>
-      <c r="L78" s="9" t="n"/>
       <c r="M78" s="9" t="n"/>
       <c r="N78" s="9" t="n"/>
       <c r="O78" s="9" t="n"/>
       <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="10" t="n">
+      <c r="Q78" s="9" t="n"/>
+      <c r="R78" s="10" t="n">
         <v>38.1</v>
       </c>
-      <c r="R78" s="9" t="n"/>
-      <c r="S78" s="10" t="n">
+      <c r="S78" s="9" t="n"/>
+      <c r="T78" s="10" t="n">
         <v>46.8</v>
       </c>
-      <c r="T78" s="9" t="n"/>
       <c r="U78" s="9" t="n"/>
       <c r="V78" s="9" t="n"/>
       <c r="W78" s="9" t="n"/>
       <c r="X78" s="9" t="n"/>
-      <c r="Y78" s="10" t="n">
+      <c r="Y78" s="9" t="n"/>
+      <c r="Z78" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="Z78" s="10" t="n">
+      <c r="AA78" s="10" t="n">
         <v>6.4</v>
       </c>
     </row>
@@ -17158,44 +17241,45 @@
       <c r="H79" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L79" s="9" t="inlineStr">
+      <c r="M79" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
       <c r="O79" s="9" t="n"/>
       <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="10" t="n">
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="R79" s="9" t="n"/>
-      <c r="S79" s="10" t="n">
+      <c r="S79" s="9" t="n"/>
+      <c r="T79" s="10" t="n">
         <v>48.9</v>
       </c>
-      <c r="T79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
       <c r="V79" s="9" t="n"/>
       <c r="W79" s="9" t="n"/>
       <c r="X79" s="9" t="n"/>
-      <c r="Y79" s="10" t="n">
+      <c r="Y79" s="9" t="n"/>
+      <c r="Z79" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="Z79" s="9" t="n"/>
+      <c r="AA79" s="9" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -17232,40 +17316,41 @@
       <c r="H80" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="9" t="inlineStr">
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L80" s="9" t="n"/>
       <c r="M80" s="9" t="n"/>
       <c r="N80" s="9" t="n"/>
       <c r="O80" s="9" t="n"/>
       <c r="P80" s="9" t="n"/>
-      <c r="Q80" s="10" t="n">
+      <c r="Q80" s="9" t="n"/>
+      <c r="R80" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="R80" s="9" t="n"/>
-      <c r="S80" s="10" t="n">
+      <c r="S80" s="9" t="n"/>
+      <c r="T80" s="10" t="n">
         <v>48.9</v>
       </c>
-      <c r="T80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
       <c r="V80" s="9" t="n"/>
       <c r="W80" s="9" t="n"/>
       <c r="X80" s="9" t="n"/>
-      <c r="Y80" s="10" t="n">
+      <c r="Y80" s="9" t="n"/>
+      <c r="Z80" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="Z80" s="10" t="n">
+      <c r="AA80" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17304,44 +17389,45 @@
       <c r="H81" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>BR-00290/2026</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
+      <c r="M81" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="9" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="10" t="n">
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R81" s="9" t="n"/>
-      <c r="S81" s="10" t="n">
+      <c r="S81" s="9" t="n"/>
+      <c r="T81" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
       <c r="W81" s="9" t="n"/>
       <c r="X81" s="9" t="n"/>
-      <c r="Y81" s="10" t="n">
+      <c r="Y81" s="9" t="n"/>
+      <c r="Z81" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z81" s="10" t="n">
+      <c r="AA81" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17380,40 +17466,41 @@
       <c r="H82" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>BR-03369/2026</t>
         </is>
       </c>
-      <c r="L82" s="9" t="n"/>
       <c r="M82" s="9" t="n"/>
       <c r="N82" s="9" t="n"/>
       <c r="O82" s="9" t="n"/>
       <c r="P82" s="9" t="n"/>
-      <c r="Q82" s="10" t="n">
+      <c r="Q82" s="9" t="n"/>
+      <c r="R82" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="R82" s="9" t="n"/>
-      <c r="S82" s="10" t="n">
+      <c r="S82" s="9" t="n"/>
+      <c r="T82" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T82" s="9" t="n"/>
       <c r="U82" s="9" t="n"/>
       <c r="V82" s="9" t="n"/>
       <c r="W82" s="9" t="n"/>
       <c r="X82" s="9" t="n"/>
-      <c r="Y82" s="10" t="n">
+      <c r="Y82" s="9" t="n"/>
+      <c r="Z82" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Z82" s="10" t="n">
+      <c r="AA82" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17452,44 +17539,45 @@
       <c r="H83" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="9" t="inlineStr">
+      <c r="I83" s="9" t="n"/>
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="K83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>BR-03598/2026</t>
         </is>
       </c>
-      <c r="L83" s="9" t="inlineStr">
+      <c r="M83" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
       <c r="O83" s="9" t="n"/>
       <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="10" t="n">
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R83" s="9" t="n"/>
-      <c r="S83" s="10" t="n">
+      <c r="S83" s="9" t="n"/>
+      <c r="T83" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
       <c r="X83" s="9" t="n"/>
-      <c r="Y83" s="10" t="n">
+      <c r="Y83" s="9" t="n"/>
+      <c r="Z83" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="Z83" s="10" t="n">
+      <c r="AA83" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17528,40 +17616,41 @@
       <c r="H84" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="9" t="inlineStr">
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="K84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>BR-03678/2026</t>
         </is>
       </c>
-      <c r="L84" s="9" t="n"/>
       <c r="M84" s="9" t="n"/>
       <c r="N84" s="9" t="n"/>
       <c r="O84" s="9" t="n"/>
       <c r="P84" s="9" t="n"/>
-      <c r="Q84" s="10" t="n">
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="10" t="n">
         <v>46.9</v>
       </c>
-      <c r="R84" s="9" t="n"/>
-      <c r="S84" s="10" t="n">
+      <c r="S84" s="9" t="n"/>
+      <c r="T84" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="T84" s="9" t="n"/>
       <c r="U84" s="9" t="n"/>
       <c r="V84" s="9" t="n"/>
       <c r="W84" s="9" t="n"/>
       <c r="X84" s="9" t="n"/>
-      <c r="Y84" s="10" t="n">
+      <c r="Y84" s="9" t="n"/>
+      <c r="Z84" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="Z84" s="10" t="n">
+      <c r="AA84" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17600,40 +17689,41 @@
       <c r="H85" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="9" t="inlineStr">
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="9" t="inlineStr">
         <is>
           <t>BR-03678/2026</t>
         </is>
       </c>
-      <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
       <c r="O85" s="9" t="n"/>
       <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="10" t="n">
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="10" t="n">
         <v>46.9</v>
       </c>
-      <c r="R85" s="9" t="n"/>
-      <c r="S85" s="10" t="n">
+      <c r="S85" s="9" t="n"/>
+      <c r="T85" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="T85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
       <c r="V85" s="9" t="n"/>
       <c r="W85" s="9" t="n"/>
       <c r="X85" s="9" t="n"/>
-      <c r="Y85" s="10" t="n">
+      <c r="Y85" s="9" t="n"/>
+      <c r="Z85" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="Z85" s="9" t="n"/>
+      <c r="AA85" s="9" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -17670,44 +17760,45 @@
       <c r="H86" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="9" t="inlineStr">
+      <c r="I86" s="9" t="n"/>
+      <c r="J86" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="9" t="inlineStr">
+      <c r="K86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
         <is>
           <t>BR-05356/2026</t>
         </is>
       </c>
-      <c r="L86" s="9" t="inlineStr">
+      <c r="M86" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M86" s="9" t="n"/>
       <c r="N86" s="9" t="n"/>
       <c r="O86" s="9" t="n"/>
       <c r="P86" s="9" t="n"/>
-      <c r="Q86" s="10" t="n">
+      <c r="Q86" s="9" t="n"/>
+      <c r="R86" s="10" t="n">
         <v>45.3</v>
       </c>
-      <c r="R86" s="9" t="n"/>
-      <c r="S86" s="10" t="n">
+      <c r="S86" s="9" t="n"/>
+      <c r="T86" s="10" t="n">
         <v>44.7</v>
       </c>
-      <c r="T86" s="9" t="n"/>
       <c r="U86" s="9" t="n"/>
       <c r="V86" s="9" t="n"/>
       <c r="W86" s="9" t="n"/>
       <c r="X86" s="9" t="n"/>
-      <c r="Y86" s="10" t="n">
+      <c r="Y86" s="9" t="n"/>
+      <c r="Z86" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="Z86" s="10" t="n">
+      <c r="AA86" s="10" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -17746,40 +17837,41 @@
       <c r="H87" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="K87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="9" t="inlineStr">
         <is>
           <t>BR-03627/2026</t>
         </is>
       </c>
-      <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
       <c r="O87" s="9" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="10" t="n">
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="R87" s="9" t="n"/>
-      <c r="S87" s="10" t="n">
+      <c r="S87" s="9" t="n"/>
+      <c r="T87" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T87" s="9" t="n"/>
       <c r="U87" s="9" t="n"/>
       <c r="V87" s="9" t="n"/>
       <c r="W87" s="9" t="n"/>
       <c r="X87" s="9" t="n"/>
-      <c r="Y87" s="10" t="n">
+      <c r="Y87" s="9" t="n"/>
+      <c r="Z87" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Z87" s="10" t="n">
+      <c r="AA87" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17818,44 +17910,45 @@
       <c r="H88" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="9" t="inlineStr">
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
+      <c r="K88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="9" t="inlineStr">
         <is>
           <t>BR-07992/2026</t>
         </is>
       </c>
-      <c r="L88" s="9" t="inlineStr">
+      <c r="M88" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M88" s="9" t="n"/>
       <c r="N88" s="9" t="n"/>
       <c r="O88" s="9" t="n"/>
       <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="10" t="n">
+      <c r="Q88" s="9" t="n"/>
+      <c r="R88" s="10" t="n">
         <v>47.8</v>
       </c>
-      <c r="R88" s="9" t="n"/>
-      <c r="S88" s="10" t="n">
+      <c r="S88" s="9" t="n"/>
+      <c r="T88" s="10" t="n">
         <v>47.5</v>
       </c>
-      <c r="T88" s="9" t="n"/>
       <c r="U88" s="9" t="n"/>
       <c r="V88" s="9" t="n"/>
       <c r="W88" s="9" t="n"/>
       <c r="X88" s="9" t="n"/>
-      <c r="Y88" s="10" t="n">
+      <c r="Y88" s="9" t="n"/>
+      <c r="Z88" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="Z88" s="9" t="n"/>
+      <c r="AA88" s="9" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
@@ -17892,40 +17985,41 @@
       <c r="H89" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
         <is>
           <t>BR-01075/2026</t>
         </is>
       </c>
-      <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
       <c r="O89" s="9" t="n"/>
       <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="10" t="n">
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R89" s="9" t="n"/>
-      <c r="S89" s="10" t="n">
+      <c r="S89" s="9" t="n"/>
+      <c r="T89" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
       <c r="V89" s="9" t="n"/>
       <c r="W89" s="9" t="n"/>
       <c r="X89" s="9" t="n"/>
-      <c r="Y89" s="10" t="n">
+      <c r="Y89" s="9" t="n"/>
+      <c r="Z89" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z89" s="10" t="n">
+      <c r="AA89" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17964,44 +18058,45 @@
       <c r="H90" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="9" t="inlineStr">
         <is>
           <t>BR-09285/2026</t>
         </is>
       </c>
-      <c r="L90" s="9" t="inlineStr">
+      <c r="M90" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M90" s="9" t="n"/>
       <c r="N90" s="9" t="n"/>
       <c r="O90" s="9" t="n"/>
       <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="10" t="n">
+      <c r="Q90" s="9" t="n"/>
+      <c r="R90" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="R90" s="9" t="n"/>
-      <c r="S90" s="10" t="n">
+      <c r="S90" s="9" t="n"/>
+      <c r="T90" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T90" s="9" t="n"/>
       <c r="U90" s="9" t="n"/>
       <c r="V90" s="9" t="n"/>
       <c r="W90" s="9" t="n"/>
       <c r="X90" s="9" t="n"/>
-      <c r="Y90" s="10" t="n">
+      <c r="Y90" s="9" t="n"/>
+      <c r="Z90" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Z90" s="10" t="n">
+      <c r="AA90" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18040,40 +18135,41 @@
       <c r="H91" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="9" t="inlineStr">
+      <c r="K91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="9" t="inlineStr">
         <is>
           <t>BR-07871/2026</t>
         </is>
       </c>
-      <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
       <c r="O91" s="9" t="n"/>
       <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="10" t="n">
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="10" t="n">
         <v>40.2</v>
       </c>
-      <c r="R91" s="9" t="n"/>
-      <c r="S91" s="10" t="n">
+      <c r="S91" s="9" t="n"/>
+      <c r="T91" s="10" t="n">
         <v>44.9</v>
       </c>
-      <c r="T91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
       <c r="V91" s="9" t="n"/>
       <c r="W91" s="9" t="n"/>
       <c r="X91" s="9" t="n"/>
-      <c r="Y91" s="10" t="n">
+      <c r="Y91" s="9" t="n"/>
+      <c r="Z91" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="Z91" s="10" t="n">
+      <c r="AA91" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18112,40 +18208,41 @@
       <c r="H92" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I92" s="9" t="inlineStr">
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="inlineStr">
+      <c r="K92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
         <is>
           <t>BR-02847/2026</t>
         </is>
       </c>
-      <c r="L92" s="9" t="n"/>
       <c r="M92" s="9" t="n"/>
       <c r="N92" s="9" t="n"/>
       <c r="O92" s="9" t="n"/>
       <c r="P92" s="9" t="n"/>
-      <c r="Q92" s="10" t="n">
+      <c r="Q92" s="9" t="n"/>
+      <c r="R92" s="10" t="n">
         <v>40.2</v>
       </c>
-      <c r="R92" s="9" t="n"/>
-      <c r="S92" s="10" t="n">
+      <c r="S92" s="9" t="n"/>
+      <c r="T92" s="10" t="n">
         <v>44.9</v>
       </c>
-      <c r="T92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
       <c r="V92" s="9" t="n"/>
       <c r="W92" s="9" t="n"/>
       <c r="X92" s="9" t="n"/>
-      <c r="Y92" s="10" t="n">
+      <c r="Y92" s="9" t="n"/>
+      <c r="Z92" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="Z92" s="10" t="n">
+      <c r="AA92" s="10" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -18184,44 +18281,45 @@
       <c r="H93" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="9" t="inlineStr">
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="K93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
         <is>
           <t>BR-08282/2026</t>
         </is>
       </c>
-      <c r="L93" s="9" t="inlineStr">
+      <c r="M93" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
       <c r="O93" s="9" t="n"/>
       <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="10" t="n">
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="R93" s="9" t="n"/>
-      <c r="S93" s="10" t="n">
+      <c r="S93" s="9" t="n"/>
+      <c r="T93" s="10" t="n">
         <v>42.6</v>
       </c>
-      <c r="T93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
       <c r="V93" s="9" t="n"/>
       <c r="W93" s="9" t="n"/>
       <c r="X93" s="9" t="n"/>
-      <c r="Y93" s="10" t="n">
+      <c r="Y93" s="9" t="n"/>
+      <c r="Z93" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z93" s="10" t="n">
+      <c r="AA93" s="10" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -18260,44 +18358,45 @@
       <c r="H94" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I94" s="9" t="inlineStr">
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="9" t="inlineStr">
+      <c r="K94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
         <is>
           <t>BR-03770/2026</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
+      <c r="M94" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M94" s="9" t="n"/>
       <c r="N94" s="9" t="n"/>
       <c r="O94" s="9" t="n"/>
       <c r="P94" s="9" t="n"/>
-      <c r="Q94" s="10" t="n">
+      <c r="Q94" s="9" t="n"/>
+      <c r="R94" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="R94" s="9" t="n"/>
-      <c r="S94" s="10" t="n">
+      <c r="S94" s="9" t="n"/>
+      <c r="T94" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T94" s="9" t="n"/>
       <c r="U94" s="9" t="n"/>
       <c r="V94" s="9" t="n"/>
       <c r="W94" s="9" t="n"/>
       <c r="X94" s="9" t="n"/>
-      <c r="Y94" s="10" t="n">
+      <c r="Y94" s="9" t="n"/>
+      <c r="Z94" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Z94" s="10" t="n">
+      <c r="AA94" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18336,44 +18435,45 @@
       <c r="H95" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I95" s="9" t="inlineStr">
+      <c r="I95" s="9" t="n"/>
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
+      <c r="K95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
         <is>
           <t>BR-00605/2026</t>
         </is>
       </c>
-      <c r="L95" s="9" t="inlineStr">
+      <c r="M95" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
       <c r="O95" s="9" t="n"/>
       <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="10" t="n">
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="10" t="n">
         <v>45.8</v>
       </c>
-      <c r="R95" s="9" t="n"/>
-      <c r="S95" s="10" t="n">
+      <c r="S95" s="9" t="n"/>
+      <c r="T95" s="10" t="n">
         <v>45.5</v>
       </c>
-      <c r="T95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
       <c r="V95" s="9" t="n"/>
       <c r="W95" s="9" t="n"/>
       <c r="X95" s="9" t="n"/>
-      <c r="Y95" s="10" t="n">
+      <c r="Y95" s="9" t="n"/>
+      <c r="Z95" s="10" t="n">
         <v>6.6</v>
       </c>
-      <c r="Z95" s="10" t="n">
+      <c r="AA95" s="10" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -18412,40 +18512,41 @@
       <c r="H96" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I96" s="9" t="inlineStr">
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>URA (telefone)</t>
         </is>
       </c>
-      <c r="J96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
+      <c r="K96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
         <is>
           <t>BR-01960/2026</t>
         </is>
       </c>
-      <c r="L96" s="9" t="n"/>
       <c r="M96" s="9" t="n"/>
       <c r="N96" s="9" t="n"/>
       <c r="O96" s="9" t="n"/>
       <c r="P96" s="9" t="n"/>
-      <c r="Q96" s="10" t="n">
+      <c r="Q96" s="9" t="n"/>
+      <c r="R96" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R96" s="9" t="n"/>
-      <c r="S96" s="10" t="n">
+      <c r="S96" s="9" t="n"/>
+      <c r="T96" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="T96" s="9" t="n"/>
       <c r="U96" s="9" t="n"/>
       <c r="V96" s="9" t="n"/>
       <c r="W96" s="9" t="n"/>
       <c r="X96" s="9" t="n"/>
-      <c r="Y96" s="10" t="n">
+      <c r="Y96" s="9" t="n"/>
+      <c r="Z96" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="Z96" s="10" t="n">
+      <c r="AA96" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18484,44 +18585,45 @@
       <c r="H97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="I97" s="9" t="n"/>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="K97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
         <is>
           <t>BR-00873/2026</t>
         </is>
       </c>
-      <c r="L97" s="9" t="inlineStr">
+      <c r="M97" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
       <c r="O97" s="9" t="n"/>
       <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="10" t="n">
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="10" t="n">
         <v>45.2</v>
       </c>
-      <c r="R97" s="9" t="n"/>
-      <c r="S97" s="10" t="n">
+      <c r="S97" s="9" t="n"/>
+      <c r="T97" s="10" t="n">
         <v>44.1</v>
       </c>
-      <c r="T97" s="9" t="n"/>
       <c r="U97" s="9" t="n"/>
       <c r="V97" s="9" t="n"/>
       <c r="W97" s="9" t="n"/>
       <c r="X97" s="9" t="n"/>
-      <c r="Y97" s="10" t="n">
+      <c r="Y97" s="9" t="n"/>
+      <c r="Z97" s="10" t="n">
         <v>6.2</v>
       </c>
-      <c r="Z97" s="10" t="n">
+      <c r="AA97" s="10" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -18560,40 +18662,41 @@
       <c r="H98" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I98" s="9" t="inlineStr">
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>BR-07875/2026</t>
         </is>
       </c>
-      <c r="L98" s="9" t="n"/>
       <c r="M98" s="9" t="n"/>
       <c r="N98" s="9" t="n"/>
       <c r="O98" s="9" t="n"/>
       <c r="P98" s="9" t="n"/>
-      <c r="Q98" s="10" t="n">
+      <c r="Q98" s="9" t="n"/>
+      <c r="R98" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="R98" s="9" t="n"/>
-      <c r="S98" s="10" t="n">
+      <c r="S98" s="9" t="n"/>
+      <c r="T98" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T98" s="9" t="n"/>
       <c r="U98" s="9" t="n"/>
       <c r="V98" s="9" t="n"/>
       <c r="W98" s="9" t="n"/>
       <c r="X98" s="9" t="n"/>
-      <c r="Y98" s="10" t="n">
+      <c r="Y98" s="9" t="n"/>
+      <c r="Z98" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Z98" s="10" t="n">
+      <c r="AA98" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18632,40 +18735,41 @@
       <c r="H99" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="I99" s="9" t="n"/>
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="9" t="inlineStr">
+      <c r="K99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
         <is>
           <t>BR-02846/2026</t>
         </is>
       </c>
-      <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
       <c r="O99" s="9" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="10" t="n">
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="R99" s="9" t="n"/>
-      <c r="S99" s="10" t="n">
+      <c r="S99" s="9" t="n"/>
+      <c r="T99" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T99" s="9" t="n"/>
       <c r="U99" s="9" t="n"/>
       <c r="V99" s="9" t="n"/>
       <c r="W99" s="9" t="n"/>
       <c r="X99" s="9" t="n"/>
-      <c r="Y99" s="10" t="n">
+      <c r="Y99" s="9" t="n"/>
+      <c r="Z99" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Z99" s="10" t="n">
+      <c r="AA99" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -18704,44 +18808,45 @@
       <c r="H100" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I100" s="9" t="inlineStr">
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="9" t="inlineStr">
+      <c r="K100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
         <is>
           <t>BR-04227/2026</t>
         </is>
       </c>
-      <c r="L100" s="9" t="inlineStr">
+      <c r="M100" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M100" s="9" t="n"/>
       <c r="N100" s="9" t="n"/>
       <c r="O100" s="9" t="n"/>
       <c r="P100" s="9" t="n"/>
-      <c r="Q100" s="10" t="n">
+      <c r="Q100" s="9" t="n"/>
+      <c r="R100" s="10" t="n">
         <v>47.6</v>
       </c>
-      <c r="R100" s="9" t="n"/>
-      <c r="S100" s="10" t="n">
+      <c r="S100" s="9" t="n"/>
+      <c r="T100" s="10" t="n">
         <v>46.6</v>
       </c>
-      <c r="T100" s="9" t="n"/>
       <c r="U100" s="9" t="n"/>
       <c r="V100" s="9" t="n"/>
       <c r="W100" s="9" t="n"/>
       <c r="X100" s="9" t="n"/>
-      <c r="Y100" s="10" t="n">
+      <c r="Y100" s="9" t="n"/>
+      <c r="Z100" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="Z100" s="9" t="n"/>
+      <c r="AA100" s="9" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -18778,40 +18883,41 @@
       <c r="H101" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="9" t="inlineStr">
+      <c r="I101" s="9" t="n"/>
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="K101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
         <is>
           <t>BR-06058/2026</t>
         </is>
       </c>
-      <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
       <c r="O101" s="9" t="n"/>
       <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="10" t="n">
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="10" t="n">
         <v>47.6</v>
       </c>
-      <c r="R101" s="9" t="n"/>
-      <c r="S101" s="10" t="n">
+      <c r="S101" s="9" t="n"/>
+      <c r="T101" s="10" t="n">
         <v>46.6</v>
       </c>
-      <c r="T101" s="9" t="n"/>
       <c r="U101" s="9" t="n"/>
       <c r="V101" s="9" t="n"/>
       <c r="W101" s="9" t="n"/>
       <c r="X101" s="9" t="n"/>
-      <c r="Y101" s="10" t="n">
+      <c r="Y101" s="9" t="n"/>
+      <c r="Z101" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="Z101" s="9" t="n"/>
+      <c r="AA101" s="9" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
@@ -18848,44 +18954,45 @@
       <c r="H102" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="9" t="inlineStr">
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="9" t="inlineStr">
+      <c r="K102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
         <is>
           <t>BR-00386/2026</t>
         </is>
       </c>
-      <c r="L102" s="9" t="inlineStr">
+      <c r="M102" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M102" s="9" t="n"/>
       <c r="N102" s="9" t="n"/>
       <c r="O102" s="9" t="n"/>
       <c r="P102" s="9" t="n"/>
-      <c r="Q102" s="10" t="n">
+      <c r="Q102" s="9" t="n"/>
+      <c r="R102" s="10" t="n">
         <v>45.3</v>
       </c>
-      <c r="R102" s="9" t="n"/>
-      <c r="S102" s="10" t="n">
+      <c r="S102" s="9" t="n"/>
+      <c r="T102" s="10" t="n">
         <v>47.4</v>
       </c>
-      <c r="T102" s="9" t="n"/>
       <c r="U102" s="9" t="n"/>
       <c r="V102" s="9" t="n"/>
       <c r="W102" s="9" t="n"/>
       <c r="X102" s="9" t="n"/>
-      <c r="Y102" s="10" t="n">
+      <c r="Y102" s="9" t="n"/>
+      <c r="Z102" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="Z102" s="10" t="n">
+      <c r="AA102" s="10" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -18924,44 +19031,45 @@
       <c r="H103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="9" t="inlineStr">
+      <c r="I103" s="9" t="n"/>
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="9" t="inlineStr">
+      <c r="K103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
         <is>
           <t>BR-05809/2026</t>
         </is>
       </c>
-      <c r="L103" s="9" t="inlineStr">
+      <c r="M103" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
       <c r="O103" s="9" t="n"/>
       <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="10" t="n">
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R103" s="9" t="n"/>
-      <c r="S103" s="10" t="n">
+      <c r="S103" s="9" t="n"/>
+      <c r="T103" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="T103" s="9" t="n"/>
       <c r="U103" s="9" t="n"/>
       <c r="V103" s="9" t="n"/>
       <c r="W103" s="9" t="n"/>
       <c r="X103" s="9" t="n"/>
-      <c r="Y103" s="10" t="n">
+      <c r="Y103" s="9" t="n"/>
+      <c r="Z103" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Z103" s="10" t="n">
+      <c r="AA103" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19000,44 +19108,45 @@
       <c r="H104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I104" s="9" t="inlineStr">
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="9" t="inlineStr">
+      <c r="K104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
         <is>
           <t>BR-03715/2026</t>
         </is>
       </c>
-      <c r="L104" s="9" t="inlineStr">
+      <c r="M104" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M104" s="9" t="n"/>
       <c r="N104" s="9" t="n"/>
       <c r="O104" s="9" t="n"/>
       <c r="P104" s="9" t="n"/>
-      <c r="Q104" s="10" t="n">
+      <c r="Q104" s="9" t="n"/>
+      <c r="R104" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="R104" s="9" t="n"/>
-      <c r="S104" s="10" t="n">
+      <c r="S104" s="9" t="n"/>
+      <c r="T104" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T104" s="9" t="n"/>
       <c r="U104" s="9" t="n"/>
       <c r="V104" s="9" t="n"/>
       <c r="W104" s="9" t="n"/>
       <c r="X104" s="9" t="n"/>
-      <c r="Y104" s="10" t="n">
+      <c r="Y104" s="9" t="n"/>
+      <c r="Z104" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z104" s="10" t="n">
+      <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19076,40 +19185,41 @@
       <c r="H105" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="I105" s="9" t="n"/>
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="9" t="inlineStr">
+      <c r="K105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="9" t="inlineStr">
         <is>
           <t>BR-09353/2026</t>
         </is>
       </c>
-      <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
       <c r="O105" s="9" t="n"/>
       <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="10" t="n">
+      <c r="Q105" s="9" t="n"/>
+      <c r="R105" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R105" s="9" t="n"/>
-      <c r="S105" s="10" t="n">
+      <c r="S105" s="9" t="n"/>
+      <c r="T105" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="T105" s="9" t="n"/>
       <c r="U105" s="9" t="n"/>
       <c r="V105" s="9" t="n"/>
       <c r="W105" s="9" t="n"/>
       <c r="X105" s="9" t="n"/>
-      <c r="Y105" s="10" t="n">
+      <c r="Y105" s="9" t="n"/>
+      <c r="Z105" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z105" s="10" t="n">
+      <c r="AA105" s="10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -19148,44 +19258,45 @@
       <c r="H106" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="9" t="inlineStr">
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="9" t="inlineStr">
+      <c r="K106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="9" t="inlineStr">
         <is>
           <t>BR-07974/2026</t>
         </is>
       </c>
-      <c r="L106" s="9" t="inlineStr">
+      <c r="M106" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-fevereiro-2026-2/</t>
         </is>
       </c>
-      <c r="M106" s="9" t="n"/>
       <c r="N106" s="9" t="n"/>
       <c r="O106" s="9" t="n"/>
       <c r="P106" s="9" t="n"/>
-      <c r="Q106" s="10" t="n">
+      <c r="Q106" s="9" t="n"/>
+      <c r="R106" s="10" t="n">
         <v>44.4</v>
       </c>
-      <c r="R106" s="9" t="n"/>
-      <c r="S106" s="10" t="n">
+      <c r="S106" s="9" t="n"/>
+      <c r="T106" s="10" t="n">
         <v>43.8</v>
       </c>
-      <c r="T106" s="9" t="n"/>
       <c r="U106" s="9" t="n"/>
       <c r="V106" s="9" t="n"/>
       <c r="W106" s="9" t="n"/>
       <c r="X106" s="9" t="n"/>
-      <c r="Y106" s="10" t="n">
+      <c r="Y106" s="9" t="n"/>
+      <c r="Z106" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="Z106" s="10" t="n">
+      <c r="AA106" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -19224,44 +19335,45 @@
       <c r="H107" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="9" t="inlineStr">
+      <c r="I107" s="9" t="n"/>
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="9" t="inlineStr">
+      <c r="K107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
         <is>
           <t>BR-07600/2026</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="M107" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
       <c r="O107" s="9" t="n"/>
       <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="10" t="n">
+      <c r="Q107" s="9" t="n"/>
+      <c r="R107" s="10" t="n">
         <v>46.3</v>
       </c>
-      <c r="R107" s="9" t="n"/>
-      <c r="S107" s="10" t="n">
+      <c r="S107" s="9" t="n"/>
+      <c r="T107" s="10" t="n">
         <v>46.2</v>
       </c>
-      <c r="T107" s="9" t="n"/>
       <c r="U107" s="9" t="n"/>
       <c r="V107" s="9" t="n"/>
       <c r="W107" s="9" t="n"/>
       <c r="X107" s="9" t="n"/>
-      <c r="Y107" s="10" t="n">
+      <c r="Y107" s="9" t="n"/>
+      <c r="Z107" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="Z107" s="9" t="n"/>
+      <c r="AA107" s="9" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -19298,40 +19410,41 @@
       <c r="H108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="9" t="inlineStr">
+      <c r="I108" s="9" t="n"/>
+      <c r="J108" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="9" t="inlineStr">
+      <c r="K108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
         <is>
           <t>BR-05112/2026</t>
         </is>
       </c>
-      <c r="L108" s="9" t="n"/>
       <c r="M108" s="9" t="n"/>
       <c r="N108" s="9" t="n"/>
       <c r="O108" s="9" t="n"/>
       <c r="P108" s="9" t="n"/>
-      <c r="Q108" s="10" t="n">
+      <c r="Q108" s="9" t="n"/>
+      <c r="R108" s="10" t="n">
         <v>47.5</v>
       </c>
-      <c r="R108" s="9" t="n"/>
-      <c r="S108" s="10" t="n">
+      <c r="S108" s="9" t="n"/>
+      <c r="T108" s="10" t="n">
         <v>46.1</v>
       </c>
-      <c r="T108" s="9" t="n"/>
       <c r="U108" s="9" t="n"/>
       <c r="V108" s="9" t="n"/>
       <c r="W108" s="9" t="n"/>
       <c r="X108" s="9" t="n"/>
-      <c r="Y108" s="10" t="n">
+      <c r="Y108" s="9" t="n"/>
+      <c r="Z108" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="Z108" s="9" t="n"/>
+      <c r="AA108" s="9" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -19368,40 +19481,41 @@
       <c r="H109" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="9" t="inlineStr">
+      <c r="I109" s="9" t="n"/>
+      <c r="J109" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
+      <c r="K109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
         <is>
           <t>BR-08165/2026</t>
         </is>
       </c>
-      <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
       <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="10" t="n">
+      <c r="Q109" s="9" t="n"/>
+      <c r="R109" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="R109" s="9" t="n"/>
-      <c r="S109" s="10" t="n">
+      <c r="S109" s="9" t="n"/>
+      <c r="T109" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="T109" s="9" t="n"/>
       <c r="U109" s="9" t="n"/>
       <c r="V109" s="9" t="n"/>
       <c r="W109" s="9" t="n"/>
       <c r="X109" s="9" t="n"/>
-      <c r="Y109" s="10" t="n">
+      <c r="Y109" s="9" t="n"/>
+      <c r="Z109" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Z109" s="10" t="n">
+      <c r="AA109" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19440,44 +19554,45 @@
       <c r="H110" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="9" t="inlineStr">
+      <c r="I110" s="9" t="n"/>
+      <c r="J110" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="K110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="9" t="inlineStr">
         <is>
           <t>BR-00249/2026</t>
         </is>
       </c>
-      <c r="L110" s="9" t="inlineStr">
+      <c r="M110" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M110" s="9" t="n"/>
       <c r="N110" s="9" t="n"/>
       <c r="O110" s="9" t="n"/>
       <c r="P110" s="9" t="n"/>
-      <c r="Q110" s="10" t="n">
+      <c r="Q110" s="9" t="n"/>
+      <c r="R110" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="R110" s="9" t="n"/>
-      <c r="S110" s="10" t="n">
+      <c r="S110" s="9" t="n"/>
+      <c r="T110" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T110" s="9" t="n"/>
       <c r="U110" s="9" t="n"/>
       <c r="V110" s="9" t="n"/>
       <c r="W110" s="9" t="n"/>
       <c r="X110" s="9" t="n"/>
-      <c r="Y110" s="10" t="n">
+      <c r="Y110" s="9" t="n"/>
+      <c r="Z110" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="Z110" s="10" t="n">
+      <c r="AA110" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19516,44 +19631,45 @@
       <c r="H111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="9" t="inlineStr">
+      <c r="I111" s="9" t="n"/>
+      <c r="J111" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="9" t="inlineStr">
+      <c r="K111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="9" t="inlineStr">
         <is>
           <t>BR-08425/2026</t>
         </is>
       </c>
-      <c r="L111" s="9" t="inlineStr">
+      <c r="M111" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="10" t="n">
+      <c r="Q111" s="9" t="n"/>
+      <c r="R111" s="10" t="n">
         <v>41.1</v>
       </c>
-      <c r="R111" s="9" t="n"/>
-      <c r="S111" s="10" t="n">
+      <c r="S111" s="9" t="n"/>
+      <c r="T111" s="10" t="n">
         <v>45.8</v>
       </c>
-      <c r="T111" s="9" t="n"/>
       <c r="U111" s="9" t="n"/>
       <c r="V111" s="9" t="n"/>
       <c r="W111" s="9" t="n"/>
       <c r="X111" s="9" t="n"/>
-      <c r="Y111" s="10" t="n">
+      <c r="Y111" s="9" t="n"/>
+      <c r="Z111" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z111" s="10" t="n">
+      <c r="AA111" s="10" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -19592,40 +19708,41 @@
       <c r="H112" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="9" t="inlineStr">
+      <c r="I112" s="9" t="n"/>
+      <c r="J112" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="9" t="inlineStr">
+      <c r="K112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
         <is>
           <t>BR-04519/2026</t>
         </is>
       </c>
-      <c r="L112" s="9" t="n"/>
       <c r="M112" s="9" t="n"/>
       <c r="N112" s="9" t="n"/>
       <c r="O112" s="9" t="n"/>
       <c r="P112" s="9" t="n"/>
-      <c r="Q112" s="10" t="n">
+      <c r="Q112" s="9" t="n"/>
+      <c r="R112" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R112" s="9" t="n"/>
-      <c r="S112" s="10" t="n">
+      <c r="S112" s="9" t="n"/>
+      <c r="T112" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T112" s="9" t="n"/>
       <c r="U112" s="9" t="n"/>
       <c r="V112" s="9" t="n"/>
       <c r="W112" s="9" t="n"/>
       <c r="X112" s="9" t="n"/>
-      <c r="Y112" s="10" t="n">
+      <c r="Y112" s="9" t="n"/>
+      <c r="Z112" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="Z112" s="9" t="n"/>
+      <c r="AA112" s="9" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -19662,44 +19779,45 @@
       <c r="H113" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I113" s="9" t="inlineStr">
+      <c r="I113" s="9" t="n"/>
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="9" t="inlineStr">
+      <c r="K113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
         <is>
           <t>BR-08254/2026</t>
         </is>
       </c>
-      <c r="L113" s="9" t="inlineStr">
+      <c r="M113" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/parana-pesquisas-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
       <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="10" t="n">
+      <c r="Q113" s="9" t="n"/>
+      <c r="R113" s="10" t="n">
         <v>42.2</v>
       </c>
-      <c r="R113" s="9" t="n"/>
-      <c r="S113" s="10" t="n">
+      <c r="S113" s="9" t="n"/>
+      <c r="T113" s="10" t="n">
         <v>44.8</v>
       </c>
-      <c r="T113" s="9" t="n"/>
       <c r="U113" s="9" t="n"/>
       <c r="V113" s="9" t="n"/>
       <c r="W113" s="9" t="n"/>
       <c r="X113" s="9" t="n"/>
-      <c r="Y113" s="10" t="n">
+      <c r="Y113" s="9" t="n"/>
+      <c r="Z113" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Z113" s="10" t="n">
+      <c r="AA113" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -19738,40 +19856,41 @@
       <c r="H114" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I114" s="9" t="inlineStr">
+      <c r="I114" s="9" t="n"/>
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="9" t="inlineStr">
+      <c r="K114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
         <is>
           <t>BR-02804/2026</t>
         </is>
       </c>
-      <c r="L114" s="9" t="n"/>
       <c r="M114" s="9" t="n"/>
       <c r="N114" s="9" t="n"/>
       <c r="O114" s="9" t="n"/>
       <c r="P114" s="9" t="n"/>
-      <c r="Q114" s="10" t="n">
+      <c r="Q114" s="9" t="n"/>
+      <c r="R114" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R114" s="9" t="n"/>
-      <c r="S114" s="10" t="n">
+      <c r="S114" s="9" t="n"/>
+      <c r="T114" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="T114" s="9" t="n"/>
       <c r="U114" s="9" t="n"/>
       <c r="V114" s="9" t="n"/>
       <c r="W114" s="9" t="n"/>
       <c r="X114" s="9" t="n"/>
-      <c r="Y114" s="10" t="n">
+      <c r="Y114" s="9" t="n"/>
+      <c r="Z114" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Z114" s="9" t="n"/>
+      <c r="AA114" s="9" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -19808,40 +19927,41 @@
       <c r="H115" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I115" s="9" t="inlineStr">
+      <c r="I115" s="9" t="n"/>
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="9" t="n"/>
-      <c r="L115" s="9" t="inlineStr">
+      <c r="K115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="9" t="n"/>
+      <c r="M115" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
       <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="10" t="n">
+      <c r="Q115" s="9" t="n"/>
+      <c r="R115" s="10" t="n">
         <v>48.1</v>
       </c>
-      <c r="R115" s="9" t="n"/>
-      <c r="S115" s="10" t="n">
+      <c r="S115" s="9" t="n"/>
+      <c r="T115" s="10" t="n">
         <v>41.9</v>
       </c>
-      <c r="T115" s="9" t="n"/>
       <c r="U115" s="9" t="n"/>
       <c r="V115" s="9" t="n"/>
       <c r="W115" s="9" t="n"/>
       <c r="X115" s="9" t="n"/>
-      <c r="Y115" s="10" t="n">
+      <c r="Y115" s="9" t="n"/>
+      <c r="Z115" s="10" t="n">
         <v>8.9</v>
       </c>
-      <c r="Z115" s="10" t="n">
+      <c r="AA115" s="10" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -19880,40 +20000,41 @@
       <c r="H116" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I116" s="9" t="inlineStr">
+      <c r="I116" s="9" t="n"/>
+      <c r="J116" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="9" t="inlineStr">
+      <c r="K116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
         <is>
           <t>BR-06845/2026</t>
         </is>
       </c>
-      <c r="L116" s="9" t="n"/>
       <c r="M116" s="9" t="n"/>
       <c r="N116" s="9" t="n"/>
       <c r="O116" s="9" t="n"/>
       <c r="P116" s="9" t="n"/>
-      <c r="Q116" s="10" t="n">
+      <c r="Q116" s="9" t="n"/>
+      <c r="R116" s="10" t="n">
         <v>42.5</v>
       </c>
-      <c r="R116" s="9" t="n"/>
-      <c r="S116" s="10" t="n">
+      <c r="S116" s="9" t="n"/>
+      <c r="T116" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="T116" s="9" t="n"/>
       <c r="U116" s="9" t="n"/>
       <c r="V116" s="9" t="n"/>
       <c r="W116" s="9" t="n"/>
       <c r="X116" s="9" t="n"/>
-      <c r="Y116" s="10" t="n">
+      <c r="Y116" s="9" t="n"/>
+      <c r="Z116" s="10" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Z116" s="10" t="n">
+      <c r="AA116" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
@@ -19952,44 +20073,45 @@
       <c r="H117" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="9" t="inlineStr">
+      <c r="I117" s="9" t="n"/>
+      <c r="J117" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="9" t="inlineStr">
+      <c r="K117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
         <is>
           <t>BR-06731/2026</t>
         </is>
       </c>
-      <c r="L117" s="9" t="inlineStr">
+      <c r="M117" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
       <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="10" t="n">
+      <c r="Q117" s="9" t="n"/>
+      <c r="R117" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="R117" s="9" t="n"/>
-      <c r="S117" s="10" t="n">
+      <c r="S117" s="9" t="n"/>
+      <c r="T117" s="10" t="n">
         <v>46.2</v>
       </c>
-      <c r="T117" s="9" t="n"/>
       <c r="U117" s="9" t="n"/>
       <c r="V117" s="9" t="n"/>
       <c r="W117" s="9" t="n"/>
       <c r="X117" s="9" t="n"/>
-      <c r="Y117" s="10" t="n">
+      <c r="Y117" s="9" t="n"/>
+      <c r="Z117" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z117" s="10" t="n">
+      <c r="AA117" s="10" t="n">
         <v>5.8</v>
       </c>
     </row>
@@ -20028,44 +20150,45 @@
       <c r="H118" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I118" s="9" t="inlineStr">
+      <c r="I118" s="9" t="n"/>
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="9" t="inlineStr">
+      <c r="K118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
         <is>
           <t>BR-00835/2026</t>
         </is>
       </c>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="M118" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M118" s="9" t="n"/>
       <c r="N118" s="9" t="n"/>
       <c r="O118" s="9" t="n"/>
       <c r="P118" s="9" t="n"/>
-      <c r="Q118" s="10" t="n">
+      <c r="Q118" s="9" t="n"/>
+      <c r="R118" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="R118" s="9" t="n"/>
-      <c r="S118" s="10" t="n">
+      <c r="S118" s="9" t="n"/>
+      <c r="T118" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T118" s="9" t="n"/>
       <c r="U118" s="9" t="n"/>
       <c r="V118" s="9" t="n"/>
       <c r="W118" s="9" t="n"/>
       <c r="X118" s="9" t="n"/>
-      <c r="Y118" s="10" t="n">
+      <c r="Y118" s="9" t="n"/>
+      <c r="Z118" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Z118" s="10" t="n">
+      <c r="AA118" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20104,40 +20227,41 @@
       <c r="H119" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I119" s="9" t="inlineStr">
+      <c r="I119" s="9" t="n"/>
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="J119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
+      <c r="K119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
         <is>
           <t>BR-04193/2026</t>
         </is>
       </c>
-      <c r="L119" s="9" t="n"/>
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="9" t="n"/>
       <c r="R119" s="9" t="n"/>
-      <c r="S119" s="10" t="n">
+      <c r="S119" s="9" t="n"/>
+      <c r="T119" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="T119" s="9" t="n"/>
       <c r="U119" s="9" t="n"/>
       <c r="V119" s="9" t="n"/>
-      <c r="W119" s="10" t="n">
+      <c r="W119" s="9" t="n"/>
+      <c r="X119" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="X119" s="9" t="n"/>
-      <c r="Y119" s="10" t="n">
+      <c r="Y119" s="9" t="n"/>
+      <c r="Z119" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Z119" s="10" t="n">
+      <c r="AA119" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20176,40 +20300,41 @@
       <c r="H120" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="9" t="inlineStr">
+      <c r="I120" s="9" t="n"/>
+      <c r="J120" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="9" t="inlineStr">
+      <c r="K120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
         <is>
           <t>BR-06529/2026</t>
         </is>
       </c>
-      <c r="L120" s="9" t="n"/>
       <c r="M120" s="9" t="n"/>
       <c r="N120" s="9" t="n"/>
       <c r="O120" s="9" t="n"/>
       <c r="P120" s="9" t="n"/>
       <c r="Q120" s="9" t="n"/>
       <c r="R120" s="9" t="n"/>
-      <c r="S120" s="10" t="n">
+      <c r="S120" s="9" t="n"/>
+      <c r="T120" s="10" t="n">
         <v>48.3</v>
       </c>
-      <c r="T120" s="9" t="n"/>
       <c r="U120" s="9" t="n"/>
       <c r="V120" s="9" t="n"/>
-      <c r="W120" s="10" t="n">
+      <c r="W120" s="9" t="n"/>
+      <c r="X120" s="10" t="n">
         <v>35.9</v>
       </c>
-      <c r="X120" s="9" t="n"/>
-      <c r="Y120" s="10" t="n">
+      <c r="Y120" s="9" t="n"/>
+      <c r="Z120" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="Z120" s="10" t="n">
+      <c r="AA120" s="10" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -20248,46 +20373,47 @@
       <c r="H121" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="9" t="inlineStr">
+      <c r="I121" s="9" t="n"/>
+      <c r="J121" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="9" t="inlineStr">
+      <c r="K121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
         <is>
           <t>BR-07489/2026</t>
         </is>
       </c>
-      <c r="L121" s="9" t="inlineStr">
+      <c r="M121" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026-2/</t>
         </is>
       </c>
-      <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
       <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="9" t="n"/>
-      <c r="S121" s="10" t="n">
+      <c r="Q121" s="9" t="n"/>
+      <c r="R121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="9" t="n"/>
+      <c r="T121" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="T121" s="9" t="n"/>
       <c r="U121" s="9" t="n"/>
       <c r="V121" s="9" t="n"/>
-      <c r="W121" s="10" t="n">
+      <c r="W121" s="9" t="n"/>
+      <c r="X121" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="X121" s="9" t="n"/>
-      <c r="Y121" s="10" t="n">
+      <c r="Y121" s="9" t="n"/>
+      <c r="Z121" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Z121" s="10" t="n">
+      <c r="AA121" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20326,44 +20452,45 @@
       <c r="H122" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="9" t="inlineStr">
+      <c r="I122" s="9" t="n"/>
+      <c r="J122" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="9" t="inlineStr">
+      <c r="K122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="9" t="inlineStr">
         <is>
           <t>BR-06939/2026</t>
         </is>
       </c>
-      <c r="L122" s="9" t="inlineStr">
+      <c r="M122" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M122" s="9" t="n"/>
       <c r="N122" s="9" t="n"/>
       <c r="O122" s="9" t="n"/>
       <c r="P122" s="9" t="n"/>
       <c r="Q122" s="9" t="n"/>
       <c r="R122" s="9" t="n"/>
-      <c r="S122" s="10" t="n">
+      <c r="S122" s="9" t="n"/>
+      <c r="T122" s="10" t="n">
         <v>47.8</v>
       </c>
-      <c r="T122" s="9" t="n"/>
       <c r="U122" s="9" t="n"/>
       <c r="V122" s="9" t="n"/>
-      <c r="W122" s="10" t="n">
+      <c r="W122" s="9" t="n"/>
+      <c r="X122" s="10" t="n">
         <v>37.6</v>
       </c>
-      <c r="X122" s="9" t="n"/>
-      <c r="Y122" s="10" t="n">
+      <c r="Y122" s="9" t="n"/>
+      <c r="Z122" s="10" t="n">
         <v>14.6</v>
       </c>
-      <c r="Z122" s="9" t="n"/>
+      <c r="AA122" s="9" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
@@ -20400,44 +20527,45 @@
       <c r="H123" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="9" t="inlineStr">
+      <c r="I123" s="9" t="n"/>
+      <c r="J123" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="9" t="inlineStr">
+      <c r="K123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
         <is>
           <t>BR-00290/2026</t>
         </is>
       </c>
-      <c r="L123" s="9" t="inlineStr">
+      <c r="M123" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="9" t="n"/>
       <c r="R123" s="9" t="n"/>
-      <c r="S123" s="10" t="n">
+      <c r="S123" s="9" t="n"/>
+      <c r="T123" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T123" s="9" t="n"/>
       <c r="U123" s="9" t="n"/>
       <c r="V123" s="9" t="n"/>
-      <c r="W123" s="10" t="n">
+      <c r="W123" s="9" t="n"/>
+      <c r="X123" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="X123" s="9" t="n"/>
-      <c r="Y123" s="10" t="n">
+      <c r="Y123" s="9" t="n"/>
+      <c r="Z123" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Z123" s="10" t="n">
+      <c r="AA123" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20476,40 +20604,41 @@
       <c r="H124" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="9" t="inlineStr">
+      <c r="I124" s="9" t="n"/>
+      <c r="J124" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="9" t="inlineStr">
+      <c r="K124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
         <is>
           <t>BR-03369/2026</t>
         </is>
       </c>
-      <c r="L124" s="9" t="n"/>
       <c r="M124" s="9" t="n"/>
       <c r="N124" s="9" t="n"/>
       <c r="O124" s="9" t="n"/>
       <c r="P124" s="9" t="n"/>
       <c r="Q124" s="9" t="n"/>
       <c r="R124" s="9" t="n"/>
-      <c r="S124" s="10" t="n">
+      <c r="S124" s="9" t="n"/>
+      <c r="T124" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T124" s="9" t="n"/>
       <c r="U124" s="9" t="n"/>
       <c r="V124" s="9" t="n"/>
-      <c r="W124" s="10" t="n">
+      <c r="W124" s="9" t="n"/>
+      <c r="X124" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="X124" s="9" t="n"/>
-      <c r="Y124" s="10" t="n">
+      <c r="Y124" s="9" t="n"/>
+      <c r="Z124" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z124" s="10" t="n">
+      <c r="AA124" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20548,44 +20677,45 @@
       <c r="H125" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="9" t="inlineStr">
+      <c r="I125" s="9" t="n"/>
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="9" t="inlineStr">
+      <c r="K125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="9" t="inlineStr">
         <is>
           <t>BR-03598/2026</t>
         </is>
       </c>
-      <c r="L125" s="9" t="inlineStr">
+      <c r="M125" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/genial-quaest-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
       <c r="P125" s="9" t="n"/>
       <c r="Q125" s="9" t="n"/>
       <c r="R125" s="9" t="n"/>
-      <c r="S125" s="10" t="n">
+      <c r="S125" s="9" t="n"/>
+      <c r="T125" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T125" s="9" t="n"/>
       <c r="U125" s="9" t="n"/>
       <c r="V125" s="9" t="n"/>
-      <c r="W125" s="10" t="n">
+      <c r="W125" s="9" t="n"/>
+      <c r="X125" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="X125" s="9" t="n"/>
-      <c r="Y125" s="10" t="n">
+      <c r="Y125" s="9" t="n"/>
+      <c r="Z125" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="Z125" s="10" t="n">
+      <c r="AA125" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20624,44 +20754,45 @@
       <c r="H126" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I126" s="9" t="inlineStr">
+      <c r="I126" s="9" t="n"/>
+      <c r="J126" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="9" t="inlineStr">
+      <c r="K126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
         <is>
           <t>BR-05356/2026</t>
         </is>
       </c>
-      <c r="L126" s="9" t="inlineStr">
+      <c r="M126" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-maio-2026/</t>
         </is>
       </c>
-      <c r="M126" s="9" t="n"/>
       <c r="N126" s="9" t="n"/>
       <c r="O126" s="9" t="n"/>
       <c r="P126" s="9" t="n"/>
       <c r="Q126" s="9" t="n"/>
       <c r="R126" s="9" t="n"/>
-      <c r="S126" s="10" t="n">
+      <c r="S126" s="9" t="n"/>
+      <c r="T126" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T126" s="9" t="n"/>
       <c r="U126" s="9" t="n"/>
       <c r="V126" s="9" t="n"/>
-      <c r="W126" s="10" t="n">
+      <c r="W126" s="9" t="n"/>
+      <c r="X126" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="X126" s="9" t="n"/>
-      <c r="Y126" s="10" t="n">
+      <c r="Y126" s="9" t="n"/>
+      <c r="Z126" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="Z126" s="10" t="n">
+      <c r="AA126" s="10" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -20700,40 +20831,41 @@
       <c r="H127" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I127" s="9" t="inlineStr">
+      <c r="I127" s="9" t="n"/>
+      <c r="J127" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="9" t="inlineStr">
+      <c r="K127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
         <is>
           <t>BR-03627/2026</t>
         </is>
       </c>
-      <c r="L127" s="9" t="n"/>
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
       <c r="P127" s="9" t="n"/>
       <c r="Q127" s="9" t="n"/>
       <c r="R127" s="9" t="n"/>
-      <c r="S127" s="10" t="n">
+      <c r="S127" s="9" t="n"/>
+      <c r="T127" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T127" s="9" t="n"/>
       <c r="U127" s="9" t="n"/>
       <c r="V127" s="9" t="n"/>
-      <c r="W127" s="10" t="n">
+      <c r="W127" s="9" t="n"/>
+      <c r="X127" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="X127" s="9" t="n"/>
-      <c r="Y127" s="10" t="n">
+      <c r="Y127" s="9" t="n"/>
+      <c r="Z127" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="Z127" s="10" t="n">
+      <c r="AA127" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -20772,44 +20904,45 @@
       <c r="H128" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I128" s="9" t="inlineStr">
+      <c r="I128" s="9" t="n"/>
+      <c r="J128" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="9" t="inlineStr">
+      <c r="K128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
         <is>
           <t>BR-07992/2026</t>
         </is>
       </c>
-      <c r="L128" s="9" t="inlineStr">
+      <c r="M128" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M128" s="9" t="n"/>
       <c r="N128" s="9" t="n"/>
       <c r="O128" s="9" t="n"/>
       <c r="P128" s="9" t="n"/>
       <c r="Q128" s="9" t="n"/>
       <c r="R128" s="9" t="n"/>
-      <c r="S128" s="10" t="n">
+      <c r="S128" s="9" t="n"/>
+      <c r="T128" s="10" t="n">
         <v>47.4</v>
       </c>
-      <c r="T128" s="9" t="n"/>
       <c r="U128" s="9" t="n"/>
       <c r="V128" s="9" t="n"/>
-      <c r="W128" s="10" t="n">
+      <c r="W128" s="9" t="n"/>
+      <c r="X128" s="10" t="n">
         <v>46.5</v>
       </c>
-      <c r="X128" s="9" t="n"/>
-      <c r="Y128" s="10" t="n">
+      <c r="Y128" s="9" t="n"/>
+      <c r="Z128" s="10" t="n">
         <v>6.1</v>
       </c>
-      <c r="Z128" s="9" t="n"/>
+      <c r="AA128" s="9" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
@@ -20846,44 +20979,45 @@
       <c r="H129" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I129" s="9" t="inlineStr">
+      <c r="I129" s="9" t="n"/>
+      <c r="J129" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="9" t="inlineStr">
+      <c r="K129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
         <is>
           <t>BR-09285/2026</t>
         </is>
       </c>
-      <c r="L129" s="9" t="inlineStr">
+      <c r="M129" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/quaest-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="9" t="n"/>
       <c r="R129" s="9" t="n"/>
-      <c r="S129" s="10" t="n">
+      <c r="S129" s="9" t="n"/>
+      <c r="T129" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T129" s="9" t="n"/>
       <c r="U129" s="9" t="n"/>
       <c r="V129" s="9" t="n"/>
-      <c r="W129" s="10" t="n">
+      <c r="W129" s="9" t="n"/>
+      <c r="X129" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="X129" s="9" t="n"/>
-      <c r="Y129" s="10" t="n">
+      <c r="Y129" s="9" t="n"/>
+      <c r="Z129" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="Z129" s="10" t="n">
+      <c r="AA129" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20922,40 +21056,41 @@
       <c r="H130" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I130" s="9" t="inlineStr">
+      <c r="I130" s="9" t="n"/>
+      <c r="J130" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="9" t="inlineStr">
+      <c r="K130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
         <is>
           <t>BR-02847/2026</t>
         </is>
       </c>
-      <c r="L130" s="9" t="n"/>
       <c r="M130" s="9" t="n"/>
       <c r="N130" s="9" t="n"/>
       <c r="O130" s="9" t="n"/>
       <c r="P130" s="9" t="n"/>
       <c r="Q130" s="9" t="n"/>
       <c r="R130" s="9" t="n"/>
-      <c r="S130" s="10" t="n">
+      <c r="S130" s="9" t="n"/>
+      <c r="T130" s="10" t="n">
         <v>45.2</v>
       </c>
-      <c r="T130" s="9" t="n"/>
       <c r="U130" s="9" t="n"/>
       <c r="V130" s="9" t="n"/>
-      <c r="W130" s="10" t="n">
+      <c r="W130" s="9" t="n"/>
+      <c r="X130" s="10" t="n">
         <v>31.6</v>
       </c>
-      <c r="X130" s="9" t="n"/>
-      <c r="Y130" s="10" t="n">
+      <c r="Y130" s="9" t="n"/>
+      <c r="Z130" s="10" t="n">
         <v>15.9</v>
       </c>
-      <c r="Z130" s="10" t="n">
+      <c r="AA130" s="10" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -20994,44 +21129,45 @@
       <c r="H131" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I131" s="9" t="inlineStr">
+      <c r="I131" s="9" t="n"/>
+      <c r="J131" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="9" t="inlineStr">
+      <c r="K131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
         <is>
           <t>BR-08282/2026</t>
         </is>
       </c>
-      <c r="L131" s="9" t="inlineStr">
+      <c r="M131" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/futura-inteligencia-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
       <c r="P131" s="9" t="n"/>
       <c r="Q131" s="9" t="n"/>
       <c r="R131" s="9" t="n"/>
-      <c r="S131" s="10" t="n">
+      <c r="S131" s="9" t="n"/>
+      <c r="T131" s="10" t="n">
         <v>44.8</v>
       </c>
-      <c r="T131" s="9" t="n"/>
       <c r="U131" s="9" t="n"/>
       <c r="V131" s="9" t="n"/>
-      <c r="W131" s="10" t="n">
+      <c r="W131" s="9" t="n"/>
+      <c r="X131" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="X131" s="9" t="n"/>
-      <c r="Y131" s="10" t="n">
+      <c r="Y131" s="9" t="n"/>
+      <c r="Z131" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="Z131" s="10" t="n">
+      <c r="AA131" s="10" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -21070,44 +21206,45 @@
       <c r="H132" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I132" s="9" t="inlineStr">
+      <c r="I132" s="9" t="n"/>
+      <c r="J132" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="9" t="inlineStr">
+      <c r="K132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
         <is>
           <t>BR-03770/2026</t>
         </is>
       </c>
-      <c r="L132" s="9" t="inlineStr">
+      <c r="M132" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/datafolha-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M132" s="9" t="n"/>
       <c r="N132" s="9" t="n"/>
       <c r="O132" s="9" t="n"/>
       <c r="P132" s="9" t="n"/>
       <c r="Q132" s="9" t="n"/>
       <c r="R132" s="9" t="n"/>
-      <c r="S132" s="10" t="n">
+      <c r="S132" s="9" t="n"/>
+      <c r="T132" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T132" s="9" t="n"/>
       <c r="U132" s="9" t="n"/>
       <c r="V132" s="9" t="n"/>
-      <c r="W132" s="10" t="n">
+      <c r="W132" s="9" t="n"/>
+      <c r="X132" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="X132" s="9" t="n"/>
-      <c r="Y132" s="10" t="n">
+      <c r="Y132" s="9" t="n"/>
+      <c r="Z132" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Z132" s="10" t="n">
+      <c r="AA132" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21146,44 +21283,45 @@
       <c r="H133" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I133" s="9" t="inlineStr">
+      <c r="I133" s="9" t="n"/>
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="9" t="inlineStr">
+      <c r="K133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
         <is>
           <t>BR-00605/2026</t>
         </is>
       </c>
-      <c r="L133" s="9" t="inlineStr">
+      <c r="M133" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-pesquisa-presidente-abril-2026/</t>
         </is>
       </c>
-      <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
       <c r="P133" s="9" t="n"/>
       <c r="Q133" s="9" t="n"/>
       <c r="R133" s="9" t="n"/>
-      <c r="S133" s="10" t="n">
+      <c r="S133" s="9" t="n"/>
+      <c r="T133" s="10" t="n">
         <v>44.7</v>
       </c>
-      <c r="T133" s="9" t="n"/>
       <c r="U133" s="9" t="n"/>
       <c r="V133" s="9" t="n"/>
-      <c r="W133" s="10" t="n">
+      <c r="W133" s="9" t="n"/>
+      <c r="X133" s="10" t="n">
         <v>38.7</v>
       </c>
-      <c r="X133" s="9" t="n"/>
-      <c r="Y133" s="10" t="n">
+      <c r="Y133" s="9" t="n"/>
+      <c r="Z133" s="10" t="n">
         <v>7.3</v>
       </c>
-      <c r="Z133" s="10" t="n">
+      <c r="AA133" s="10" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -21222,44 +21360,45 @@
       <c r="H134" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I134" s="9" t="inlineStr">
+      <c r="I134" s="9" t="n"/>
+      <c r="J134" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="9" t="inlineStr">
+      <c r="K134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="9" t="inlineStr">
         <is>
           <t>BR-04227/2026</t>
         </is>
       </c>
-      <c r="L134" s="9" t="inlineStr">
+      <c r="M134" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/atlasintel-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M134" s="9" t="n"/>
       <c r="N134" s="9" t="n"/>
       <c r="O134" s="9" t="n"/>
       <c r="P134" s="9" t="n"/>
       <c r="Q134" s="9" t="n"/>
       <c r="R134" s="9" t="n"/>
-      <c r="S134" s="10" t="n">
+      <c r="S134" s="9" t="n"/>
+      <c r="T134" s="10" t="n">
         <v>46.6</v>
       </c>
-      <c r="T134" s="9" t="n"/>
       <c r="U134" s="9" t="n"/>
       <c r="V134" s="9" t="n"/>
-      <c r="W134" s="10" t="n">
+      <c r="W134" s="9" t="n"/>
+      <c r="X134" s="10" t="n">
         <v>43.7</v>
       </c>
-      <c r="X134" s="9" t="n"/>
-      <c r="Y134" s="10" t="n">
+      <c r="Y134" s="9" t="n"/>
+      <c r="Z134" s="10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z134" s="9" t="n"/>
+      <c r="AA134" s="9" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
@@ -21296,44 +21435,45 @@
       <c r="H135" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I135" s="9" t="inlineStr">
+      <c r="I135" s="9" t="n"/>
+      <c r="J135" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="9" t="inlineStr">
+      <c r="K135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="9" t="inlineStr">
         <is>
           <t>BR-00386/2026</t>
         </is>
       </c>
-      <c r="L135" s="9" t="inlineStr">
+      <c r="M135" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/meio-ideia-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
       <c r="P135" s="9" t="n"/>
       <c r="Q135" s="9" t="n"/>
       <c r="R135" s="9" t="n"/>
-      <c r="S135" s="10" t="n">
+      <c r="S135" s="9" t="n"/>
+      <c r="T135" s="10" t="n">
         <v>46.1</v>
       </c>
-      <c r="T135" s="9" t="n"/>
       <c r="U135" s="9" t="n"/>
       <c r="V135" s="9" t="n"/>
-      <c r="W135" s="10" t="n">
+      <c r="W135" s="9" t="n"/>
+      <c r="X135" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="X135" s="9" t="n"/>
-      <c r="Y135" s="10" t="n">
+      <c r="Y135" s="9" t="n"/>
+      <c r="Z135" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="Z135" s="10" t="n">
+      <c r="AA135" s="10" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -21372,44 +21512,45 @@
       <c r="H136" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I136" s="9" t="inlineStr">
+      <c r="I136" s="9" t="n"/>
+      <c r="J136" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="9" t="inlineStr">
+      <c r="K136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="9" t="inlineStr">
         <is>
           <t>BR-05809/2026</t>
         </is>
       </c>
-      <c r="L136" s="9" t="inlineStr">
+      <c r="M136" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-marco-2026/</t>
         </is>
       </c>
-      <c r="M136" s="9" t="n"/>
       <c r="N136" s="9" t="n"/>
       <c r="O136" s="9" t="n"/>
       <c r="P136" s="9" t="n"/>
       <c r="Q136" s="9" t="n"/>
       <c r="R136" s="9" t="n"/>
-      <c r="S136" s="10" t="n">
+      <c r="S136" s="9" t="n"/>
+      <c r="T136" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T136" s="9" t="n"/>
       <c r="U136" s="9" t="n"/>
       <c r="V136" s="9" t="n"/>
-      <c r="W136" s="10" t="n">
+      <c r="W136" s="9" t="n"/>
+      <c r="X136" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="X136" s="9" t="n"/>
-      <c r="Y136" s="10" t="n">
+      <c r="Y136" s="9" t="n"/>
+      <c r="Z136" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="Z136" s="10" t="n">
+      <c r="AA136" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21448,40 +21589,41 @@
       <c r="H137" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I137" s="9" t="inlineStr">
+      <c r="I137" s="9" t="n"/>
+      <c r="J137" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="9" t="inlineStr">
+      <c r="K137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="9" t="inlineStr">
         <is>
           <t>BR-09353/2026</t>
         </is>
       </c>
-      <c r="L137" s="9" t="n"/>
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
       <c r="P137" s="9" t="n"/>
       <c r="Q137" s="9" t="n"/>
       <c r="R137" s="9" t="n"/>
-      <c r="S137" s="10" t="n">
+      <c r="S137" s="9" t="n"/>
+      <c r="T137" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="T137" s="9" t="n"/>
       <c r="U137" s="9" t="n"/>
       <c r="V137" s="9" t="n"/>
-      <c r="W137" s="10" t="n">
+      <c r="W137" s="9" t="n"/>
+      <c r="X137" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="X137" s="9" t="n"/>
-      <c r="Y137" s="10" t="n">
+      <c r="Y137" s="9" t="n"/>
+      <c r="Z137" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Z137" s="10" t="n">
+      <c r="AA137" s="10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21520,40 +21662,41 @@
       <c r="H138" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I138" s="9" t="inlineStr">
+      <c r="I138" s="9" t="n"/>
+      <c r="J138" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="9" t="inlineStr">
+      <c r="K138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="9" t="inlineStr">
         <is>
           <t>BR-07600/2026</t>
         </is>
       </c>
-      <c r="L138" s="9" t="n"/>
       <c r="M138" s="9" t="n"/>
       <c r="N138" s="9" t="n"/>
       <c r="O138" s="9" t="n"/>
       <c r="P138" s="9" t="n"/>
       <c r="Q138" s="9" t="n"/>
       <c r="R138" s="9" t="n"/>
-      <c r="S138" s="10" t="n">
+      <c r="S138" s="9" t="n"/>
+      <c r="T138" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T138" s="9" t="n"/>
       <c r="U138" s="9" t="n"/>
       <c r="V138" s="9" t="n"/>
-      <c r="W138" s="10" t="n">
+      <c r="W138" s="9" t="n"/>
+      <c r="X138" s="10" t="n">
         <v>41.7</v>
       </c>
-      <c r="X138" s="9" t="n"/>
-      <c r="Y138" s="10" t="n">
+      <c r="Y138" s="9" t="n"/>
+      <c r="Z138" s="10" t="n">
         <v>12.3</v>
       </c>
-      <c r="Z138" s="9" t="n"/>
+      <c r="AA138" s="9" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
@@ -21590,40 +21733,41 @@
       <c r="H139" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I139" s="9" t="inlineStr">
+      <c r="I139" s="9" t="n"/>
+      <c r="J139" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="9" t="inlineStr">
+      <c r="K139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="9" t="inlineStr">
         <is>
           <t>BR-08165/2026</t>
         </is>
       </c>
-      <c r="L139" s="9" t="n"/>
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
       <c r="P139" s="9" t="n"/>
       <c r="Q139" s="9" t="n"/>
       <c r="R139" s="9" t="n"/>
-      <c r="S139" s="10" t="n">
+      <c r="S139" s="9" t="n"/>
+      <c r="T139" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="T139" s="9" t="n"/>
       <c r="U139" s="9" t="n"/>
       <c r="V139" s="9" t="n"/>
-      <c r="W139" s="10" t="n">
+      <c r="W139" s="9" t="n"/>
+      <c r="X139" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="X139" s="9" t="n"/>
-      <c r="Y139" s="10" t="n">
+      <c r="Y139" s="9" t="n"/>
+      <c r="Z139" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="Z139" s="10" t="n">
+      <c r="AA139" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21662,44 +21806,45 @@
       <c r="H140" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I140" s="9" t="inlineStr">
+      <c r="I140" s="9" t="n"/>
+      <c r="J140" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" s="9" t="inlineStr">
+      <c r="K140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="9" t="inlineStr">
         <is>
           <t>BR-00249/2026</t>
         </is>
       </c>
-      <c r="L140" s="9" t="inlineStr">
+      <c r="M140" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M140" s="9" t="n"/>
       <c r="N140" s="9" t="n"/>
       <c r="O140" s="9" t="n"/>
       <c r="P140" s="9" t="n"/>
       <c r="Q140" s="9" t="n"/>
       <c r="R140" s="9" t="n"/>
-      <c r="S140" s="10" t="n">
+      <c r="S140" s="9" t="n"/>
+      <c r="T140" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="T140" s="9" t="n"/>
       <c r="U140" s="9" t="n"/>
       <c r="V140" s="9" t="n"/>
-      <c r="W140" s="10" t="n">
+      <c r="W140" s="9" t="n"/>
+      <c r="X140" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="X140" s="9" t="n"/>
-      <c r="Y140" s="10" t="n">
+      <c r="Y140" s="9" t="n"/>
+      <c r="Z140" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="Z140" s="10" t="n">
+      <c r="AA140" s="10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21738,44 +21883,45 @@
       <c r="H141" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I141" s="9" t="inlineStr">
+      <c r="I141" s="9" t="n"/>
+      <c r="J141" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" s="9" t="inlineStr">
+      <c r="K141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="9" t="inlineStr">
         <is>
           <t>BR-08425/2026</t>
         </is>
       </c>
-      <c r="L141" s="9" t="inlineStr">
+      <c r="M141" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-meio-ideia-presidente-republica-fevereiro-2026/</t>
         </is>
       </c>
-      <c r="M141" s="9" t="n"/>
       <c r="N141" s="9" t="n"/>
       <c r="O141" s="9" t="n"/>
       <c r="P141" s="9" t="n"/>
       <c r="Q141" s="9" t="n"/>
       <c r="R141" s="9" t="n"/>
-      <c r="S141" s="10" t="n">
+      <c r="S141" s="9" t="n"/>
+      <c r="T141" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="T141" s="9" t="n"/>
       <c r="U141" s="9" t="n"/>
       <c r="V141" s="9" t="n"/>
-      <c r="W141" s="10" t="n">
+      <c r="W141" s="9" t="n"/>
+      <c r="X141" s="10" t="n">
         <v>34.5</v>
       </c>
-      <c r="X141" s="9" t="n"/>
-      <c r="Y141" s="10" t="n">
+      <c r="Y141" s="9" t="n"/>
+      <c r="Z141" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z141" s="10" t="n">
+      <c r="AA141" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -21814,40 +21960,41 @@
       <c r="H142" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I142" s="9" t="inlineStr">
+      <c r="I142" s="9" t="n"/>
+      <c r="J142" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="9" t="inlineStr">
+      <c r="K142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="9" t="inlineStr">
         <is>
           <t>BR-02804/2026</t>
         </is>
       </c>
-      <c r="L142" s="9" t="n"/>
       <c r="M142" s="9" t="n"/>
       <c r="N142" s="9" t="n"/>
       <c r="O142" s="9" t="n"/>
       <c r="P142" s="9" t="n"/>
       <c r="Q142" s="9" t="n"/>
       <c r="R142" s="9" t="n"/>
-      <c r="S142" s="10" t="n">
+      <c r="S142" s="9" t="n"/>
+      <c r="T142" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="T142" s="9" t="n"/>
       <c r="U142" s="9" t="n"/>
       <c r="V142" s="9" t="n"/>
-      <c r="W142" s="10" t="n">
+      <c r="W142" s="9" t="n"/>
+      <c r="X142" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="X142" s="9" t="n"/>
-      <c r="Y142" s="10" t="n">
+      <c r="Y142" s="9" t="n"/>
+      <c r="Z142" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="Z142" s="9" t="n"/>
+      <c r="AA142" s="9" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
@@ -21884,40 +22031,41 @@
       <c r="H143" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I143" s="9" t="inlineStr">
+      <c r="I143" s="9" t="n"/>
+      <c r="J143" s="9" t="inlineStr">
         <is>
           <t>telefonica</t>
         </is>
       </c>
-      <c r="J143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" s="9" t="n"/>
-      <c r="L143" s="9" t="inlineStr">
+      <c r="K143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="9" t="n"/>
+      <c r="M143" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-100-cidades-futura-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M143" s="9" t="n"/>
       <c r="N143" s="9" t="n"/>
       <c r="O143" s="9" t="n"/>
       <c r="P143" s="9" t="n"/>
       <c r="Q143" s="9" t="n"/>
       <c r="R143" s="9" t="n"/>
-      <c r="S143" s="10" t="n">
+      <c r="S143" s="9" t="n"/>
+      <c r="T143" s="10" t="n">
         <v>42.8</v>
       </c>
-      <c r="T143" s="9" t="n"/>
       <c r="U143" s="9" t="n"/>
       <c r="V143" s="9" t="n"/>
-      <c r="W143" s="10" t="n">
+      <c r="W143" s="9" t="n"/>
+      <c r="X143" s="10" t="n">
         <v>40.5</v>
       </c>
-      <c r="X143" s="9" t="n"/>
-      <c r="Y143" s="10" t="n">
+      <c r="Y143" s="9" t="n"/>
+      <c r="Z143" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="Z143" s="10" t="n">
+      <c r="AA143" s="10" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -21956,40 +22104,41 @@
       <c r="H144" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I144" s="9" t="inlineStr">
+      <c r="I144" s="9" t="n"/>
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>online</t>
         </is>
       </c>
-      <c r="J144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="9" t="inlineStr">
+      <c r="K144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="9" t="inlineStr">
         <is>
           <t>BR-06845/2026</t>
         </is>
       </c>
-      <c r="L144" s="9" t="n"/>
       <c r="M144" s="9" t="n"/>
       <c r="N144" s="9" t="n"/>
       <c r="O144" s="9" t="n"/>
       <c r="P144" s="9" t="n"/>
       <c r="Q144" s="9" t="n"/>
       <c r="R144" s="9" t="n"/>
-      <c r="S144" s="10" t="n">
+      <c r="S144" s="9" t="n"/>
+      <c r="T144" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="T144" s="9" t="n"/>
       <c r="U144" s="9" t="n"/>
       <c r="V144" s="9" t="n"/>
-      <c r="W144" s="10" t="n">
+      <c r="W144" s="9" t="n"/>
+      <c r="X144" s="10" t="n">
         <v>36.9</v>
       </c>
-      <c r="X144" s="9" t="n"/>
-      <c r="Y144" s="10" t="n">
+      <c r="Y144" s="9" t="n"/>
+      <c r="Z144" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="Z144" s="10" t="n">
+      <c r="AA144" s="10" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -22028,44 +22177,45 @@
       <c r="H145" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I145" s="9" t="inlineStr">
+      <c r="I145" s="9" t="n"/>
+      <c r="J145" s="9" t="inlineStr">
         <is>
           <t>presencial</t>
         </is>
       </c>
-      <c r="J145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="9" t="inlineStr">
+      <c r="K145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="9" t="inlineStr">
         <is>
           <t>BR-00835/2026</t>
         </is>
       </c>
-      <c r="L145" s="9" t="inlineStr">
+      <c r="M145" s="9" t="inlineStr">
         <is>
           <t>https://www.gazetadopovo.com.br/eleicoes/2026/pesquisa-eleitoral-2026/pesquisa-quaest-presidente-janeiro-2026/</t>
         </is>
       </c>
-      <c r="M145" s="9" t="n"/>
       <c r="N145" s="9" t="n"/>
       <c r="O145" s="9" t="n"/>
       <c r="P145" s="9" t="n"/>
       <c r="Q145" s="9" t="n"/>
       <c r="R145" s="9" t="n"/>
-      <c r="S145" s="10" t="n">
+      <c r="S145" s="9" t="n"/>
+      <c r="T145" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="T145" s="9" t="n"/>
       <c r="U145" s="9" t="n"/>
       <c r="V145" s="9" t="n"/>
-      <c r="W145" s="10" t="n">
+      <c r="W145" s="9" t="n"/>
+      <c r="X145" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="X145" s="9" t="n"/>
-      <c r="Y145" s="10" t="n">
+      <c r="Y145" s="9" t="n"/>
+      <c r="Z145" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="Z145" s="10" t="n">
+      <c r="AA145" s="10" t="n">
         <v>4</v>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="8">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>34.21</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="11">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="12">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>40.68</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="13">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="16">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="18">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="20">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>42.33</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="22">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45.08</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="23">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>10.61</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="24">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="26">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>15.11</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="28">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>38.85</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="30">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12.8</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="31">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="33">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="9">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="10">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>34.21</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="13">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="14">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>40.68</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="15">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="17">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="18">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="19">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="23">
@@ -2190,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.8462453562252571</v>
+        <v>0.7616208206027314</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.9117224885582168</v>
+        <v>0.8205502397023952</v>
       </c>
       <c r="K26" s="10" t="n">
         <v/>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.6453456181883783</v>
+        <v>0.5808110563695406</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>2.517920317061483</v>
+        <v>2.014336253649187</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>0.2</v>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>2.027549432420576</v>
+        <v>1.824794489178518</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.4409723674632056</v>
+        <v>0.396875130716885</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>0.3</v>
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.148698354997035</v>
+        <v>0.9189586839976281</v>
       </c>
       <c r="K37" s="10" t="n">
         <v/>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.546261095737613</v>
+        <v>1.23700887659009</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>0.3</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.061720302151183</v>
+        <v>0.9555482719360651</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.1546146572043905</v>
+        <v>0.1004995271828538</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>0.4</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1595514354976879</v>
+        <v>0.1435962919479191</v>
       </c>
       <c r="K47" s="10" t="n">
         <v/>
@@ -3961,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.6901550050719714</v>
+        <v>0.5521240040575771</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>0.6</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4729426281050314</v>
+        <v>0.4256483652945283</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>1</v>
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.3682969720803814</v>
+        <v>0.2946375776643052</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>1.1</v>
@@ -4417,7 +4417,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2779833581305687</v>
+        <v>0.2501850223175118</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.04910771461353507</v>
+        <v>0.04419694315218156</v>
       </c>
       <c r="K56" s="10" t="n">
         <v/>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.1710172229957937</v>
+        <v>0.136813778396635</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>1</v>
@@ -4796,7 +4796,7 @@
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="10" t="n">
-        <v>0.03553604234058531</v>
+        <v>0.02842883387246825</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>0.4</v>
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.043184777498993</v>
+        <v>0.0388662997490937</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>0.2</v>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.126721839526286</v>
+        <v>0.1140496555736574</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>2</v>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>42.33</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="9">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45.08</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="10">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>10.61</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="11">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="14">
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.8462453562252571</v>
+        <v>0.7616208206027314</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>41.4</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.9117224885582168</v>
+        <v>0.8205502397023952</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>41</v>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.6453456181883783</v>
+        <v>0.5808110563695406</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>43</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2.517920317061483</v>
+        <v>2.014336253649187</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>41.8</v>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.027549432420576</v>
+        <v>1.824794489178518</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>41</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.4409723674632056</v>
+        <v>0.396875130716885</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>46.9</v>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.148698354997035</v>
+        <v>0.9189586839976281</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>44</v>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1.546261095737613</v>
+        <v>1.23700887659009</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>47.8</v>
@@ -6221,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.336525792349203</v>
+        <v>0.3028732131142827</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>41</v>
@@ -6271,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.336525792349203</v>
+        <v>0.3028732131142827</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>45</v>
@@ -6321,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.336525792349203</v>
+        <v>0.3028732131142827</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>41</v>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.061720302151183</v>
+        <v>0.9555482719360651</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>42</v>
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.1546146572043905</v>
+        <v>0.1004995271828538</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>41</v>
@@ -6721,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>46</v>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1595514354976879</v>
+        <v>0.1435962919479191</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>48</v>
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.6901550050719714</v>
+        <v>0.5521240040575771</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>47.6</v>
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4729426281050314</v>
+        <v>0.4256483652945283</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>41</v>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.3682969720803814</v>
+        <v>0.2946375776643052</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>46.3</v>
@@ -7115,7 +7115,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2779833581305687</v>
+        <v>0.2501850223175118</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>42</v>
@@ -7165,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.04910771461353507</v>
+        <v>0.04419694315218156</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>45</v>
@@ -7265,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.1710172229957937</v>
+        <v>0.136813778396635</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>45</v>
@@ -7309,7 +7309,7 @@
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.04061261981781178</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>42.5</v>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.043184777498993</v>
+        <v>0.0388662997490937</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>37</v>
@@ -7409,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.126721839526286</v>
+        <v>0.1140496555736574</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>41</v>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>15.11</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="9">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>38.85</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="11">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>12.8</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="15">
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.8462453562252571</v>
+        <v>0.7616208206027314</v>
       </c>
       <c r="K17" s="10" t="n">
         <v/>
@@ -7722,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.6453456181883783</v>
+        <v>0.5808110563695406</v>
       </c>
       <c r="K18" s="10" t="n">
         <v/>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2.517920317061483</v>
+        <v>2.014336253649187</v>
       </c>
       <c r="K22" s="10" t="n">
         <v/>
@@ -8093,7 +8093,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2.027549432420576</v>
+        <v>1.824794489178518</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -8199,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1.148698354997035</v>
+        <v>0.9189586839976281</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1.546261095737613</v>
+        <v>1.23700887659009</v>
       </c>
       <c r="K28" s="10" t="n">
         <v/>
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1.061720302151183</v>
+        <v>0.9555482719360651</v>
       </c>
       <c r="K29" s="10" t="n">
         <v/>
@@ -8570,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>40</v>
@@ -8623,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.6901550050719714</v>
+        <v>0.5521240040575771</v>
       </c>
       <c r="K35" s="10" t="n">
         <v/>
@@ -8676,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.4729426281050314</v>
+        <v>0.4256483652945283</v>
       </c>
       <c r="K36" s="10" t="n">
         <v/>
@@ -8835,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.3682969720803814</v>
+        <v>0.2946375776643052</v>
       </c>
       <c r="K39" s="10" t="n">
         <v/>
@@ -8882,7 +8882,7 @@
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="10" t="n">
-        <v>0.2779833581305687</v>
+        <v>0.2501850223175118</v>
       </c>
       <c r="K40" s="10" t="n">
         <v/>
@@ -8935,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.1710172229957937</v>
+        <v>0.136813778396635</v>
       </c>
       <c r="K41" s="10" t="n">
         <v/>
@@ -8982,7 +8982,7 @@
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="10" t="n">
-        <v>0.05076577477226472</v>
+        <v>0.04061261981781178</v>
       </c>
       <c r="K42" s="10" t="n">
         <v/>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.126721839526286</v>
+        <v>0.1140496555736574</v>
       </c>
       <c r="K43" s="10" t="n">
         <v/>
@@ -9274,19 +9274,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>43.47</v>
+        <v>43.24</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>33.07</v>
+        <v>32.95</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
@@ -9300,19 +9300,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>42.54</v>
+        <v>42.26</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>33.07</v>
+        <v>32.99</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="H9" s="5" t="n"/>
     </row>
@@ -9326,19 +9326,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>41.51</v>
+        <v>41.24</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>32.53</v>
+        <v>32.4</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="H10" s="5" t="n"/>
     </row>
@@ -9352,22 +9352,22 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>40.81</v>
+        <v>40.58</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>33.03</v>
+        <v>32.91</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>2.91</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -9380,19 +9380,19 @@
         <v>4</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>38.71</v>
+        <v>38.74</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>32.41</v>
+        <v>32.36</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>1</v>
@@ -9408,19 +9408,19 @@
         <v>5</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>41.03</v>
+        <v>40.83</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>34.53</v>
+        <v>34.32</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>4.52</v>
+        <v>4.47</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>1</v>
@@ -9436,19 +9436,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>40.27</v>
+        <v>40.1</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>33.75</v>
+        <v>33.58</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>1</v>
@@ -9464,19 +9464,19 @@
         <v>6</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>40.08</v>
+        <v>39.95</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>33.63</v>
+        <v>33.52</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>3.16</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>1</v>
@@ -9492,19 +9492,19 @@
         <v>5</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>40.4</v>
+        <v>40.24</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>33.73</v>
+        <v>33.6</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>3.19</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
@@ -9518,19 +9518,19 @@
         <v>6</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>41.25</v>
+        <v>41.01</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>35.51</v>
+        <v>35.25</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
@@ -9544,19 +9544,19 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>41.92</v>
+        <v>41.73</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>36.41</v>
+        <v>36.23</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H18" s="5" t="n"/>
     </row>
@@ -9570,19 +9570,19 @@
         <v>9</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>40.6</v>
+        <v>40.51</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>36.08</v>
+        <v>35.91</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H19" s="5" t="n"/>
     </row>
@@ -9596,22 +9596,22 @@
         <v>10</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>39.76</v>
+        <v>39.72</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>35.14</v>
+        <v>35.03</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>4.69</v>
+        <v>4.73</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21">
@@ -9624,22 +9624,22 @@
         <v>8</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>38.71</v>
+        <v>38.83</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>34.18</v>
+        <v>34.2</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>1.97</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="22">
@@ -9652,22 +9652,22 @@
         <v>7</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>41.04</v>
+        <v>40.83</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>35.79</v>
+        <v>35.6</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -9680,22 +9680,22 @@
         <v>7</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>41.29</v>
+        <v>41.11</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>35.73</v>
+        <v>35.62</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24">
@@ -9708,22 +9708,22 @@
         <v>7</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>40.13</v>
+        <v>39.9</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>35.55</v>
+        <v>35.49</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="25">
@@ -9736,22 +9736,22 @@
         <v>13</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>41.08</v>
+        <v>40.84</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>34.24</v>
+        <v>34.15</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>3.56</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>
@@ -9856,10 +9856,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>44.61</v>
+        <v>44.44</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>42.5</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="9">
@@ -9872,10 +9872,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>43.6</v>
+        <v>43.34</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>40.36</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="10">
@@ -9888,10 +9888,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>43.72</v>
+        <v>43.49</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>40.76</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="11">
@@ -9904,10 +9904,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>42.81</v>
+        <v>42.6</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>41.47</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="12">
@@ -9920,10 +9920,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>40.68</v>
+        <v>40.67</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>40.02</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="13">
@@ -9936,10 +9936,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>42.98</v>
+        <v>42.78</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>41.92</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="14">
@@ -9952,10 +9952,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>43.57</v>
+        <v>43.51</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>41.97</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="15">
@@ -9968,10 +9968,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>42.98</v>
+        <v>42.95</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>41.74</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="16">
@@ -9984,10 +9984,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>43.45</v>
+        <v>43.39</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>41.7</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="17">
@@ -10000,10 +10000,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>44.55</v>
+        <v>44.48</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>44.37</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="18">
@@ -10016,10 +10016,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>43.77</v>
+        <v>43.59</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>43</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="19">
@@ -10032,10 +10032,10 @@
         <v>9</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>44.47</v>
+        <v>44.44</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>44.28</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="20">
@@ -10048,10 +10048,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>43.43</v>
+        <v>43.44</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>43.75</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="21">
@@ -10064,10 +10064,10 @@
         <v>11</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>43.32</v>
+        <v>43.39</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>42.75</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="22">
@@ -10080,10 +10080,10 @@
         <v>10</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>44.57</v>
+        <v>44.53</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>44.65</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="23">
@@ -10096,10 +10096,10 @@
         <v>12</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.45</v>
+        <v>44.42</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>42.96</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="24">
@@ -10112,10 +10112,10 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>44.5</v>
+        <v>44.49</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>43.41</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="25">
@@ -10128,10 +10128,10 @@
         <v>22</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>45.63</v>
+        <v>45.58</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>42.16</v>
+        <v>42.06</v>
       </c>
     </row>
   </sheetData>
@@ -10244,10 +10244,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>45.77</v>
+        <v>45.65</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>36.88</v>
+        <v>36.75</v>
       </c>
       <c r="E8" s="5" t="n"/>
     </row>
@@ -10261,10 +10261,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>45.77</v>
+        <v>45.65</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>36.88</v>
+        <v>36.75</v>
       </c>
       <c r="E9" s="5" t="n"/>
     </row>
@@ -10278,10 +10278,10 @@
         <v>3</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>45.77</v>
+        <v>45.65</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>36.88</v>
+        <v>36.75</v>
       </c>
       <c r="E10" s="5" t="n"/>
     </row>
@@ -10295,10 +10295,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>44.38</v>
+        <v>44.22</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>36.56</v>
+        <v>36.46</v>
       </c>
       <c r="E11" s="5" t="n"/>
     </row>
@@ -10329,10 +10329,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>44.28</v>
+        <v>44.16</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>38.82</v>
+        <v>38.62</v>
       </c>
       <c r="E13" s="5" t="n"/>
     </row>
@@ -10346,10 +10346,10 @@
         <v>4</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>44.78</v>
+        <v>44.76</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>37.7</v>
+        <v>37.43</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>40</v>
@@ -10368,7 +10368,7 @@
         <v>44.57</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>36.44</v>
+        <v>36.25</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>40</v>
@@ -10384,10 +10384,10 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>45.04</v>
+        <v>45.02</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>36.8</v>
+        <v>36.57</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>40</v>
@@ -10403,10 +10403,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>45.48</v>
+        <v>45.42</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>38.87</v>
+        <v>38.51</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>40</v>
@@ -10422,10 +10422,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>45.6</v>
+        <v>45.54</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>39.76</v>
+        <v>39.48</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>40</v>
@@ -10441,10 +10441,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>45.46</v>
+        <v>45.39</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>40.31</v>
+        <v>40.11</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>40</v>
@@ -10460,10 +10460,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>44.76</v>
+        <v>44.73</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>39.02</v>
+        <v>38.93</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>40</v>
@@ -10479,10 +10479,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>44.34</v>
+        <v>44.38</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>37.9</v>
+        <v>37.98</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>40</v>
@@ -10498,10 +10498,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>45.35</v>
+        <v>45.25</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>40.91</v>
+        <v>40.61</v>
       </c>
       <c r="E22" s="5" t="n"/>
     </row>
@@ -10515,10 +10515,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>44.83</v>
+        <v>44.78</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>41.09</v>
+        <v>40.73</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>38.7</v>
@@ -10534,10 +10534,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>45.06</v>
+        <v>45.05</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>40.91</v>
+        <v>40.74</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>38.7</v>
@@ -10553,10 +10553,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>46.5</v>
+        <v>46.52</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>39.22</v>
+        <v>39.09</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>11</v>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9555482719360651</v>
+        <v>0.9555482719360652</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>0</v>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9555482719360651</v>
+        <v>0.9555482719360652</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>42</v>
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.9555482719360651</v>
+        <v>0.9555482719360652</v>
       </c>
       <c r="K29" s="10" t="n">
         <v/>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.7616208206027314</v>
+        <v>0.7442253770190295</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.8205502397023952</v>
+        <v>0.8018088463263053</v>
       </c>
       <c r="K26" s="10" t="n">
         <v/>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.5808110563695406</v>
+        <v>0.5675453135083213</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.8323110314995047</v>
+        <v>0.8133010212675307</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>0.1</v>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>2.014336253649187</v>
+        <v>1.968328750031797</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>0.2</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>2.173073675648897</v>
+        <v>2.123440604302367</v>
       </c>
       <c r="K32" s="10" t="n">
         <v/>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.4836695079887215</v>
+        <v>0.4726224811588665</v>
       </c>
       <c r="K33" s="10" t="n">
         <v/>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.824794489178518</v>
+        <v>1.783116125444667</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.396875130716885</v>
+        <v>0.3878104902036487</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>0.3</v>
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.5090271751036068</v>
+        <v>0.4974009783564138</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>0.6</v>
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.9189586839976281</v>
+        <v>0.8979696386474985</v>
       </c>
       <c r="K37" s="10" t="n">
         <v/>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.23700887659009</v>
+        <v>1.208755554801655</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>0.3</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9555482719360652</v>
+        <v>0.9337235192424436</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>0</v>
@@ -3345,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.3456509159387414</v>
+        <v>0.3377562381079687</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>1.5</v>
@@ -3422,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.2363112405794332</v>
+        <v>0.2309138843852565</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>0.3</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.9679942760300587</v>
+        <v>0.9458852562100629</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>1</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.1004995271828538</v>
+        <v>0.09820411480965412</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>0.4</v>
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.2665505844209967</v>
+        <v>0.260462560658951</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>0.6</v>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.5218203444992953</v>
+        <v>0.5099019513592785</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>0.2</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.1575</v>
+        <v>0.1539026950283937</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1435962919479191</v>
+        <v>0.1403165481071034</v>
       </c>
       <c r="K47" s="10" t="n">
         <v/>
@@ -3961,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.5521240040575771</v>
+        <v>0.5395134743766915</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>0.6</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4256483652945283</v>
+        <v>0.4159265431952898</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>1</v>
@@ -4115,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.4311924298411825</v>
+        <v>0.4213439811326959</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>2</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.2679433656340733</v>
+        <v>0.2618235307051567</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>2</v>
@@ -4269,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.2434377985364723</v>
+        <v>0.2378776715336016</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>0.2</v>
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.2946375776643052</v>
+        <v>0.2879080460899952</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>1.1</v>
@@ -4417,7 +4417,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2501850223175118</v>
+        <v>0.2444707885105009</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.1574901312368592</v>
+        <v>0.1538930516681146</v>
       </c>
       <c r="K55" s="10" t="n">
         <v/>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.04419694315218156</v>
+        <v>0.04318748357547589</v>
       </c>
       <c r="K56" s="10" t="n">
         <v/>
@@ -4648,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.1274754878398196</v>
+        <v>0.1245639436736982</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>0.3</v>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.136813778396635</v>
+        <v>0.1336889473794257</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>1</v>
@@ -4796,7 +4796,7 @@
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="10" t="n">
-        <v>0.02842883387246825</v>
+        <v>0.02777951840944349</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>0.4</v>
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.0388662997490937</v>
+        <v>0.03797859223598035</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>0.2</v>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.1140496555736574</v>
+        <v>0.1114447578402917</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>2</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.7616208206027314</v>
+        <v>0.7442253770190295</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>41.4</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.8205502397023952</v>
+        <v>0.8018088463263053</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>41</v>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.5808110563695406</v>
+        <v>0.5675453135083213</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>43</v>
@@ -5371,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>31</v>
@@ -5421,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>47</v>
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>32</v>
@@ -5521,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>41.6</v>
@@ -5571,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>42.2</v>
@@ -5621,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>43</v>
@@ -5671,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.8323110314995047</v>
+        <v>0.8133010212675307</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>38.1</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2.014336253649187</v>
+        <v>1.968328750031797</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>41.8</v>
@@ -5771,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2.173073675648897</v>
+        <v>2.123440604302367</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>45</v>
@@ -5821,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.4836695079887215</v>
+        <v>0.4726224811588665</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>50</v>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1.824794489178518</v>
+        <v>1.783116125444667</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>41</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.396875130716885</v>
+        <v>0.3878104902036487</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>46.9</v>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.5090271751036068</v>
+        <v>0.4974009783564138</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>45.8</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.5090271751036068</v>
+        <v>0.4974009783564138</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>39</v>
@@ -6071,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.5090271751036068</v>
+        <v>0.4974009783564138</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>26.4</v>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.9189586839976281</v>
+        <v>0.8979696386474985</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>44</v>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1.23700887659009</v>
+        <v>1.208755554801655</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>47.8</v>
@@ -6221,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.3028732131142827</v>
+        <v>0.2959555793663311</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>41</v>
@@ -6271,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.3028732131142827</v>
+        <v>0.2959555793663311</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>45</v>
@@ -6321,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.3028732131142827</v>
+        <v>0.2959555793663311</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>41</v>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9555482719360652</v>
+        <v>0.9337235192424436</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>42</v>
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.3456509159387414</v>
+        <v>0.3377562381079687</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>40.2</v>
@@ -6471,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.2363112405794332</v>
+        <v>0.2309138843852565</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>48</v>
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.9679942760300587</v>
+        <v>0.9458852562100629</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>46</v>
@@ -6571,7 +6571,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.2665505844209967</v>
+        <v>0.260462560658951</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>45.8</v>
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.1004995271828538</v>
+        <v>0.09820411480965412</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>41</v>
@@ -6671,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.5218203444992953</v>
+        <v>0.5099019513592785</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>36.2</v>
@@ -6721,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.1575</v>
+        <v>0.1539026950283937</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>46</v>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1435962919479191</v>
+        <v>0.1403165481071034</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>48</v>
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.5521240040575771</v>
+        <v>0.5395134743766915</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>47.6</v>
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4256483652945283</v>
+        <v>0.4159265431952898</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>41</v>
@@ -6921,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.4311924298411825</v>
+        <v>0.4213439811326959</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>43</v>
@@ -6971,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.2679433656340733</v>
+        <v>0.2618235307051567</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>41</v>
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.2434377985364723</v>
+        <v>0.2378776715336016</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>34.6</v>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.2946375776643052</v>
+        <v>0.2879080460899952</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>46.3</v>
@@ -7115,7 +7115,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2501850223175118</v>
+        <v>0.2444707885105009</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>42</v>
@@ -7165,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.04419694315218156</v>
+        <v>0.04318748357547589</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>45</v>
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.1274754878398196</v>
+        <v>0.1245639436736982</v>
       </c>
       <c r="K56" s="10" t="n">
         <v>33.8</v>
@@ -7265,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.136813778396635</v>
+        <v>0.1336889473794257</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>45</v>
@@ -7309,7 +7309,7 @@
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="10" t="n">
-        <v>0.04061261981781178</v>
+        <v>0.03968502629920499</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>42.5</v>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.0388662997490937</v>
+        <v>0.03797859223598035</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>37</v>
@@ -7409,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.1140496555736574</v>
+        <v>0.1114447578402917</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>41</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.7616208206027314</v>
+        <v>0.7442253770190295</v>
       </c>
       <c r="K17" s="10" t="n">
         <v/>
@@ -7722,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.5808110563695406</v>
+        <v>0.5675453135083213</v>
       </c>
       <c r="K18" s="10" t="n">
         <v/>
@@ -7775,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.6093853943072869</v>
+        <v>0.595467012665599</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>34</v>
@@ -7828,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K20" s="10" t="n">
         <v/>
@@ -7881,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2.554552209609086</v>
+        <v>2.496206156505248</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2.014336253649187</v>
+        <v>1.968328750031797</v>
       </c>
       <c r="K22" s="10" t="n">
         <v/>
@@ -7987,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>2.173073675648897</v>
+        <v>2.123440604302367</v>
       </c>
       <c r="K23" s="10" t="n">
         <v/>
@@ -8040,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.4836695079887215</v>
+        <v>0.4726224811588665</v>
       </c>
       <c r="K24" s="10" t="n">
         <v/>
@@ -8093,7 +8093,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1.824794489178518</v>
+        <v>1.783116125444667</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -8146,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.5090271751036068</v>
+        <v>0.4974009783564138</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>38.7</v>
@@ -8199,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.9189586839976281</v>
+        <v>0.8979696386474985</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1.23700887659009</v>
+        <v>1.208755554801655</v>
       </c>
       <c r="K28" s="10" t="n">
         <v/>
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.9555482719360652</v>
+        <v>0.9337235192424436</v>
       </c>
       <c r="K29" s="10" t="n">
         <v/>
@@ -8358,7 +8358,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3456509159387414</v>
+        <v>0.3377562381079687</v>
       </c>
       <c r="K30" s="10" t="n">
         <v/>
@@ -8411,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.2363112405794332</v>
+        <v>0.2309138843852565</v>
       </c>
       <c r="K31" s="10" t="n">
         <v/>
@@ -8464,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.9679942760300587</v>
+        <v>0.9458852562100629</v>
       </c>
       <c r="K32" s="10" t="n">
         <v/>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.2665505844209967</v>
+        <v>0.260462560658951</v>
       </c>
       <c r="K33" s="10" t="n">
         <v/>
@@ -8570,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.1575</v>
+        <v>0.1539026950283937</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>40</v>
@@ -8623,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.5521240040575771</v>
+        <v>0.5395134743766915</v>
       </c>
       <c r="K35" s="10" t="n">
         <v/>
@@ -8676,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.4256483652945283</v>
+        <v>0.4159265431952898</v>
       </c>
       <c r="K36" s="10" t="n">
         <v/>
@@ -8729,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.4311924298411825</v>
+        <v>0.4213439811326959</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>40</v>
@@ -8782,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.2679433656340733</v>
+        <v>0.2618235307051567</v>
       </c>
       <c r="K38" s="10" t="n">
         <v/>
@@ -8835,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.2946375776643052</v>
+        <v>0.2879080460899952</v>
       </c>
       <c r="K39" s="10" t="n">
         <v/>
@@ -8882,7 +8882,7 @@
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="10" t="n">
-        <v>0.2501850223175118</v>
+        <v>0.2444707885105009</v>
       </c>
       <c r="K40" s="10" t="n">
         <v/>
@@ -8935,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.136813778396635</v>
+        <v>0.1336889473794257</v>
       </c>
       <c r="K41" s="10" t="n">
         <v/>
@@ -8982,7 +8982,7 @@
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="10" t="n">
-        <v>0.04061261981781178</v>
+        <v>0.03968502629920499</v>
       </c>
       <c r="K42" s="10" t="n">
         <v/>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.1140496555736574</v>
+        <v>0.1114447578402917</v>
       </c>
       <c r="K43" s="10" t="n">
         <v/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.7442253770190295</v>
+        <v>0.7272272459158797</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.8018088463263053</v>
+        <v>0.7834955069665117</v>
       </c>
       <c r="K26" s="10" t="n">
         <v/>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.5675453135083213</v>
+        <v>0.5545825606327954</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>2.439192729096038</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.8133010212675307</v>
+        <v>0.7947252002693204</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>0.1</v>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1.968328750031797</v>
+        <v>1.92337205924929</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>0.2</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>2.123440604302367</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="K32" s="10" t="n">
         <v/>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.4726224811588665</v>
+        <v>0.461827768770513</v>
       </c>
       <c r="K33" s="10" t="n">
         <v/>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.783116125444667</v>
+        <v>1.742389696854106</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.3878104902036487</v>
+        <v>0.3789528863658667</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>0.3</v>
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.4974009783564138</v>
+        <v>0.4860403243099164</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>0.6</v>
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.8979696386474985</v>
+        <v>0.8774599837557009</v>
       </c>
       <c r="K37" s="10" t="n">
         <v/>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.208755554801655</v>
+        <v>1.181147539774704</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>0.3</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9337235192424436</v>
+        <v>0.9123972445892592</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>0</v>
@@ -3345,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.3377562381079687</v>
+        <v>0.3300418749680524</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>1.5</v>
@@ -3422,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.2309138843852565</v>
+        <v>0.2256398039769263</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>0.3</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.9458852562100629</v>
+        <v>0.9242812071006439</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>1</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.09820411480965412</v>
+        <v>0.09596112972751467</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>0.4</v>
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.260462560658951</v>
+        <v>0.2545135875518034</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>0.6</v>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.5099019513592785</v>
+        <v>0.498255774694793</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>0.2</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.1539026950283937</v>
+        <v>0.1503875526158906</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1403165481071034</v>
+        <v>0.1371117137191396</v>
       </c>
       <c r="K47" s="10" t="n">
         <v/>
@@ -3961,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.5395134743766915</v>
+        <v>0.5271909695917781</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>0.6</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4159265431952898</v>
+        <v>0.4064267678196744</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>1</v>
@@ -4115,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.4213439811326959</v>
+        <v>0.4117204713035846</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>2</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.2618235307051567</v>
+        <v>0.2558434729991938</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>2</v>
@@ -4269,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.2378776715336016</v>
+        <v>0.2324445380069861</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>0.2</v>
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.2879080460899952</v>
+        <v>0.2813322172292652</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>1.1</v>
@@ -4417,7 +4417,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2444707885105009</v>
+        <v>0.2388870679840163</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.1538930516681146</v>
+        <v>0.1503781295102646</v>
       </c>
       <c r="K55" s="10" t="n">
         <v/>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.04318748357547589</v>
+        <v>0.04220108008736655</v>
       </c>
       <c r="K56" s="10" t="n">
         <v/>
@@ -4648,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.1245639436736982</v>
+        <v>0.1217188992682362</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>0.3</v>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.1336889473794257</v>
+        <v>0.1306354876012872</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>1</v>
@@ -4796,7 +4796,7 @@
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="10" t="n">
-        <v>0.02777951840944349</v>
+        <v>0.02714503333209035</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>0.4</v>
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.03797859223598035</v>
+        <v>0.03711115999048765</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>0.2</v>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.1114447578402917</v>
+        <v>0.1088993560533816</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>2</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.7442253770190295</v>
+        <v>0.7272272459158797</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>41.4</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.8018088463263053</v>
+        <v>0.7834955069665117</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>41</v>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.5675453135083213</v>
+        <v>0.5545825606327954</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>43</v>
@@ -5371,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>31</v>
@@ -5421,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>47</v>
@@ -5471,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>32</v>
@@ -5521,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>41.6</v>
@@ -5571,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>42.2</v>
@@ -5621,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>2.439192729096038</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>43</v>
@@ -5671,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.8133010212675307</v>
+        <v>0.7947252002693204</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>38.1</v>
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1.968328750031797</v>
+        <v>1.92337205924929</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>41.8</v>
@@ -5771,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2.123440604302367</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>45</v>
@@ -5821,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.4726224811588665</v>
+        <v>0.461827768770513</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>50</v>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1.783116125444667</v>
+        <v>1.742389696854106</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>41</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3878104902036487</v>
+        <v>0.3789528863658667</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>46.9</v>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.4974009783564138</v>
+        <v>0.4860403243099164</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>45.8</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.4974009783564138</v>
+        <v>0.4860403243099164</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>39</v>
@@ -6071,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.4974009783564138</v>
+        <v>0.4860403243099164</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>26.4</v>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.8979696386474985</v>
+        <v>0.8774599837557009</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>44</v>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1.208755554801655</v>
+        <v>1.181147539774704</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>47.8</v>
@@ -6221,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.2959555793663311</v>
+        <v>0.2891959445915431</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>41</v>
@@ -6271,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.2959555793663311</v>
+        <v>0.2891959445915431</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>45</v>
@@ -6321,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.2959555793663311</v>
+        <v>0.2891959445915431</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>41</v>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.9337235192424436</v>
+        <v>0.9123972445892592</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>42</v>
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.3377562381079687</v>
+        <v>0.3300418749680524</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>40.2</v>
@@ -6471,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.2309138843852565</v>
+        <v>0.2256398039769263</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>48</v>
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.9458852562100629</v>
+        <v>0.9242812071006439</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>46</v>
@@ -6571,7 +6571,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.260462560658951</v>
+        <v>0.2545135875518034</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>45.8</v>
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.09820411480965412</v>
+        <v>0.09596112972751467</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>41</v>
@@ -6671,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.5099019513592785</v>
+        <v>0.498255774694793</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>36.2</v>
@@ -6721,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.1539026950283937</v>
+        <v>0.1503875526158906</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>46</v>
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1403165481071034</v>
+        <v>0.1371117137191396</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>48</v>
@@ -6821,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.5395134743766915</v>
+        <v>0.5271909695917781</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>47.6</v>
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.4159265431952898</v>
+        <v>0.4064267678196744</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>41</v>
@@ -6921,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.4213439811326959</v>
+        <v>0.4117204713035846</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>43</v>
@@ -6971,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.2618235307051567</v>
+        <v>0.2558434729991938</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>41</v>
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.2378776715336016</v>
+        <v>0.2324445380069861</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>34.6</v>
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.2879080460899952</v>
+        <v>0.2813322172292652</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>46.3</v>
@@ -7115,7 +7115,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="10" t="n">
-        <v>0.2444707885105009</v>
+        <v>0.2388870679840163</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>42</v>
@@ -7165,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.04318748357547589</v>
+        <v>0.04220108008736655</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>45</v>
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.1245639436736982</v>
+        <v>0.1217188992682362</v>
       </c>
       <c r="K56" s="10" t="n">
         <v>33.8</v>
@@ -7265,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.1336889473794257</v>
+        <v>0.1306354876012872</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>45</v>
@@ -7309,7 +7309,7 @@
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="10" t="n">
-        <v>0.03968502629920499</v>
+        <v>0.03877861904584336</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>42.5</v>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.03797859223598035</v>
+        <v>0.03711115999048765</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>37</v>
@@ -7409,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.1114447578402917</v>
+        <v>0.1088993560533816</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>41</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.7442253770190295</v>
+        <v>0.7272272459158797</v>
       </c>
       <c r="K17" s="10" t="n">
         <v/>
@@ -7722,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.5675453135083213</v>
+        <v>0.5545825606327954</v>
       </c>
       <c r="K18" s="10" t="n">
         <v/>
@@ -7775,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.595467012665599</v>
+        <v>0.5818665272999514</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>34</v>
@@ -7828,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K20" s="10" t="n">
         <v/>
@@ -7881,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2.496206156505248</v>
+        <v>2.439192729096038</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1.968328750031797</v>
+        <v>1.92337205924929</v>
       </c>
       <c r="K22" s="10" t="n">
         <v/>
@@ -7987,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>2.123440604302367</v>
+        <v>2.074941153872097</v>
       </c>
       <c r="K23" s="10" t="n">
         <v/>
@@ -8040,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.4726224811588665</v>
+        <v>0.461827768770513</v>
       </c>
       <c r="K24" s="10" t="n">
         <v/>
@@ -8093,7 +8093,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1.783116125444667</v>
+        <v>1.742389696854106</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -8146,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.4974009783564138</v>
+        <v>0.4860403243099164</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>38.7</v>
@@ -8199,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.8979696386474985</v>
+        <v>0.8774599837557009</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -8252,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1.208755554801655</v>
+        <v>1.181147539774704</v>
       </c>
       <c r="K28" s="10" t="n">
         <v/>
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.9337235192424436</v>
+        <v>0.9123972445892592</v>
       </c>
       <c r="K29" s="10" t="n">
         <v/>
@@ -8358,7 +8358,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.3377562381079687</v>
+        <v>0.3300418749680524</v>
       </c>
       <c r="K30" s="10" t="n">
         <v/>
@@ -8411,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.2309138843852565</v>
+        <v>0.2256398039769263</v>
       </c>
       <c r="K31" s="10" t="n">
         <v/>
@@ -8464,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.9458852562100629</v>
+        <v>0.9242812071006439</v>
       </c>
       <c r="K32" s="10" t="n">
         <v/>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.260462560658951</v>
+        <v>0.2545135875518034</v>
       </c>
       <c r="K33" s="10" t="n">
         <v/>
@@ -8570,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.1539026950283937</v>
+        <v>0.1503875526158906</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>40</v>
@@ -8623,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.5395134743766915</v>
+        <v>0.5271909695917781</v>
       </c>
       <c r="K35" s="10" t="n">
         <v/>
@@ -8676,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.4159265431952898</v>
+        <v>0.4064267678196744</v>
       </c>
       <c r="K36" s="10" t="n">
         <v/>
@@ -8729,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.4213439811326959</v>
+        <v>0.4117204713035846</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>40</v>
@@ -8782,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.2618235307051567</v>
+        <v>0.2558434729991938</v>
       </c>
       <c r="K38" s="10" t="n">
         <v/>
@@ -8835,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.2879080460899952</v>
+        <v>0.2813322172292652</v>
       </c>
       <c r="K39" s="10" t="n">
         <v/>
@@ -8882,7 +8882,7 @@
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="J40" s="10" t="n">
-        <v>0.2444707885105009</v>
+        <v>0.2388870679840163</v>
       </c>
       <c r="K40" s="10" t="n">
         <v/>
@@ -8935,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.1336889473794257</v>
+        <v>0.1306354876012872</v>
       </c>
       <c r="K41" s="10" t="n">
         <v/>
@@ -8982,7 +8982,7 @@
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="10" t="n">
-        <v>0.03968502629920499</v>
+        <v>0.03877861904584336</v>
       </c>
       <c r="K42" s="10" t="n">
         <v/>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.1114447578402917</v>
+        <v>0.1088993560533816</v>
       </c>
       <c r="K43" s="10" t="n">
         <v/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -253,12 +253,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$C$6:$C$25</f>
+              <f>'Evolução 1º Turno'!$C$6:$C$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$D$6:$D$25</f>
+              <f>'Evolução 1º Turno'!$D$6:$D$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -319,12 +319,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$E$6:$E$25</f>
+              <f>'Evolução 1º Turno'!$E$6:$E$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -352,12 +352,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$F$6:$F$25</f>
+              <f>'Evolução 1º Turno'!$F$6:$F$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$G$6:$G$25</f>
+              <f>'Evolução 1º Turno'!$G$6:$G$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -418,12 +418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução 1º Turno'!$A$6:$A$25</f>
+              <f>'Evolução 1º Turno'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução 1º Turno'!$H$6:$H$25</f>
+              <f>'Evolução 1º Turno'!$H$6:$H$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -538,12 +538,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$A$6:$A$25</f>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$C$6:$C$25</f>
+              <f>'Evolução Lula vs Flávio'!$C$6:$C$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$A$6:$A$25</f>
+              <f>'Evolução Lula vs Flávio'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Flávio'!$D$6:$D$25</f>
+              <f>'Evolução Lula vs Flávio'!$D$6:$D$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -691,12 +691,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$A$6:$A$25</f>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$C$6:$C$25</f>
+              <f>'Evolução Lula vs Zema'!$C$6:$C$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -724,12 +724,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$A$6:$A$25</f>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$D$6:$D$25</f>
+              <f>'Evolução Lula vs Zema'!$D$6:$D$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -757,12 +757,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$A$6:$A$25</f>
+              <f>'Evolução Lula vs Zema'!$A$6:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Lula vs Zema'!$E$6:$E$25</f>
+              <f>'Evolução Lula vs Zema'!$E$6:$E$26</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -8925,7 +8925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9531,6 +9531,34 @@
         <v>3.26</v>
       </c>
       <c r="H25" s="12" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>1.76</v>
       </c>
     </row>
@@ -9549,7 +9577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9912,6 +9940,22 @@
       </c>
       <c r="D25" s="12" t="n">
         <v>43.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>42.88</v>
       </c>
     </row>
   </sheetData>
@@ -9929,7 +9973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10319,6 +10363,23 @@
         <v>39.09</v>
       </c>
       <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/agregador_pesquisas.xlsx
+++ b/output/agregador_pesquisas.xlsx
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.9413789135510666</v>
+        <v>0.919877789450225</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.7272272459158797</v>
+        <v>0.7106173526636846</v>
       </c>
       <c r="K26" s="10" t="n">
         <v/>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.5545825606327954</v>
+        <v>0.5419158774421257</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.7834955069665117</v>
+        <v>0.7656004448557702</v>
       </c>
       <c r="K28" s="10" t="n">
         <v/>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.5685766774493648</v>
+        <v>0.5555903681888698</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>0.4</v>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>2.439192729096038</v>
+        <v>2.383481490168527</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>1</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.7947252002693204</v>
+        <v>0.776573651609069</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>0.1</v>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1.92337205924929</v>
+        <v>1.879442180703346</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>0.2</v>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="K34" s="10" t="n">
         <v/>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.461827768770513</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="K35" s="10" t="n">
         <v/>
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.742389696854106</v>
+        <v>1.702593461178113</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.4860403243099164</v>
+        <v>0.4749391479604486</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>0.6</v>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.8774599837557009</v>
+        <v>0.8574187700290345</v>
       </c>
       <c r="K38" s="10" t="n">
         <v/>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.181147539774704</v>
+        <v>1.154170092682437</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>0.3</v>
@@ -3345,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.9123972445892592</v>
+        <v>0.8915580627223337</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.3300418749680524</v>
+        <v>0.3225037081257614</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>1.5</v>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.2256398039769263</v>
+        <v>0.2204861837316028</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>0.3</v>
@@ -3576,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.9242812071006439</v>
+        <v>0.9031705951548319</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>1</v>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.09596112972751467</v>
+        <v>0.09376937449545282</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>0.4</v>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.2545135875518034</v>
+        <v>0.2487004891782069</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>0.6</v>
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.498255774694793</v>
+        <v>0.4868755970729447</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.1503875526158906</v>
+        <v>0.1469526961670472</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.1371117137191396</v>
+        <v>0.1339800778497598</v>
       </c>
       <c r="K48" s="10" t="n">
         <v/>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.5271909695917781</v>
+        <v>0.5151499112051214</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>0.6</v>
@@ -4115,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.4064267678196744</v>
+        <v>0.3971439676135057</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.4117204713035846</v>
+        <v>0.4023167627427436</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>2</v>
@@ -4269,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.2558434729991938</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>2</v>
@@ -4346,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.2324445380069861</v>
+        <v>0.2271354974216195</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>0.2</v>
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.2813322172292652</v>
+        <v>0.2749065805072852</v>
       </c>
       <c r="K54" s="10" t="n">
         <v>1.1</v>
@@ -4494,7 +4494,7 @@
       <c r="H55" s="9" t="n"/>
       <c r="I55" s="9" t="n"/>
       <c r="J55" s="10" t="n">
-        <v>0.2388870679840163</v>
+        <v>0.2334308798106109</v>
       </c>
       <c r="K55" s="10" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.1503781295102646</v>
+        <v>0.1469434882854511</v>
       </c>
       <c r="K56" s="10" t="n">
         <v/>
@@ -4648,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.04220108008736655</v>
+        <v>0.04123720608606219</v>
       </c>
       <c r="K57" s="10" t="n">
         <v/>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.1217188992682362</v>
+        <v>0.1189388357668008</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>0.3</v>
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.1306354876012872</v>
+        <v>0.1276517689408661</v>
       </c>
       <c r="K59" s="10" t="n">
         <v>1</v>
@@ -4873,7 +4873,7 @@
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="10" t="n">
-        <v>0.02714503333209035</v>
+        <v>0.02652503991393198</v>
       </c>
       <c r="K60" s="10" t="n">
         <v>0.4</v>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.03711115999048765</v>
+        <v>0.03626353992486316</v>
       </c>
       <c r="K61" s="10" t="n">
         <v>0.2</v>
@@ -5027,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.1088993560533816</v>
+        <v>0.1064120913236321</v>
       </c>
       <c r="K62" s="10" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.9413789135510666</v>
+        <v>0.919877789450225</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>42</v>
@@ -5348,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.7272272459158797</v>
+        <v>0.7106173526636846</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>41.4</v>
@@ -5398,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.5545825606327954</v>
+        <v>0.5419158774421257</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>43</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.7834955069665117</v>
+        <v>0.7656004448557702</v>
       </c>
       <c r="K19" s="10" t="n">
         <v>41</v>
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K20" s="10" t="n">
         <v>47</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.5685766774493648</v>
+        <v>0.5555903681888698</v>
       </c>
       <c r="K21" s="10" t="n">
         <v>42.2</v>
@@ -5598,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2.439192729096038</v>
+        <v>2.383481490168527</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>43</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.7947252002693204</v>
+        <v>0.776573651609069</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>38.1</v>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1.92337205924929</v>
+        <v>1.879442180703346</v>
       </c>
       <c r="K24" s="10" t="n">
         <v>41.8</v>
@@ -5748,7 +5748,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>45</v>
@@ -5798,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.461827768770513</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>50</v>
@@ -5848,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1.742389696854106</v>
+        <v>1.702593461178113</v>
       </c>
       <c r="K27" s="10" t="n">
         <v>41</v>
@@ -5898,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.4860403243099164</v>
+        <v>0.4749391479604486</v>
       </c>
       <c r="K28" s="10" t="n">
         <v>45.8</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.8774599837557009</v>
+        <v>0.8574187700290345</v>
       </c>
       <c r="K29" s="10" t="n">
         <v>44</v>
@@ -5998,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.181147539774704</v>
+        <v>1.154170092682437</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>47.8</v>
@@ -6048,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.2891959445915431</v>
+        <v>0.2825907000883842</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>45</v>
@@ -6098,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.9123972445892592</v>
+        <v>0.8915580627223337</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>42</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.3300418749680524</v>
+        <v>0.3225037081257614</v>
       </c>
       <c r="K33" s="10" t="n">
         <v>40.2</v>
@@ -6198,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.2256398039769263</v>
+        <v>0.2204861837316028</v>
       </c>
       <c r="K34" s="10" t="n">
         <v>48</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.9242812071006439</v>
+        <v>0.9031705951548319</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>46</v>
@@ -6298,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.2545135875518034</v>
+        <v>0.2487004891782069</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>45.8</v>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.09596112972751467</v>
+        <v>0.09376937449545282</v>
       </c>
       <c r="K37" s="10" t="n">
         <v>41</v>
@@ -6398,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.498255774694793</v>
+        <v>0.4868755970729447</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>36.2</v>
@@ -6448,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.1503875526158906</v>
+        <v>0.1469526961670472</v>
       </c>
       <c r="K39" s="10" t="n">
         <v>46</v>
@@ -6498,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.1371117137191396</v>
+        <v>0.1339800778497598</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>48</v>
@@ -6548,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.5271909695917781</v>
+        <v>0.5151499112051214</v>
       </c>
       <c r="K41" s="10" t="n">
         <v>47.6</v>
@@ -6598,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.4064267678196744</v>
+        <v>0.3971439676135057</v>
       </c>
       <c r="K42" s="10" t="n">
         <v>41</v>
@@ -6648,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.4117204713035846</v>
+        <v>0.4023167627427436</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>43</v>
@@ -6698,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.2558434729991938</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="K44" s="10" t="n">
         <v>41</v>
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.2324445380069861</v>
+        <v>0.2271354974216195</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>34.6</v>
@@ -6798,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.2813322172292652</v>
+        <v>0.2749065805072852</v>
       </c>
       <c r="K46" s="10" t="n">
         <v>46.3</v>
@@ -6842,7 +6842,7 @@
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
       <c r="J47" s="10" t="n">
-        <v>0.2388870679840163</v>
+        <v>0.2334308798106109</v>
       </c>
       <c r="K47" s="10" t="n">
         <v>42</v>
@@ -6892,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.04220108008736655</v>
+        <v>0.04123720608606219</v>
       </c>
       <c r="K48" s="10" t="n">
         <v>45</v>
@@ -6942,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.1217188992682362</v>
+        <v>0.1189388357668008</v>
       </c>
       <c r="K49" s="10" t="n">
         <v>33.8</v>
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.1306354876012872</v>
+        <v>0.1276517689408661</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>45</v>
@@ -7036,7 +7036,7 @@
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
       <c r="J51" s="10" t="n">
-        <v>0.03877861904584336</v>
+        <v>0.03789291416275997</v>
       </c>
       <c r="K51" s="10" t="n">
         <v>42.5</v>
@@ -7086,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.03711115999048765</v>
+        <v>0.03626353992486316</v>
       </c>
       <c r="K52" s="10" t="n">
         <v>37</v>
@@ -7136,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.1088993560533816</v>
+        <v>0.1064120913236321</v>
       </c>
       <c r="K53" s="10" t="n">
         <v>41</v>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.9413789135510666</v>
+        <v>0.919877789450225</v>
       </c>
       <c r="K17" s="10" t="n">
         <v/>
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.7272272459158797</v>
+        <v>0.7106173526636846</v>
       </c>
       <c r="K18" s="10" t="n">
         <v/>
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.5545825606327954</v>
+        <v>0.5419158774421257</v>
       </c>
       <c r="K19" s="10" t="n">
         <v/>
@@ -7555,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.5818665272999514</v>
+        <v>0.5685766774493648</v>
       </c>
       <c r="K20" s="10" t="n">
         <v/>
@@ -7608,7 +7608,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.5685766774493648</v>
+        <v>0.5555903681888698</v>
       </c>
       <c r="K21" s="10" t="n">
         <v/>
@@ -7661,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2.439192729096038</v>
+        <v>2.383481490168527</v>
       </c>
       <c r="K22" s="10" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1.92337205924929</v>
+        <v>1.879442180703346</v>
       </c>
       <c r="K23" s="10" t="n">
         <v/>
@@ -7767,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2.074941153872097</v>
+        <v>2.027549432420576</v>
       </c>
       <c r="K24" s="10" t="n">
         <v/>
@@ -7820,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.461827768770513</v>
+        <v>0.4512796079538526</v>
       </c>
       <c r="K25" s="10" t="n">
         <v/>
@@ -7873,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1.742389696854106</v>
+        <v>1.702593461178113</v>
       </c>
       <c r="K26" s="10" t="n">
         <v/>
@@ -7926,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.4860403243099164</v>
+        <v>0.4749391479604486</v>
       </c>
       <c r="K27" s="10" t="n">
         <v/>
@@ -7979,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.8774599837557009</v>
+        <v>0.8574187700290345</v>
       </c>
       <c r="K28" s="10" t="n">
         <v/>
@@ -8032,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1.181147539774704</v>
+        <v>1.154170092682437</v>
       </c>
       <c r="K29" s="10" t="n">
         <v/>
@@ -8085,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.9123972445892592</v>
+        <v>0.8915580627223337</v>
       </c>
       <c r="K30" s="10" t="n">
         <v/>
@@ -8138,7 +8138,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.3300418749680524</v>
+        <v>0.3225037081257614</v>
       </c>
       <c r="K31" s="10" t="n">
         <v/>
@@ -8191,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.2256398039769263</v>
+        <v>0.2204861837316028</v>
       </c>
       <c r="K32" s="10" t="n">
         <v/>
@@ -8244,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.9242812071006439</v>
+        <v>0.9031705951548319</v>
       </c>
       <c r="K33" s="10" t="n">
         <v/>
@@ -8297,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.2545135875518034</v>
+        <v>0.2487004891782069</v>
       </c>
       <c r="K34" s="10" t="n">
         <v/>
@@ -8350,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.1503875526158906</v>
+        <v>0.1469526961670472</v>
       </c>
       <c r="K35" s="10" t="n">
         <v/>
@@ -8403,7 +8403,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.5271909695917781</v>
+        <v>0.5151499112051214</v>
       </c>
       <c r="K36" s="10" t="n">
         <v/>
@@ -8456,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.4064267678196744</v>
+        <v>0.3971439676135057</v>
       </c>
       <c r="K37" s="10" t="n">
         <v/>
@@ -8509,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.4117204713035846</v>
+        <v>0.4023167627427436</v>
       </c>
       <c r="K38" s="10" t="n">
         <v/>
@@ -8562,7 +8562,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.2558434729991938</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="K39" s="10" t="n">
         <v/>
@@ -8615,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.2813322172292652</v>
+        <v>0.2749065805072852</v>
       </c>
       <c r="K40" s="10" t="n">
         <v/>
@@ -8662,7 +8662,7 @@
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="10" t="n">
-        <v>0.2388870679840163</v>
+        <v>0.2334308798106109</v>
       </c>
       <c r="K41" s="10" t="n">
         <v/>
@@ -8715,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.1306354876012872</v>
+        <v>0.1276517689408661</v>
       </c>
       <c r="K42" s="10" t="n">
         <v/>
@@ -8762,7 +8762,7 @@
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
       <c r="J43" s="10" t="n">
-        <v>0.03877861904584336</v>
+        <v>0.03789291416275997</v>
       </c>
       <c r="K43" s="10" t="n">
         <v/>
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.1088993560533816</v>
+        <v>0.1064120913236321</v>
       </c>
       <c r="K44" s="10" t="n">
         <v/>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -9945,7 +9945,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -10367,7 +10367,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
